--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -960,25 +960,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1319207930213133</v>
+        <v>0.1319207930213132</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13192.07930213133</v>
+        <v>13192.07930213132</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>577.0389471339888</v>
+        <v>577.0389471339845</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>234.1111810047456</v>
+        <v>234.1111810047455</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>213.0850028991699</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8748263771288307</v>
+        <v>0.8748263771288256</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1003,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09914425429287414</v>
+        <v>0.09914425429287406</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9914.425429287414</v>
+        <v>9914.425429287407</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>170.2053832525326</v>
+        <v>170.2053832525275</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>96.42747717689483</v>
+        <v>96.42747717689477</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2160730580000092</v>
+        <v>0.2160730580000031</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1044,16 +1044,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09732031456006449</v>
+        <v>0.09732031456006451</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9732.031456006449</v>
+        <v>9732.031456006451</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0695500946938858</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>676.8637093291238</v>
+        <v>676.8637093291239</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>426.2157127355135</v>
@@ -1103,7 +1103,7 @@
         <v>36.23975304114958</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.594290083864031</v>
+        <v>0.5942900838640295</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1126,25 +1126,25 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08114172203589044</v>
+        <v>0.08114172203589055</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8114.172203589044</v>
+        <v>8114.172203589055</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>189.1561894716127</v>
+        <v>189.1561894716146</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>136.5097916537755</v>
+        <v>136.5097916537756</v>
       </c>
       <c r="I24" s="8" t="n">
         <v>126.7299942016601</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4662365666529613</v>
+        <v>0.4662365666529656</v>
       </c>
       <c r="K24" s="9" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1443,7 +1443,7 @@
         <v>0.0371203025212296</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.120622641333925</v>
@@ -1452,7 +1452,7 @@
         <v>232.6260870205518</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>234.1111810047456</v>
+        <v>234.1111810047455</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>251.3556618710683</v>
@@ -1554,7 +1554,7 @@
         <v>24.97999954223633</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.07844690697526251</v>
+        <v>-0.0784469069752626</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>-0.0190929272018391</v>
@@ -1563,7 +1563,7 @@
         <v>0.09315584596891301</v>
       </c>
       <c r="H10" s="18" t="n">
-        <v>23.02039584190442</v>
+        <v>23.02039584190441</v>
       </c>
       <c r="I10" s="18" t="n">
         <v>24.50305822947444</v>
@@ -1572,7 +1572,7 @@
         <v>27.30703253189641</v>
       </c>
       <c r="K10" s="18" t="n">
-        <v>23.02039584190442</v>
+        <v>23.02039584190441</v>
       </c>
       <c r="L10" s="17" t="inlineStr">
         <is>
@@ -1608,28 +1608,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>94.80000305175781</v>
+        <v>94.8000030517578</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0794520528549532</v>
+        <v>-0.0794520528549533</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
       <c r="G11" s="16" t="n">
         <v>0.0870869998031074</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>96.42747717689483</v>
+        <v>96.42747717689477</v>
       </c>
       <c r="J11" s="15" t="n">
         <v>103.0558508988608</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>87.26794819863983</v>
+        <v>87.2679481986398</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1668,10 +1668,10 @@
         <v>44.06000137329102</v>
       </c>
       <c r="E12" s="22" t="n">
-        <v>-0.084296702806661</v>
+        <v>-0.08429670280666079</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>0.0004088702928312</v>
+        <v>0.0004088702928311</v>
       </c>
       <c r="G12" s="22" t="n">
         <v>0.1101031122376878</v>
@@ -1731,7 +1731,7 @@
         <v>-0.0036968005684216</v>
       </c>
       <c r="G13" s="19" t="n">
-        <v>0.1486665754350491</v>
+        <v>0.1486665754350493</v>
       </c>
       <c r="H13" s="18" t="n">
         <v>424.0458804389618</v>
@@ -1740,7 +1740,7 @@
         <v>428.4103757555787</v>
       </c>
       <c r="J13" s="18" t="n">
-        <v>493.9266274370711</v>
+        <v>493.9266274370712</v>
       </c>
       <c r="K13" s="18" t="n">
         <v>408.5</v>
@@ -1782,7 +1782,7 @@
         <v>72.09999847412109</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>-0.1073109919236646</v>
+        <v>-0.1073109919236645</v>
       </c>
       <c r="F14" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -1839,7 +1839,7 @@
         <v>38.97999954223633</v>
       </c>
       <c r="E15" s="16" t="n">
-        <v>-0.0702987822798095</v>
+        <v>-0.0702987822798096</v>
       </c>
       <c r="F15" s="16" t="n">
         <v>0.0417778692166073</v>
@@ -1956,19 +1956,19 @@
         <v>-0.0353227048870178</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.1081830165120092</v>
+        <v>0.108183016512009</v>
       </c>
       <c r="H17" s="15" t="n">
         <v>128.6879452801489</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>136.5097916537755</v>
+        <v>136.5097916537756</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>147.8316076388897</v>
+        <v>147.8316076388896</v>
       </c>
       <c r="K17" s="15" t="n">
         <v>126.7299942016601</v>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2151,7 +2151,7 @@
         <v>0.0195327504943525</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0437413188564415</v>
+        <v>0.0437413188564412</v>
       </c>
     </row>
     <row r="5">
@@ -2260,10 +2260,10 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>0.0821918345097203</v>
+        <v>0.0821918345097201</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.0349345483727359</v>
+        <v>0.0349345483727356</v>
       </c>
       <c r="G7" s="16" t="n">
         <v>0.0065102745953808</v>
@@ -2277,10 +2277,10 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0175239369224565</v>
+        <v>0.0175239369224564</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0171674480247481</v>
+        <v>0.0171674480247476</v>
       </c>
     </row>
     <row r="8">
@@ -2323,7 +2323,7 @@
         <v>0.0291195183035908</v>
       </c>
       <c r="K8" s="22" t="n">
-        <v>0.0004088702928312</v>
+        <v>0.0004088702928311</v>
       </c>
     </row>
     <row r="9">
@@ -2352,7 +2352,7 @@
         <v>0.1359779535346976</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.2201541438032379</v>
+        <v>0.2201541438032381</v>
       </c>
       <c r="H9" s="19" t="n">
         <v>0.0096886004836262</v>
@@ -2406,7 +2406,7 @@
         </is>
       </c>
       <c r="J10" s="19" t="n">
-        <v>0.0242987733054774</v>
+        <v>0.0242987733054775</v>
       </c>
       <c r="K10" s="19" t="n">
         <v>-0.0366894684105838</v>
@@ -2449,7 +2449,7 @@
         </is>
       </c>
       <c r="J11" s="16" t="n">
-        <v>0.0244714614971411</v>
+        <v>0.0244714614971412</v>
       </c>
       <c r="K11" s="16" t="n">
         <v>0.0417778692166073</v>
@@ -2538,7 +2538,7 @@
         <v>0.0171812701253963</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.0233118283326481</v>
+        <v>0.0233118283326483</v>
       </c>
     </row>
     <row r="14">
@@ -2739,7 +2739,7 @@
         <v>-0.0537261855796603</v>
       </c>
       <c r="G18" s="24" t="n">
-        <v>-0.244328041464684</v>
+        <v>-0.2443280414646841</v>
       </c>
       <c r="H18" s="24" t="n">
         <v>-0.0419382538842088</v>
@@ -2750,7 +2750,7 @@
         </is>
       </c>
       <c r="J18" s="24" t="n">
-        <v>0.018326546308491</v>
+        <v>0.0183265463084909</v>
       </c>
       <c r="K18" s="24" t="n">
         <v>0.0999999076690971</v>
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="J19" s="24" t="n">
-        <v>0.0139213599674617</v>
+        <v>0.0139213599674618</v>
       </c>
       <c r="K19" s="24" t="n">
         <v>0.0999999076690971</v>
@@ -2836,7 +2836,7 @@
         </is>
       </c>
       <c r="J20" s="24" t="n">
-        <v>0.0188455307128114</v>
+        <v>0.0188455307128113</v>
       </c>
       <c r="K20" s="24" t="n">
         <v>0.0294396733991557</v>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-12 06:36</t>
+          <t>Son Güncelleme: 2026-09-13 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>-1763.40361076151</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3474,7 +3474,7 @@
         <v>402757.4632715508</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3504,7 +3504,7 @@
         <v>-56270.17347722268</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3525,16 +3525,16 @@
         <v>96.5</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>94.80000305175781</v>
+        <v>94.8000030517578</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>-0.01761654868644758</v>
+        <v>-0.01761654868644769</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>-1546.988053709545</v>
+        <v>-1546.98805370956</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3564,7 +3564,7 @@
         <v>-2067.772894119626</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12035505.24630628</v>
+        <v>12217153.95918872</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0503429940619526</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -629,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1243,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2040,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2872,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2991,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3242,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3367,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-13 06:51</t>
+          <t>Son Güncelleme: 2026-09-14 07:16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3444,7 +3444,7 @@
         <v>-1763.40361076151</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3474,7 +3474,7 @@
         <v>402757.4632715508</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3504,7 +3504,7 @@
         <v>-56270.17347722268</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3534,7 +3534,7 @@
         <v>-1546.98805370956</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3564,7 +3564,7 @@
         <v>-2067.772894119626</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>0.0503429940619526</v>
@@ -3594,7 +3594,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="25" t="n">
-        <v>12217153.95918872</v>
+        <v>12398802.67207116</v>
       </c>
       <c r="H9" s="26" t="n">
         <v>0.0503429940619526</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -91,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,10 +157,10 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,19 +190,10 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -612,7 +603,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +620,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -680,7 +671,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 69.57/100</t>
+          <t>Güven Puanı: 67.66/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +731,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, SAHOL.IS, ASELS.IS, EREGL.IS, GARAN.IS</t>
+          <t>AL: KCHOL.IS, SISE.IS, SAHOL.IS, TOASO.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +748,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: SISE.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +765,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS</t>
+          <t>ÇIK: TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -960,29 +951,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1319207930213132</v>
+        <v>0.1290309135858313</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13192.07930213132</v>
+        <v>12903.09135858313</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0437413188564412</v>
+        <v>0.0416391852085011</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>577.0389471339845</v>
+        <v>537.2742108422531</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>234.1111810047455</v>
+        <v>234.889636264517</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>213.0850028991699</v>
+        <v>214.225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8748263771288256</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.8327837041700226</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -994,7 +985,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,29 +994,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09914425429287406</v>
+        <v>0.1224121260986969</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9914.425429287407</v>
+        <v>12241.21260986969</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0171674480247476</v>
+        <v>0.0450215489018153</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>170.2053832525275</v>
+        <v>551.1183521327662</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>96.42747717689477</v>
+        <v>47.00506879123075</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>87.2679481986398</v>
+        <v>42.3652559241991</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2160730580000031</v>
+        <v>0.7744809988348101</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1035,7 +1026,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1044,29 +1035,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09732031456006451</v>
+        <v>0.09916100380896488</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9732.031456006451</v>
+        <v>9916.100380896487</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0695500946938858</v>
+        <v>0.022532255067367</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>676.8637093291239</v>
+        <v>223.4321030559747</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>426.2157127355135</v>
+        <v>97.44732702844087</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>374.8310947630716</v>
+        <v>90.53500289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.170975693978077</v>
+        <v>0.450645101347339</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1076,7 +1067,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1085,29 +1076,29 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.09047291608985762</v>
+        <v>0.07975506544653042</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>9047.291608985763</v>
+        <v>7975.506544653043</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0417778692166073</v>
+        <v>0.0355140318659195</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>377.9765656047158</v>
+        <v>283.2423935736576</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>40.60850086517529</v>
+        <v>310.3953310518094</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>36.23975304114958</v>
+        <v>284.7625</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.5942900838640295</v>
+        <v>0.7102806373183891</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1126,27 +1117,27 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.08114172203589055</v>
+        <v>0.06964089105997651</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>8114.172203589055</v>
+        <v>6964.08910599765</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0233118283326483</v>
+        <v>0.0109975418263577</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>189.1561894716146</v>
+        <v>76.58786122569117</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>136.5097916537756</v>
+        <v>135.6758670277776</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>126.7299942016601</v>
+        <v>123.905294893559</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.4662365666529656</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
+        <v>0.1433620974843069</v>
+      </c>
+      <c r="K24" s="10" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -1222,7 +1213,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1234,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1437,36 +1428,36 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>224.3000030517578</v>
+        <v>225.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.0371203025212296</v>
+        <v>0.0371203067330339</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0437413188564412</v>
+        <v>0.0416391852085011</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.120622641333925</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>232.6260870205518</v>
+        <v>233.8706291682991</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>234.1111810047455</v>
+        <v>234.889636264517</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>251.3556618710683</v>
+        <v>252.7004056208001</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>213.0850028991699</v>
+        <v>214.225</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1494,28 +1485,28 @@
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>416.75</v>
+        <v>413.5</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.098571395911871</v>
+        <v>-0.09857145531209779</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>-0.0035847038800045</v>
+        <v>-0.0035847527809796</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.1274261809752426</v>
+        <v>0.1274260827597302</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>375.6703707537278</v>
+        <v>372.7407032284476</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>415.2560746580081</v>
+        <v>412.017704725065</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>469.8548609214324</v>
+        <v>466.1906852211484</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>375.6703707537278</v>
+        <v>372.7407032284476</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1523,7 +1514,7 @@
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1537,228 +1528,228 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="15" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.050406473588474</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0450215489018153</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.178823664050683</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>42.71271638330102</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>47.00506879123075</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>53.02348786937708</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>42.3652559241991</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="14" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>24.97999954223633</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0784469069752626</v>
-      </c>
-      <c r="F10" s="19" t="n">
+      <c r="D11" s="18" t="n">
+        <v>24.68000030517578</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.07844690697526251</v>
+      </c>
+      <c r="F11" s="19" t="n">
         <v>-0.0190929272018391</v>
       </c>
-      <c r="G10" s="19" t="n">
+      <c r="G11" s="19" t="n">
         <v>0.09315584596891301</v>
       </c>
-      <c r="H10" s="18" t="n">
-        <v>23.02039584190441</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>24.50305822947444</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>27.30703253189641</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>23.02039584190441</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="H11" s="18" t="n">
+        <v>22.74393061708621</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>24.20878685600769</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>26.97908661211746</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>22.74393061708621</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M11" s="17" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="18" t="n">
+        <v>434.75</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.013846894786177</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-0.0036968005684216</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.1486668544898615</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>428.7300624917096</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>433.1428159528787</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>499.3829149894673</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>413.0125</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C11" s="14" t="inlineStr">
+      <c r="C13" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="15" t="n">
-        <v>94.8000030517578</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0794520528549533</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0171674480247476</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.0870869998031074</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>87.2679481986398</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>96.42747717689477</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>103.0558508988608</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>87.2679481986398</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="D13" s="15" t="n">
+        <v>95.30000305175781</v>
+      </c>
+      <c r="E13" s="16" t="n">
+        <v>-0.0212766842896149</v>
+      </c>
+      <c r="F13" s="16" t="n">
+        <v>0.022532255067367</v>
+      </c>
+      <c r="G13" s="16" t="n">
+        <v>0.093714156045322</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>93.27233497402622</v>
+      </c>
+      <c r="I13" s="15" t="n">
+        <v>97.44732702844087</v>
+      </c>
+      <c r="J13" s="15" t="n">
+        <v>104.2309624088699</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>90.53500289916992</v>
+      </c>
+      <c r="L13" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>44.06000137329102</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.08429670280666079</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0004088702928311</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.1101031122376878</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>40.34588853186563</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>44.07801619895465</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>48.91114464968716</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>40.34588853186563</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="20" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>430</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.0138467896768329</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0036968005684216</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.1486665754350493</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>424.0458804389618</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>428.4103757555787</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>493.9266274370712</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>408.5</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="M13" s="14" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="N13" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O13" s="14" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
@@ -1779,28 +1770,28 @@
         </is>
       </c>
       <c r="D14" s="18" t="n">
-        <v>72.09999847412109</v>
+        <v>72.69999694824219</v>
       </c>
       <c r="E14" s="19" t="n">
-        <v>-0.1073109919236645</v>
+        <v>-0.121064815881965</v>
       </c>
       <c r="F14" s="19" t="n">
-        <v>-0.0366894684105838</v>
+        <v>-0.031845613590586</v>
       </c>
       <c r="G14" s="19" t="n">
-        <v>0.0515933324042807</v>
+        <v>0.067861770494477</v>
       </c>
       <c r="H14" s="18" t="n">
-        <v>64.36287612016845</v>
+        <v>63.89858520308383</v>
       </c>
       <c r="I14" s="18" t="n">
-        <v>69.45468785770169</v>
+        <v>70.38482093739168</v>
       </c>
       <c r="J14" s="18" t="n">
-        <v>75.81987766174456</v>
+        <v>77.63354745609298</v>
       </c>
       <c r="K14" s="18" t="n">
-        <v>64.36287612016845</v>
+        <v>63.89858520308383</v>
       </c>
       <c r="L14" s="17" t="inlineStr">
         <is>
@@ -1808,7 +1799,7 @@
         </is>
       </c>
       <c r="M14" s="17" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="N14" s="17" t="inlineStr">
         <is>
@@ -1822,57 +1813,57 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="14" t="n">
+      <c r="A15" s="17" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>38.97999954223633</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0702987822798096</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0417778692166073</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.0831933556570565</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>36.23975304114958</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>40.60850086517529</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>42.2228765076655</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>36.23975304114958</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>39.40000152587891</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.061000020827669</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.0254997664885543</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.07049092682525041</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>36.9966006121901</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>38.39531068732031</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>42.17734415035439</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>36.9966006121901</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>67.66</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O15" s="14" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
@@ -1884,7 +1875,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1893,36 +1884,36 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>398.5</v>
+        <v>299.75</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.0443022979797426</v>
+        <v>-0.0245398668646306</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.0695500946938858</v>
+        <v>0.0355140318659195</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1249444054842199</v>
+        <v>0.1492028070010846</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>380.8455342550726</v>
+        <v>292.394174907327</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>426.2157127355135</v>
+        <v>310.3953310518094</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>448.2903455854616</v>
+        <v>344.4735413985752</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>374.8310947630716</v>
+        <v>284.7625</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M16" s="14" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
@@ -1950,28 +1941,28 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>133.3999938964844</v>
+        <v>134.1999969482422</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0353227048870178</v>
+        <v>-0.0767116414961887</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0233118283326483</v>
+        <v>0.0109975418263577</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.108183016512009</v>
+        <v>0.0656887346990392</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>128.6879452801489</v>
+        <v>123.905294893559</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>136.5097916537756</v>
+        <v>135.6758670277776</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>147.8316076388896</v>
+        <v>143.0154249443871</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>126.7299942016601</v>
+        <v>123.905294893559</v>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
@@ -1979,16 +1970,16 @@
         </is>
       </c>
       <c r="M17" s="14" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var; hacim artışı var</t>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2014,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +2031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2131,16 +2122,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1220610800413963</v>
+        <v>0.09572398763904651</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2176981909222464</v>
+        <v>0.2026666666666667</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.2025144146954265</v>
+        <v>0.2164919872232833</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.2388619535196479</v>
+        <v>0.211266354296213</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2148,10 +2139,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0195327504943525</v>
+        <v>0.0194452515494341</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0437413188564412</v>
+        <v>0.0416391852085011</v>
       </c>
     </row>
     <row r="5">
@@ -2174,16 +2165,16 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2384843982169391</v>
+        <v>0.1772241992882561</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.7658898305084745</v>
+        <v>0.7686056227657998</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.7493550756551532</v>
+        <v>0.7336156423433065</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.1223819545685662</v>
+        <v>0.0981554057068143</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2191,182 +2182,182 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0266705212809367</v>
+        <v>0.0266539433970383</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>-0.0035847038800045</v>
+        <v>-0.0035847527809796</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="17" t="n">
+      <c r="A6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="16" t="n">
+        <v>0.0981445446195723</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.0049151302268322</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.0864234261020719</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>0.4390738924446715</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.0290656252184038</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0450215489018153</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>0.3539294584970258</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.2673770016516807</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.405739949281916</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>0.0784176668284155</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="E7" s="19" t="n">
+        <v>0.3261686993953059</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>0.2728210975783458</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>0.3896396389139926</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.09133922051353879</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0387382857975753</v>
-      </c>
-      <c r="K6" s="19" t="n">
+      <c r="J7" s="19" t="n">
+        <v>0.0387055024162966</v>
+      </c>
+      <c r="K7" s="19" t="n">
         <v>-0.0190929272018391</v>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="19" t="n">
+        <v>0.1321614583333332</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.150037756344753</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>0.2362498448817933</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.0084528247140903</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.0191055357019943</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>-0.0036968005684216</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="14" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="16" t="n">
-        <v>0.0821918345097201</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.0349345483727356</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.0065102745953808</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.166812658219172</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="E9" s="16" t="n">
+        <v>0.07988672013323291</v>
+      </c>
+      <c r="F9" s="16" t="n">
+        <v>-0.0067742982507336</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.0086568460030058</v>
+      </c>
+      <c r="H9" s="16" t="n">
+        <v>0.143880722551591</v>
+      </c>
+      <c r="I9" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.0175239369224564</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0171674480247476</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0.0788442999185219</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.0091617390581053</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>0.0586490083172681</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0.4035374089576886</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0291195183035908</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0004088702928311</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0.1398277004638832</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.1359779535346976</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.2201541438032381</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>0.0096886004836262</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="19" t="n">
-        <v>0.0190787555640604</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>-0.0036968005684216</v>
+      <c r="J9" s="16" t="n">
+        <v>0.0164818947768469</v>
+      </c>
+      <c r="K9" s="16" t="n">
+        <v>0.022532255067367</v>
       </c>
     </row>
     <row r="10">
@@ -2389,70 +2380,70 @@
         </is>
       </c>
       <c r="E10" s="19" t="n">
-        <v>0.0899470417383807</v>
+        <v>0.0566859552833223</v>
       </c>
       <c r="F10" s="19" t="n">
-        <v>0.079341245213069</v>
+        <v>0.0013773894796531</v>
       </c>
       <c r="G10" s="19" t="n">
-        <v>-0.0348790112563344</v>
+        <v>-0.0324944605888269</v>
       </c>
       <c r="H10" s="19" t="n">
-        <v>0.1807192120307617</v>
+        <v>0.1765403779916317</v>
       </c>
       <c r="I10" s="17" t="inlineStr">
         <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J10" s="19" t="n">
+        <v>0.0217295591533899</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>-0.031845613590586</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>0.0597095535901348</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.0010162834071913</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.3789960160085972</v>
+      </c>
+      <c r="H11" s="19" t="n">
+        <v>0.1411151222172568</v>
+      </c>
+      <c r="I11" s="17" t="inlineStr">
+        <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0242987733054775</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>-0.0366894684105838</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0575148913939354</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0151041144091241</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.3475447208486557</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.1621523287574862</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0244714614971412</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0417778692166073</v>
+      <c r="J11" s="19" t="n">
+        <v>0.0243071344813338</v>
+      </c>
+      <c r="K11" s="19" t="n">
+        <v>-0.0254997664885543</v>
       </c>
     </row>
     <row r="12">
@@ -2461,7 +2452,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -2475,16 +2466,16 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.1185964912280701</v>
+        <v>0.1174277726001864</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.0549305095962937</v>
+        <v>0.0143824027072758</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.1922213911742707</v>
+        <v>0.0522318906284782</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>-0.0203557401597226</v>
+        <v>-0.0653905113355023</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
@@ -2492,10 +2483,10 @@
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.0296974971605124</v>
+        <v>0.0239150705522644</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>0.0695500946938858</v>
+        <v>0.0355140318659195</v>
       </c>
     </row>
     <row r="13">
@@ -2518,16 +2509,16 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.0545454062963191</v>
+        <v>0.0244274576201692</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.0341084798177082</v>
+        <v>-0.0125091760455638</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>-0.0163656245488981</v>
+        <v>0.0023197702088397</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>0.1023784950166619</v>
+        <v>0.093888274143099</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
@@ -2535,311 +2526,311 @@
         </is>
       </c>
       <c r="J13" s="16" t="n">
-        <v>0.0171812701253963</v>
+        <v>0.0158142377417917</v>
       </c>
       <c r="K13" s="16" t="n">
-        <v>0.0233118283326483</v>
+        <v>0.0109975418263577</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="23" t="n">
+      <c r="A14" s="20" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="23" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C14" s="23" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="23" t="inlineStr">
+      <c r="D14" s="20" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="24" t="n">
-        <v>-0.0145489817866147</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>-0.0548837351244549</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>-0.088789251353174</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>0.2605259645772744</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
+      <c r="E14" s="21" t="n">
+        <v>-0.003842473888012</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.06323396741621271</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>-0.0494958900220315</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>0.2754202463029134</v>
+      </c>
+      <c r="I14" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0207359414752272</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0593008635432975</v>
+      <c r="J14" s="21" t="n">
+        <v>0.0205513225793467</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>0.0585457682616472</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="23" t="n">
+      <c r="A15" s="20" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="23" t="inlineStr">
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>0.0334645669291338</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0.0606060606060605</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.172747580044676</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>-0.0636808955939812</v>
+      </c>
+      <c r="I15" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>0.0296518405995465</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>0.0599572762440211</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="24" t="n">
-        <v>0.0628302790183259</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>0.0336950396845063</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.0216216010016363</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>0.0380098547322975</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="E16" s="21" t="n">
+        <v>0.0280112038831694</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>-0.0367453482218003</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.001637592093082</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>0.0260973082789615</v>
+      </c>
+      <c r="I16" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.025864305461405</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0662461449400904</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
+      <c r="J16" s="21" t="n">
+        <v>0.0234074018350842</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>0.0551630966573649</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="20" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="20" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="23" t="inlineStr">
+      <c r="D17" s="20" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="24" t="n">
-        <v>0.0889513108614232</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>0.0273851590106006</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.0214772673421124</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.0747646830309296</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0242421789089247</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0358586773669118</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
+      <c r="E17" s="21" t="n">
+        <v>0.038871454220954</v>
+      </c>
+      <c r="F17" s="21" t="n">
+        <v>-0.0444059816567173</v>
+      </c>
+      <c r="G17" s="21" t="n">
+        <v>-0.2321377142522179</v>
+      </c>
+      <c r="H17" s="21" t="n">
+        <v>-0.0452796696971707</v>
+      </c>
+      <c r="I17" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="21" t="n">
+        <v>0.0183898389304276</v>
+      </c>
+      <c r="K17" s="21" t="n">
+        <v>0.0766731872627277</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="21" t="n">
+        <v>-0.0138960211314199</v>
+      </c>
+      <c r="F18" s="21" t="n">
+        <v>-0.0689990123307769</v>
+      </c>
+      <c r="G18" s="21" t="n">
+        <v>-0.1529619421376187</v>
+      </c>
+      <c r="H18" s="21" t="n">
+        <v>0.014174275884534</v>
+      </c>
+      <c r="I18" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="21" t="n">
+        <v>0.0138580840698411</v>
+      </c>
+      <c r="K18" s="21" t="n">
+        <v>0.0949826980521894</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="20" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="20" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C17" s="23" t="inlineStr">
+      <c r="C19" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="23" t="inlineStr">
+      <c r="D19" s="20" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.0058139534883721</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>0.0204603580562658</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>0.0075757575757575</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.06494137756684409</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
+      <c r="E19" s="21" t="n">
+        <v>-0.0275303643724695</v>
+      </c>
+      <c r="F19" s="21" t="n">
+        <v>-0.0243704305442729</v>
+      </c>
+      <c r="G19" s="21" t="n">
+        <v>0.0186598812553011</v>
+      </c>
+      <c r="H19" s="21" t="n">
+        <v>-0.06740262125769519</v>
+      </c>
+      <c r="I19" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0190402991202696</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0643275474197377</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="J19" s="21" t="n">
+        <v>0.0179854767446905</v>
+      </c>
+      <c r="K19" s="21" t="n">
+        <v>0.08833658943450449</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="20" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
+      <c r="D20" s="20" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="24" t="n">
-        <v>0.0386810794011471</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0537261855796603</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.2443280414646841</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.0419382538842088</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0183265463084909</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0999999076690971</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0216494688053721</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0650246155085821</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.1675438462642201</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>0.0162518302278014</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
+      <c r="E20" s="21" t="n">
+        <v>0.0151415611861394</v>
+      </c>
+      <c r="F20" s="21" t="n">
+        <v>-0.1034883898358012</v>
+      </c>
+      <c r="G20" s="21" t="n">
+        <v>-0.1433333502875433</v>
+      </c>
+      <c r="H20" s="21" t="n">
+        <v>-0.0260802057590543</v>
+      </c>
+      <c r="I20" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0139213599674618</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.0999999076690971</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>0.0240481374542733</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.07371599364496791</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.1454849037496987</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.0470849341061426</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0188455307128113</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.0294396733991557</v>
+      <c r="J20" s="21" t="n">
+        <v>0.0181500238753827</v>
+      </c>
+      <c r="K20" s="21" t="n">
+        <v>0.08833658943450449</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2855,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2863,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2888,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, SAHOL.IS, EREGL.IS, ASELS.IS, GARAN.IS</t>
+          <t>KCHOL.IS, SISE.IS, SAHOL.IS, TOASO.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2900,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2912,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS</t>
+          <t>TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2924,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, YKBNK.IS, TOASO.IS, THYAO.IS, FROTO.IS, ARCLK.IS, PGSUS.IS</t>
+          <t>TCELL.IS, ASELS.IS, YKBNK.IS, FROTO.IS, ARCLK.IS, THYAO.IS, PGSUS.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2936,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.88 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.37 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2974,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +2982,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3040,7 +3031,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3064,7 +3055,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3139,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3175,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3234,7 +3225,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +3233,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +3257,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14467.2998046875</v>
+        <v>14235.7998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +3267,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13433.98852539062</v>
+        <v>13450.72752441406</v>
       </c>
     </row>
     <row r="6">
@@ -3310,7 +3301,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>69.56999999999999</v>
+        <v>67.66</v>
       </c>
     </row>
     <row r="9">
@@ -3337,23 +3328,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-10</t>
+          <t>Rapor Tarihi: 2026-09-11</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3358,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-14 07:16</t>
+          <t>Son Güncelleme: 2026-09-15 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3422,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="22" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>398.5</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>-0.002503128911138908</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>-1763.40361076151</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0503429940619526</v>
+      <c r="D4" s="22" t="n">
+        <v>393.75</v>
+      </c>
+      <c r="E4" s="23" t="n">
+        <v>-0.0143929912390488</v>
+      </c>
+      <c r="F4" s="22" t="n">
+        <v>-10139.57076187839</v>
+      </c>
+      <c r="G4" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H4" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
     <row r="5">
@@ -3461,23 +3452,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="22" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>224.3000030517578</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.1385786956942021</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>402757.4632715508</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0503429940619526</v>
+      <c r="D5" s="22" t="n">
+        <v>225.5</v>
+      </c>
+      <c r="E5" s="23" t="n">
+        <v>0.1446700507614214</v>
+      </c>
+      <c r="F5" s="22" t="n">
+        <v>420461.0410290817</v>
+      </c>
+      <c r="G5" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H5" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
     <row r="6">
@@ -3491,23 +3482,23 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="22" t="n">
         <v>103.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>101.5999984741211</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.01835750266549663</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-56270.17347722268</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0503429940619526</v>
+      <c r="D6" s="22" t="n">
+        <v>103.6999969482422</v>
+      </c>
+      <c r="E6" s="23" t="n">
+        <v>0.001932337664175776</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>5923.081018209923</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H6" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
     <row r="7">
@@ -3521,87 +3512,117 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="22" t="n">
         <v>96.5</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>94.8000030517578</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.01761654868644769</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-1546.98805370956</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0503429940619526</v>
+      <c r="D7" s="22" t="n">
+        <v>95.30000305175781</v>
+      </c>
+      <c r="E7" s="23" t="n">
+        <v>-0.01243520153618849</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>-1091.990750535231</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H7" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>39.91999816894531</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>38.97999954223633</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.02354706086735825</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-2067.772894119626</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0503429940619526</v>
+          <t>2026-09-10</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="n">
+        <v>133.3999938964844</v>
+      </c>
+      <c r="D8" s="22" t="n">
+        <v>134.1999969482422</v>
+      </c>
+      <c r="E8" s="23" t="n">
+        <v>0.005997024650380434</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>29041.80015604291</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H8" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>133.3999938964844</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>133.3999938964844</v>
-      </c>
-      <c r="E9" s="26" t="n">
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="D9" s="22" t="n">
+        <v>44.97999954223633</v>
+      </c>
+      <c r="E9" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="22" t="n">
+        <v>-2.91038304567337e-11</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.0556990517139155</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-11</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>299.75</v>
+      </c>
+      <c r="D10" s="22" t="n">
+        <v>299.75</v>
+      </c>
+      <c r="E10" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G9" s="25" t="n">
-        <v>12398802.67207116</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0503429940619526</v>
+      <c r="F10" s="22" t="n">
+        <v>-2.91038304567337e-11</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>12500744.0388727</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0.0556990517139155</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,7 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,10 +190,19 @@
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -603,7 +612,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -620,7 +629,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -671,7 +680,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 67.66/100</t>
+          <t>Güven Puanı: 60.67/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -731,7 +740,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, SISE.IS, SAHOL.IS, TOASO.IS, GARAN.IS</t>
+          <t>AL: KCHOL.IS, EREGL.IS, SAHOL.IS, GARAN.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -748,7 +757,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: TUPRS.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -765,7 +774,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS, EREGL.IS</t>
+          <t>ÇIK: PETKM.IS, SISE.IS, AKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -951,29 +960,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1290309135858313</v>
+        <v>0.1340221997111379</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12903.09135858313</v>
+        <v>13402.21997111379</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0416391852085011</v>
+        <v>0.0493252973688849</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>537.2742108422531</v>
+        <v>661.0684854783956</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>234.889636264517</v>
+        <v>236.6228545566835</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>214.225</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8327837041700226</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.9865059473776966</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -985,7 +994,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -994,25 +1003,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1224121260986969</v>
+        <v>0.09856326579837003</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>12241.21260986969</v>
+        <v>9856.326579837003</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0450215489018153</v>
+        <v>0.0521951315406046</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>551.1183521327662</v>
+        <v>514.4522623417498</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>47.00506879123075</v>
+        <v>40.88830345387684</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>42.3652559241991</v>
+        <v>36.77983023365233</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.7744809988348101</v>
+        <v>0.9750657283869907</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1035,25 +1044,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09916100380896488</v>
+        <v>0.09457033532365614</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9916.100380896487</v>
+        <v>9457.033532365613</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.022532255067367</v>
+        <v>0.0224111679198997</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>223.4321030559747</v>
+        <v>211.943166517968</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>97.44732702844087</v>
+        <v>97.0779372738432</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>90.53500289916992</v>
+        <v>87.61030481266786</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.450645101347339</v>
+        <v>0.2899222864249615</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1067,7 +1076,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C23" s="6" t="inlineStr">
@@ -1076,25 +1085,25 @@
         </is>
       </c>
       <c r="D23" s="7" t="n">
-        <v>0.07975506544653042</v>
+        <v>0.08803480032718682</v>
       </c>
       <c r="E23" s="8" t="n">
-        <v>7975.506544653043</v>
+        <v>8803.480032718682</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>0.0355140318659195</v>
+        <v>0.0292262535427767</v>
       </c>
       <c r="G23" s="8" t="n">
-        <v>283.2423935736576</v>
+        <v>257.2927394950083</v>
       </c>
       <c r="H23" s="8" t="n">
-        <v>310.3953310518094</v>
+        <v>137.8133890674793</v>
       </c>
       <c r="I23" s="8" t="n">
-        <v>284.7625</v>
+        <v>127.2049942016602</v>
       </c>
       <c r="J23" s="6" t="n">
-        <v>0.7102806373183891</v>
+        <v>0.5845250708555337</v>
       </c>
       <c r="K23" s="10" t="inlineStr">
         <is>
@@ -1108,7 +1117,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C24" s="6" t="inlineStr">
@@ -1117,29 +1126,29 @@
         </is>
       </c>
       <c r="D24" s="7" t="n">
-        <v>0.06964089105997651</v>
+        <v>0.08480939883964915</v>
       </c>
       <c r="E24" s="8" t="n">
-        <v>6964.08910599765</v>
+        <v>8480.939883964915</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>0.0109975418263577</v>
+        <v>0.0585457682616472</v>
       </c>
       <c r="G24" s="8" t="n">
-        <v>76.58786122569117</v>
+        <v>496.523141087571</v>
       </c>
       <c r="H24" s="8" t="n">
-        <v>135.6758670277776</v>
+        <v>108.3950882852053</v>
       </c>
       <c r="I24" s="8" t="n">
-        <v>123.905294893559</v>
+        <v>97.28000144958496</v>
       </c>
       <c r="J24" s="6" t="n">
-        <v>0.1433620974843069</v>
-      </c>
-      <c r="K24" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>1.170915365232943</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1222,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1234,7 +1243,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1434,7 +1443,7 @@
         <v>0.0371203067330339</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0416391852085011</v>
+        <v>0.0493252973688849</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>0.120622641333925</v>
@@ -1443,7 +1452,7 @@
         <v>233.8706291682991</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>234.889636264517</v>
+        <v>236.6228545566835</v>
       </c>
       <c r="J8" s="15" t="n">
         <v>252.7004056208001</v>
@@ -1453,11 +1462,11 @@
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1481,163 +1490,163 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>415.75</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.09857159599125891</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0028743310356713</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.1274262917059938</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>374.7688589666341</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>416.9450031280804</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>468.7274807767669</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>374.7688589666341</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>413.5</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.09857145531209779</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>-0.0035847527809796</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.1274260827597302</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>372.7407032284476</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>412.017704725065</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>466.1906852211484</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>372.7407032284476</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D10" s="21" t="n">
+        <v>23.65999984741211</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.1400832487570158</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.0271741120711617</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>20.34563020319612</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>23.01706035995486</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>23.65999984741211</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>20.34563020319612</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M10" s="20" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>43.52000045776367</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.1374999561178063</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.0504066518392087</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.0619999332492389</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>37.53600230457425</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>41.32630294664698</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>46.21823758115187</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>37.53600230457425</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>44.97999954223633</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.050406473588474</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0450215489018153</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.178823664050683</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>42.71271638330102</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>47.00506879123075</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>53.02348786937708</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>42.3652559241991</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>24.68000030517578</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.07844690697526251</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>-0.0190929272018391</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.09315584596891301</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>22.74393061708621</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>24.20878685600769</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>26.97908661211746</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>22.74393061708621</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1652,32 +1661,32 @@
       </c>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D12" s="18" t="n">
-        <v>434.75</v>
+        <v>429.75</v>
       </c>
       <c r="E12" s="19" t="n">
-        <v>-0.013846894786177</v>
+        <v>-0.012842558577034</v>
       </c>
       <c r="F12" s="19" t="n">
-        <v>-0.0036968005684216</v>
+        <v>0.0211505713869569</v>
       </c>
       <c r="G12" s="19" t="n">
-        <v>0.1486668544898615</v>
+        <v>0.1354168120573042</v>
       </c>
       <c r="H12" s="18" t="n">
-        <v>428.7300624917096</v>
+        <v>424.2309104515197</v>
       </c>
       <c r="I12" s="18" t="n">
-        <v>433.1428159528787</v>
+        <v>438.8394580535447</v>
       </c>
       <c r="J12" s="18" t="n">
-        <v>499.3829149894673</v>
+        <v>487.9453749816265</v>
       </c>
       <c r="K12" s="18" t="n">
-        <v>413.0125</v>
+        <v>408.2625</v>
       </c>
       <c r="L12" s="17" t="inlineStr">
         <is>
@@ -1685,7 +1694,7 @@
         </is>
       </c>
       <c r="M12" s="17" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
       <c r="N12" s="17" t="inlineStr">
         <is>
@@ -1713,28 +1722,28 @@
         </is>
       </c>
       <c r="D13" s="15" t="n">
-        <v>95.30000305175781</v>
+        <v>94.94999694824219</v>
       </c>
       <c r="E13" s="16" t="n">
-        <v>-0.0212766842896149</v>
+        <v>-0.07730060422829969</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>0.022532255067367</v>
+        <v>0.0224111679198997</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.093714156045322</v>
+        <v>0.09470956359125229</v>
       </c>
       <c r="H13" s="15" t="n">
-        <v>93.27233497402622</v>
+        <v>87.61030481266786</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>97.44732702844087</v>
+        <v>97.0779372738432</v>
       </c>
       <c r="J13" s="15" t="n">
-        <v>104.2309624088699</v>
+        <v>103.9426697222009</v>
       </c>
       <c r="K13" s="15" t="n">
-        <v>90.53500289916992</v>
+        <v>87.61030481266786</v>
       </c>
       <c r="L13" s="14" t="inlineStr">
         <is>
@@ -1742,7 +1751,7 @@
         </is>
       </c>
       <c r="M13" s="14" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
       <c r="N13" s="14" t="inlineStr">
         <is>
@@ -1751,119 +1760,119 @@
       </c>
       <c r="O13" s="14" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="n">
+      <c r="A14" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>72.69999694824219</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.121064815881965</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.031845613590586</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.067861770494477</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>63.89858520308383</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>70.38482093739168</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>77.63354745609298</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>63.89858520308383</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="D14" s="21" t="n">
+        <v>72.55000305175781</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.1195457879117688</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.0301236938145638</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0.05159344410234</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>63.87695577393419</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>70.36452897358099</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>76.29310757883327</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>63.87695577393419</v>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
+      <c r="M14" s="20" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>trend desteği var; hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="n">
+      <c r="A15" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>39.40000152587891</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.061000020827669</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.0254997664885543</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.07049092682525041</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>36.9966006121901</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>38.39531068732031</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>42.17734415035439</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>36.9966006121901</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>67.66</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
+      <c r="C15" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D15" s="15" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="E15" s="16" t="n">
+        <v>-0.0535298595992588</v>
+      </c>
+      <c r="F15" s="16" t="n">
+        <v>0.0521951315406046</v>
+      </c>
+      <c r="G15" s="16" t="n">
+        <v>0.1392962007538372</v>
+      </c>
+      <c r="H15" s="15" t="n">
+        <v>36.77983023365233</v>
+      </c>
+      <c r="I15" s="15" t="n">
+        <v>40.88830345387684</v>
+      </c>
+      <c r="J15" s="15" t="n">
+        <v>44.27305105666533</v>
+      </c>
+      <c r="K15" s="15" t="n">
+        <v>36.77983023365233</v>
+      </c>
+      <c r="L15" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M15" s="14" t="n">
+        <v>60.67</v>
+      </c>
+      <c r="N15" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="14" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
@@ -1875,7 +1884,7 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C16" s="14" t="inlineStr">
@@ -1884,28 +1893,28 @@
         </is>
       </c>
       <c r="D16" s="15" t="n">
-        <v>299.75</v>
+        <v>133.8999938964844</v>
       </c>
       <c r="E16" s="16" t="n">
-        <v>-0.0245398668646306</v>
+        <v>-0.0375302339476217</v>
       </c>
       <c r="F16" s="16" t="n">
-        <v>0.0355140318659195</v>
+        <v>0.0292262535427767</v>
       </c>
       <c r="G16" s="16" t="n">
-        <v>0.1492028070010846</v>
+        <v>0.148990099438721</v>
       </c>
       <c r="H16" s="15" t="n">
-        <v>292.394174907327</v>
+        <v>128.8746957999642</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>310.3953310518094</v>
+        <v>137.8133890674793</v>
       </c>
       <c r="J16" s="15" t="n">
-        <v>344.4735413985752</v>
+        <v>153.8497673019657</v>
       </c>
       <c r="K16" s="15" t="n">
-        <v>284.7625</v>
+        <v>127.2049942016602</v>
       </c>
       <c r="L16" s="14" t="inlineStr">
         <is>
@@ -1913,11 +1922,11 @@
         </is>
       </c>
       <c r="M16" s="14" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
       <c r="N16" s="14" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
       <c r="O16" s="14" t="inlineStr">
@@ -1932,7 +1941,7 @@
       </c>
       <c r="B17" s="14" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C17" s="14" t="inlineStr">
@@ -1941,45 +1950,45 @@
         </is>
       </c>
       <c r="D17" s="15" t="n">
-        <v>134.1999969482422</v>
+        <v>102.4000015258789</v>
       </c>
       <c r="E17" s="16" t="n">
-        <v>-0.0767116414961887</v>
+        <v>-0.0002837898210087</v>
       </c>
       <c r="F17" s="16" t="n">
-        <v>0.0109975418263577</v>
+        <v>0.0585457682616472</v>
       </c>
       <c r="G17" s="16" t="n">
-        <v>0.0656887346990392</v>
+        <v>0.07823596948359129</v>
       </c>
       <c r="H17" s="15" t="n">
-        <v>123.905294893559</v>
+        <v>102.3709414477746</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>135.6758670277776</v>
+        <v>108.3950882852053</v>
       </c>
       <c r="J17" s="15" t="n">
-        <v>143.0154249443871</v>
+        <v>110.4113649203773</v>
       </c>
       <c r="K17" s="15" t="n">
-        <v>123.905294893559</v>
+        <v>97.28000144958496</v>
       </c>
       <c r="L17" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M17" s="14" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
       <c r="N17" s="14" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+          <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O17" s="14" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2023,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2031,7 +2040,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2122,16 +2131,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.09572398763904651</v>
+        <v>0.1141304683800035</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.2026666666666667</v>
+        <v>0.1458333155650113</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.2164919872232833</v>
+        <v>0.1965800588720865</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.211266354296213</v>
+        <v>0.2024233381883688</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2139,10 +2148,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0194452515494341</v>
+        <v>0.0185148051688734</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0416391852085011</v>
+        <v>0.0493252973688849</v>
       </c>
     </row>
     <row r="5">
@@ -2156,122 +2165,122 @@
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>0.2015895953757225</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.7927986672806153</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.63474615066625</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.1029603441310553</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0265643910667515</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0028743310356713</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D6" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.1772241992882561</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.7686056227657998</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.7336156423433065</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.0981554057068143</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E6" s="22" t="n">
+        <v>0.2578416012318978</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>0.222738986096858</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>0.2518518690452751</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>0.1034505425853444</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0266539433970383</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>-0.0035847527809796</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
+      <c r="J6" s="22" t="n">
+        <v>0.0391273262732771</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>-0.0271741120711617</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0981445446195723</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.0049151302268322</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.0864234261020719</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>0.4390738924446715</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>0.0451489216059546</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>-0.0620689864958077</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>0.0496576987240895</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>0.4183348304057541</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0290656252184038</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0450215489018153</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>0.3261686993953059</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.2728210975783458</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>0.3896396389139926</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.09133922051353879</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0387055024162966</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>-0.0190929272018391</v>
+      <c r="J7" s="22" t="n">
+        <v>0.0289823540103764</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>-0.0504066518392087</v>
       </c>
     </row>
     <row r="8">
@@ -2290,20 +2299,20 @@
       </c>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E8" s="19" t="n">
-        <v>0.1321614583333332</v>
+        <v>0.1414342629482072</v>
       </c>
       <c r="F8" s="19" t="n">
-        <v>0.150037756344753</v>
+        <v>0.0964170207378762</v>
       </c>
       <c r="G8" s="19" t="n">
-        <v>0.2362498448817933</v>
+        <v>0.2649730410389019</v>
       </c>
       <c r="H8" s="19" t="n">
-        <v>-0.0084528247140903</v>
+        <v>-0.0251099705853021</v>
       </c>
       <c r="I8" s="17" t="inlineStr">
         <is>
@@ -2311,10 +2320,10 @@
         </is>
       </c>
       <c r="J8" s="19" t="n">
-        <v>0.0191055357019943</v>
+        <v>0.0186656426342911</v>
       </c>
       <c r="K8" s="19" t="n">
-        <v>-0.0036968005684216</v>
+        <v>0.0211505713869569</v>
       </c>
     </row>
     <row r="9">
@@ -2337,16 +2346,16 @@
         </is>
       </c>
       <c r="E9" s="16" t="n">
-        <v>0.07988672013323291</v>
+        <v>0.0692566856433529</v>
       </c>
       <c r="F9" s="16" t="n">
-        <v>-0.0067742982507336</v>
+        <v>-0.0617588951430156</v>
       </c>
       <c r="G9" s="16" t="n">
-        <v>0.0086568460030058</v>
+        <v>0.009157212133674901</v>
       </c>
       <c r="H9" s="16" t="n">
-        <v>0.143880722551591</v>
+        <v>0.09960302631248361</v>
       </c>
       <c r="I9" s="14" t="inlineStr">
         <is>
@@ -2354,96 +2363,96 @@
         </is>
       </c>
       <c r="J9" s="16" t="n">
-        <v>0.0164818947768469</v>
+        <v>0.0149250392895053</v>
       </c>
       <c r="K9" s="16" t="n">
-        <v>0.022532255067367</v>
+        <v>0.0224111679198997</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="20" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="20" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="19" t="n">
-        <v>0.0566859552833223</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0013773894796531</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>-0.0324944605888269</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>0.1765403779916317</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0217295591533899</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>-0.031845613590586</v>
+      <c r="E10" s="22" t="n">
+        <v>0.0506879050733206</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.0547230872735138</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>-0.0115477911032093</v>
+      </c>
+      <c r="H10" s="22" t="n">
+        <v>0.1755526359764718</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="22" t="n">
+        <v>0.0204725739816463</v>
+      </c>
+      <c r="K10" s="22" t="n">
+        <v>-0.0301236938145638</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="17" t="n">
+      <c r="A11" s="14" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="14" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>0.0597095535901348</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0010162834071913</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.3789960160085972</v>
-      </c>
-      <c r="H11" s="19" t="n">
-        <v>0.1411151222172568</v>
-      </c>
-      <c r="I11" s="17" t="inlineStr">
+      <c r="D11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>0.0162133604778027</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>-0.0333333364964322</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.3743328706990612</v>
+      </c>
+      <c r="H11" s="16" t="n">
+        <v>0.09195942259908341</v>
+      </c>
+      <c r="I11" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J11" s="19" t="n">
-        <v>0.0243071344813338</v>
-      </c>
-      <c r="K11" s="19" t="n">
-        <v>-0.0254997664885543</v>
+      <c r="J11" s="16" t="n">
+        <v>0.0242188458215557</v>
+      </c>
+      <c r="K11" s="16" t="n">
+        <v>0.0521951315406046</v>
       </c>
     </row>
     <row r="12">
@@ -2452,7 +2461,7 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
@@ -2466,27 +2475,27 @@
         </is>
       </c>
       <c r="E12" s="16" t="n">
-        <v>0.1174277726001864</v>
+        <v>0.0331789165930611</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.0143824027072758</v>
+        <v>-0.0503546532164228</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0522318906284782</v>
+        <v>0.0102323313211429</v>
       </c>
       <c r="H12" s="16" t="n">
-        <v>-0.0653905113355023</v>
+        <v>0.08954328356413629</v>
       </c>
       <c r="I12" s="14" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J12" s="16" t="n">
-        <v>0.0239150705522644</v>
+        <v>0.0150649269816227</v>
       </c>
       <c r="K12" s="16" t="n">
-        <v>0.0355140318659195</v>
+        <v>0.0292262535427767</v>
       </c>
     </row>
     <row r="13">
@@ -2495,7 +2504,7 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C13" s="14" t="inlineStr">
@@ -2509,328 +2518,328 @@
         </is>
       </c>
       <c r="E13" s="16" t="n">
-        <v>0.0244274576201692</v>
+        <v>-0.0067894952337743</v>
       </c>
       <c r="F13" s="16" t="n">
-        <v>-0.0125091760455638</v>
+        <v>-0.1087902509486444</v>
       </c>
       <c r="G13" s="16" t="n">
-        <v>0.0023197702088397</v>
+        <v>-0.0799640726131888</v>
       </c>
       <c r="H13" s="16" t="n">
-        <v>0.093888274143099</v>
+        <v>0.2700034016408581</v>
       </c>
       <c r="I13" s="14" t="inlineStr">
         <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="16" t="n">
+        <v>0.0199919385612366</v>
+      </c>
+      <c r="K13" s="16" t="n">
+        <v>0.0585457682616472</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="23" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n">
+        <v>0.0309509973490322</v>
+      </c>
+      <c r="F14" s="24" t="n">
+        <v>-0.094414230876496</v>
+      </c>
+      <c r="G14" s="24" t="n">
+        <v>0.0217512204690737</v>
+      </c>
+      <c r="H14" s="24" t="n">
+        <v>0.0072564934881456</v>
+      </c>
+      <c r="I14" s="23" t="inlineStr">
+        <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0158142377417917</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>0.0109975418263577</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
+      <c r="J14" s="24" t="n">
+        <v>0.0220082165121914</v>
+      </c>
+      <c r="K14" s="24" t="n">
+        <v>0.0485436298099814</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.003842473888012</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.06323396741621271</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>-0.0494958900220315</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>0.2754202463029134</v>
-      </c>
-      <c r="I14" s="20" t="inlineStr">
+      <c r="E15" s="24" t="n">
+        <v>0.0537534754402224</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.09833465503568591</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.0062582137855674</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.072675383982487</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.0232667503068911</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0531914626506075</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n">
+        <v>-0.0587492103600758</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-0.008649367930805001</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>0.1287878787878789</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>-0.07283062755943109</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J16" s="24" t="n">
+        <v>0.0304241894949795</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0109466332367203</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>0.0257214947334201</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.0926747904054562</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.2450385606721304</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.0450095842442002</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0177363021312252</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0020191724169313</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="23" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>0.028909390561747</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.1357615411646683</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-0.1251396307066166</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>-0.0032480593059114</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="21" t="n">
-        <v>0.0205513225793467</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>0.0585457682616472</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="20" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="20" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="20" t="inlineStr">
+      <c r="J18" s="24" t="n">
+        <v>0.0168788378065433</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>0.0609242801466308</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="21" t="n">
-        <v>0.0334645669291338</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.0606060606060605</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.172747580044676</v>
-      </c>
-      <c r="H15" s="21" t="n">
-        <v>-0.0636808955939812</v>
-      </c>
-      <c r="I15" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J15" s="21" t="n">
-        <v>0.0296518405995465</v>
-      </c>
-      <c r="K15" s="21" t="n">
-        <v>0.0599572762440211</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="20" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="20" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.0405844155844156</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.09286262471220259</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.009393680614859099</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>-0.0580067976671495</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>0.0164427984381051</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.07134075330888549</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="21" t="n">
-        <v>0.0280112038831694</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>-0.0367453482218003</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.001637592093082</v>
-      </c>
-      <c r="H16" s="21" t="n">
-        <v>0.0260973082789615</v>
-      </c>
-      <c r="I16" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="21" t="n">
-        <v>0.0234074018350842</v>
-      </c>
-      <c r="K16" s="21" t="n">
-        <v>0.0551630966573649</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="20" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="20" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="21" t="n">
-        <v>0.038871454220954</v>
-      </c>
-      <c r="F17" s="21" t="n">
-        <v>-0.0444059816567173</v>
-      </c>
-      <c r="G17" s="21" t="n">
-        <v>-0.2321377142522179</v>
-      </c>
-      <c r="H17" s="21" t="n">
-        <v>-0.0452796696971707</v>
-      </c>
-      <c r="I17" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="21" t="n">
-        <v>0.0183898389304276</v>
-      </c>
-      <c r="K17" s="21" t="n">
-        <v>0.0766731872627277</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="20" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="21" t="n">
-        <v>-0.0138960211314199</v>
-      </c>
-      <c r="F18" s="21" t="n">
-        <v>-0.0689990123307769</v>
-      </c>
-      <c r="G18" s="21" t="n">
-        <v>-0.1529619421376187</v>
-      </c>
-      <c r="H18" s="21" t="n">
-        <v>0.014174275884534</v>
-      </c>
-      <c r="I18" s="20" t="inlineStr">
+      <c r="E20" s="24" t="n">
+        <v>-0.0031696042992221</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1107445821770294</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>-0.1560823264875783</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.0205906250469637</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="21" t="n">
-        <v>0.0138580840698411</v>
-      </c>
-      <c r="K18" s="21" t="n">
-        <v>0.0949826980521894</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="20" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="21" t="n">
-        <v>-0.0275303643724695</v>
-      </c>
-      <c r="F19" s="21" t="n">
-        <v>-0.0243704305442729</v>
-      </c>
-      <c r="G19" s="21" t="n">
-        <v>0.0186598812553011</v>
-      </c>
-      <c r="H19" s="21" t="n">
-        <v>-0.06740262125769519</v>
-      </c>
-      <c r="I19" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="21" t="n">
-        <v>0.0179854767446905</v>
-      </c>
-      <c r="K19" s="21" t="n">
-        <v>0.08833658943450449</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="20" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="20" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="21" t="n">
-        <v>0.0151415611861394</v>
-      </c>
-      <c r="F20" s="21" t="n">
-        <v>-0.1034883898358012</v>
-      </c>
-      <c r="G20" s="21" t="n">
-        <v>-0.1433333502875433</v>
-      </c>
-      <c r="H20" s="21" t="n">
-        <v>-0.0260802057590543</v>
-      </c>
-      <c r="I20" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="21" t="n">
-        <v>0.0181500238753827</v>
-      </c>
-      <c r="K20" s="21" t="n">
-        <v>0.08833658943450449</v>
+      <c r="J20" s="24" t="n">
+        <v>0.0133433275136874</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.1000000839371915</v>
       </c>
     </row>
   </sheetData>
@@ -2855,7 +2864,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2863,7 +2872,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2888,7 +2897,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, SISE.IS, SAHOL.IS, TOASO.IS, GARAN.IS</t>
+          <t>KCHOL.IS, SAHOL.IS, EREGL.IS, GARAN.IS, TCELL.IS</t>
         </is>
       </c>
     </row>
@@ -2900,7 +2909,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>TUPRS.IS, BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2912,7 +2921,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, PETKM.IS, BIMAS.IS, AKBNK.IS, EREGL.IS</t>
+          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2933,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ASELS.IS, YKBNK.IS, FROTO.IS, ARCLK.IS, THYAO.IS, PGSUS.IS</t>
+          <t>YKBNK.IS, TOASO.IS, ASELS.IS, FROTO.IS, PGSUS.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2945,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.37 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.18 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2974,7 +2983,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2982,7 +2991,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3064,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3139,7 +3148,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3160,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3175,7 +3184,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3225,7 +3234,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3233,7 +3242,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3257,7 +3266,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>14235.7998046875</v>
+        <v>13892.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3267,7 +3276,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13450.72752441406</v>
+        <v>13465.90302246094</v>
       </c>
     </row>
     <row r="6">
@@ -3301,7 +3310,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>67.66</v>
+        <v>60.67</v>
       </c>
     </row>
     <row r="9">
@@ -3337,14 +3346,14 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-11</t>
+          <t>Rapor Tarihi: 2026-09-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3358,7 +3367,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-15 06:51</t>
+          <t>Son Güncelleme: 2026-09-16 06:55</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3422,23 +3431,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="22" t="n">
+      <c r="C4" s="25" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="22" t="n">
-        <v>393.75</v>
-      </c>
-      <c r="E4" s="23" t="n">
-        <v>-0.0143929912390488</v>
-      </c>
-      <c r="F4" s="22" t="n">
-        <v>-10139.57076187839</v>
-      </c>
-      <c r="G4" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H4" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="D4" s="25" t="n">
+        <v>372.5</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>-0.06758448060075095</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>-47611.89749055915</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="5">
@@ -3452,23 +3461,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="22" t="n">
+      <c r="C5" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="22" t="n">
+      <c r="D5" s="25" t="n">
         <v>225.5</v>
       </c>
-      <c r="E5" s="23" t="n">
+      <c r="E5" s="26" t="n">
         <v>0.1446700507614214</v>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="25" t="n">
         <v>420461.0410290817</v>
       </c>
-      <c r="G5" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H5" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="G5" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="6">
@@ -3482,23 +3491,23 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C6" s="22" t="n">
+      <c r="C6" s="25" t="n">
         <v>103.5</v>
       </c>
-      <c r="D6" s="22" t="n">
-        <v>103.6999969482422</v>
-      </c>
-      <c r="E6" s="23" t="n">
-        <v>0.001932337664175776</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>5923.081018209923</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H6" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="D6" s="25" t="n">
+        <v>102.4000015258789</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.01062800458088009</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-32577.39750226866</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="7">
@@ -3512,23 +3521,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C7" s="22" t="n">
+      <c r="C7" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D7" s="22" t="n">
-        <v>95.30000305175781</v>
-      </c>
-      <c r="E7" s="23" t="n">
-        <v>-0.01243520153618849</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>-1091.990750535231</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H7" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="D7" s="25" t="n">
+        <v>94.94999694824219</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.01606220779023637</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-1410.494416923553</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="8">
@@ -3542,29 +3551,29 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C8" s="22" t="n">
+      <c r="C8" s="25" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D8" s="22" t="n">
-        <v>134.1999969482422</v>
-      </c>
-      <c r="E8" s="23" t="n">
-        <v>0.005997024650380434</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>29041.80015604291</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H8" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="D8" s="25" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.003748126108521266</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>18151.0558567429</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -3572,53 +3581,53 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C9" s="22" t="n">
-        <v>44.97999954223633</v>
-      </c>
-      <c r="D9" s="22" t="n">
-        <v>44.97999954223633</v>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="22" t="n">
-        <v>-2.91038304567337e-11</v>
-      </c>
-      <c r="G9" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="C9" s="25" t="n">
+        <v>299.75</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>-0.05170975813177647</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>-11633.86917042549</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="n">
-        <v>299.75</v>
-      </c>
-      <c r="D10" s="22" t="n">
-        <v>299.75</v>
-      </c>
-      <c r="E10" s="23" t="n">
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C10" s="25" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="D10" s="25" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="E10" s="26" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>-2.91038304567337e-11</v>
       </c>
-      <c r="G10" s="22" t="n">
-        <v>12500744.0388727</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>0.0556990517139155</v>
+      <c r="G10" s="25" t="n">
+        <v>12394625.39385293</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>0.0388061737220883</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -172,15 +172,6 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -197,6 +188,21 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -576,13 +582,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -612,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -629,7 +635,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -646,7 +652,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Piyasa Rejimi: Risk ON</t>
+          <t>Piyasa Rejimi: Risk OFF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -663,7 +669,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aktif Model: volume_heavy</t>
+          <t>Aktif Model: low_volatility</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -680,7 +686,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 60.67/100</t>
+          <t>Güven Puanı: 61.83/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -740,7 +746,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, EREGL.IS, SAHOL.IS, GARAN.IS, TCELL.IS</t>
+          <t>AL: TUPRS.IS, GARAN.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -757,7 +763,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS, BIMAS.IS</t>
+          <t>AZALT: KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -774,7 +780,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>ÇIK: BIMAS.IS, THYAO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -791,7 +797,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %50</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -889,7 +895,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 5</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -946,12 +952,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 5</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -960,41 +966,41 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.1340221997111379</v>
+        <v>0.215740306630336</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>13402.21997111379</v>
+        <v>21574.0306630336</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0493252973688849</v>
+        <v>0.0584414874691192</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>661.0684854783956</v>
+        <v>1260.818442652072</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>236.6228545566835</v>
+        <v>436.6071135810117</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>214.225</v>
+        <v>390.8670301069489</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9865059473776966</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>1.114369118072656</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %50</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1003,25 +1009,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.09856326579837003</v>
+        <v>0.2019553622193581</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>9856.326579837003</v>
+        <v>20195.53622193581</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0521951315406046</v>
+        <v>0.0327412900152173</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>514.4522623417498</v>
+        <v>661.2279084552264</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>40.88830345387684</v>
+        <v>131.9843400156211</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>36.77983023365233</v>
+        <v>121.4100028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9750657283869907</v>
+        <v>0.6548258003043428</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1044,25 +1050,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09457033532365614</v>
+        <v>0.1823043311503058</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9457.033532365613</v>
+        <v>18230.43311503058</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0224111679198997</v>
+        <v>0.0305622771399269</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>211.943166517968</v>
+        <v>557.1635492424656</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>97.0779372738432</v>
+        <v>93.05977677076189</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>87.61030481266786</v>
+        <v>85.78500289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2899222864249615</v>
+        <v>0.6112455427985397</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1071,124 +1077,42 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.08803480032718682</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>8803.480032718682</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.0292262535427767</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>257.2927394950083</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>137.8133890674793</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>127.2049942016602</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>0.5845250708555337</v>
-      </c>
-      <c r="K23" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.08480939883964915</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>8480.939883964915</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.0585457682616472</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>496.523141087571</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>108.3950882852053</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>97.28000144958496</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>1.170915365232943</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="11" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" s="11" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="11" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="12" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="13" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F25" s="12" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="13" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="13" t="inlineStr"/>
-      <c r="I25" s="13" t="inlineStr"/>
-      <c r="J25" s="11" t="inlineStr"/>
-      <c r="K25" s="11" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K25"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1199,7 +1123,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1222,7 +1146,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1243,7 +1167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1285,7 +1209,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1433,40 +1357,40 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>225.5</v>
+        <v>218.8000030517578</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>0.0371203067330339</v>
+        <v>-0.0674846665340597</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0493252973688849</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.120622641333925</v>
+        <v>0.0914169657590902</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>233.8706291682991</v>
+        <v>204.0343578081587</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>236.6228545566835</v>
+        <v>223.8910588259786</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>252.7004056208001</v>
+        <v>238.8020354388292</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>214.225</v>
+        <v>204.0343578081587</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>60.67</v>
+        <v>61.83</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1475,7 +1399,7 @@
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1485,45 +1409,45 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>415.75</v>
+        <v>413.25</v>
       </c>
       <c r="E9" s="19" t="n">
-        <v>-0.09857159599125891</v>
+        <v>-0.0156773693904196</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0028743310356713</v>
+        <v>-0.000942521339213</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.1274262917059938</v>
+        <v>0.06844627048378669</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>374.7688589666341</v>
+        <v>406.7713270994091</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>416.9450031280804</v>
+        <v>412.8605030565702</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>468.7274807767669</v>
+        <v>441.5354212774249</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>374.7688589666341</v>
+        <v>392.5875</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>60.67</v>
+        <v>61.83</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
@@ -1532,7 +1456,7 @@
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
@@ -1542,54 +1466,54 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D10" s="21" t="n">
-        <v>23.65999984741211</v>
+        <v>127.8000030517578</v>
       </c>
       <c r="E10" s="22" t="n">
-        <v>-0.1400832487570158</v>
+        <v>-0.0446735791747727</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>-0.0271741120711617</v>
+        <v>0.0327412900152173</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>0</v>
+        <v>0.0795560183272892</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>20.34563020319612</v>
+        <v>122.0907194968889</v>
       </c>
       <c r="I10" s="21" t="n">
-        <v>23.01706035995486</v>
+        <v>131.9843400156211</v>
       </c>
       <c r="J10" s="21" t="n">
-        <v>23.65999984741211</v>
+        <v>137.9672624367711</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>20.34563020319612</v>
+        <v>121.4100028991699</v>
       </c>
       <c r="L10" s="20" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M10" s="20" t="n">
-        <v>60.67</v>
+        <v>61.83</v>
       </c>
       <c r="N10" s="20" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O10" s="20" t="inlineStr">
         <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1599,401 +1523,173 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.0289964214106895</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>0.0584414874691192</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.1756284689632632</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>400.5389761680906</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>436.6071135810117</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>484.9467434473461</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>390.8670301069489</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="20" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>90.30000305175781</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.0122824827871298</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0305622771399269</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.0937142265175849</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>89.19089481859683</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>93.05977677076189</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>98.76239799228885</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>85.78500289916992</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="21" t="n">
-        <v>43.52000045776367</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.1374999561178063</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.0504066518392087</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.0619999332492389</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>37.53600230457425</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>41.32630294664698</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>46.21823758115187</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>37.53600230457425</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="D13" s="18" t="n">
+        <v>285.25</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.0557185041218549</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0102041004987833</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0891252177983346</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>269.3562966992409</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>282.3392803327221</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>310.6729683769749</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>269.3562966992409</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="20" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>429.75</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.012842558577034</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.0211505713869569</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.1354168120573042</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>424.2309104515197</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>438.8394580535447</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>487.9453749816265</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>408.2625</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="15" t="n">
-        <v>94.94999694824219</v>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.07730060422829969</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>0.0224111679198997</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>0.09470956359125229</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>87.61030481266786</v>
-      </c>
-      <c r="I13" s="15" t="n">
-        <v>97.0779372738432</v>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>103.9426697222009</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>87.61030481266786</v>
-      </c>
-      <c r="L13" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="14" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N13" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O13" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>72.55000305175781</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.1195457879117688</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.0301236938145638</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.05159344410234</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>63.87695577393419</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>70.36452897358099</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>76.29310757883327</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>63.87695577393419</v>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>trend desteği var; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="20" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D15" s="15" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="E15" s="16" t="n">
-        <v>-0.0535298595992588</v>
-      </c>
-      <c r="F15" s="16" t="n">
-        <v>0.0521951315406046</v>
-      </c>
-      <c r="G15" s="16" t="n">
-        <v>0.1392962007538372</v>
-      </c>
-      <c r="H15" s="15" t="n">
-        <v>36.77983023365233</v>
-      </c>
-      <c r="I15" s="15" t="n">
-        <v>40.88830345387684</v>
-      </c>
-      <c r="J15" s="15" t="n">
-        <v>44.27305105666533</v>
-      </c>
-      <c r="K15" s="15" t="n">
-        <v>36.77983023365233</v>
-      </c>
-      <c r="L15" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M15" s="14" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N15" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="15" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E16" s="16" t="n">
-        <v>-0.0375302339476217</v>
-      </c>
-      <c r="F16" s="16" t="n">
-        <v>0.0292262535427767</v>
-      </c>
-      <c r="G16" s="16" t="n">
-        <v>0.148990099438721</v>
-      </c>
-      <c r="H16" s="15" t="n">
-        <v>128.8746957999642</v>
-      </c>
-      <c r="I16" s="15" t="n">
-        <v>137.8133890674793</v>
-      </c>
-      <c r="J16" s="15" t="n">
-        <v>153.8497673019657</v>
-      </c>
-      <c r="K16" s="15" t="n">
-        <v>127.2049942016602</v>
-      </c>
-      <c r="L16" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="14" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N16" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="15" t="n">
-        <v>102.4000015258789</v>
-      </c>
-      <c r="E17" s="16" t="n">
-        <v>-0.0002837898210087</v>
-      </c>
-      <c r="F17" s="16" t="n">
-        <v>0.0585457682616472</v>
-      </c>
-      <c r="G17" s="16" t="n">
-        <v>0.07823596948359129</v>
-      </c>
-      <c r="H17" s="15" t="n">
-        <v>102.3709414477746</v>
-      </c>
-      <c r="I17" s="15" t="n">
-        <v>108.3950882852053</v>
-      </c>
-      <c r="J17" s="15" t="n">
-        <v>110.4113649203773</v>
-      </c>
-      <c r="K17" s="15" t="n">
-        <v>97.28000144958496</v>
-      </c>
-      <c r="L17" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>60.67</v>
-      </c>
-      <c r="N17" s="14" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="14" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="M13" s="17" t="n">
+        <v>61.83</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2023,7 +1719,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2040,7 +1736,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2127,20 +1823,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>0.1141304683800035</v>
+        <v>0.05598458626625</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.1458333155650113</v>
+        <v>0.09345325526161311</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1965800588720865</v>
+        <v>0.1712120671309878</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>0.2024233381883688</v>
+        <v>0.1925965225083146</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2148,10 +1844,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0185148051688734</v>
+        <v>0.0188532240450182</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0493252973688849</v>
+        <v>0.0232680790823229</v>
       </c>
     </row>
     <row r="5">
@@ -2160,30 +1856,30 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>0.2015895953757225</v>
+        <v>0.1094062436839293</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.7927986672806153</v>
+        <v>0.0826822974966194</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.63474615066625</v>
+        <v>0.2148702230576522</v>
       </c>
       <c r="H5" s="19" t="n">
-        <v>0.1029603441310553</v>
+        <v>-0.0237745674910492</v>
       </c>
       <c r="I5" s="17" t="inlineStr">
         <is>
@@ -2191,10 +1887,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0265643910667515</v>
+        <v>0.0189600016509259</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.0028743310356713</v>
+        <v>-0.000942521339213</v>
       </c>
     </row>
     <row r="6">
@@ -2203,7 +1899,7 @@
       </c>
       <c r="B6" s="20" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C6" s="20" t="inlineStr">
@@ -2213,31 +1909,31 @@
       </c>
       <c r="D6" s="20" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E6" s="22" t="n">
-        <v>0.2578416012318978</v>
+        <v>-0.0244274576201694</v>
       </c>
       <c r="F6" s="22" t="n">
-        <v>0.222738986096858</v>
+        <v>-0.0884450368501941</v>
       </c>
       <c r="G6" s="22" t="n">
-        <v>0.2518518690452751</v>
+        <v>0.0012388917695613</v>
       </c>
       <c r="H6" s="22" t="n">
-        <v>0.1034505425853444</v>
+        <v>0.08155505377528489</v>
       </c>
       <c r="I6" s="20" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J6" s="22" t="n">
-        <v>0.0391273262732771</v>
+        <v>0.016080675014834</v>
       </c>
       <c r="K6" s="22" t="n">
-        <v>-0.0271741120711617</v>
+        <v>0.0327412900152173</v>
       </c>
     </row>
     <row r="7">
@@ -2246,600 +1942,600 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="22" t="n">
+        <v>0.1402902557014513</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>0.8300799075861638</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>0.6296613607144284</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>0.0862299307679437</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="22" t="n">
+        <v>0.0262217816885468</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>0.0584414874691192</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="20" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>0.0100671309901307</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>-0.1041666635129818</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>-0.0331851120432711</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>0.0745651900503541</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.0161046396019991</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0.0305622771399269</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>0.0235419269200769</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>-0.0506203710706606</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0.3655007563629175</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>0.0714109130424105</v>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0.0242913783321116</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0.008960632080292101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>-0.0435238761645628</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.1355450526232967</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.184257652425813</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.0147699774830133</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>0.0139184324941441</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>0.1837161005113008</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>0.1483544458316852</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>0.1261172290220056</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>0.1215979397589577</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>0.0394788088920892</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.002557432846991</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>0.0109011623071553</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>-0.097924715587348</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>-0.0106257209845535</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.1784934526235051</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>0.0210905983796827</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.0111110916693351</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.06552006552006551</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.1263399693721286</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>-0.0239520958083832</v>
+      </c>
+      <c r="H13" s="19" t="n">
+        <v>-0.0477911128248186</v>
+      </c>
+      <c r="I13" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="19" t="n">
+        <v>0.0169602756515284</v>
+      </c>
+      <c r="K13" s="19" t="n">
+        <v>-0.0102041004987833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>0.058659217877095</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.1226851851851852</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.0214603528931218</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.07671393723405789</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.0229670667349307</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.0355139613832504</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C7" s="20" t="inlineStr">
+      <c r="C15" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>0.0451489216059546</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>-0.0620689864958077</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0.0496576987240895</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>0.4183348304057541</v>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>0.0241545884817155</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.0770569701056099</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>0.0329741328636228</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0.4172946821346979</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.029132286850575</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0.0199776849855937</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.0112063083878781</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.1847826086956522</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.1539763258988119</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0.0172821677934933</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0.0174587020368874</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.0204081632653061</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.0270967741935483</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.0431472081218273</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0.1698991466252908</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.1090999412102676</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="22" t="n">
-        <v>0.0289823540103764</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>-0.0504066518392087</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="J17" s="26" t="n">
+        <v>0.0298323340087646</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.0485099953300594</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="n">
-        <v>0.1414342629482072</v>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.0964170207378762</v>
-      </c>
-      <c r="G8" s="19" t="n">
-        <v>0.2649730410389019</v>
-      </c>
-      <c r="H8" s="19" t="n">
-        <v>-0.0251099705853021</v>
-      </c>
-      <c r="I8" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="19" t="n">
-        <v>0.0186656426342911</v>
-      </c>
-      <c r="K8" s="19" t="n">
-        <v>0.0211505713869569</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="14" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.0088495191118265</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.1412924544872787</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.260795744573102</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>-0.029237019864496</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0183196672164969</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.0013443469214756</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>0.0692566856433529</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>-0.0617588951430156</v>
-      </c>
-      <c r="G9" s="16" t="n">
-        <v>0.009157212133674901</v>
-      </c>
-      <c r="H9" s="16" t="n">
-        <v>0.09960302631248361</v>
-      </c>
-      <c r="I9" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J9" s="16" t="n">
-        <v>0.0149250392895053</v>
-      </c>
-      <c r="K9" s="16" t="n">
-        <v>0.0224111679198997</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.0451488666391344</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.1371527416746547</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>-0.08639707042477909</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>0.2435990625973061</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>0.0202848756435761</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.0835821125918427</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>0.0506879050733206</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>-0.0547230872735138</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>-0.0115477911032093</v>
-      </c>
-      <c r="H10" s="22" t="n">
-        <v>0.1755526359764718</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="22" t="n">
-        <v>0.0204725739816463</v>
-      </c>
-      <c r="K10" s="22" t="n">
-        <v>-0.0301236938145638</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>0.0162133604778027</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>-0.0333333364964322</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.3743328706990612</v>
-      </c>
-      <c r="H11" s="16" t="n">
-        <v>0.09195942259908341</v>
-      </c>
-      <c r="I11" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="16" t="n">
-        <v>0.0242188458215557</v>
-      </c>
-      <c r="K11" s="16" t="n">
-        <v>0.0521951315406046</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>0.0331789165930611</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>-0.0503546532164228</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0102323313211429</v>
-      </c>
-      <c r="H12" s="16" t="n">
-        <v>0.08954328356413629</v>
-      </c>
-      <c r="I12" s="14" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="16" t="n">
-        <v>0.0150649269816227</v>
-      </c>
-      <c r="K12" s="16" t="n">
-        <v>0.0292262535427767</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="14" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="14" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="16" t="n">
-        <v>-0.0067894952337743</v>
-      </c>
-      <c r="F13" s="16" t="n">
-        <v>-0.1087902509486444</v>
-      </c>
-      <c r="G13" s="16" t="n">
-        <v>-0.0799640726131888</v>
-      </c>
-      <c r="H13" s="16" t="n">
-        <v>0.2700034016408581</v>
-      </c>
-      <c r="I13" s="14" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.0208920920955418</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1437036961684992</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.0034482452447002</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>0.0202434963345725</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="16" t="n">
-        <v>0.0199919385612366</v>
-      </c>
-      <c r="K13" s="16" t="n">
-        <v>0.0585457682616472</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="23" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="23" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="24" t="n">
-        <v>0.0309509973490322</v>
-      </c>
-      <c r="F14" s="24" t="n">
-        <v>-0.094414230876496</v>
-      </c>
-      <c r="G14" s="24" t="n">
-        <v>0.0217512204690737</v>
-      </c>
-      <c r="H14" s="24" t="n">
-        <v>0.0072564934881456</v>
-      </c>
-      <c r="I14" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="24" t="n">
-        <v>0.0220082165121914</v>
-      </c>
-      <c r="K14" s="24" t="n">
-        <v>0.0485436298099814</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>0.0537534754402224</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.09833465503568591</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.0062582137855674</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.072675383982487</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0232667503068911</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0531914626506075</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-0.0587492103600758</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>-0.008649367930805001</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>0.1287878787878789</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>-0.07283062755943109</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0304241894949795</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0109466332367203</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>0.0257214947334201</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.0926747904054562</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.2450385606721304</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.0450095842442002</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0177363021312252</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0020191724169313</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="23" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>0.028909390561747</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.1357615411646683</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.1251396307066166</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>-0.0032480593059114</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0168788378065433</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>0.0609242801466308</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0405844155844156</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.09286262471220259</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.009393680614859099</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>-0.0580067976671495</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0164427984381051</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.07134075330888549</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.0031696042992221</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1107445821770294</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>-0.1560823264875783</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.0205906250469637</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.0133433275136874</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.1000000839371915</v>
+      <c r="J20" s="26" t="n">
+        <v>0.0229650470108602</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.037452235290006</v>
       </c>
     </row>
   </sheetData>
@@ -2864,7 +2560,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2872,7 +2568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2897,7 +2593,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, SAHOL.IS, EREGL.IS, GARAN.IS, TCELL.IS</t>
+          <t>GARAN.IS, TUPRS.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2909,7 +2605,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2921,7 +2617,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>BIMAS.IS, THYAO.IS</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2629,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, TOASO.IS, ASELS.IS, FROTO.IS, PGSUS.IS, THYAO.IS, ARCLK.IS</t>
+          <t>EREGL.IS, ARCLK.IS, PETKM.IS, AKBNK.IS, TOASO.IS, SISE.IS, PGSUS.IS, ASELS.IS, FROTO.IS, TCELL.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2945,7 +2641,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.18 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.06 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2957,7 +2653,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2983,7 +2679,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2991,7 +2687,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3064,7 +2760,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3100,7 +2796,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3160,7 +2856,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3196,7 +2892,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3234,7 +2930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3242,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3266,7 +2962,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13892.2998046875</v>
+        <v>13122.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3276,7 +2972,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13465.90302246094</v>
+        <v>13476.94251953125</v>
       </c>
     </row>
     <row r="6">
@@ -3287,7 +2983,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Risk ON</t>
+          <t>Risk OFF</t>
         </is>
       </c>
     </row>
@@ -3299,7 +2995,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>volume_heavy</t>
+          <t>low_volatility</t>
         </is>
       </c>
     </row>
@@ -3310,7 +3006,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60.67</v>
+        <v>61.83</v>
       </c>
     </row>
     <row r="9">
@@ -3321,7 +3017,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
+          <t>BIST100 MA200 altında olduğu için savunmacı rejim izleniyor.</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3041,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3353,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-14</t>
+          <t>Rapor Tarihi: 2026-09-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3367,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-16 06:55</t>
+          <t>Son Güncelleme: 2026-09-17 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3431,23 +3127,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="27" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>372.5</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>-0.06758448060075095</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>-47611.89749055915</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D4" s="27" t="n">
+        <v>377</v>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>-0.05632040050062581</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>-39676.5812421327</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="5">
@@ -3461,23 +3157,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="27" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>225.5</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.1446700507614214</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>420461.0410290817</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D5" s="27" t="n">
+        <v>218.8000030517578</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>0.1106599139683138</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>321615.8588624299</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="6">
@@ -3491,23 +3187,23 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="27" t="n">
         <v>103.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>102.4000015258789</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.01062800458088009</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-32577.39750226866</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D6" s="27" t="n">
+        <v>99.40000152587891</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>-0.03961351182725692</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>-121424.9684817605</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="7">
@@ -3521,23 +3217,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="27" t="n">
         <v>96.5</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>94.94999694824219</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.01606220779023637</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-1410.494416923553</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D7" s="27" t="n">
+        <v>90.30000305175781</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>-0.06424867303877912</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>-5641.963782278472</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="8">
@@ -3551,23 +3247,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="27" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>0.003748126108521266</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>18151.0558567429</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D8" s="27" t="n">
+        <v>127.8000030517578</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>-0.04197894378520017</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>-203291.4932397706</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="9">
@@ -3581,23 +3277,23 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="27" t="n">
         <v>299.75</v>
       </c>
-      <c r="D9" s="25" t="n">
+      <c r="D9" s="27" t="n">
         <v>284.25</v>
       </c>
-      <c r="E9" s="26" t="n">
+      <c r="E9" s="28" t="n">
         <v>-0.05170975813177647</v>
       </c>
-      <c r="F9" s="25" t="n">
+      <c r="F9" s="27" t="n">
         <v>-11633.86917042549</v>
       </c>
-      <c r="G9" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="G9" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
     <row r="10">
@@ -3611,23 +3307,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="27" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D10" s="25" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="E10" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="25" t="n">
-        <v>-2.91038304567337e-11</v>
-      </c>
-      <c r="G10" s="25" t="n">
-        <v>12394625.39385293</v>
-      </c>
-      <c r="H10" s="26" t="n">
-        <v>0.0388061737220883</v>
+      <c r="D10" s="27" t="n">
+        <v>38.2599983215332</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>-0.01544009983001726</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>-3361.020936387358</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>11985832.91755696</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>0.0137404994663967</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -86,22 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,10 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -170,6 +162,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -190,19 +191,13 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -582,13 +577,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -618,7 +613,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -635,7 +630,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -652,7 +647,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Piyasa Rejimi: Risk OFF</t>
+          <t>Piyasa Rejimi: Risk ON</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -669,7 +664,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aktif Model: low_volatility</t>
+          <t>Aktif Model: volume_heavy</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -686,7 +681,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 61.83/100</t>
+          <t>Güven Puanı: 51.86/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -746,7 +741,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: TUPRS.IS, GARAN.IS, SAHOL.IS</t>
+          <t>AL: KCHOL.IS, BIMAS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -763,7 +758,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS</t>
+          <t>AZALT: PETKM.IS, SISE.IS, AKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -780,7 +775,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: BIMAS.IS, THYAO.IS</t>
+          <t>ÇIK: TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -797,7 +792,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %40</t>
+          <t>NAKIT: %50</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -895,7 +890,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 3</t>
+          <t>Qualified opportunities count: 5</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -952,12 +947,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 2</t>
+          <t>Rejected opportunities count: 5</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -966,25 +961,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.215740306630336</v>
+        <v>0.12307111833361</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21574.0306630336</v>
+        <v>12307.111833361</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0584414874691192</v>
+        <v>0.0379876477441236</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1260.818442652072</v>
+        <v>467.5182290732529</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>436.6071135810117</v>
+        <v>214.3444492591615</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>390.8670301069489</v>
+        <v>196.175</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.114369118072656</v>
+        <v>0.759752954882472</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -995,12 +990,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %40</t>
+          <t>Cash allocation %: %50</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1009,25 +1004,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2019553622193581</v>
+        <v>0.1083549289094442</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20195.53622193581</v>
+        <v>10835.49289094442</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0327412900152173</v>
+        <v>0.0485933057984229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>661.2279084552264</v>
+        <v>526.5324195262998</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>131.9843400156211</v>
+        <v>425.2045855012605</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>121.4100028991699</v>
+        <v>385.225</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6548258003043428</v>
+        <v>0.9718661159684575</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1041,78 +1036,160 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.09211535586320244</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>9211.535586320244</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>305.0624412184431</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>124.9038996016319</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>114.855001449585</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.662348722120733</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C22" s="6" t="inlineStr">
+      <c r="C23" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D22" s="7" t="n">
-        <v>0.1823043311503058</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>18230.43311503058</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0305622771399269</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>557.1635492424656</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>93.05977677076189</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>85.78500289916992</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.6112455427985397</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="11" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="D23" s="7" t="n">
+        <v>0.08923779370436544</v>
+      </c>
+      <c r="E23" s="8" t="n">
+        <v>8923.779370436543</v>
+      </c>
+      <c r="F23" s="7" t="n">
+        <v>0.061538473957351</v>
+      </c>
+      <c r="G23" s="8" t="n">
+        <v>549.1557643887553</v>
+      </c>
+      <c r="H23" s="8" t="n">
+        <v>89.48769659416303</v>
+      </c>
+      <c r="I23" s="8" t="n">
+        <v>80.08500289916992</v>
+      </c>
+      <c r="J23" s="6" t="n">
+        <v>1.230769479147021</v>
+      </c>
+      <c r="K23" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>0.08722080318937789</v>
+      </c>
+      <c r="E24" s="8" t="n">
+        <v>8722.080318937789</v>
+      </c>
+      <c r="F24" s="7" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+      <c r="G24" s="8" t="n">
+        <v>364.3891427389418</v>
+      </c>
+      <c r="H24" s="8" t="n">
+        <v>36.23302987695052</v>
+      </c>
+      <c r="I24" s="8" t="n">
+        <v>32.33501002394477</v>
+      </c>
+      <c r="J24" s="6" t="n">
+        <v>0.5942894806665029</v>
+      </c>
+      <c r="K24" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="B25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D25" s="11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="E25" s="12" t="n">
+        <v>50000</v>
+      </c>
+      <c r="F25" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G25" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="H25" s="12" t="inlineStr"/>
+      <c r="I25" s="12" t="inlineStr"/>
+      <c r="J25" s="10" t="inlineStr"/>
+      <c r="K25" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K23"/>
+  <autoFilter ref="A19:K25"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1123,7 +1200,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1223,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1167,7 +1244,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1209,7 +1286,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 12</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1347,349 +1424,691 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.039087920591243</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0379876477441236</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.1206226545342643</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>198.4283443979083</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>214.3444492591615</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>231.4085781613256</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>196.175</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0985715365910573</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>-0.003584755659184</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.1274261934904716</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>362.1488851745427</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>400.3098244139228</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>452.943473234797</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>362.1488851745427</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>218.8000030517578</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0674846665340597</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0232680790823229</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0914169657590902</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>204.0343578081587</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>223.8910588259786</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>238.8020354388292</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>204.0343578081587</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D10" s="20" t="n">
+        <v>20.97999954223633</v>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.0954999923706054</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>0.09315584596891301</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>18.97640974601746</v>
+      </c>
+      <c r="I10" s="20" t="n">
+        <v>20.97999954223633</v>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>22.93440914802076</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>18.97640974601746</v>
+      </c>
+      <c r="L10" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="19" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N10" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0082994402169681</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0485933057984229</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1486667759327886</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>402.1345769920194</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>425.2045855012605</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>465.7843776407458</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>385.225</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M11" s="13" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>BIMAS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>38.22000122070312</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0842967976871922</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.000408918900135</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.1015857338863732</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>34.99817751019727</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>38.23563010156546</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>42.10260809384634</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>34.99817751019727</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D13" s="14" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0371959299442395</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>0.1272217020935506</v>
+      </c>
+      <c r="H13" s="14" t="n">
+        <v>116.4030135388639</v>
+      </c>
+      <c r="I13" s="14" t="n">
+        <v>124.9038996016319</v>
+      </c>
+      <c r="J13" s="14" t="n">
+        <v>136.2811055031141</v>
+      </c>
+      <c r="K13" s="14" t="n">
+        <v>114.855001449585</v>
+      </c>
+      <c r="L13" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N13" s="13" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>413.25</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0156773693904196</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>-0.000942521339213</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.06844627048378669</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>406.7713270994091</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>412.8605030565702</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>441.5354212774249</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>392.5875</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D14" s="17" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.06865539483568921</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.0285467446983213</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.0289374356535263</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>89.17624594448276</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>93.01664919513574</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>98.52075946382514</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>89.17624594448276</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="M14" s="16" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>65.19999694824219</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.0621387669809665</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>0.0306241627672483</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.1086638342048738</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>61.14854953071563</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>67.19669226720924</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>72.28487860678426</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>61.14854953071563</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
-        <v>127.8000030517578</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.0446735791747727</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>0.0327412900152173</v>
-      </c>
-      <c r="G10" s="22" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>122.0907194968889</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>131.9843400156211</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>137.9672624367711</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>121.4100028991699</v>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="D16" s="14" t="n">
+        <v>34.77999877929688</v>
+      </c>
+      <c r="E16" s="15" t="n">
+        <v>-0.0702987015861401</v>
+      </c>
+      <c r="F16" s="15" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+      <c r="G16" s="15" t="n">
+        <v>0.0831932668372119</v>
+      </c>
+      <c r="H16" s="14" t="n">
+        <v>32.33501002394477</v>
+      </c>
+      <c r="I16" s="14" t="n">
+        <v>36.23302987695052</v>
+      </c>
+      <c r="J16" s="14" t="n">
+        <v>37.67346049834082</v>
+      </c>
+      <c r="K16" s="14" t="n">
+        <v>32.33501002394477</v>
+      </c>
+      <c r="L16" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="20" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="M16" s="13" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N16" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D17" s="14" t="n">
+        <v>84.30000305175781</v>
+      </c>
+      <c r="E17" s="15" t="n">
+        <v>-0.0181378772961786</v>
+      </c>
+      <c r="F17" s="15" t="n">
+        <v>0.061538473957351</v>
+      </c>
+      <c r="G17" s="15" t="n">
+        <v>0.1293435773389155</v>
+      </c>
+      <c r="H17" s="14" t="n">
+        <v>82.77097994033755</v>
+      </c>
+      <c r="I17" s="14" t="n">
+        <v>89.48769659416303</v>
+      </c>
+      <c r="J17" s="14" t="n">
+        <v>95.20366701615366</v>
+      </c>
+      <c r="K17" s="14" t="n">
+        <v>80.08500289916992</v>
+      </c>
+      <c r="L17" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N17" s="13" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O17" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>412.5</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.0289964214106895</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>0.0584414874691192</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.1756284689632632</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>400.5389761680906</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>436.6071135810117</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>484.9467434473461</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>390.8670301069489</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="20" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>90.30000305175781</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.0122824827871298</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0305622771399269</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0937142265175849</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>89.19089481859683</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>93.05977677076189</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>98.76239799228885</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>85.78500289916992</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="n">
+        <v>145.1999969482422</v>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0392156862745097</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0007077205736818</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>0.1293359288901121</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>139.5058794208602</v>
+      </c>
+      <c r="I18" s="23" t="n">
+        <v>145.0972359231034</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <v>163.9795734283845</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>137.9399971008301</v>
+      </c>
+      <c r="L18" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
+      <c r="M18" s="22" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N18" s="22" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+      <c r="O18" s="22" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>285.25</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.0557185041218549</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0102041004987833</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0891252177983346</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>269.3562966992409</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>282.3392803327221</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>310.6729683769749</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>269.3562966992409</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="D19" s="23" t="n">
+        <v>32.11999893188477</v>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>-0.0532446188809735</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.0190620607116771</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>0.0428598924856524</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>30.40978183029928</v>
+      </c>
+      <c r="I19" s="23" t="n">
+        <v>31.50772556218617</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <v>33.49665863274462</v>
+      </c>
+      <c r="K19" s="23" t="n">
+        <v>30.40978183029928</v>
+      </c>
+      <c r="L19" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="17" t="n">
-        <v>61.83</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="M19" s="22" t="n">
+        <v>51.86</v>
+      </c>
+      <c r="N19" s="22" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O19" s="22" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1719,7 +2138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1736,7 +2155,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1808,433 +2227,433 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>0.0043774020903055</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.0551865264188744</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.1088043175022459</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>0.2057032864944392</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>0.0200019040925806</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0379876477441236</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.08949152542372869</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.772165881818355</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.5754901960784313</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.09061475678536079</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0266079182148352</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>-0.003584755659184</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="19" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.05598458626625</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.09345325526161311</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.1712120671309878</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>0.1925965225083146</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E6" s="21" t="n">
+        <v>0.0955613556219225</v>
+      </c>
+      <c r="F6" s="21" t="n">
+        <v>0.044820698304274</v>
+      </c>
+      <c r="G6" s="21" t="n">
+        <v>0.0595959773052476</v>
+      </c>
+      <c r="H6" s="21" t="n">
+        <v>0.1643757802273222</v>
+      </c>
+      <c r="I6" s="19" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0188532240450182</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.0232680790823229</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="17" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="J6" s="21" t="n">
+        <v>0.0406349141733305</v>
+      </c>
+      <c r="K6" s="21" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0679401059595536</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.0665440612239525</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.2150456013908888</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.0056807080181966</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0191191082032721</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0485933057984229</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>-0.0108695180015409</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.1487750574201126</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-0.0885889870129208</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0.387106135015776</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.031520714084673</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.000408918900135</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0627906858458999</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>-0.1425531806675255</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>-0.0620008227748822</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>0.1044133754393505</v>
+      </c>
+      <c r="I9" s="13" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>0.0173661554830595</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0.1094062436839293</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.0826822974966194</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.2148702230576522</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0237745674910492</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0189600016509259</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>-0.000942521339213</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="20" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="E10" s="18" t="n">
+        <v>-0.0694849506302555</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.1458519063039557</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>-0.122364790658432</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>0.2636171930649325</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>0.0205145061613839</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>-0.0285467446983213</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0411765154670266</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.1641026032276642</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.0744198020732777</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.225460329022473</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.0223810594655514</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.0306241627672483</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
-        <v>-0.0244274576201694</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>-0.0884450368501941</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>0.0012388917695613</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>0.08155505377528489</v>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="E12" s="15" t="n">
+        <v>-0.0832894033155693</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>-0.1172589484177429</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.2518786862216586</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>0.07263925691405849</v>
+      </c>
+      <c r="I12" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>0.0267034739778493</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>0.0417777788571567</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E13" s="15" t="n">
+        <v>-0.0517435140063752</v>
+      </c>
+      <c r="F13" s="15" t="n">
+        <v>-0.1553106164932827</v>
+      </c>
+      <c r="G13" s="15" t="n">
+        <v>-0.0892681064853825</v>
+      </c>
+      <c r="H13" s="15" t="n">
+        <v>0.1017734892899173</v>
+      </c>
+      <c r="I13" s="13" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="22" t="n">
-        <v>0.016080675014834</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>0.0327412900152173</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="20" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="20" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="22" t="n">
-        <v>0.1402902557014513</v>
-      </c>
-      <c r="F7" s="22" t="n">
-        <v>0.8300799075861638</v>
-      </c>
-      <c r="G7" s="22" t="n">
-        <v>0.6296613607144284</v>
-      </c>
-      <c r="H7" s="22" t="n">
-        <v>0.0862299307679437</v>
-      </c>
-      <c r="I7" s="20" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="22" t="n">
-        <v>0.0262217816885468</v>
-      </c>
-      <c r="K7" s="22" t="n">
-        <v>0.0584414874691192</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>0.0100671309901307</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>-0.1041666635129818</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-0.0331851120432711</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>0.0745651900503541</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0161046396019991</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0305622771399269</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E9" s="24" t="n">
-        <v>0.0235419269200769</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.0506203710706606</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0.3655007563629175</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>0.0714109130424105</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0.0242913783321116</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0.008960632080292101</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E10" s="24" t="n">
-        <v>-0.0435238761645628</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>-0.1355450526232967</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.184257652425813</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>-0.0147699774830133</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="24" t="n">
-        <v>0.0139184324941441</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.0007363095911598</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>0.1837161005113008</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>0.1483544458316852</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>0.1261172290220056</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>0.1215979397589577</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="24" t="n">
-        <v>0.0394788088920892</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.002557432846991</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>0.0109011623071553</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>-0.097924715587348</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.0106257209845535</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.1784934526235051</v>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>0.0210905983796827</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>0.0111110916693351</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.06552006552006551</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.1263399693721286</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>-0.0239520958083832</v>
-      </c>
-      <c r="H13" s="19" t="n">
-        <v>-0.0477911128248186</v>
-      </c>
-      <c r="I13" s="17" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="19" t="n">
-        <v>0.0169602756515284</v>
-      </c>
-      <c r="K13" s="19" t="n">
-        <v>-0.0102041004987833</v>
+      <c r="J13" s="15" t="n">
+        <v>0.0180337362813238</v>
+      </c>
+      <c r="K13" s="15" t="n">
+        <v>0.061538473957351</v>
       </c>
     </row>
     <row r="14">
@@ -2243,7 +2662,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2257,70 +2676,70 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>0.058659217877095</v>
+        <v>-0.0745501285347043</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.1226851851851852</v>
+        <v>-0.08860759493670881</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.0214603528931218</v>
+        <v>0.1232449297971918</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.07671393723405789</v>
+        <v>-0.1014754690653146</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.0229670667349307</v>
+        <v>0.0303591105771636</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.0355139613832504</v>
+        <v>0.0245003718359859</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="25" t="n">
+      <c r="A15" s="22" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>0.0241545884817155</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.0770569701056099</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>0.0329741328636228</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>0.4172946821346979</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>0.029132286850575</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.0199776849855937</v>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.0396825404834755</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.1933333502875434</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.1791972755340619</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>0.0432479046991434</v>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="24" t="n">
+        <v>0.01768194495492</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>-0.0007077205736818</v>
       </c>
     </row>
     <row r="16">
@@ -2329,7 +2748,7 @@
       </c>
       <c r="B16" s="25" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C16" s="25" t="inlineStr">
@@ -2343,16 +2762,16 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.0112063083878781</v>
+        <v>0.0206185567010308</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.1847826086956522</v>
+        <v>-0.173120728929385</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.1539763258988119</v>
+        <v>-0.0450871551413537</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>0.0172821677934933</v>
+        <v>-0.062282119385654</v>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -2360,10 +2779,10 @@
         </is>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.0174587020368874</v>
+        <v>0.0234029498955229</v>
       </c>
       <c r="K16" s="26" t="n">
-        <v>0.0204081632653061</v>
+        <v>0.0445250258600058</v>
       </c>
     </row>
     <row r="17">
@@ -2372,7 +2791,7 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C17" s="25" t="inlineStr">
@@ -2386,27 +2805,27 @@
         </is>
       </c>
       <c r="E17" s="26" t="n">
-        <v>-0.0270967741935483</v>
+        <v>-0.0930232558139535</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>-0.0431472081218273</v>
+        <v>-0.1515151515151515</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>0.1698991466252908</v>
+        <v>-0.0586206896551724</v>
       </c>
       <c r="H17" s="26" t="n">
-        <v>-0.1090999412102676</v>
+        <v>-0.0162517774614465</v>
       </c>
       <c r="I17" s="25" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J17" s="26" t="n">
-        <v>0.0298323340087646</v>
+        <v>0.0176619745094825</v>
       </c>
       <c r="K17" s="26" t="n">
-        <v>0.0485099953300594</v>
+        <v>0.1028940851473592</v>
       </c>
     </row>
     <row r="18">
@@ -2415,84 +2834,84 @@
       </c>
       <c r="B18" s="25" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C18" s="25" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.07704569731734751</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.1616795390608436</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.231415942706893</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.0099801366801068</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.014927802410026</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.1658137063821738</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.0088495191118265</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.1412924544872787</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.260795744573102</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>-0.029237019864496</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E19" s="24" t="n">
+        <v>-0.0801832584158213</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.2146699820643947</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.0817610248078556</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>0.062087038248501</v>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0183196672164969</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.0013443469214756</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.0451488666391344</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.1371527416746547</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>-0.08639707042477909</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>0.2435990625973061</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0202848756435761</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.0835821125918427</v>
+      <c r="J19" s="24" t="n">
+        <v>0.0246165692883249</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>-0.0190620607116771</v>
       </c>
     </row>
     <row r="20">
@@ -2501,7 +2920,7 @@
       </c>
       <c r="B20" s="25" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C20" s="25" t="inlineStr">
@@ -2515,16 +2934,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.0208920920955418</v>
+        <v>-0.0550632718243176</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1437036961684992</v>
+        <v>-0.1663875043897771</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.0034482452447002</v>
+        <v>-0.293087096547894</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>0.0202434963345725</v>
+        <v>0.0036869731660258</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2532,10 +2951,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0229650470108602</v>
+        <v>0.0190864561409881</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.037452235290006</v>
+        <v>0.0283622708857007</v>
       </c>
     </row>
   </sheetData>
@@ -2560,7 +2979,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2568,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2593,7 +3012,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, TUPRS.IS, SAHOL.IS</t>
+          <t>KCHOL.IS, BIMAS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2605,7 +3024,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2617,7 +3036,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, THYAO.IS</t>
+          <t>TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2629,7 +3048,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, ARCLK.IS, PETKM.IS, AKBNK.IS, TOASO.IS, SISE.IS, PGSUS.IS, ASELS.IS, FROTO.IS, TCELL.IS, YKBNK.IS</t>
+          <t>ASELS.IS, TOASO.IS, THYAO.IS, ARCLK.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2641,7 +3060,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.06 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2653,7 +3072,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -2679,7 +3098,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2687,7 +3106,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2748,7 +3167,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2760,7 +3179,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2796,7 +3215,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2856,7 +3275,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2892,7 +3311,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2904,7 +3323,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2930,7 +3349,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2938,7 +3357,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2962,7 +3381,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13122.599609375</v>
+        <v>13509.7998046875</v>
       </c>
     </row>
     <row r="5">
@@ -2972,7 +3391,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13476.94251953125</v>
+        <v>13489.76401855469</v>
       </c>
     </row>
     <row r="6">
@@ -2983,7 +3402,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Risk OFF</t>
+          <t>Risk ON</t>
         </is>
       </c>
     </row>
@@ -2995,7 +3414,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>low_volatility</t>
+          <t>volume_heavy</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3425,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>61.83</v>
+        <v>51.86</v>
       </c>
     </row>
     <row r="9">
@@ -3017,7 +3436,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BIST100 MA200 altında olduğu için savunmacı rejim izleniyor.</t>
+          <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
         </is>
       </c>
     </row>
@@ -3043,13 +3462,13 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-15</t>
+          <t>Rapor Tarihi: 2026-09-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3063,7 +3482,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-17 06:51</t>
+          <t>Son Güncelleme: 2026-09-18 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3131,19 +3550,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="27" t="n">
-        <v>377</v>
+        <v>360</v>
       </c>
       <c r="E4" s="28" t="n">
-        <v>-0.05632040050062581</v>
+        <v>-0.09887359198998746</v>
       </c>
       <c r="F4" s="27" t="n">
-        <v>-39676.5812421327</v>
+        <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H4" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="5">
@@ -3161,169 +3580,169 @@
         <v>197</v>
       </c>
       <c r="D5" s="27" t="n">
-        <v>218.8000030517578</v>
+        <v>206.5</v>
       </c>
       <c r="E5" s="28" t="n">
-        <v>0.1106599139683138</v>
+        <v>0.0482233502538072</v>
       </c>
       <c r="F5" s="27" t="n">
-        <v>321615.8588624299</v>
+        <v>140153.6803430272</v>
       </c>
       <c r="G5" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H5" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-08-26</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C6" s="27" t="n">
-        <v>103.5</v>
+        <v>96.5</v>
       </c>
       <c r="D6" s="27" t="n">
-        <v>99.40000152587891</v>
+        <v>84.30000305175781</v>
       </c>
       <c r="E6" s="28" t="n">
-        <v>-0.03961351182725692</v>
+        <v>-0.1264248388418879</v>
       </c>
       <c r="F6" s="27" t="n">
-        <v>-121424.9684817605</v>
+        <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H6" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C7" s="27" t="n">
-        <v>96.5</v>
+        <v>133.3999938964844</v>
       </c>
       <c r="D7" s="27" t="n">
-        <v>90.30000305175781</v>
+        <v>120.9000015258789</v>
       </c>
       <c r="E7" s="28" t="n">
-        <v>-0.06424867303877912</v>
+        <v>-0.09370309552116773</v>
       </c>
       <c r="F7" s="27" t="n">
-        <v>-5641.963782278472</v>
+        <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H7" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-11</t>
         </is>
       </c>
       <c r="C8" s="27" t="n">
-        <v>133.3999938964844</v>
+        <v>299.75</v>
       </c>
       <c r="D8" s="27" t="n">
-        <v>127.8000030517578</v>
+        <v>272.25</v>
       </c>
       <c r="E8" s="28" t="n">
-        <v>-0.04197894378520017</v>
+        <v>-0.09174311926605505</v>
       </c>
       <c r="F8" s="27" t="n">
-        <v>-203291.4932397706</v>
+        <v>-20640.73562494843</v>
       </c>
       <c r="G8" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H8" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
+          <t>2026-09-14</t>
         </is>
       </c>
       <c r="C9" s="27" t="n">
-        <v>299.75</v>
+        <v>38.86000061035156</v>
       </c>
       <c r="D9" s="27" t="n">
-        <v>284.25</v>
+        <v>34.77999877929688</v>
       </c>
       <c r="E9" s="28" t="n">
-        <v>-0.05170975813177647</v>
+        <v>-0.1049923254496258</v>
       </c>
       <c r="F9" s="27" t="n">
-        <v>-11633.86917042549</v>
+        <v>-22854.86544006292</v>
       </c>
       <c r="G9" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H9" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C10" s="27" t="n">
-        <v>38.86000061035156</v>
+        <v>405.5</v>
       </c>
       <c r="D10" s="27" t="n">
-        <v>38.2599983215332</v>
+        <v>405.5</v>
       </c>
       <c r="E10" s="28" t="n">
-        <v>-0.01544009983001726</v>
+        <v>0</v>
       </c>
       <c r="F10" s="27" t="n">
-        <v>-3361.020936387358</v>
+        <v>0</v>
       </c>
       <c r="G10" s="27" t="n">
-        <v>11985832.91755696</v>
+        <v>11381849.64962737</v>
       </c>
       <c r="H10" s="28" t="n">
-        <v>0.0137404994663967</v>
+        <v>-0.0424255976813339</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$25</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -164,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +180,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -191,13 +191,16 @@
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -577,13 +580,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="21" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
@@ -630,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -647,7 +650,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Piyasa Rejimi: Risk ON</t>
+          <t>Piyasa Rejimi: Risk OFF</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -664,7 +667,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>Aktif Model: volume_heavy</t>
+          <t>Aktif Model: low_volatility</t>
         </is>
       </c>
       <c r="B5" s="2" t="n"/>
@@ -681,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 51.86/100</t>
+          <t>Güven Puanı: 64.21/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -741,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, BIMAS.IS, GARAN.IS, SAHOL.IS, EREGL.IS</t>
+          <t>AL: KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -758,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>AZALT: BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -775,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>ÇIK: THYAO.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -792,7 +795,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %50</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -890,7 +893,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 5</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -947,7 +950,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 5</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -961,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.12307111833361</v>
+        <v>0.2118012179582496</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>12307.111833361</v>
+        <v>21180.12179582496</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>467.5182290732529</v>
+        <v>492.8207489184861</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>214.3444492591615</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>196.175</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.759752954882472</v>
+        <v>0.3518217892616204</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -990,12 +993,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %50</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1004,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1083549289094442</v>
+        <v>0.2046838490225011</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>10835.49289094442</v>
+        <v>20468.38490225011</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>526.5324195262998</v>
+        <v>677.8604291940321</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>425.2045855012605</v>
+        <v>124.9038996016319</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>385.225</v>
+        <v>114.855001449585</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.9718661159684575</v>
+        <v>0.662348722120733</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1036,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1045,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.09211535586320244</v>
+        <v>0.1835149330192493</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>9211.535586320244</v>
+        <v>18351.49330192493</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>305.0624412184431</v>
+        <v>544.659007315847</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>124.9038996016319</v>
+        <v>89.42764341974173</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>114.855001449585</v>
+        <v>82.50749855041504</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.662348722120733</v>
+        <v>0.5935854901341648</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1072,124 +1075,42 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="6" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="6" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C23" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D23" s="7" t="n">
-        <v>0.08923779370436544</v>
-      </c>
-      <c r="E23" s="8" t="n">
-        <v>8923.779370436543</v>
-      </c>
-      <c r="F23" s="7" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G23" s="8" t="n">
-        <v>549.1557643887553</v>
-      </c>
-      <c r="H23" s="8" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="I23" s="8" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="J23" s="6" t="n">
-        <v>1.230769479147021</v>
-      </c>
-      <c r="K23" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="B24" s="6" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C24" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="n">
-        <v>0.08722080318937789</v>
-      </c>
-      <c r="E24" s="8" t="n">
-        <v>8722.080318937789</v>
-      </c>
-      <c r="F24" s="7" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G24" s="8" t="n">
-        <v>364.3891427389418</v>
-      </c>
-      <c r="H24" s="8" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="I24" s="8" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="J24" s="6" t="n">
-        <v>0.5942894806665029</v>
-      </c>
-      <c r="K24" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="10" t="n">
-        <v>6</v>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C25" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D25" s="11" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="E25" s="12" t="n">
-        <v>50000</v>
-      </c>
-      <c r="F25" s="11" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G25" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H25" s="12" t="inlineStr"/>
-      <c r="I25" s="12" t="inlineStr"/>
-      <c r="J25" s="10" t="inlineStr"/>
-      <c r="K25" s="10" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K25"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1200,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O19"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1244,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1286,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 12</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1429,37 +1350,37 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>206.5</v>
+        <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.039087920591243</v>
+        <v>-0.0339316179450966</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.1206226545342643</v>
+        <v>0.0770489383118369</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>198.4283443979083</v>
+        <v>391.7407289232634</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>214.3444492591615</v>
+        <v>413.2162352085374</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>231.4085781613256</v>
+        <v>436.7433444854499</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>196.175</v>
+        <v>385.225</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1467,7 +1388,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1486,45 +1407,45 @@
       </c>
       <c r="B9" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>401.75</v>
+        <v>206.5</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.0985715365910573</v>
+        <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>-0.003584755659184</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>0.1274261934904716</v>
+        <v>0.0690438632887718</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>400.3098244139228</v>
+        <v>211.3048583304997</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>452.943473234797</v>
+        <v>220.7575577691314</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>362.1488851745427</v>
+        <v>192.8429199749572</v>
       </c>
       <c r="L9" s="16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M9" s="16" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
@@ -1533,64 +1454,64 @@
       </c>
       <c r="O9" s="16" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="19" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.0954999923706054</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>0.09315584596891301</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="I10" s="20" t="n">
-        <v>20.97999954223633</v>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>22.93440914802076</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>18.97640974601746</v>
-      </c>
-      <c r="L10" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N10" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="19" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>120.9000015258789</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0446735791747727</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>115.4989657354824</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>124.9038996016319</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>135.8966593492442</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>114.855001449585</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1600,515 +1521,230 @@
       </c>
       <c r="B11" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>401.75</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0855565177750571</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1267042006856777</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>408.636624115174</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>452.653412625471</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>367.3776689838708</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0082994402169681</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1486667759327886</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>402.1345769920194</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>425.2045855012605</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>465.7843776407458</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>385.225</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
+      <c r="D12" s="17" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0450302501162372</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0884521142598899</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>82.93912132023661</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>89.42764341974173</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>94.53206446262533</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>82.50749855041504</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M11" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>38.22000122070312</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0842967976871922</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1015857338863732</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>38.23563010156546</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>42.10260809384634</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.99817751019727</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0762004294665497</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.0475785896346643</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>261.0262798277541</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>285.9889549702634</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>252.1972827556319</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>120.9000015258789</v>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0371959299442395</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>0.1272217020935506</v>
-      </c>
-      <c r="H13" s="14" t="n">
-        <v>116.4030135388639</v>
-      </c>
-      <c r="I13" s="14" t="n">
-        <v>124.9038996016319</v>
-      </c>
-      <c r="J13" s="14" t="n">
-        <v>136.2811055031141</v>
-      </c>
-      <c r="K13" s="14" t="n">
-        <v>114.855001449585</v>
-      </c>
-      <c r="L13" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N13" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="M13" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
+      <c r="A14" s="19" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="17" t="n">
-        <v>95.75</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.06865539483568921</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0289374356535263</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>93.01664919513574</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>98.52075946382514</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>89.17624594448276</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
+      <c r="D14" s="20" t="n">
+        <v>272.25</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.082926169656068</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.1059737014525552</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>272.1274167124678</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>301.1013402204582</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>249.6733503111355</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="16" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>65.19999694824219</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.0621387669809665</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.1086638342048738</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>67.19669226720924</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>72.28487860678426</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>61.14854953071563</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B16" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D16" s="14" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E16" s="15" t="n">
-        <v>-0.0702987015861401</v>
-      </c>
-      <c r="F16" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-      <c r="G16" s="15" t="n">
-        <v>0.0831932668372119</v>
-      </c>
-      <c r="H16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="I16" s="14" t="n">
-        <v>36.23302987695052</v>
-      </c>
-      <c r="J16" s="14" t="n">
-        <v>37.67346049834082</v>
-      </c>
-      <c r="K16" s="14" t="n">
-        <v>32.33501002394477</v>
-      </c>
-      <c r="L16" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M16" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N16" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B17" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D17" s="14" t="n">
-        <v>84.30000305175781</v>
-      </c>
-      <c r="E17" s="15" t="n">
-        <v>-0.0181378772961786</v>
-      </c>
-      <c r="F17" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-      <c r="G17" s="15" t="n">
-        <v>0.1293435773389155</v>
-      </c>
-      <c r="H17" s="14" t="n">
-        <v>82.77097994033755</v>
-      </c>
-      <c r="I17" s="14" t="n">
-        <v>89.48769659416303</v>
-      </c>
-      <c r="J17" s="14" t="n">
-        <v>95.20366701615366</v>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>80.08500289916992</v>
-      </c>
-      <c r="L17" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M17" s="13" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N17" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O17" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n">
-        <v>145.1999969482422</v>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0392156862745097</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>0.1293359288901121</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>139.5058794208602</v>
-      </c>
-      <c r="I18" s="23" t="n">
-        <v>145.0972359231034</v>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>163.9795734283845</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>137.9399971008301</v>
-      </c>
-      <c r="L18" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M18" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N18" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O18" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="n">
-        <v>32.11999893188477</v>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0532446188809735</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>0.0428598924856524</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="I19" s="23" t="n">
-        <v>31.50772556218617</v>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>33.49665863274462</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>30.40978183029928</v>
-      </c>
-      <c r="L19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M19" s="22" t="n">
-        <v>51.86</v>
-      </c>
-      <c r="N19" s="22" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O19" s="22" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M14" s="19" t="n">
+        <v>64.20999999999999</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O19"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2155,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2232,7 +1868,7 @@
       </c>
       <c r="B4" s="13" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="13" t="inlineStr">
@@ -2242,20 +1878,20 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0043774020903055</v>
+        <v>0.0072916582962114</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0551865264188744</v>
+        <v>0.0413608561912206</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1088043175022459</v>
+        <v>0.1851961795211201</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>0.2057032864944392</v>
+        <v>-0.0623598620860903</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -2263,10 +1899,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0200019040925806</v>
+        <v>0.0188637341167536</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0379876477441236</v>
+        <v>0.0190289400950367</v>
       </c>
     </row>
     <row r="5">
@@ -2275,84 +1911,84 @@
       </c>
       <c r="B5" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.0067339775737629</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.034051092416993</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.0985692087568079</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.2031171068964992</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0194217173689601</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>0.08949152542372869</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.772165881818355</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.5754901960784313</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.09061475678536079</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0266079182148352</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>-0.003584755659184</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="21" t="n">
-        <v>0.0955613556219225</v>
-      </c>
-      <c r="F6" s="21" t="n">
-        <v>0.044820698304274</v>
-      </c>
-      <c r="G6" s="21" t="n">
-        <v>0.0595959773052476</v>
-      </c>
-      <c r="H6" s="21" t="n">
-        <v>0.1643757802273222</v>
-      </c>
-      <c r="I6" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="21" t="n">
-        <v>0.0406349141733305</v>
-      </c>
-      <c r="K6" s="21" t="n">
-        <v>0</v>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>-0.064965207483533</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>-0.1604166560702853</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0918000573807312</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.1338440657530808</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.0168100770079203</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
@@ -2361,600 +1997,600 @@
       </c>
       <c r="B7" s="13" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D7" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.07419786096256679</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.7927264125750395</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.5974155069582505</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.0866514907563507</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0264956263736686</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0171415659369608</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0679401059595536</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.0665440612239525</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.2150456013908888</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0056807080181966</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>-0.0666308906426155</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>-0.16329483698748</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.2434669323574443</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.0447946090151196</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0144115919578272</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.0296792745067082</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0522764930412542</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.1775609458365091</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.1068369587850867</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.0974086401731955</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.0172418278494896</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0125688346543615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.0915141430948419</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.1689497716894977</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>-0.0737913486005089</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>-0.0009174564930963</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>0.0173415165449425</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>-0.0438597808507175</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0274615272586047</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.2138603175563069</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1928849256560219</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.0526434538225228</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.0170949295625193</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.006131117760765</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>0.0585267338684687</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>0.0274240677693482</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.031465063168498</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0.1705560918196227</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0191191082032721</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0485933057984229</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0355156641914875</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.002557432846991</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>-0.0774536319509322</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.130500030517578</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>0.228324143503479</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.0673904056469028</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0257858693771773</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.019070255160478</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0.0254237288135592</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1799698795180723</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.0768923210325955</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0341755137155445</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0228770438599459</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.000450260009301</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.0538656516832387</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1872618098419274</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.3081556953641494</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>0.0216399265741287</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0175418542292546</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>0.0006695213718759</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="27" t="n">
+        <v>-0.0748792270531401</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>-0.1745689655172413</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>-0.1358303487115206</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.2731285195859629</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0.0197620982238175</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0556585878468132</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0557377049180327</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.1235544735240413</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0549450549450549</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.1018704487088503</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0299429051249194</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0485096508933775</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>-0.0362158835532249</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.1960542765109</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.1122733625312385</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>0.2410422103922216</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0.0213786434561666</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>0.05159344410234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
         <is>
           <t>SISE.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C19" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.0108695180015409</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1487750574201126</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0885889870129208</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.387106135015776</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="D19" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="27" t="n">
+        <v>0.0026233549743024</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>-0.1936708862796933</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>-0.1256381990168611</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0.3991606220660881</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.031520714084673</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.000408918900135</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>0.026262986561954</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>0.06799392425498541</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0627906858458999</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>-0.1425531806675255</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>-0.0620008227748822</v>
-      </c>
-      <c r="H9" s="15" t="n">
-        <v>0.1044133754393505</v>
-      </c>
-      <c r="I9" s="13" t="inlineStr">
+      <c r="D20" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="27" t="n">
+        <v>-0.07860016151729959</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.2477752140987634</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>-0.1072818415636823</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0.0655210596212267</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="15" t="n">
-        <v>0.0173661554830595</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0694849506302555</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.1458519063039557</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>-0.122364790658432</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>0.2636171930649325</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0205145061613839</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>-0.0285467446983213</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0411765154670266</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.1641026032276642</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.0744198020732777</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.225460329022473</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0223810594655514</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0306241627672483</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0832894033155693</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>-0.1172589484177429</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.2518786862216586</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>0.07263925691405849</v>
-      </c>
-      <c r="I12" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>0.0267034739778493</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>0.0417777788571567</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E13" s="15" t="n">
-        <v>-0.0517435140063752</v>
-      </c>
-      <c r="F13" s="15" t="n">
-        <v>-0.1553106164932827</v>
-      </c>
-      <c r="G13" s="15" t="n">
-        <v>-0.0892681064853825</v>
-      </c>
-      <c r="H13" s="15" t="n">
-        <v>0.1017734892899173</v>
-      </c>
-      <c r="I13" s="13" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="15" t="n">
-        <v>0.0180337362813238</v>
-      </c>
-      <c r="K13" s="15" t="n">
-        <v>0.061538473957351</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.0745501285347043</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.08860759493670881</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>0.1232449297971918</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>-0.1014754690653146</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0303591105771636</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0245003718359859</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0396825404834755</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1933333502875434</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.1791972755340619</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>0.0432479046991434</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.01768194495492</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.0007077205736818</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>0.0206185567010308</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.173120728929385</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.0450871551413537</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.062282119385654</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0234029498955229</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.0445250258600058</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0930232558139535</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.1515151515151515</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0586206896551724</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.0162517774614465</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0176619745094825</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.1028940851473592</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.07704569731734751</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.1616795390608436</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.231415942706893</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.0099801366801068</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.014927802410026</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.1658137063821738</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0801832584158213</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.2146699820643947</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.0817610248078556</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>0.062087038248501</v>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0246165692883249</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>-0.0190620607116771</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.0550632718243176</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1663875043897771</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.293087096547894</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.0036869731660258</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0190864561409881</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0283622708857007</v>
+      <c r="J20" s="27" t="n">
+        <v>0.0235895708006696</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.0248447886632294</v>
       </c>
     </row>
   </sheetData>
@@ -2987,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3012,7 +2648,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, BIMAS.IS, GARAN.IS, EREGL.IS, SAHOL.IS</t>
+          <t>KCHOL.IS, GARAN.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -3024,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS, SISE.IS, AKBNK.IS</t>
+          <t>BIMAS.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -3036,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, TCELL.IS, PGSUS.IS, YKBNK.IS</t>
+          <t>THYAO.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -3048,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS, TOASO.IS, THYAO.IS, ARCLK.IS, FROTO.IS</t>
+          <t>SAHOL.IS, PGSUS.IS, PETKM.IS, EREGL.IS, FROTO.IS, TCELL.IS, ASELS.IS, AKBNK.IS, SISE.IS, YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -3060,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.19 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -3072,7 +2708,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -3106,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3143,7 +2779,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3167,7 +2803,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3179,7 +2815,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3251,7 +2887,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3275,7 +2911,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3323,7 +2959,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -3357,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3381,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13509.7998046875</v>
+        <v>13284.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3391,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13489.76401855469</v>
+        <v>13501.69251953125</v>
       </c>
     </row>
     <row r="6">
@@ -3402,7 +3038,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Risk ON</t>
+          <t>Risk OFF</t>
         </is>
       </c>
     </row>
@@ -3414,7 +3050,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>volume_heavy</t>
+          <t>low_volatility</t>
         </is>
       </c>
     </row>
@@ -3425,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>51.86</v>
+        <v>64.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3436,7 +3072,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>BIST100 MA200 üzerinde olduğu için risk alma rejimi aktif.</t>
+          <t>BIST100 MA200 altında olduğu için savunmacı rejim izleniyor.</t>
         </is>
       </c>
     </row>
@@ -3460,7 +3096,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="24" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3482,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-18 06:46</t>
+          <t>Son Güncelleme: 2026-09-19 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3546,22 +3182,22 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="27" t="n">
+      <c r="D4" s="28" t="n">
         <v>360</v>
       </c>
-      <c r="E4" s="28" t="n">
+      <c r="E4" s="29" t="n">
         <v>-0.09887359198998746</v>
       </c>
-      <c r="F4" s="27" t="n">
+      <c r="F4" s="28" t="n">
         <v>-69654.44262507732</v>
       </c>
-      <c r="G4" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H4" s="28" t="n">
+      <c r="G4" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3576,22 +3212,22 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="27" t="n">
+      <c r="D5" s="28" t="n">
         <v>206.5</v>
       </c>
-      <c r="E5" s="28" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.0482233502538072</v>
       </c>
-      <c r="F5" s="27" t="n">
+      <c r="F5" s="28" t="n">
         <v>140153.6803430272</v>
       </c>
-      <c r="G5" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H5" s="28" t="n">
+      <c r="G5" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3606,22 +3242,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="27" t="n">
+      <c r="D6" s="28" t="n">
         <v>84.30000305175781</v>
       </c>
-      <c r="E6" s="28" t="n">
+      <c r="E6" s="29" t="n">
         <v>-0.1264248388418879</v>
       </c>
-      <c r="F6" s="27" t="n">
+      <c r="F6" s="28" t="n">
         <v>-11101.93142037037</v>
       </c>
-      <c r="G6" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H6" s="28" t="n">
+      <c r="G6" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
@@ -3636,89 +3272,89 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="27" t="n">
+      <c r="D7" s="28" t="n">
         <v>120.9000015258789</v>
       </c>
-      <c r="E7" s="28" t="n">
+      <c r="E7" s="29" t="n">
         <v>-0.09370309552116773</v>
       </c>
-      <c r="F7" s="27" t="n">
+      <c r="F7" s="28" t="n">
         <v>-453776.1194554595</v>
       </c>
-      <c r="G7" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H7" s="28" t="n">
+      <c r="G7" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-11</t>
-        </is>
-      </c>
-      <c r="C8" s="27" t="n">
-        <v>299.75</v>
-      </c>
-      <c r="D8" s="27" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-0.09174311926605505</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>-20640.73562494843</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H8" s="28" t="n">
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="C8" s="28" t="n">
+        <v>38.86000061035156</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <v>34.77999877929688</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.1049923254496258</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-22854.86544006292</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="D9" s="27" t="n">
-        <v>34.77999877929688</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>-0.1049923254496258</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>-22854.86544006292</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H9" s="28" t="n">
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -3726,22 +3362,22 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D10" s="27" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="E10" s="28" t="n">
+      <c r="C10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="D10" s="28" t="n">
+        <v>86.84999847412109</v>
+      </c>
+      <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>11381849.64962737</v>
-      </c>
-      <c r="H10" s="28" t="n">
+      <c r="F10" s="28" t="n">
+        <v>-4.656612873077393e-10</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>14217567.95672282</v>
+      </c>
+      <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>
       </c>
     </row>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -964,16 +964,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2118012179582496</v>
+        <v>0.2118012179582497</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21180.12179582496</v>
+        <v>21180.12179582497</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>492.8207489184861</v>
+        <v>492.8207489184928</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>211.3048583304997</v>
@@ -982,7 +982,7 @@
         <v>192.8429199749572</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3518217892616204</v>
+        <v>0.3518217892616246</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1007,16 +1007,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2046838490225011</v>
+        <v>0.204683849022501</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20468.38490225011</v>
+        <v>20468.3849022501</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>677.8604291940321</v>
+        <v>677.860429194032</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>124.9038996016319</v>
@@ -1057,7 +1057,7 @@
         <v>0.0296792745067082</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>544.659007315847</v>
+        <v>544.6590073158468</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>89.42764341974173</v>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1362,7 +1362,7 @@
         <v>405.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316179450966</v>
+        <v>-0.0339316179450965</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1422,7 +1422,7 @@
         <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="18" t="n">
         <v>0.0690438632887718</v>
@@ -1539,7 +1539,7 @@
         <v>0.0171415659369608</v>
       </c>
       <c r="G11" s="15" t="n">
-        <v>0.1267042006856777</v>
+        <v>0.1267042006856775</v>
       </c>
       <c r="H11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1548,7 +1548,7 @@
         <v>408.636624115174</v>
       </c>
       <c r="J11" s="14" t="n">
-        <v>452.653412625471</v>
+        <v>452.6534126254709</v>
       </c>
       <c r="K11" s="14" t="n">
         <v>367.3776689838708</v>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0072916582962114</v>
+        <v>0.0072916582962112</v>
       </c>
       <c r="F4" s="15" t="n">
         <v>0.0413608561912206</v>
@@ -1925,7 +1925,7 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-0.0067339775737629</v>
+        <v>-0.006733977573763</v>
       </c>
       <c r="F5" s="18" t="n">
         <v>0.034051092416993</v>
@@ -1945,7 +1945,7 @@
         <v>0.0194217173689601</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -2014,7 +2014,7 @@
         <v>0.07419786096256679</v>
       </c>
       <c r="F7" s="15" t="n">
-        <v>0.7927264125750395</v>
+        <v>0.7927264125750397</v>
       </c>
       <c r="G7" s="15" t="n">
         <v>0.5974155069582505</v>
@@ -2054,13 +2054,13 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.0666308906426155</v>
+        <v>-0.0666308906426154</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>-0.16329483698748</v>
+        <v>-0.1632948369874799</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0.2434669323574443</v>
+        <v>-0.2434669323574442</v>
       </c>
       <c r="H8" s="18" t="n">
         <v>0.0447946090151196</v>
@@ -2071,7 +2071,7 @@
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0144115919578272</v>
+        <v>0.0144115919578273</v>
       </c>
       <c r="K8" s="18" t="n">
         <v>0.0296792745067082</v>
@@ -2114,7 +2114,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0172418278494896</v>
+        <v>0.0172418278494895</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.0125688346543615</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0173415165449425</v>
+        <v>0.0173415165449426</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>-0.0438597808507175</v>
@@ -2243,7 +2243,7 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0355156641914875</v>
+        <v>0.0355156641914876</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>0.002557432846991</v>
@@ -2286,7 +2286,7 @@
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0257858693771773</v>
+        <v>0.0257858693771772</v>
       </c>
       <c r="K13" s="23" t="n">
         <v>0.019070255160478</v>
@@ -2318,7 +2318,7 @@
         <v>-0.1799698795180723</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.0768923210325955</v>
+        <v>-0.0768923210325954</v>
       </c>
       <c r="H14" s="25" t="n">
         <v>-0.0341755137155445</v>
@@ -2329,7 +2329,7 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0228770438599459</v>
+        <v>0.022877043859946</v>
       </c>
       <c r="K14" s="25" t="n">
         <v>-0.000450260009301</v>
@@ -2404,7 +2404,7 @@
         <v>-0.1745689655172413</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>-0.1358303487115206</v>
+        <v>-0.1358303487115205</v>
       </c>
       <c r="H16" s="27" t="n">
         <v>0.2731285195859629</v>
@@ -2501,7 +2501,7 @@
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0213786434561666</v>
+        <v>0.0213786434561665</v>
       </c>
       <c r="K18" s="27" t="n">
         <v>0.05159344410234</v>
@@ -2533,7 +2533,7 @@
         <v>-0.1936708862796933</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>-0.1256381990168611</v>
+        <v>-0.1256381990168612</v>
       </c>
       <c r="H19" s="27" t="n">
         <v>0.3991606220660881</v>
@@ -2587,7 +2587,7 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0235895708006696</v>
+        <v>0.0235895708006695</v>
       </c>
       <c r="K20" s="27" t="n">
         <v>0.0248447886632294</v>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-19 06:46</t>
+          <t>Son Güncelleme: 2026-09-20 07:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>14217567.95672282</v>
+        <v>17257629.54650526</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1791,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2623,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2742,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2993,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3097,7 +3097,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="24" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3118,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-20 07:10</t>
+          <t>Son Güncelleme: 2026-09-21 07:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3195,7 +3195,7 @@
         <v>-69654.44262507732</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H4" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3225,7 +3225,7 @@
         <v>140153.6803430272</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H5" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3255,7 +3255,7 @@
         <v>-11101.93142037037</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H6" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3285,7 +3285,7 @@
         <v>-453776.1194554595</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H7" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3315,7 +3315,7 @@
         <v>-22854.86544006292</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H8" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3345,7 +3345,7 @@
         <v>0</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H9" s="29" t="n">
         <v>-0.0424255976813339</v>
@@ -3375,7 +3375,7 @@
         <v>-4.656612873077393e-10</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>17257629.54650526</v>
+        <v>20297691.1362877</v>
       </c>
       <c r="H10" s="29" t="n">
         <v>-0.0424255976813339</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -164,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +180,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,7 +587,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -616,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 64.21/100</t>
+          <t>Güven Puanı: 54.79/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, GARAN.IS, ARCLK.IS</t>
+          <t>AL: BIMAS.IS, TUPRS.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS, TUPRS.IS</t>
+          <t>AZALT: KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, PGSUS.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -964,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2118012179582497</v>
+        <v>0.227086665563358</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21180.12179582497</v>
+        <v>22708.6665563358</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232680790823232</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>492.8207489184928</v>
+        <v>887.39800432953</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>211.3048583304997</v>
+        <v>436.1527822326448</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>192.8429199749572</v>
+        <v>398.7625</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3518217892616246</v>
+        <v>0.7815500766001103</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.204683849022501</v>
+        <v>0.194108935052226</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20468.3849022501</v>
+        <v>19410.8935052226</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.042473454091193</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>677.860429194032</v>
+        <v>824.4476941631086</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>124.9038996016319</v>
+        <v>434.9720487195503</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>114.855001449585</v>
+        <v>395.4357446682952</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.662348722120733</v>
+        <v>0.8124067702550941</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1835149330192493</v>
+        <v>0.1788043993844159</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18351.49330192493</v>
+        <v>17880.4399384416</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0296792745067082</v>
+        <v>0.0748220103803021</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>544.6590073158468</v>
+        <v>1337.850462678445</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>89.42764341974173</v>
+        <v>305.786861953196</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>82.50749855041504</v>
+        <v>270.275</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.5935854901341648</v>
+        <v>1.496440207606041</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>39999.99999999999</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1355,32 +1355,32 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>405.5</v>
+        <v>419.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316179450965</v>
+        <v>-0.0205578496996079</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0770489383118369</v>
+        <v>0.0814230457829332</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>391.7407289232634</v>
+        <v>411.1208425885895</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>413.2162352085374</v>
+        <v>436.1527822326448</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>436.7433444854499</v>
+        <v>453.9273234673862</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>385.225</v>
+        <v>398.7625</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1388,7 +1388,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>64.20999999999999</v>
+        <v>54.79</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1412,226 +1412,226 @@
       </c>
       <c r="C9" s="16" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>214.6999969482422</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0120989868586411</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.0729761101061803</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>212.1023445066151</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>219.6956534562084</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>230.3679675653337</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>203.9649971008301</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>206.5</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.06613598075081251</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.0232680790823232</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0690438632887718</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>192.8429199749572</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>211.3048583304997</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>220.7575577691314</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>192.8429199749572</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="D10" s="14" t="n">
+        <v>417.25</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0261975976177936</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.042473454091193</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.127426389921516</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>406.3190523939756</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>434.9720487195503</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>470.4186611947525</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>395.4357446682952</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="M10" s="13" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>129.8999938964844</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0076394197603308</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.0795559387098858</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>128.9076333162447</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>134.2019486445257</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>140.2343098493276</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>123.4049942016601</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>120.9000015258789</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0446735791747727</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1240418332017574</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>115.4989657354824</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>124.9038996016319</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>135.8966593492442</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>114.855001449585</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="D12" s="14" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.003760332626605</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.0748220103803021</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.1307691594971161</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>283.4301853677309</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>305.786861953196</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>321.7038258769296</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>270.275</v>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>401.75</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0855565177750571</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0171415659369608</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1267042006856775</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>367.3776689838708</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>408.636624115174</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>452.6534126254709</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>367.3776689838708</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>86.84999847412109</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0450302501162372</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0.0296792745067082</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.0884521142598899</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>82.93912132023661</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>89.42764341974173</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>94.53206446262533</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>82.50749855041504</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="M12" s="13" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -1644,28 +1644,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>273</v>
+        <v>285.5</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0762004294665497</v>
+        <v>-0.0573248422045384</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0438597808507175</v>
+        <v>-0.0407844352132465</v>
       </c>
       <c r="G13" s="21" t="n">
         <v>0.0475785896346643</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>252.1972827556319</v>
+        <v>269.1337575506043</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>261.0262798277541</v>
+        <v>273.8560437466181</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>285.9889549702634</v>
+        <v>299.0836873406967</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>252.1972827556319</v>
+        <v>269.1337575506043</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>64.20999999999999</v>
+        <v>54.79</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
@@ -1688,63 +1688,177 @@
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>147.6000061035156</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.0461145394060134</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0171127424349814</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.0615545291580976</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>140.7934998057272</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>145.0741652156645</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>156.6854549829499</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>140.2200057983398</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>87.15000152587891</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.0437032076168698</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>-0.0116184883401088</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.0849377720435755</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>83.3412669153829</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>86.13745024931002</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>94.55232848908128</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>82.79250144958496</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>272.25</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.082926169656068</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.000450260009301</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.1059737014525552</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>249.6733503111355</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>272.1274167124678</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>301.1013402204582</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>249.6733503111355</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="D16" s="20" t="n">
+        <v>21.44000053405762</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>-0.0753137768113169</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>-0.0271741120711617</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.052217597125587</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>19.82527311900109</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>20.85738755673937</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>22.55954584431741</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>19.82527311900109</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="19" t="n">
-        <v>64.20999999999999</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M16" s="19" t="n">
+        <v>54.79</v>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1774,7 +1888,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1878,20 +1992,20 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0072916582962112</v>
+        <v>0.0274679337585526</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0413608561912206</v>
+        <v>0.1142198729415047</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1851961795211201</v>
+        <v>0.2494150506792569</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0623598620860903</v>
+        <v>-0.058321730831083</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1899,10 +2013,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0188637341167536</v>
+        <v>0.0189448735168681</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0390775038300055</v>
       </c>
     </row>
     <row r="5">
@@ -1916,208 +2030,208 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.0151376286777881</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.0887423948824559</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.1451289950600338</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.2221047096245418</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0206781965315894</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>-0.006733977573763</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.034051092416993</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.0985692087568079</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.2031171068964992</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="E6" s="15" t="n">
+        <v>0.0556609740670461</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.8905754679183437</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.6475814412635736</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.0512215026195899</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0194217173689601</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.0232680790823232</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="J6" s="15" t="n">
+        <v>0.0261405096844875</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.042473454091193</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>0.0046403003137316</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.0960334261992246</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.0003654517218298</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>0.1823333958386286</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0210305047791659</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>-0.064965207483533</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>-0.1604166560702853</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-0.0918000573807312</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>0.1338440657530808</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="E8" s="15" t="n">
+        <v>0.0498154981549816</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>-0.1424265259984928</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>-0.0198105081826012</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>-0.018789406786501</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>0.0238878268157538</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>0.0748220103803021</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>-0.0522821576763485</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>-0.1208622016936105</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>-0.0138169257340241</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>0.0253496094892917</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.0168100770079203</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.07419786096256679</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.7927264125750397</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.5974155069582505</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.0866514907563507</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0264956263736686</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0171415659369608</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>-0.0666308906426154</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>-0.1632948369874799</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>-0.2434669323574442</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>0.0447946090151196</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0144115919578273</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>0.0296792745067082</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0522764930412542</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.1775609458365091</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-0.1068369587850867</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>0.0974086401731955</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0172418278494895</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0125688346543615</v>
+      <c r="J9" s="21" t="n">
+        <v>0.0190754319523366</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>-0.0407844352132465</v>
       </c>
     </row>
     <row r="10">
@@ -2126,7 +2240,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -2140,16 +2254,16 @@
         </is>
       </c>
       <c r="E10" s="21" t="n">
-        <v>-0.0915141430948419</v>
+        <v>-0.0133689834117793</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>-0.1689497716894977</v>
+        <v>-0.1912328432684075</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.0737913486005089</v>
+        <v>-0.1684506698393486</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>-0.0009174564930963</v>
+        <v>0.0832408574095935</v>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
@@ -2157,53 +2271,53 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0173415165449426</v>
+        <v>0.0178397660475483</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>-0.0438597808507175</v>
+        <v>-0.0171127424349814</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0274615272586047</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.2138603175563069</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.1928849256560219</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.0526434538225228</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0573282379374275</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.1547041433976913</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.255128192086505</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.100918752864745</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0170949295625193</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.006131117760765</v>
+      <c r="J11" s="21" t="n">
+        <v>0.0154850630480728</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>-0.0116184883401088</v>
       </c>
     </row>
     <row r="12">
@@ -2212,7 +2326,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2226,27 +2340,27 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>0.0585267338684687</v>
+        <v>0.0216763015339713</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>0.0274240677693482</v>
+        <v>-0.1378049152653392</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>0.031465063168498</v>
+        <v>-0.0086146672723308</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>0.1705560918196227</v>
+        <v>0.2732488766635601</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0355156641914876</v>
+        <v>0.0248438756637884</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>0.002557432846991</v>
+        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="13">
@@ -2255,7 +2369,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2269,27 +2383,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0774536319509322</v>
+        <v>-0.0232944918311316</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.130500030517578</v>
+        <v>-0.1325122852043565</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>0.228324143503479</v>
+        <v>-0.0333378898639641</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>0.0673904056469028</v>
+        <v>0.07361627837494381</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0257858693771772</v>
+        <v>0.0199866178232683</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.019070255160478</v>
+        <v>0.0483516267572325</v>
       </c>
     </row>
     <row r="14">
@@ -2298,7 +2412,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2312,27 +2426,27 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>0.0254237288135592</v>
+        <v>0.039767199876346</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.1799698795180723</v>
+        <v>0.0582428574454614</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.0768923210325954</v>
+        <v>0.0551181523648682</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>-0.0341755137155445</v>
+        <v>0.2134146447780767</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.022877043859946</v>
+        <v>0.0356048859553225</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>-0.000450260009301</v>
+        <v>-0.0271741120711617</v>
       </c>
     </row>
     <row r="15">
@@ -2341,7 +2455,7 @@
       </c>
       <c r="B15" s="26" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C15" s="26" t="inlineStr">
@@ -2355,27 +2469,27 @@
         </is>
       </c>
       <c r="E15" s="27" t="n">
-        <v>-0.0538656516832387</v>
+        <v>-0.0440944979647938</v>
       </c>
       <c r="F15" s="27" t="n">
-        <v>-0.1872618098419274</v>
+        <v>-0.0971740696285322</v>
       </c>
       <c r="G15" s="27" t="n">
-        <v>-0.3081556953641494</v>
+        <v>0.3231255072702177</v>
       </c>
       <c r="H15" s="27" t="n">
-        <v>0.0216399265741287</v>
+        <v>0.0535752482172524</v>
       </c>
       <c r="I15" s="26" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J15" s="27" t="n">
-        <v>0.0175418542292546</v>
+        <v>0.0262956623444027</v>
       </c>
       <c r="K15" s="27" t="n">
-        <v>0.0006695213718759</v>
+        <v>0.0133234131632889</v>
       </c>
     </row>
     <row r="16">
@@ -2384,7 +2498,7 @@
       </c>
       <c r="B16" s="26" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C16" s="26" t="inlineStr">
@@ -2398,16 +2512,16 @@
         </is>
       </c>
       <c r="E16" s="27" t="n">
-        <v>-0.0748792270531401</v>
+        <v>-0.0452261123508876</v>
       </c>
       <c r="F16" s="27" t="n">
-        <v>-0.1745689655172413</v>
+        <v>-0.1541457841884128</v>
       </c>
       <c r="G16" s="27" t="n">
-        <v>-0.1358303487115205</v>
+        <v>-0.3078324418244786</v>
       </c>
       <c r="H16" s="27" t="n">
-        <v>0.2731285195859629</v>
+        <v>0.0602535105833923</v>
       </c>
       <c r="I16" s="26" t="inlineStr">
         <is>
@@ -2415,10 +2529,10 @@
         </is>
       </c>
       <c r="J16" s="27" t="n">
-        <v>0.0197620982238175</v>
+        <v>0.0183204431263809</v>
       </c>
       <c r="K16" s="27" t="n">
-        <v>0.0556585878468132</v>
+        <v>0.0020191724169313</v>
       </c>
     </row>
     <row r="17">
@@ -2427,7 +2541,7 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
@@ -2441,27 +2555,27 @@
         </is>
       </c>
       <c r="E17" s="27" t="n">
-        <v>-0.0557377049180327</v>
+        <v>-0.0544747659267688</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.1235544735240413</v>
+        <v>-0.1413427599942038</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>0.0549450549450549</v>
+        <v>-0.0881801281466332</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-0.1018704487088503</v>
+        <v>0.2822590393148394</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0299429051249194</v>
+        <v>0.0203033503526897</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0485096508933775</v>
+        <v>0.0166220506858436</v>
       </c>
     </row>
     <row r="18">
@@ -2470,7 +2584,7 @@
       </c>
       <c r="B18" s="26" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C18" s="26" t="inlineStr">
@@ -2484,27 +2598,27 @@
         </is>
       </c>
       <c r="E18" s="27" t="n">
-        <v>-0.0362158835532249</v>
+        <v>0.0413793814073624</v>
       </c>
       <c r="F18" s="27" t="n">
-        <v>-0.1960542765109</v>
+        <v>-0.1733576288245625</v>
       </c>
       <c r="G18" s="27" t="n">
-        <v>-0.1122733625312385</v>
+        <v>0.0419782331918596</v>
       </c>
       <c r="H18" s="27" t="n">
-        <v>0.2410422103922216</v>
+        <v>0.0937057382612978</v>
       </c>
       <c r="I18" s="26" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J18" s="27" t="n">
-        <v>0.0213786434561665</v>
+        <v>0.0270668778622527</v>
       </c>
       <c r="K18" s="27" t="n">
-        <v>0.05159344410234</v>
+        <v>0.0453430688902101</v>
       </c>
     </row>
     <row r="19">
@@ -2513,7 +2627,7 @@
       </c>
       <c r="B19" s="26" t="inlineStr">
         <is>
-          <t>SISE.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -2527,27 +2641,27 @@
         </is>
       </c>
       <c r="E19" s="27" t="n">
-        <v>0.0026233549743024</v>
+        <v>-0.0733374766935984</v>
       </c>
       <c r="F19" s="27" t="n">
-        <v>-0.1936708862796933</v>
+        <v>-0.0557314756174793</v>
       </c>
       <c r="G19" s="27" t="n">
-        <v>-0.1256381990168612</v>
+        <v>0.1003690036900368</v>
       </c>
       <c r="H19" s="27" t="n">
-        <v>0.3991606220660881</v>
+        <v>-0.1189022064185915</v>
       </c>
       <c r="I19" s="26" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J19" s="27" t="n">
-        <v>0.026262986561954</v>
+        <v>0.030670519645955</v>
       </c>
       <c r="K19" s="27" t="n">
-        <v>0.06799392425498541</v>
+        <v>0.1070429210315777</v>
       </c>
     </row>
     <row r="20">
@@ -2556,7 +2670,7 @@
       </c>
       <c r="B20" s="26" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>SISE.IS</t>
         </is>
       </c>
       <c r="C20" s="26" t="inlineStr">
@@ -2570,16 +2684,16 @@
         </is>
       </c>
       <c r="E20" s="27" t="n">
-        <v>-0.07860016151729959</v>
+        <v>-0.0095000267028808</v>
       </c>
       <c r="F20" s="27" t="n">
-        <v>-0.2477752140987634</v>
+        <v>-0.1446459587021135</v>
       </c>
       <c r="G20" s="27" t="n">
-        <v>-0.1072818415636823</v>
+        <v>-0.0932007419131328</v>
       </c>
       <c r="H20" s="27" t="n">
-        <v>0.0655210596212267</v>
+        <v>0.3953232345168789</v>
       </c>
       <c r="I20" s="26" t="inlineStr">
         <is>
@@ -2587,10 +2701,10 @@
         </is>
       </c>
       <c r="J20" s="27" t="n">
-        <v>0.0235895708006695</v>
+        <v>0.0270427043731032</v>
       </c>
       <c r="K20" s="27" t="n">
-        <v>0.0248447886632294</v>
+        <v>0.032852620702457</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2729,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2623,7 +2737,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2648,7 +2762,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, GARAN.IS, ARCLK.IS</t>
+          <t>BIMAS.IS, TUPRS.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2774,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS</t>
+          <t>KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2786,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TOASO.IS</t>
+          <t>THYAO.IS, PGSUS.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2798,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, PGSUS.IS, PETKM.IS, EREGL.IS, FROTO.IS, TCELL.IS, ASELS.IS, AKBNK.IS, SISE.IS, YKBNK.IS</t>
+          <t>AKBNK.IS, SAHOL.IS, EREGL.IS, FROTO.IS, TCELL.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2810,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.91 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2848,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2742,7 +2856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2779,7 +2893,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2803,7 +2917,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2953,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2965,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2935,7 +3049,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3061,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3099,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2993,7 +3107,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3017,7 +3131,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13284.400390625</v>
+        <v>13337.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3027,7 +3141,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13501.69251953125</v>
+        <v>13512.79852050781</v>
       </c>
     </row>
     <row r="6">
@@ -3061,7 +3175,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>64.20999999999999</v>
+        <v>54.79</v>
       </c>
     </row>
     <row r="9">
@@ -3088,7 +3202,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3096,7 +3210,7 @@
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="24" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3104,7 +3218,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-16</t>
+          <t>Rapor Tarihi: 2026-09-18</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3118,7 +3232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-21 07:19</t>
+          <t>Son Güncelleme: 2026-09-22 06:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3186,19 +3300,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>360</v>
+        <v>372.75</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>-0.09887359198998746</v>
+        <v>-0.0669586983729662</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>-69654.44262507732</v>
+        <v>-47171.04658786883</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="5">
@@ -3216,19 +3330,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>206.5</v>
+        <v>214.6999969482422</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>0.0482233502538072</v>
+        <v>0.08984770024488431</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>140153.6803430272</v>
+        <v>261128.3909848942</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="6">
@@ -3246,19 +3360,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>84.30000305175781</v>
+        <v>88.05000305175781</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.1264248388418879</v>
+        <v>-0.0875647352149449</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-11101.93142037037</v>
+        <v>-7689.451646562942</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="7">
@@ -3276,19 +3390,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>120.9000015258789</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.09370309552116773</v>
+        <v>-0.0262368827596493</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>-453776.1194554595</v>
+        <v>-127057.3909972059</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="8">
@@ -3306,19 +3420,19 @@
         <v>38.86000061035156</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>34.77999877929688</v>
+        <v>36.41999816894531</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>-0.1049923254496258</v>
+        <v>-0.06278956261149105</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>-22854.86544006292</v>
+        <v>-13668.11334428971</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="9">
@@ -3336,53 +3450,83 @@
         <v>405.5</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>405.5</v>
+        <v>419.75</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>0</v>
+        <v>0.03514180024660907</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>0</v>
+        <v>99652.24630360119</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-18</t>
         </is>
       </c>
       <c r="C10" s="28" t="n">
-        <v>86.84999847412109</v>
+        <v>417.25</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>86.84999847412109</v>
+        <v>417.25</v>
       </c>
       <c r="E10" s="29" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>-4.656612873077393e-10</v>
+        <v>0</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>20297691.1362877</v>
+        <v>20890620.6329084</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>-0.0424255976813339</v>
+        <v>-0.0306187689269554</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="C11" s="28" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="D11" s="28" t="n">
+        <v>284.5</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>20890620.6329084</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-0.0306187689269554</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H10"/>
+  <autoFilter ref="A3:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -195,12 +195,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,7 +581,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -616,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 54.79/100</t>
+          <t>Güven Puanı: 54.81/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, TUPRS.IS, TOASO.IS</t>
+          <t>AL: BIMAS.IS, TUPRS.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -778,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, PGSUS.IS, ARCLK.IS, PETKM.IS</t>
+          <t>ÇIK: PGSUS.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -964,25 +958,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.227086665563358</v>
+        <v>0.2301296797959418</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22708.6665563358</v>
+        <v>23012.96797959418</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>887.39800432953</v>
+        <v>899.2893443623856</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>436.1527822326448</v>
+        <v>449.9205591583924</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>398.7625</v>
+        <v>411.35</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7815500766001103</v>
+        <v>0.7815500766001093</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1007,25 +1001,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.194108935052226</v>
+        <v>0.1948042649380666</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19410.8935052226</v>
+        <v>19480.42649380666</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.042473454091193</v>
+        <v>0.0584414033940758</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>824.4476941631086</v>
+        <v>1138.463463013197</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>434.9720487195503</v>
+        <v>438.988572057693</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>395.4357446682952</v>
+        <v>393.0329661539714</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.8124067702550941</v>
+        <v>1.11610877569846</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,25 +1042,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1788043993844159</v>
+        <v>0.1750660552659915</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17880.4399384416</v>
+        <v>17506.60552659915</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0748220103803021</v>
+        <v>0.058882145534205</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1337.850462678445</v>
+        <v>1030.826494427129</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>305.786861953196</v>
+        <v>95.88178150957413</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>270.275</v>
+        <v>86.02250289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.496440207606041</v>
+        <v>1.1776429106841</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1121,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1201,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,28 +1353,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>419.75</v>
+        <v>433</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205578496996079</v>
+        <v>-0.0365855290080902</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0390775038300055</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0814230457829332</v>
+        <v>0.0814230397476265</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>411.1208425885895</v>
+        <v>417.1584659394969</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>436.1527822326448</v>
+        <v>449.9205591583924</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>453.9273234673862</v>
+        <v>468.2561762107223</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>398.7625</v>
+        <v>411.35</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1388,7 +1382,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1416,28 +1410,28 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>214.6999969482422</v>
+        <v>222.3000030517578</v>
       </c>
       <c r="E9" s="18" t="n">
-        <v>-0.0120989868586411</v>
+        <v>-0.0120988634880525</v>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0344346643343227</v>
       </c>
       <c r="G9" s="18" t="n">
-        <v>0.0729761101061803</v>
+        <v>0.0914169657590902</v>
       </c>
       <c r="H9" s="17" t="n">
-        <v>212.1023445066151</v>
+        <v>219.610425661441</v>
       </c>
       <c r="I9" s="17" t="n">
-        <v>219.6956534562084</v>
+        <v>229.954829038364</v>
       </c>
       <c r="J9" s="17" t="n">
-        <v>230.3679675653337</v>
+        <v>242.621994818986</v>
       </c>
       <c r="K9" s="17" t="n">
-        <v>203.9649971008301</v>
+        <v>211.1850028991699</v>
       </c>
       <c r="L9" s="16" t="inlineStr">
         <is>
@@ -1445,7 +1439,7 @@
         </is>
       </c>
       <c r="M9" s="16" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N9" s="16" t="inlineStr">
         <is>
@@ -1473,28 +1467,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>417.25</v>
+        <v>414.75</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0261975976177936</v>
+        <v>-0.0289967370151656</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.042473454091193</v>
+        <v>0.0584414033940758</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.127426389921516</v>
+        <v>0.1756283561124567</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>406.3190523939756</v>
+        <v>402.7236033229601</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>434.9720487195503</v>
+        <v>438.988572057693</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>470.4186611947525</v>
+        <v>487.5918606976414</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>395.4357446682952</v>
+        <v>393.0329661539714</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1502,7 +1496,7 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1530,10 +1524,10 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>129.8999938964844</v>
+        <v>133.1000061035156</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0076394197603308</v>
+        <v>-0.007255186827286</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>0.0331174361060366</v>
@@ -1542,16 +1536,16 @@
         <v>0.0795559387098858</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>128.9076333162447</v>
+        <v>132.1343406925217</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>134.2019486445257</v>
+        <v>137.5079370513619</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>140.2343098493276</v>
+        <v>143.6889020313724</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>123.4049942016601</v>
+        <v>126.4450057983398</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1553,7 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
@@ -1578,7 +1572,7 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C12" s="13" t="inlineStr">
@@ -1587,28 +1581,28 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>284.5</v>
+        <v>90.55000305175781</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.003760332626605</v>
+        <v>-0.00167218809266</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.0748220103803021</v>
+        <v>0.058882145534205</v>
       </c>
       <c r="G12" s="15" t="n">
-        <v>0.1307691594971161</v>
+        <v>0.1183067031137687</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>283.4301853677309</v>
+        <v>90.39858641486434</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>305.786861953196</v>
+        <v>95.88178150957413</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>321.7038258769296</v>
+        <v>101.262675379753</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>270.275</v>
+        <v>86.02250289916992</v>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
@@ -1616,16 +1610,16 @@
         </is>
       </c>
       <c r="M12" s="13" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
-          <t>trend desteği var; volatilite görece düşük</t>
+          <t>trend desteği var; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O12" s="13" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1635,7 +1629,7 @@
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1644,28 +1638,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>285.5</v>
+        <v>151.1999969482422</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0573248422045384</v>
+        <v>-0.0461145394060134</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0407844352132465</v>
+        <v>-0.0171127424349814</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.0475785896346643</v>
+        <v>0.0615545291580976</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>269.1337575506043</v>
+        <v>144.2274787307834</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>273.8560437466181</v>
+        <v>148.6125503442969</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>299.0836873406967</v>
+        <v>160.507041569097</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>269.1337575506043</v>
+        <v>143.6399971008301</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1673,7 +1667,7 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
@@ -1682,7 +1676,7 @@
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1692,7 +1686,7 @@
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -1701,28 +1695,28 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>147.6000061035156</v>
+        <v>86.90000152587891</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>-0.0461145394060134</v>
+        <v>-0.0437032076168698</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>-0.0171127424349814</v>
+        <v>-0.0081012994825111</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>0.0615545291580976</v>
+        <v>0.1088380129700114</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>140.7934998057272</v>
+        <v>83.10219271728712</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>145.0741652156645</v>
+        <v>86.19599858848709</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>156.6854549829499</v>
+        <v>96.35802501904654</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>140.2200057983398</v>
+        <v>82.55500144958496</v>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
@@ -1730,7 +1724,7 @@
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
@@ -1743,122 +1737,8 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>87.15000152587891</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.0437032076168698</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>-0.0116184883401088</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0849377720435755</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>83.3412669153829</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>86.13745024931002</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>94.55232848908128</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>82.79250144958496</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>21.44000053405762</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>-0.0753137768113169</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>-0.0271741120711617</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.052217597125587</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>19.82527311900109</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>20.85738755673937</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>22.55954584431741</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>19.82527311900109</v>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>54.79</v>
-      </c>
-      <c r="N16" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1888,7 +1768,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1905,7 +1785,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1996,16 +1876,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0274679337585526</v>
+        <v>0.0459051302819943</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1142198729415047</v>
+        <v>0.1381305230362726</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2494150506792569</v>
+        <v>0.2422364511852537</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.058321730831083</v>
+        <v>-0.03882482299824</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -2013,7 +1893,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0189448735168681</v>
+        <v>0.0192861772526677</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0390775038300055</v>
@@ -2030,7 +1910,7 @@
       </c>
       <c r="C5" s="16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D5" s="16" t="inlineStr">
@@ -2039,16 +1919,16 @@
         </is>
       </c>
       <c r="E5" s="18" t="n">
-        <v>-0.0151376286777881</v>
+        <v>-0.0004495991343106</v>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.0887423948824559</v>
+        <v>0.1602296240619947</v>
       </c>
       <c r="G5" s="18" t="n">
-        <v>0.1451289950600338</v>
+        <v>0.1814127694551341</v>
       </c>
       <c r="H5" s="18" t="n">
-        <v>0.2221047096245418</v>
+        <v>0.2178742027707727</v>
       </c>
       <c r="I5" s="16" t="inlineStr">
         <is>
@@ -2056,10 +1936,10 @@
         </is>
       </c>
       <c r="J5" s="18" t="n">
-        <v>0.0206781965315894</v>
+        <v>0.0207493896457705</v>
       </c>
       <c r="K5" s="18" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0344346643343227</v>
       </c>
     </row>
     <row r="6">
@@ -2082,16 +1962,16 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.0556609740670461</v>
+        <v>0.0196681007990164</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.8905754679183437</v>
+        <v>0.8818058597351699</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.6475814412635736</v>
+        <v>0.6264705882352941</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0512215026195899</v>
+        <v>0.0568053374296593</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -2099,10 +1979,10 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0261405096844875</v>
+        <v>0.0261808726293292</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.042473454091193</v>
+        <v>0.0584414033940758</v>
       </c>
     </row>
     <row r="7">
@@ -2125,16 +2005,16 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.0046403003137316</v>
+        <v>0.024634429233163</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.0960334261992246</v>
+        <v>-0.0540155722073134</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0.0003654517218298</v>
+        <v>0.031114743529351</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0.1823333958386286</v>
+        <v>0.1885245809935705</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -2142,7 +2022,7 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0210305047791659</v>
+        <v>0.0211316400469987</v>
       </c>
       <c r="K7" s="18" t="n">
         <v>0.0331174361060366</v>
@@ -2154,7 +2034,7 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C8" s="13" t="inlineStr">
@@ -2168,27 +2048,27 @@
         </is>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0498154981549816</v>
+        <v>-0.02002162817717</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.1424265259984928</v>
+        <v>-0.0867372500430716</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.0198105081826012</v>
+        <v>-0.0154655239934742</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>-0.018789406786501</v>
+        <v>0.0712659619406239</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.0238878268157538</v>
+        <v>0.0201633772695993</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.0748220103803021</v>
+        <v>0.058882145534205</v>
       </c>
     </row>
     <row r="9">
@@ -2197,7 +2077,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2211,16 +2091,16 @@
         </is>
       </c>
       <c r="E9" s="21" t="n">
-        <v>-0.0522821576763485</v>
+        <v>0.0113712170450981</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>-0.1208622016936105</v>
+        <v>-0.1510387885087357</v>
       </c>
       <c r="G9" s="21" t="n">
-        <v>-0.0138169257340241</v>
+        <v>-0.1669421655744232</v>
       </c>
       <c r="H9" s="21" t="n">
-        <v>0.0253496094892917</v>
+        <v>0.0876941910603603</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
@@ -2228,10 +2108,10 @@
         </is>
       </c>
       <c r="J9" s="21" t="n">
-        <v>0.0190754319523366</v>
+        <v>0.0179691597831174</v>
       </c>
       <c r="K9" s="21" t="n">
-        <v>-0.0407844352132465</v>
+        <v>-0.0171127424349814</v>
       </c>
     </row>
     <row r="10">
@@ -2240,7 +2120,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -2254,16 +2134,16 @@
         </is>
       </c>
       <c r="E10" s="21" t="n">
-        <v>-0.0133689834117793</v>
+        <v>-0.0605405240445523</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>-0.1912328432684075</v>
+        <v>-0.1429980254615614</v>
       </c>
       <c r="G10" s="21" t="n">
-        <v>-0.1684506698393486</v>
+        <v>-0.2515072982946759</v>
       </c>
       <c r="H10" s="21" t="n">
-        <v>0.0832408574095935</v>
+        <v>0.1009651450953732</v>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
@@ -2271,53 +2151,53 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0178397660475483</v>
+        <v>0.0153819958179133</v>
       </c>
       <c r="K10" s="21" t="n">
-        <v>-0.0171127424349814</v>
+        <v>-0.0081012994825111</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0573282379374275</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.1547041433976913</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.255128192086505</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.100918752864745</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0249169435215946</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.09692307692307681</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.0067681895093062</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.0290770040125245</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0154850630480728</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>-0.0116184883401088</v>
+      <c r="J11" s="23" t="n">
+        <v>0.0194415718219093</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0183754572592703</v>
       </c>
     </row>
     <row r="12">
@@ -2340,16 +2220,16 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>0.0216763015339713</v>
+        <v>0.0394548080402656</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.1378049152653392</v>
+        <v>-0.1000000379100349</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>-0.0086146672723308</v>
+        <v>0.0228734680459419</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>0.2732488766635601</v>
+        <v>0.2674257314311745</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
@@ -2357,7 +2237,7 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0248438756637884</v>
+        <v>0.0249814864018785</v>
       </c>
       <c r="K12" s="23" t="n">
         <v>0.0111110916693351</v>
@@ -2369,7 +2249,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2383,27 +2263,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0232944918311316</v>
+        <v>0.0349853895055232</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.1325122852043565</v>
+        <v>0.058648029254859</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-0.0333378898639641</v>
+        <v>0.0895140699894534</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>0.07361627837494381</v>
+        <v>0.2133031766838957</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0199866178232683</v>
+        <v>0.035603466446733</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0483516267572325</v>
+        <v>0.0012787164234955</v>
       </c>
     </row>
     <row r="14">
@@ -2412,7 +2292,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2422,289 +2302,289 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>PORTFOY_DISI</t>
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>0.039767199876346</v>
+        <v>-0.0199265425719821</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>0.0582428574454614</v>
+        <v>-0.0612757068158926</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>0.0551181523648682</v>
+        <v>0.3219908226401857</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.2134146447780767</v>
+        <v>0.0283392255787411</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0264803735519619</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.029948947983406</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>-0.0293017277249734</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.1148379627581437</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.2851239909705522</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.0585038563270767</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.0184690515737341</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0082246806454282</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>0.031111111111111</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.1594202898550725</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.0211267605633802</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.0409336575100016</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0356048859553225</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>-0.0271741120711617</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0234389678513488</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0218373705587808</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.0440944979647938</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.0971740696285322</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>0.3231255072702177</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>0.0535752482172524</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="E17" s="25" t="n">
+        <v>-0.0421860153129185</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.0999999862533431</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.07841328302906669</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.2652490251057262</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0205273993504984</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0230245283671322</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>0.0421653396374015</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.1469216203388835</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0511495009487963</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0.1002105576390692</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0262956623444027</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>0.0133234131632889</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0269950772736376</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0505952630994552</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="26" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="27" t="n">
-        <v>-0.0452261123508876</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>-0.1541457841884128</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>-0.3078324418244786</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>0.0602535105833923</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.06261624302541841</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.0357142857142857</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0.07006369426751589</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.123655090764607</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0307130013102403</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.07234277227380791</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>0.0115287986686993</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1058927524131299</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1601365451703175</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.3942855985514568</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="27" t="n">
-        <v>0.0183204431263809</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0020191724169313</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.0544747659267688</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.1413427599942038</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.0881801281466332</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>0.2822590393148394</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0203033503526897</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>0.0166220506858436</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>0.0413793814073624</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.1733576288245625</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0.0419782331918596</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>0.0937057382612978</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0270668778622527</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>0.0453430688902101</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.0733374766935984</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>-0.0557314756174793</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0.1003690036900368</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>-0.1189022064185915</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>0.030670519645955</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>0.1070429210315777</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>-0.0095000267028808</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>-0.1446459587021135</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>-0.0932007419131328</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>0.3953232345168789</v>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.0270427043731032</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>0.032852620702457</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0269996997014378</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0288486642856891</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2609,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2737,7 +2617,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2762,7 +2642,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS, TOASO.IS</t>
+          <t>BIMAS.IS, TUPRS.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2666,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, PGSUS.IS, ARCLK.IS, PETKM.IS</t>
+          <t>PGSUS.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2678,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, SAHOL.IS, EREGL.IS, FROTO.IS, TCELL.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>THYAO.IS, AKBNK.IS, PETKM.IS, EREGL.IS, FROTO.IS, TOASO.IS, TCELL.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2728,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2856,7 +2736,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +2881,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2929,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3099,7 +2979,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3107,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3175,7 +3055,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>54.79</v>
+        <v>54.81</v>
       </c>
     </row>
     <row r="9">
@@ -3209,16 +3089,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-18</t>
+          <t>Rapor Tarihi: 2026-09-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3232,7 +3112,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-22 06:56</t>
+          <t>Son Güncelleme: 2026-09-23 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3296,23 +3176,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="26" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>372.75</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>-0.0669586983729662</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>-47171.04658786883</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D4" s="26" t="n">
+        <v>378</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>-0.0538172715894869</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>-37913.17763137119</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="5">
@@ -3326,23 +3206,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>214.6999969482422</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.08984770024488431</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>261128.3909848942</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D5" s="26" t="n">
+        <v>222.3000030517578</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>0.1284264114302427</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>373251.4253045977</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="6">
@@ -3356,23 +3236,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>88.05000305175781</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.0875647352149449</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-7689.451646562942</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D6" s="26" t="n">
+        <v>90.55000305175781</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.06165799946364958</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-5414.465130691315</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="7">
@@ -3386,23 +3266,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="26" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>129.8999938964844</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.0262368827596493</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-127057.3909972059</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D7" s="26" t="n">
+        <v>133.1000061035156</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.002248784158127681</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-10890.19037303422</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="8">
@@ -3416,23 +3296,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="26" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>36.41999816894531</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.06278956261149105</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-13668.11334428971</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D8" s="26" t="n">
+        <v>37.38000106811523</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.03808542251649072</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-8290.484119812842</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="9">
@@ -3446,23 +3326,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="26" t="n">
         <v>405.5</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>419.75</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0.03514180024660907</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>99652.24630360119</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D9" s="26" t="n">
+        <v>433</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>0.06781750924784213</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>192311.3525157212</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="10">
@@ -3476,23 +3356,23 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="26" t="n">
         <v>417.25</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>417.25</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D10" s="26" t="n">
+        <v>414.75</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>-0.005991611743559</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>-27353.76259034593</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
     <row r="11">
@@ -3506,23 +3386,23 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C11" s="26" t="n">
         <v>284.5</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>284.5</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>20890620.6329084</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>-0.0306187689269554</v>
+      <c r="D11" s="26" t="n">
+        <v>290</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>0.01933216168717045</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>88257.94857577514</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>21289384.64474668</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-0.0267294078143243</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -610,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 54.81/100</t>
+          <t>Güven Puanı: 60.73/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -738,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, TUPRS.IS, SAHOL.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -755,7 +755,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, GARAN.IS</t>
+          <t>AZALT: TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -772,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PGSUS.IS, ARCLK.IS</t>
+          <t>ÇIK: AKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,29 +958,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2301296797959418</v>
+        <v>0.236703758413594</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23012.96797959418</v>
+        <v>23670.3758413594</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485935221290569</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>899.2893443623856</v>
+        <v>1150.226932250192</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>449.9205591583924</v>
+        <v>451.1573628960268</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>411.35</v>
+        <v>408.7375</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7815500766001093</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.9718704425811376</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1001,25 +1001,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1948042649380666</v>
+        <v>0.1923716456723683</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19480.42649380666</v>
+        <v>19237.16456723683</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0584414033940758</v>
+        <v>0.0259673500152164</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1138.463463013197</v>
+        <v>499.5381856177578</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>438.988572057693</v>
+        <v>226.8413873503721</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>393.0329661539714</v>
+        <v>210.0450057983398</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.11610877569846</v>
+        <v>0.5193470003043297</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1042,25 +1042,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1750660552659915</v>
+        <v>0.1709245959140376</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17506.60552659915</v>
+        <v>17092.45959140376</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.058882145534205</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>1030.826494427129</v>
+        <v>566.0584384133266</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>95.88178150957413</v>
+        <v>138.3344183889499</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>86.02250289916992</v>
+        <v>127.2049942016602</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>1.1776429106841</v>
+        <v>0.6623487221207338</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,102 +1353,102 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>433</v>
+        <v>430.25</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0365855290080902</v>
+        <v>-0.0314235293714596</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485935221290569</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>0.0814230397476265</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>417.1584659394969</v>
+        <v>416.7300264879295</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>449.9205591583924</v>
+        <v>451.1573628960268</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>468.2561762107223</v>
+        <v>465.2822628514163</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>411.35</v>
+        <v>408.7375</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>221.1000061035156</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0120989247979147</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0259673500152164</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.0914169657590902</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>218.4249337568507</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>226.8413873503721</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>241.3122977908153</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>210.0450057983398</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M9" s="13" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>222.3000030517578</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0120988634880525</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.0344346643343227</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0914169657590902</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>219.610425661441</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>229.954829038364</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>242.621994818986</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>211.1850028991699</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1467,28 +1467,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>414.75</v>
+        <v>133.8999938964844</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0289967370151656</v>
+        <v>-0.0072550407786147</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.0584414033940758</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.1756283561124567</v>
+        <v>0.0727866394764026</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>402.7236033229601</v>
+        <v>132.9285439805091</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>438.988572057693</v>
+        <v>138.3344183889499</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>487.5918606976414</v>
+        <v>143.6461244781203</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>393.0329661539714</v>
+        <v>127.2049942016602</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1496,11 +1496,11 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>54.81</v>
+        <v>60.73</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
       <c r="O10" s="13" t="inlineStr">
@@ -1515,7 +1515,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1524,112 +1524,112 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>133.1000061035156</v>
+        <v>397</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.007255186827286</v>
+        <v>-0.08640226646425481</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0073025780500444</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.0795559387098858</v>
+        <v>0.1262861266103623</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>132.1343406925217</v>
+        <v>362.6983002136909</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>137.5079370513619</v>
+        <v>399.8991234858676</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>143.6889020313724</v>
+        <v>447.1355922643139</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>126.4450057983398</v>
+        <v>362.6983002136909</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>54.81</v>
+        <v>60.73</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>73.09999847412109</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0860925862176307</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0353915104889933</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.0665741628795484</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>66.80663055297914</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>70.51287911137885</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>77.96656967903198</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>66.80663055297914</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="19" t="n">
+        <v>60.73</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>90.55000305175781</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.00167218809266</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.058882145534205</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.1183067031137687</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>90.39858641486434</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>95.88178150957413</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>101.262675379753</v>
-      </c>
-      <c r="K12" s="14" t="n">
-        <v>86.02250289916992</v>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>54.81</v>
-      </c>
-      <c r="N12" s="13" t="inlineStr">
-        <is>
-          <t>trend desteği var; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>151.1999969482422</v>
+        <v>298</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0461145394060134</v>
+        <v>-0.0594382207306622</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0171127424349814</v>
+        <v>-0.0407844352132465</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.0615545291580976</v>
+        <v>0.0521832799398017</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>144.2274787307834</v>
+        <v>280.2874102222627</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>148.6125503442969</v>
+        <v>285.8462383064526</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>160.507041569097</v>
+        <v>313.5506174220609</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>143.6399971008301</v>
+        <v>280.2874102222627</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1667,22 +1667,22 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>54.81</v>
+        <v>60.73</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
+          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>trend desteği zayıf</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>86.90000152587891</v>
+        <v>88</v>
       </c>
       <c r="E14" s="21" t="n">
         <v>-0.0437032076168698</v>
@@ -1707,16 +1707,16 @@
         <v>0.1088380129700114</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>83.10219271728712</v>
+        <v>84.15411772971547</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>86.19599858848709</v>
+        <v>87.28708564553902</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>96.35802501904654</v>
+        <v>97.57774514136101</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>82.55500144958496</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
@@ -1724,7 +1724,7 @@
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>54.81</v>
+        <v>60.73</v>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
@@ -1768,7 +1768,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1785,7 +1785,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1876,16 +1876,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0459051302819943</v>
+        <v>0.0499765479157583</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1381305230362726</v>
+        <v>0.157360494433421</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2422364511852537</v>
+        <v>0.2930380317442207</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.03882482299824</v>
+        <v>-0.0394073991538652</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1893,53 +1893,53 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0192861772526677</v>
+        <v>0.0190503627883537</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485935221290569</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>-0.0004495991343106</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.1602296240619947</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.1814127694551341</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.2178742027707727</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>0.0105118967992599</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.145595886546713</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.210379418184631</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.1993531366667877</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0207493896457705</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.0344346643343227</v>
+      <c r="J5" s="15" t="n">
+        <v>0.0207643788216232</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0259673500152164</v>
       </c>
     </row>
     <row r="6">
@@ -1948,12 +1948,12 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D6" s="13" t="inlineStr">
@@ -1962,27 +1962,27 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>0.0196681007990164</v>
+        <v>0.0174771100782442</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.8818058597351699</v>
+        <v>-0.0462962983089044</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.6264705882352941</v>
+        <v>0.0716232632910167</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0568053374296593</v>
+        <v>0.1564642457372413</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0261808726293292</v>
+        <v>0.0211474137590532</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.0584414033940758</v>
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2005,242 +2005,242 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>0.024634429233163</v>
+        <v>-0.008739076154806499</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.0540155722073134</v>
+        <v>0.8311807860317331</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0.031114743529351</v>
+        <v>0.5328185328185329</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>0.1885245809935705</v>
+        <v>0.06566802001021239</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0268214947432082</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0073025780500444</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.013869625813639</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.09697342520148849</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0.073156097358821</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>0.2483711765443628</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.0250003007255031</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-0.0353915104889933</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>0.0113636155005627</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.1451977228714247</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.154748586303029</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>0.08798396285136829</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.0179668558638038</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0293749779565115</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>-0.0328912304946534</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-0.0866733593323928</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.0296207836457733</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0.041147599661206</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0211316400469987</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="J10" s="23" t="n">
+        <v>0.0201638182738833</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.0588822602991307</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.02002162817717</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>-0.0867372500430716</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>-0.0154655239934742</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.0712659619406239</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>0.0201633772695993</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0.058882145534205</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0083194675540765</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.08237105465742869</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0.0240549828178693</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.021802670474379</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.0195559090761658</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>-0.0407844352132465</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
-        <v>0.0113712170450981</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>-0.1510387885087357</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>-0.1669421655744232</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>0.0876941910603603</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E12" s="21" t="n">
+        <v>-0.05223477171594</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.1269841534150092</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.2280701754385965</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>0.1147200583660179</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="21" t="n">
-        <v>0.0179691597831174</v>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>-0.0171127424349814</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.0605405240445523</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>-0.1429980254615614</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>-0.2515072982946759</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>0.1009651450953732</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>0.0153819958179133</v>
-      </c>
-      <c r="K10" s="21" t="n">
+      <c r="J12" s="21" t="n">
+        <v>0.0154897728507844</v>
+      </c>
+      <c r="K12" s="21" t="n">
         <v>-0.0081012994825111</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0249169435215946</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.09692307692307681</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.0067681895093062</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.0290770040125245</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0194415718219093</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0183754572592703</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>0.0394548080402656</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.1000000379100349</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.0228734680459419</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>0.2674257314311745</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0249814864018785</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="13">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -2263,27 +2263,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>0.0349853895055232</v>
+        <v>-0.0112359743198956</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>0.058648029254859</v>
+        <v>-0.0838635078765889</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>0.0895140699894534</v>
+        <v>-0.2399232315948906</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>0.2133031766838957</v>
+        <v>0.06020283289409</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.035603466446733</v>
+        <v>0.0185181572285961</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0012787164234955</v>
+        <v>0.1100915926663814</v>
       </c>
     </row>
     <row r="14">
@@ -2306,16 +2306,16 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0199265425719821</v>
+        <v>-0.0094290363403365</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0612757068158926</v>
+        <v>-0.0530795945112292</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>0.3219908226401857</v>
+        <v>0.3799221550939602</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.0283392255787411</v>
+        <v>0.001299222641399</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
@@ -2323,10 +2323,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0264803735519619</v>
+        <v>0.0265228853995872</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.029948947983406</v>
+        <v>0.0176862670340702</v>
       </c>
     </row>
     <row r="15">
@@ -2335,7 +2335,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -2349,16 +2349,16 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0293017277249734</v>
+        <v>-0.0271580549350454</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.1148379627581437</v>
+        <v>-0.09148549216055531</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.2851239909705522</v>
+        <v>-0.0555554996800969</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.0585038563270767</v>
+        <v>0.2348899595529274</v>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
@@ -2366,10 +2366,10 @@
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0184690515737341</v>
+        <v>0.0205324632618941</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0082246806454282</v>
+        <v>0.0243974981951412</v>
       </c>
     </row>
     <row r="16">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -2392,16 +2392,16 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>0.031111111111111</v>
+        <v>0.0057692713286059</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.1594202898550725</v>
+        <v>0.07502574822761621</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>0.0211267605633802</v>
+        <v>0.070076772004999</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>-0.0409336575100016</v>
+        <v>0.2082752826227347</v>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
@@ -2409,10 +2409,10 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0234389678513488</v>
+        <v>0.0354202149778968</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.0218373705587808</v>
+        <v>0.0209345019135112</v>
       </c>
     </row>
     <row r="17">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -2435,27 +2435,27 @@
         </is>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.0421860153129185</v>
+        <v>0.0234445446348061</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>-0.0999999862533431</v>
+        <v>-0.1678885630498533</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>-0.07841328302906669</v>
+        <v>0.0271493212669682</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>0.2652490251057262</v>
+        <v>-0.040773702629152</v>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J17" s="25" t="n">
-        <v>0.0205273993504984</v>
+        <v>0.0235347716646357</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.0230245283671322</v>
+        <v>0.0017867096296519</v>
       </c>
     </row>
     <row r="18">
@@ -2478,16 +2478,16 @@
         </is>
       </c>
       <c r="E18" s="25" t="n">
-        <v>0.0421653396374015</v>
+        <v>0.0065716829343169</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.1469216203388835</v>
+        <v>-0.1395131724921759</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0511495009487963</v>
+        <v>0.1025794287130454</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>0.1002105576390692</v>
+        <v>0.08379698040637</v>
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
@@ -2495,10 +2495,10 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0269950772736376</v>
+        <v>0.0270089725946684</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.0505952630994552</v>
+        <v>0.0423503831348128</v>
       </c>
     </row>
     <row r="19">
@@ -2521,27 +2521,27 @@
         </is>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.06261624302541841</v>
+        <v>-0.06316447779862409</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>-0.0357142857142857</v>
+        <v>0.0190476190476189</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.07006369426751589</v>
+        <v>0.0639204545454545</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>-0.123655090764607</v>
+        <v>-0.1380445118492993</v>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0307130013102403</v>
+        <v>0.029683957187403</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.07234277227380791</v>
+        <v>0.0478183090941359</v>
       </c>
     </row>
     <row r="20">
@@ -2564,16 +2564,16 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>0.0115287986686993</v>
+        <v>0.0130849678184128</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.1058927524131299</v>
+        <v>-0.1073170801849392</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1601365451703175</v>
+        <v>-0.1403193322556694</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.3942855985514568</v>
+        <v>0.3909598574876443</v>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
@@ -2581,10 +2581,10 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0269996997014378</v>
+        <v>0.0269999400224776</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0288486642856891</v>
+        <v>0.0339372324271623</v>
       </c>
     </row>
   </sheetData>
@@ -2609,7 +2609,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2617,7 +2617,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2642,7 +2642,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS, SAHOL.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, ARCLK.IS</t>
+          <t>AKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2678,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, AKBNK.IS, PETKM.IS, EREGL.IS, FROTO.IS, TOASO.IS, TCELL.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>PGSUS.IS, SAHOL.IS, FROTO.IS, EREGL.IS, TCELL.IS, PETKM.IS, TOASO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.91 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.60 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2728,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2736,7 +2736,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2833,7 +2833,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2845,7 +2845,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2987,7 +2987,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3011,7 +3011,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13337.7001953125</v>
+        <v>13251.900390625</v>
       </c>
     </row>
     <row r="5">
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13512.79852050781</v>
+        <v>13523.44052246094</v>
       </c>
     </row>
     <row r="6">
@@ -3055,7 +3055,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>54.81</v>
+        <v>60.73</v>
       </c>
     </row>
     <row r="9">
@@ -3098,7 +3098,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-21</t>
+          <t>Rapor Tarihi: 2026-09-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3112,7 +3112,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-23 06:51</t>
+          <t>Son Güncelleme: 2026-09-24 06:51</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3180,16 +3180,16 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>378</v>
+        <v>374.5</v>
       </c>
       <c r="E4" s="27" t="n">
-        <v>-0.0538172715894869</v>
+        <v>-0.06257822277847314</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>-37913.17763137119</v>
+        <v>-44085.09026903624</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H4" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3210,16 +3210,16 @@
         <v>197</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>222.3000030517578</v>
+        <v>221.1000061035156</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0.1284264114302427</v>
+        <v>0.1223350563630234</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>373251.4253045977</v>
+        <v>355547.8475470669</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H5" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3240,16 +3240,16 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>90.55000305175781</v>
+        <v>91.15000152587891</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>-0.06165799946364958</v>
+        <v>-0.05544039869555539</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>-5414.465130691315</v>
+        <v>-4868.469755423692</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H6" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3270,16 +3270,16 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>133.1000061035156</v>
+        <v>133.8999938964844</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>-0.002248784158127681</v>
+        <v>0.003748126108521266</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>-10890.19037303422</v>
+        <v>18151.0558567429</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H7" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3300,16 +3300,16 @@
         <v>38.86000061035156</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>37.38000106811523</v>
+        <v>37.81999969482422</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>-0.03808542251649072</v>
+        <v>-0.02676276117325405</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>-8290.484119812842</v>
+        <v>-5825.7525281001</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H8" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3330,16 +3330,16 @@
         <v>405.5</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>433</v>
+        <v>430.25</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>0.06781750924784213</v>
+        <v>0.06103575832305785</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>192311.3525157212</v>
+        <v>173080.2172641489</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H9" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3360,16 +3360,16 @@
         <v>417.25</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>414.75</v>
+        <v>397</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>-0.005991611743559</v>
+        <v>-0.04853205512282799</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>-27353.76259034593</v>
+        <v>-221565.4769818028</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H10" s="27" t="n">
         <v>-0.0267294078143243</v>
@@ -3390,16 +3390,16 @@
         <v>284.5</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>290</v>
+        <v>283.75</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>0.01933216168717045</v>
+        <v>-0.002636203866432374</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>88257.94857577514</v>
+        <v>-12035.17480578739</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>21289384.64474668</v>
+        <v>20983825.15452364</v>
       </c>
       <c r="H11" s="27" t="n">
         <v>-0.0267294078143243</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -22,7 +22,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -201,6 +201,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 60.73/100</t>
+          <t>Güven Puanı: 60.88/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -755,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS</t>
+          <t>AZALT: TUPRS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -772,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: AKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>ÇIK: ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,29 +964,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.236703758413594</v>
+        <v>0.2305860355400591</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23670.3758413594</v>
+        <v>23058.60355400591</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0485935221290569</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1150.226932250192</v>
+        <v>901.0726686962445</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>451.1573628960268</v>
+        <v>450.6998672862649</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>408.7375</v>
+        <v>412.0625</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9718704425811376</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.7815500766001116</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1001,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1923716456723683</v>
+        <v>0.1976750945659504</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19237.16456723683</v>
+        <v>19767.50945659503</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0259673500152164</v>
+        <v>0.0288506858218793</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>499.5381856177578</v>
+        <v>570.3062048132514</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>226.8413873503721</v>
+        <v>227.4788929148237</v>
       </c>
       <c r="I21" s="8" t="n">
         <v>210.0450057983398</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5193470003043297</v>
+        <v>0.5770137164375856</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1042,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1709245959140376</v>
+        <v>0.1717388698939905</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17092.45959140376</v>
+        <v>17173.88698939905</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0426715939840771</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>566.0584384133266</v>
+        <v>732.8371327400604</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>138.3344183889499</v>
+        <v>139.5094624570507</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>127.2049942016602</v>
+        <v>127.1100028991699</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6623487221207338</v>
+        <v>0.8534318796815435</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1138,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,36 +1359,36 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>430.25</v>
+        <v>433.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0314235293714596</v>
+        <v>-0.0205582539340234</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0485935221290569</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0814230397476265</v>
+        <v>0.0814229535541966</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>416.7300264879295</v>
+        <v>424.8328573561174</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>451.1573628960268</v>
+        <v>450.6998672862649</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>465.2822628514163</v>
+        <v>469.0672061041328</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>408.7375</v>
+        <v>412.0625</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>60.73</v>
+        <v>60.88</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1416,7 +1422,7 @@
         <v>-0.0120989247979147</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0259673500152164</v>
+        <v>0.0288506858218793</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>0.0914169657590902</v>
@@ -1425,7 +1431,7 @@
         <v>218.4249337568507</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>226.8413873503721</v>
+        <v>227.4788929148237</v>
       </c>
       <c r="J9" s="14" t="n">
         <v>241.3122977908153</v>
@@ -1439,7 +1445,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>60.73</v>
+        <v>60.88</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1453,183 +1459,183 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>411</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.08640226646425481</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0231982012942197</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1262861266103623</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>375.4886684831913</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>420.5344607319244</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>462.9035980368589</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>375.4886684831913</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C11" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0072550407786147</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.0727866394764026</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>132.9285439805091</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>138.3344183889499</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>143.6461244781203</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>127.2049942016602</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
+      <c r="D11" s="14" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.021913693588956</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0426715939840771</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.0899376920918622</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>130.8679507826802</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>139.5094624570507</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>145.833666528117</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>127.1100028991699</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n">
-        <v>60.73</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="M11" s="13" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="O11" s="13" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>397</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.08640226646425481</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.0073025780500444</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.1262861266103623</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>362.6983002136909</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>399.8991234858676</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>447.1355922643139</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>362.6983002136909</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="D12" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0538957289245235</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0729092547856522</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>21.76039823473596</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>23</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>24.67691286007</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>21.27623771492112</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="16" t="n">
-        <v>60.73</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>60.88</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>73.09999847412109</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0860925862176307</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0353915104889933</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.0665741628795484</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>66.80663055297914</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>70.51287911137885</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>77.96656967903198</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>66.80663055297914</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>60.73</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1638,28 +1644,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>298</v>
+        <v>88.30000305175781</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0594382207306622</v>
+        <v>-0.0434165016624163</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0407844352132465</v>
+        <v>-0.0062980681240358</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.0521832799398017</v>
+        <v>0.1080537552156288</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>280.2874102222627</v>
+        <v>84.46632582246981</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>285.8462383064526</v>
+        <v>87.74388361718528</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>313.5506174220609</v>
+        <v>97.84114996705173</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>280.2874102222627</v>
+        <v>83.88500289916992</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1667,26 +1673,26 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>60.73</v>
+        <v>60.88</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
+          <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -1695,28 +1701,28 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>88</v>
+        <v>279</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>-0.0437032076168698</v>
+        <v>-0.0712638969807638</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>-0.0081012994825111</v>
+        <v>-0.0045871559633027</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>0.1088380129700114</v>
+        <v>0.0517095609237237</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>84.15411772971547</v>
+        <v>259.1173727423669</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>87.28708564553902</v>
+        <v>277.7201834862386</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>97.57774514136101</v>
+        <v>293.4269674977189</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>83.59999999999999</v>
+        <v>259.1173727423669</v>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
@@ -1724,16 +1730,16 @@
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>60.73</v>
+        <v>60.88</v>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1768,7 +1774,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1785,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1876,16 +1882,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0499765479157583</v>
+        <v>0.0452072398356422</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.157360494433421</v>
+        <v>0.1621145514924089</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2930380317442207</v>
+        <v>0.3084170653041249</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0394073991538652</v>
+        <v>-0.0433607340298419</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1893,10 +1899,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0190503627883537</v>
+        <v>0.0190627202731149</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0485935221290569</v>
+        <v>0.0390775038300055</v>
       </c>
     </row>
     <row r="5">
@@ -1919,16 +1925,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0105118967992599</v>
+        <v>0.0165517522000717</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.145595886546713</v>
+        <v>0.13442797859166</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.210379418184631</v>
+        <v>0.184252864046966</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>0.1993531366667877</v>
+        <v>0.1888845473075688</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1936,139 +1942,139 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0207643788216232</v>
+        <v>0.0207442689180219</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0259673500152164</v>
+        <v>0.0288506858218793</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.09966555183946491</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.8750000261042243</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.6407185628742516</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>0.0394621596645399</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="18" t="n">
+        <v>0.0270096076422816</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.0231982012942197</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0174771100782442</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>-0.0462962983089044</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.0716232632910167</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.1564642457372413</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="E7" s="15" t="n">
+        <v>0.009049750324335601</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>-0.0276163000232652</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.06753831282353449</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>0.1342455507592934</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0211474137590532</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="J7" s="15" t="n">
+        <v>0.0210010558001496</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0426715939840771</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.008739076154806499</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.8311807860317331</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.5328185328185329</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>0.06566802001021239</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>0.1657374826980371</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.1904762092807717</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.2086179280140792</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>0.2042774020708375</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0268214947432082</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.0073025780500444</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>0.013869625813639</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.09697342520148849</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>0.073156097358821</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>0.2483711765443628</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0250003007255031</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-0.0353915104889933</v>
+      <c r="J8" s="18" t="n">
+        <v>0.0374730931538888</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -2077,7 +2083,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2091,27 +2097,27 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>0.0113636155005627</v>
+        <v>-0.0256684655174214</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.1451977228714247</v>
+        <v>-0.0608247579987516</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-0.154748586303029</v>
+        <v>0.015508268706688</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>0.08798396285136829</v>
+        <v>0.0413454148343286</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0179668558638038</v>
+        <v>0.0198694016645619</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.0293749779565115</v>
+        <v>0.0588821519160343</v>
       </c>
     </row>
     <row r="10">
@@ -2120,7 +2126,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2134,16 +2140,16 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>-0.0328912304946534</v>
+        <v>0.0131944020589191</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0866733593323928</v>
+        <v>-0.0550518156477306</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0296207836457733</v>
+        <v>0.0618910067400306</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>0.041147599661206</v>
+        <v>0.2344056756352319</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2151,53 +2157,53 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0201638182738833</v>
+        <v>0.024327823690841</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.0588822602991307</v>
+        <v>0.0153096520178395</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="22" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0083194675540765</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.08237105465742869</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>0.0240549828178693</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.021802670474379</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>0.001332424650964</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.1682346121189577</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1649999830457899</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.0923817308130758</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0195559090761658</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>-0.0407844352132465</v>
+      <c r="J11" s="23" t="n">
+        <v>0.0177258200355405</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0147321564810616</v>
       </c>
     </row>
     <row r="12">
@@ -2220,16 +2226,16 @@
         </is>
       </c>
       <c r="E12" s="21" t="n">
-        <v>-0.05223477171594</v>
+        <v>-0.0433369433125259</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>-0.1269841534150092</v>
+        <v>-0.1178820739484221</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.2280701754385965</v>
+        <v>-0.2288209340457833</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>0.1147200583660179</v>
+        <v>0.1220935892741679</v>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
@@ -2237,10 +2243,10 @@
         </is>
       </c>
       <c r="J12" s="21" t="n">
-        <v>0.0154897728507844</v>
+        <v>0.0154917671238364</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>-0.0081012994825111</v>
+        <v>-0.0062980681240358</v>
       </c>
     </row>
     <row r="13">
@@ -2249,12 +2255,12 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D13" s="22" t="inlineStr">
@@ -2263,27 +2269,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0112359743198956</v>
+        <v>0.0078451679888256</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0838635078765889</v>
+        <v>-0.0441467954555905</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-0.2399232315948906</v>
+        <v>0.3991414894421425</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>0.06020283289409</v>
+        <v>-0.0103715283441999</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0185181572285961</v>
+        <v>0.026607966568499</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.1100915926663814</v>
+        <v>0.0133234131632889</v>
       </c>
     </row>
     <row r="14">
@@ -2292,7 +2298,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2306,27 +2312,27 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0094290363403365</v>
+        <v>-0.001272245242524</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0530795945112292</v>
+        <v>-0.0909090748446709</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>0.3799221550939602</v>
+        <v>-0.2495219775799371</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.001299222641399</v>
+        <v>0.0522758997052235</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0265228853995872</v>
+        <v>0.018542999701104</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0176862670340702</v>
+        <v>0.0417062635931273</v>
       </c>
     </row>
     <row r="15">
@@ -2335,7 +2341,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -2349,27 +2355,27 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0271580549350454</v>
+        <v>0.0060011244304098</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.09148549216055531</v>
+        <v>-0.089382689676167</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.0555554996800969</v>
+        <v>0.08343125958296981</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.2348899595529274</v>
+        <v>0.0853144102173872</v>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0205324632618941</v>
+        <v>0.0262474305020953</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0243974981951412</v>
+        <v>0.06530449138086419</v>
       </c>
     </row>
     <row r="16">
@@ -2378,7 +2384,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -2392,27 +2398,27 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>0.0057692713286059</v>
+        <v>-0.0132231404958678</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>0.07502574822761621</v>
+        <v>-0.091324200913242</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>0.070076772004999</v>
+        <v>0.0135823429541594</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>0.2082752826227347</v>
+        <v>-0.0004730378106675</v>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0354202149778968</v>
+        <v>0.0194917722383952</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.0209345019135112</v>
+        <v>0.0198183071616275</v>
       </c>
     </row>
     <row r="17">
@@ -2421,84 +2427,84 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.0185004279741304</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.0877827778121465</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.0614524988859592</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.2138724393593791</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.020545994466986</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0243974981951412</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>0.0234445446348061</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.1678885630498533</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.0271493212669682</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.040773702629152</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="27" t="n">
+        <v>0.0145454545454546</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.1684053651266766</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>0.0017953321364452</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.034316998413657</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0235347716646357</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.0017867096296519</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>0.0065716829343169</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.1395131724921759</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.1025794287130454</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>0.08379698040637</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0270089725946684</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0423503831348128</v>
+      <c r="J18" s="27" t="n">
+        <v>0.0235405450267687</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>-0.0045871559633027</v>
       </c>
     </row>
     <row r="19">
@@ -2521,27 +2527,27 @@
         </is>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.06316447779862409</v>
+        <v>-0.0551083591331269</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.0190476190476189</v>
+        <v>0.0214190093708166</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0639204545454545</v>
+        <v>0.1303703703703704</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>-0.1380445118492993</v>
+        <v>-0.1528604550965118</v>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.029683957187403</v>
+        <v>0.0297054862017969</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.0478183090941359</v>
+        <v>0.072342689966194</v>
       </c>
     </row>
     <row r="20">
@@ -2564,16 +2570,16 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>0.0130849678184128</v>
+        <v>0.0176322606923704</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.1073170801849392</v>
+        <v>-0.08679927682862081</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1403193322556694</v>
+        <v>-0.132207907902396</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.3909598574876443</v>
+        <v>0.3786655443862086</v>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
@@ -2581,10 +2587,10 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0269999400224776</v>
+        <v>0.0269118107415914</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0339372324271623</v>
+        <v>0.0679939152051368</v>
       </c>
     </row>
   </sheetData>
@@ -2609,7 +2615,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2617,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2654,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>TUPRS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>ARCLK.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, SAHOL.IS, FROTO.IS, EREGL.IS, TCELL.IS, PETKM.IS, TOASO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>SAHOL.IS, AKBNK.IS, PGSUS.IS, EREGL.IS, FROTO.IS, YKBNK.IS, THYAO.IS, TCELL.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2690,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.60 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2728,7 +2734,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2736,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2979,7 +2985,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2987,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3011,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>13251.900390625</v>
+        <v>12888.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3021,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13523.44052246094</v>
+        <v>13532.69802246094</v>
       </c>
     </row>
     <row r="6">
@@ -3055,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60.73</v>
+        <v>60.88</v>
       </c>
     </row>
     <row r="9">
@@ -3082,7 +3088,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3091,14 +3097,14 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-22</t>
+          <t>Rapor Tarihi: 2026-09-23</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3112,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-24 06:51</t>
+          <t>Son Güncelleme: 2026-09-25 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3176,23 +3182,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>374.5</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>-0.06257822277847314</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>-44085.09026903624</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D4" s="28" t="n">
+        <v>381.5</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>-0.04505632040050067</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>-31741.26499370614</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="5">
@@ -3206,23 +3212,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="26" t="n">
+      <c r="D5" s="28" t="n">
         <v>221.1000061035156</v>
       </c>
-      <c r="E5" s="27" t="n">
+      <c r="E5" s="29" t="n">
         <v>0.1223350563630234</v>
       </c>
-      <c r="F5" s="26" t="n">
+      <c r="F5" s="28" t="n">
         <v>355547.8475470669</v>
       </c>
-      <c r="G5" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="G5" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="6">
@@ -3236,23 +3242,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>91.15000152587891</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.05544039869555539</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-4868.469755423692</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D6" s="28" t="n">
+        <v>91.09999847412109</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.05595856503501462</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-4913.972262824274</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="7">
@@ -3266,23 +3272,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0.003748126108521266</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>18151.0558567429</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D7" s="28" t="n">
+        <v>133.8000030517578</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>0.002998569517055794</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>14521.17704115342</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="8">
@@ -3296,23 +3302,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="28" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>37.81999969482422</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.02676276117325405</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-5825.7525281001</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D8" s="28" t="n">
+        <v>38.54000091552734</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.008234680643287917</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-1792.535951920989</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="9">
@@ -3326,23 +3332,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="28" t="n">
         <v>405.5</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>430.25</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0.06103575832305785</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>173080.2172641489</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D9" s="28" t="n">
+        <v>433.75</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0.06966707768187419</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>197556.2075843317</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
     <row r="10">
@@ -3356,57 +3362,27 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="28" t="n">
         <v>417.25</v>
       </c>
-      <c r="D10" s="26" t="n">
-        <v>397</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>-0.04853205512282799</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>-221565.4769818028</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-0.0267294078143243</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C11" s="26" t="n">
-        <v>284.5</v>
-      </c>
-      <c r="D11" s="26" t="n">
-        <v>283.75</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>-0.002636203866432374</v>
-      </c>
-      <c r="F11" s="26" t="n">
-        <v>-12035.17480578739</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>20983825.15452364</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-0.0267294078143243</v>
+      <c r="D10" s="28" t="n">
+        <v>411</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.0149790293588975</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-68384.40647586435</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>21097961.1021083</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>-0.0329903392713806</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H11"/>
+  <autoFilter ref="A3:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -201,12 +201,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 60.88/100</t>
+          <t>Güven Puanı: 61.27/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>AL: BIMAS.IS, FROTO.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +755,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS, PETKM.IS</t>
+          <t>AZALT: TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: ARCLK.IS, TOASO.IS</t>
+          <t>ÇIK: PETKM.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -964,29 +958,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2305860355400591</v>
+        <v>0.2262039331984107</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23058.60355400591</v>
+        <v>22620.39331984107</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485933057984229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>901.0726686962445</v>
+        <v>1099.19968987164</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>450.6998672862649</v>
+        <v>443.2928200262833</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>412.0625</v>
+        <v>401.6125</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7815500766001116</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.9718661159684552</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -998,7 +992,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,29 +1001,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1976750945659504</v>
+        <v>0.1899558085524913</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19767.50945659503</v>
+        <v>18995.58085524913</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0288506858218793</v>
+        <v>0.0955196579070878</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>570.3062048132514</v>
+        <v>1814.451385039823</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>227.4788929148237</v>
+        <v>84.79322319363894</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>210.0450057983398</v>
+        <v>73.53000144958496</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5770137164375856</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>1.910393158141756</v>
+      </c>
+      <c r="K21" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1039,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,25 +1042,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1717388698939905</v>
+        <v>0.183840258249098</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17173.88698939905</v>
+        <v>18384.0258249098</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0426715939840771</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>732.8371327400604</v>
+        <v>427.7609667454678</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>139.5094624570507</v>
+        <v>221.0259050817818</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>127.1100028991699</v>
+        <v>205.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8534318796815435</v>
+        <v>0.4653615816464586</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1121,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1201,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,36 +1353,36 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>433.75</v>
+        <v>422.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205582539340234</v>
+        <v>-0.0340045699699408</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485933057984229</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0814229535541966</v>
+        <v>0.0801730736352934</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>424.8328573561174</v>
+        <v>408.3745680452075</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>450.6998672862649</v>
+        <v>443.2928200262833</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>469.0672061041328</v>
+        <v>456.6431668793203</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>412.0625</v>
+        <v>401.6125</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>60.88</v>
+        <v>61.27</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1416,28 +1410,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>221.1000061035156</v>
+        <v>216</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0120989247979147</v>
+        <v>-0.0120987386157355</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0288506858218793</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>0.0914169657590902</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>218.4249337568507</v>
+        <v>213.3866724590011</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>227.4788929148237</v>
+        <v>221.0259050817818</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>241.3122977908153</v>
+        <v>235.7460646039635</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>210.0450057983398</v>
+        <v>205.2</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1445,7 +1439,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>60.88</v>
+        <v>61.27</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1473,28 +1467,28 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>411</v>
+        <v>410.75</v>
       </c>
       <c r="E10" s="18" t="n">
         <v>-0.08640226646425481</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.0231982012942197</v>
+        <v>0.0228858964847257</v>
       </c>
       <c r="G10" s="18" t="n">
         <v>0.1262861266103623</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>375.4886684831913</v>
+        <v>375.2602690498073</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>420.5344607319244</v>
+        <v>420.150381981101</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>462.9035980368589</v>
+        <v>462.6220265052063</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>375.4886684831913</v>
+        <v>375.2602690498073</v>
       </c>
       <c r="L10" s="16" t="inlineStr">
         <is>
@@ -1502,7 +1496,7 @@
         </is>
       </c>
       <c r="M10" s="16" t="n">
-        <v>60.88</v>
+        <v>61.27</v>
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
@@ -1516,116 +1510,116 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>22</v>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0753137768113169</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.0031957788743339</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>0.0729092547856522</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>20.34309691015103</v>
+      </c>
+      <c r="I11" s="20" t="n">
+        <v>21.92969286476465</v>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>23.60400360528435</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>20.33187462275656</v>
+      </c>
+      <c r="L11" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="19" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="N11" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="19" t="inlineStr">
+        <is>
+          <t>volatilite yüksek; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
-        <v>133.8000030517578</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.021913693588956</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0426715939840771</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.0899376920918622</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>130.8679507826802</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>139.5094624570507</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>145.833666528117</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>127.1100028991699</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0538957289245235</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.0729092547856522</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>21.76039823473596</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>23</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>24.67691286007</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>21.27623771492112</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="D12" s="14" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="E12" s="15" t="n">
+        <v>-0.0181830798692272</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.0955196579070878</v>
+      </c>
+      <c r="G12" s="15" t="n">
+        <v>0.1388396415680386</v>
+      </c>
+      <c r="H12" s="14" t="n">
+        <v>75.99263111625554</v>
+      </c>
+      <c r="I12" s="14" t="n">
+        <v>84.79322319363894</v>
+      </c>
+      <c r="J12" s="14" t="n">
+        <v>88.14618999509757</v>
+      </c>
+      <c r="K12" s="14" t="n">
+        <v>73.53000144958496</v>
+      </c>
+      <c r="L12" s="13" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>61.27</v>
+      </c>
+      <c r="N12" s="13" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1644,28 +1638,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>88.30000305175781</v>
+        <v>86.44999694824219</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0434165016624163</v>
+        <v>-0.0445633254802306</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>-0.0062980681240358</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.1080537552156288</v>
+        <v>0.1019455727900049</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>84.46632582246981</v>
+        <v>82.59749759647273</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>87.74388361718528</v>
+        <v>85.90552897813947</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>97.84114996705173</v>
+        <v>95.26319140482492</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>83.88500289916992</v>
+        <v>82.12749710083007</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1673,7 +1667,7 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>60.88</v>
+        <v>61.27</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
@@ -1686,65 +1680,8 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>279</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.0712638969807638</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.0045871559633027</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.0517095609237237</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>259.1173727423669</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>277.7201834862386</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>293.4269674977189</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>259.1173727423669</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>60.88</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1774,7 +1711,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,16 +1819,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0452072398356422</v>
+        <v>0.016873765489102</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1621145514924089</v>
+        <v>0.1356674764285825</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.3084170653041249</v>
+        <v>0.2629915565469924</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0433607340298419</v>
+        <v>-0.06364895643760821</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1899,10 +1836,10 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0190627202731149</v>
+        <v>0.019375046925623</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0485933057984229</v>
       </c>
     </row>
     <row r="5">
@@ -1916,7 +1853,7 @@
       </c>
       <c r="C5" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D5" s="13" t="inlineStr">
@@ -1925,16 +1862,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0165517522000717</v>
+        <v>0.008403375711498001</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.13442797859166</v>
+        <v>0.0898082912504085</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.184252864046966</v>
+        <v>0.1410459404004445</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>0.1888845473075688</v>
+        <v>0.1513062493220087</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1942,10 +1879,10 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0207442689180219</v>
+        <v>0.0208981225974997</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0288506858218793</v>
+        <v>0.0232680790823229</v>
       </c>
     </row>
     <row r="6">
@@ -1968,16 +1905,16 @@
         </is>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.09966555183946491</v>
+        <v>0.08092105263157889</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.8750000261042243</v>
+        <v>0.8738595151394408</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.6407185628742516</v>
+        <v>0.7100333273047776</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.0394621596645399</v>
+        <v>0.0057801718763421</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -1985,96 +1922,96 @@
         </is>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0.0270096076422816</v>
+        <v>0.0270134881240675</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0.0231982012942197</v>
+        <v>0.0228858964847257</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="19" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D7" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="21" t="n">
+        <v>0.088031688778045</v>
+      </c>
+      <c r="F7" s="21" t="n">
+        <v>0.1235955099960948</v>
+      </c>
+      <c r="G7" s="21" t="n">
+        <v>0.1476264951717811</v>
+      </c>
+      <c r="H7" s="21" t="n">
+        <v>0.2149767695184756</v>
+      </c>
+      <c r="I7" s="19" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="21" t="n">
+        <v>0.0379119403918964</v>
+      </c>
+      <c r="K7" s="21" t="n">
+        <v>-0.0031957788743339</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.009049750324335601</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>-0.0276163000232652</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.06753831282353449</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>0.1342455507592934</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0210010558001496</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0426715939840771</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.1657374826980371</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0.1904762092807717</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.2086179280140792</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>0.2042774020708375</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0374730931538888</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>0</v>
+      <c r="E8" s="15" t="n">
+        <v>-0.0270270451715765</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>-0.1026086779608242</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>-0.2463485508681537</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>0.0294478279074266</v>
+      </c>
+      <c r="I8" s="13" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>0.0186115303364237</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>0.0955196579070878</v>
       </c>
     </row>
     <row r="9">
@@ -2083,7 +2020,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2097,16 +2034,16 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0256684655174214</v>
+        <v>-0.0196382977066572</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.0608247579987516</v>
+        <v>-0.09924027566894179</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.015508268706688</v>
+        <v>0.4295862429600472</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>0.0413454148343286</v>
+        <v>-0.0463635917944209</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
@@ -2114,10 +2051,10 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0198694016645619</v>
+        <v>0.0260406298593469</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.0588821519160343</v>
+        <v>0.012842734528077</v>
       </c>
     </row>
     <row r="10">
@@ -2126,7 +2063,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2140,27 +2077,27 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>0.0131944020589191</v>
+        <v>-0.0292573823404875</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0550518156477306</v>
+        <v>-0.0650289046019142</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0618910067400306</v>
+        <v>0.0625823294254592</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>0.2344056756352319</v>
+        <v>0.07447914883926041</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.024327823690841</v>
+        <v>0.0213838784267614</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.0153096520178395</v>
+        <v>0.01715475009491</v>
       </c>
     </row>
     <row r="11">
@@ -2169,7 +2106,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -2183,27 +2120,27 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>0.001332424650964</v>
+        <v>-0.034176349252919</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>-0.1682346121189577</v>
+        <v>-0.0854368734514057</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-0.1649999830457899</v>
+        <v>0.050557643507493</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>0.0923817308130758</v>
+        <v>0.1951579618097842</v>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0177258200355405</v>
+        <v>0.0246367814914132</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>0.0147321564810616</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
@@ -2226,16 +2163,16 @@
         </is>
       </c>
       <c r="E12" s="21" t="n">
-        <v>-0.0433369433125259</v>
+        <v>-0.07391538980894299</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>-0.1178820739484221</v>
+        <v>-0.1695485281901001</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.2288209340457833</v>
+        <v>-0.2232704889680877</v>
       </c>
       <c r="H12" s="21" t="n">
-        <v>0.1220935892741679</v>
+        <v>0.1048848031430502</v>
       </c>
       <c r="I12" s="19" t="inlineStr">
         <is>
@@ -2243,7 +2180,7 @@
         </is>
       </c>
       <c r="J12" s="21" t="n">
-        <v>0.0154917671238364</v>
+        <v>0.0147205548238683</v>
       </c>
       <c r="K12" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -2255,7 +2192,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2269,27 +2206,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>0.0078451679888256</v>
+        <v>-0.0612027694175202</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0441467954555905</v>
+        <v>-0.09492047500948481</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>0.3991414894421425</v>
+        <v>-0.0037021562789459</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.0103715283441999</v>
+        <v>0.0172722110388683</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.026607966568499</v>
+        <v>0.0202362846087154</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0133234131632889</v>
+        <v>0.0444883459564572</v>
       </c>
     </row>
     <row r="14">
@@ -2298,7 +2235,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2312,16 +2249,16 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.001272245242524</v>
+        <v>-0.0495760336087512</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.0909090748446709</v>
+        <v>-0.1910050415850703</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.2495219775799371</v>
+        <v>-0.1796171624942414</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.0522758997052235</v>
+        <v>0.0408610500281017</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
@@ -2329,10 +2266,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.018542999701104</v>
+        <v>0.0180696158519192</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0417062635931273</v>
+        <v>0.0290598638376957</v>
       </c>
     </row>
     <row r="15">
@@ -2341,7 +2278,7 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C15" s="24" t="inlineStr">
@@ -2355,27 +2292,27 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>0.0060011244304098</v>
+        <v>-0.0391304642681914</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.089382689676167</v>
+        <v>-0.1032462075752526</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>0.08343125958296981</v>
+        <v>-0.0617924816203567</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.0853144102173872</v>
+        <v>0.1755718149091731</v>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0262474305020953</v>
+        <v>0.0205927546794307</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.06530449138086419</v>
+        <v>0.0138761110298257</v>
       </c>
     </row>
     <row r="16">
@@ -2384,7 +2321,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -2398,27 +2335,27 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.0132231404958678</v>
+        <v>0.0154405086285194</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.091324200913242</v>
+        <v>-0.14</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>0.0135823429541594</v>
+        <v>0.0256880733944953</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>-0.0004730378106675</v>
+        <v>-0.038674221596768</v>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0194917722383952</v>
+        <v>0.0232585633457884</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.0198183071616275</v>
+        <v>0.0218373705587808</v>
       </c>
     </row>
     <row r="17">
@@ -2427,7 +2364,7 @@
       </c>
       <c r="B17" s="24" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C17" s="24" t="inlineStr">
@@ -2441,16 +2378,16 @@
         </is>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.0185004279741304</v>
+        <v>-0.0648298217179902</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>-0.0877827778121465</v>
+        <v>-0.127739984882842</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>-0.0614524988859592</v>
+        <v>-0.0170357751277683</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>0.2138724393593791</v>
+        <v>-0.0373764328753959</v>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
@@ -2458,53 +2395,53 @@
         </is>
       </c>
       <c r="J17" s="25" t="n">
-        <v>0.020545994466986</v>
+        <v>0.0198777168655203</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.0243974981951412</v>
+        <v>0.0383031418515351</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="26" t="n">
+      <c r="A18" s="24" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>0.0145454545454546</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.1684053651266766</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>0.0017953321364452</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.034316998413657</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0372168554468483</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.1219871889593315</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0759493801864303</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0.0510324769608887</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0235405450267687</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>-0.0045871559633027</v>
+      <c r="J18" s="25" t="n">
+        <v>0.0265240406867316</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0505952630994552</v>
       </c>
     </row>
     <row r="19">
@@ -2527,27 +2464,27 @@
         </is>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0551083591331269</v>
+        <v>-0.0765850596359071</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.0214190093708166</v>
+        <v>0.0172890733056707</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.1303703703703704</v>
+        <v>0.0880177514792899</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>-0.1528604550965118</v>
+        <v>-0.1618223652309838</v>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0297054862017969</v>
+        <v>0.0297793875768886</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.072342689966194</v>
+        <v>0.1070430290873052</v>
       </c>
     </row>
     <row r="20">
@@ -2570,16 +2507,16 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>0.0176322606923704</v>
+        <v>-0.0273360398343868</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.08679927682862081</v>
+        <v>-0.136363644015681</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.132207907902396</v>
+        <v>-0.1251391122396601</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.3786655443862086</v>
+        <v>0.3618103710149756</v>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
@@ -2587,10 +2524,10 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0269118107415914</v>
+        <v>0.0269738111759092</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0679939152051368</v>
+        <v>0.0303867688593402</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2552,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2623,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2648,7 +2585,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2597,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, PETKM.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2609,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ARCLK.IS, TOASO.IS</t>
+          <t>PETKM.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2621,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, AKBNK.IS, PGSUS.IS, EREGL.IS, FROTO.IS, YKBNK.IS, THYAO.IS, TCELL.IS, ASELS.IS, SISE.IS</t>
+          <t>EREGL.IS, GARAN.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TCELL.IS, TOASO.IS, THYAO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2633,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.89 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2671,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2742,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2827,7 +2764,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2776,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2922,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2993,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3017,7 +2954,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12888.2998046875</v>
+        <v>12899.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3027,7 +2964,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13532.69802246094</v>
+        <v>13553.55952148437</v>
       </c>
     </row>
     <row r="6">
@@ -3061,7 +2998,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>60.88</v>
+        <v>61.27</v>
       </c>
     </row>
     <row r="9">
@@ -3088,23 +3025,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-23</t>
+          <t>Rapor Tarihi: 2026-09-24</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3118,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-25 06:46</t>
+          <t>Son Güncelleme: 2026-09-26 06:45</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3182,23 +3119,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="26" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>381.5</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>-0.04505632040050067</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>-31741.26499370614</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D4" s="26" t="n">
+        <v>367.75</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>-0.07947434292866085</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>-55988.06464167603</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="5">
@@ -3212,23 +3149,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>221.1000061035156</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.1223350563630234</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>355547.8475470669</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D5" s="26" t="n">
+        <v>216</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>0.09644670050761417</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>280307.3606860545</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="6">
@@ -3242,23 +3179,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>91.09999847412109</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.05595856503501462</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-4913.972262824274</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D6" s="26" t="n">
+        <v>88.19999694824219</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.08601039431873381</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-7552.958009776936</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="7">
@@ -3272,23 +3209,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="26" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>133.8000030517578</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>0.002998569517055794</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>14521.17704115342</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D7" s="26" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.02998500886817068</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-145208.4468539497</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="8">
@@ -3302,23 +3239,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="26" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>38.54000091552734</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.008234680643287917</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-1792.535951920989</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D8" s="26" t="n">
+        <v>37.93999862670898</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.02367478047330518</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-5153.556888308289</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="9">
@@ -3332,23 +3269,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="26" t="n">
         <v>405.5</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>433.75</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0.06966707768187419</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>197556.2075843317</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D9" s="26" t="n">
+        <v>422.75</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>0.04254007398273729</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>120631.6665780433</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
     <row r="10">
@@ -3362,27 +3299,57 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="26" t="n">
         <v>417.25</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>411</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.0149790293588975</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-68384.40647586435</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>21097961.1021083</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>-0.0329903392713806</v>
+      <c r="D10" s="26" t="n">
+        <v>410.75</v>
+      </c>
+      <c r="E10" s="27" t="n">
+        <v>-0.01557819053325349</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>-71119.78273489885</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H10" s="27" t="n">
+        <v>-0.0595227813275321</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C11" s="26" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="D11" s="26" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="E11" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" s="26" t="n">
+        <v>20753084.26775555</v>
+      </c>
+      <c r="H11" s="27" t="n">
+        <v>-0.0595227813275321</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H10"/>
+  <autoFilter ref="A3:H11"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -958,16 +958,16 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2262039331984107</v>
+        <v>0.2262039331984106</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22620.39331984107</v>
+        <v>22620.39331984106</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1099.19968987164</v>
+        <v>1099.199689871639</v>
       </c>
       <c r="H20" s="8" t="n">
         <v>443.2928200262833</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1899558085524913</v>
+        <v>0.1899558085524912</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18995.58085524913</v>
+        <v>18995.58085524912</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0955196579070878</v>
@@ -1042,16 +1042,16 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.183840258249098</v>
+        <v>0.1838402582490981</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18384.0258249098</v>
+        <v>18384.02582490982</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>427.7609667454678</v>
+        <v>427.7609667454736</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>221.0259050817818</v>
@@ -1060,7 +1060,7 @@
         <v>205.2</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4653615816464586</v>
+        <v>0.4653615816464639</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1356,13 +1356,13 @@
         <v>422.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0340045699699408</v>
+        <v>-0.0340045699699409</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0485933057984229</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0801730736352934</v>
+        <v>0.0801730736352933</v>
       </c>
       <c r="H8" s="14" t="n">
         <v>408.3745680452075</v>
@@ -1371,7 +1371,7 @@
         <v>443.2928200262833</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>456.6431668793203</v>
+        <v>456.6431668793202</v>
       </c>
       <c r="K8" s="14" t="n">
         <v>401.6125</v>
@@ -1416,7 +1416,7 @@
         <v>-0.0120987386157355</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="15" t="n">
         <v>0.0914169657590902</v>
@@ -1470,7 +1470,7 @@
         <v>410.75</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-0.08640226646425481</v>
+        <v>-0.0864022664642549</v>
       </c>
       <c r="F10" s="18" t="n">
         <v>0.0228858964847257</v>
@@ -1527,7 +1527,7 @@
         <v>22</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>-0.0753137768113169</v>
+        <v>-0.075313776811317</v>
       </c>
       <c r="F11" s="21" t="n">
         <v>-0.0031957788743339</v>
@@ -1641,7 +1641,7 @@
         <v>86.44999694824219</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0445633254802306</v>
+        <v>-0.0445633254802305</v>
       </c>
       <c r="F13" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,7 +1882,7 @@
         <v>0.0208981225974997</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1948,7 +1948,7 @@
         </is>
       </c>
       <c r="E7" s="21" t="n">
-        <v>0.088031688778045</v>
+        <v>0.08803168877804519</v>
       </c>
       <c r="F7" s="21" t="n">
         <v>0.1235955099960948</v>
@@ -1997,7 +1997,7 @@
         <v>-0.1026086779608242</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.2463485508681537</v>
+        <v>-0.2463485508681538</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>0.0294478279074266</v>
@@ -2008,7 +2008,7 @@
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.0186115303364237</v>
+        <v>0.0186115303364236</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>0.0955196579070878</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0196382977066572</v>
+        <v>-0.0196382977066574</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.09924027566894179</v>
+        <v>-0.099240275668942</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.4295862429600472</v>
+        <v>0.429586242960047</v>
       </c>
       <c r="H9" s="23" t="n">
         <v>-0.0463635917944209</v>
@@ -2051,7 +2051,7 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0260406298593469</v>
+        <v>0.026040629859347</v>
       </c>
       <c r="K9" s="23" t="n">
         <v>0.012842734528077</v>
@@ -2094,7 +2094,7 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0213838784267614</v>
+        <v>0.0213838784267613</v>
       </c>
       <c r="K10" s="23" t="n">
         <v>0.01715475009491</v>
@@ -2137,7 +2137,7 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0246367814914132</v>
+        <v>0.0246367814914131</v>
       </c>
       <c r="K11" s="23" t="n">
         <v>0</v>
@@ -2169,7 +2169,7 @@
         <v>-0.1695485281901001</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>-0.2232704889680877</v>
+        <v>-0.2232704889680876</v>
       </c>
       <c r="H12" s="21" t="n">
         <v>0.1048848031430502</v>
@@ -2180,7 +2180,7 @@
         </is>
       </c>
       <c r="J12" s="21" t="n">
-        <v>0.0147205548238683</v>
+        <v>0.0147205548238684</v>
       </c>
       <c r="K12" s="21" t="n">
         <v>-0.0062980681240358</v>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0612027694175202</v>
+        <v>-0.0612027694175204</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.09492047500948481</v>
+        <v>-0.0949204750094849</v>
       </c>
       <c r="G13" s="23" t="n">
         <v>-0.0037021562789459</v>
@@ -2226,7 +2226,7 @@
         <v>0.0202362846087154</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0444883459564572</v>
+        <v>0.0444883459564573</v>
       </c>
     </row>
     <row r="14">
@@ -2292,13 +2292,13 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0391304642681914</v>
+        <v>-0.0391304642681913</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.1032462075752526</v>
+        <v>-0.1032462075752523</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.0617924816203567</v>
+        <v>-0.0617924816203565</v>
       </c>
       <c r="H15" s="25" t="n">
         <v>0.1755718149091731</v>
@@ -2312,7 +2312,7 @@
         <v>0.0205927546794307</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0138761110298257</v>
+        <v>0.0138761110298255</v>
       </c>
     </row>
     <row r="16">
@@ -2352,7 +2352,7 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0232585633457884</v>
+        <v>0.0232585633457885</v>
       </c>
       <c r="K16" s="25" t="n">
         <v>0.0218373705587808</v>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-26 06:45</t>
+          <t>Son Güncelleme: 2026-09-27 07:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3246,10 +3246,10 @@
         <v>37.93999862670898</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>-0.02367478047330518</v>
+        <v>-0.0236747804733054</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>-5153.556888308289</v>
+        <v>-5153.556888308318</v>
       </c>
       <c r="G8" s="26" t="n">
         <v>20753084.26775555</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-27 07:14</t>
+          <t>Son Güncelleme: 2026-09-28 07:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -610,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 61.27/100</t>
+          <t>Güven Puanı: 66.10/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -738,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, FROTO.IS, KCHOL.IS</t>
+          <t>AL: BIMAS.IS, TOASO.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -755,7 +755,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS</t>
+          <t>AZALT: KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -772,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PETKM.IS, ARCLK.IS</t>
+          <t>ÇIK: ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,29 +958,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2262039331984106</v>
+        <v>0.2395979348997341</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22620.39331984106</v>
+        <v>23959.79348997341</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0232721257482955</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1099.199689871639</v>
+        <v>557.5953270018532</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>443.2928200262833</v>
+        <v>434.6348354115885</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>401.6125</v>
+        <v>403.5125</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9718661159684552</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.465442514965911</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -992,7 +992,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1001,29 +1001,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1899558085524912</v>
+        <v>0.182910266005868</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18995.58085524912</v>
+        <v>18291.0266005868</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0955196579070878</v>
+        <v>0.0440718553247694</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1814.451385039823</v>
+        <v>806.1194780825703</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>84.79322319363894</v>
+        <v>302.7808380441832</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>73.53000144958496</v>
+        <v>265.8793125755992</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.910393158141756</v>
-      </c>
-      <c r="K21" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.5298703896495865</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1033,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1042,25 +1042,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1838402582490981</v>
+        <v>0.1774917990943978</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18384.02582490982</v>
+        <v>17749.17990943978</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0232680790823232</v>
+        <v>0.0436874311853043</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>427.7609667454736</v>
+        <v>775.4160758892361</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>221.0259050817818</v>
+        <v>80.15519790011265</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>205.2</v>
+        <v>72.96000289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.4653615816464639</v>
+        <v>0.8737486237060891</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,36 +1353,36 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>422.75</v>
+        <v>424.75</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0340045699699409</v>
+        <v>-0.031423347761997</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0232721257482955</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0801730736352933</v>
+        <v>0.0814231940286049</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>408.3745680452075</v>
+        <v>411.4029330380918</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>443.2928200262833</v>
+        <v>434.6348354115885</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>456.6431668793202</v>
+        <v>459.33450166365</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>401.6125</v>
+        <v>403.5125</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>61.27</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1396,59 +1396,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>216</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0120987386157355</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0232680790823232</v>
-      </c>
-      <c r="G9" s="15" t="n">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>216.5</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0674846665340597</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0185277170790933</v>
+      </c>
+      <c r="G9" s="18" t="n">
         <v>0.0914169657590902</v>
       </c>
-      <c r="H9" s="14" t="n">
-        <v>213.3866724590011</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>221.0259050817818</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>235.7460646039635</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>205.2</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="H9" s="17" t="n">
+        <v>201.8895696953761</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>220.5112507476237</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>236.291773086843</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>201.8895696953761</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="13" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="M9" s="16" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1467,28 +1467,28 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>410.75</v>
+        <v>406</v>
       </c>
       <c r="E10" s="18" t="n">
-        <v>-0.0864022664642549</v>
+        <v>-0.08576801418596321</v>
       </c>
       <c r="F10" s="18" t="n">
-        <v>0.0228858964847257</v>
+        <v>0.0195381889719499</v>
       </c>
       <c r="G10" s="18" t="n">
-        <v>0.1262861266103623</v>
+        <v>0.1467398346446296</v>
       </c>
       <c r="H10" s="17" t="n">
-        <v>375.2602690498073</v>
+        <v>371.1781862404989</v>
       </c>
       <c r="I10" s="17" t="n">
-        <v>420.150381981101</v>
+        <v>413.9325047226117</v>
       </c>
       <c r="J10" s="17" t="n">
-        <v>462.6220265052063</v>
+        <v>465.5763728657196</v>
       </c>
       <c r="K10" s="17" t="n">
-        <v>375.2602690498073</v>
+        <v>371.1781862404989</v>
       </c>
       <c r="L10" s="16" t="inlineStr">
         <is>
@@ -1496,7 +1496,7 @@
         </is>
       </c>
       <c r="M10" s="16" t="n">
-        <v>61.27</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N10" s="16" t="inlineStr">
         <is>
@@ -1510,59 +1510,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="19" t="n">
+      <c r="A11" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="n">
-        <v>22</v>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.075313776811317</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.0031957788743339</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>0.0729092547856522</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>20.34309691015103</v>
-      </c>
-      <c r="I11" s="20" t="n">
-        <v>21.92969286476465</v>
-      </c>
-      <c r="J11" s="20" t="n">
-        <v>23.60400360528435</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>20.33187462275656</v>
-      </c>
-      <c r="L11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="19" t="n">
-        <v>61.27</v>
-      </c>
-      <c r="N11" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="19" t="inlineStr">
-        <is>
-          <t>volatilite yüksek; alt bant riski belirgin</t>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>290</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.08317478422207179</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0440718553247694</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1217073782813475</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>265.8793125755992</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>302.7808380441832</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>325.2951397015908</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>265.8793125755992</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>66.09999999999999</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1581,36 +1581,36 @@
         </is>
       </c>
       <c r="D12" s="14" t="n">
-        <v>77.40000152587891</v>
+        <v>76.80000305175781</v>
       </c>
       <c r="E12" s="15" t="n">
-        <v>-0.0181830798692272</v>
+        <v>-0.0181828709961684</v>
       </c>
       <c r="F12" s="15" t="n">
-        <v>0.0955196579070878</v>
+        <v>0.0436874311853043</v>
       </c>
       <c r="G12" s="15" t="n">
         <v>0.1388396415680386</v>
       </c>
       <c r="H12" s="14" t="n">
-        <v>75.99263111625554</v>
+        <v>75.40355850376235</v>
       </c>
       <c r="I12" s="14" t="n">
-        <v>84.79322319363894</v>
+        <v>80.15519790011265</v>
       </c>
       <c r="J12" s="14" t="n">
-        <v>88.14618999509757</v>
+        <v>87.46288794788813</v>
       </c>
       <c r="K12" s="14" t="n">
-        <v>73.53000144958496</v>
+        <v>72.96000289916992</v>
       </c>
       <c r="L12" s="13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M12" s="13" t="n">
-        <v>61.27</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N12" s="13" t="inlineStr">
         <is>
@@ -1625,7 +1625,7 @@
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
@@ -1638,28 +1638,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>86.44999694824219</v>
+        <v>85.80000305175781</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0445633254802305</v>
+        <v>-0.0535024643406818</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0062980681240358</v>
+        <v>-0.0176822004387343</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.1019455727900049</v>
+        <v>0.1080537552156288</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>82.59749759647273</v>
+        <v>81.20949144805074</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>85.90552897813947</v>
+        <v>84.28287020015262</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>95.26319140482492</v>
+        <v>95.07101557901267</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>82.12749710083007</v>
+        <v>81.20949144805074</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1667,7 +1667,7 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>61.27</v>
+        <v>66.09999999999999</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
@@ -1676,7 +1676,7 @@
       </c>
       <c r="O13" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1711,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1728,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1819,16 +1819,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.016873765489102</v>
+        <v>0.0327965513213854</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1356674764285825</v>
+        <v>0.1518047346924724</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2629915565469924</v>
+        <v>0.2578190477481508</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.06364895643760821</v>
+        <v>-0.07205546430306629</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1836,53 +1836,53 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.019375046925623</v>
+        <v>0.01932078417901</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0485933057984229</v>
+        <v>0.0232721257482955</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>0.008403375711498001</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.0898082912504085</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.1410459404004445</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.1513062493220087</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>0.0107376427849041</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.1062851475529602</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.124091345478146</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.1356084928899614</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0208981225974997</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0232680790823232</v>
+      <c r="J5" s="18" t="n">
+        <v>0.0208190671400168</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0185277170790933</v>
       </c>
     </row>
     <row r="6">
@@ -1905,16 +1905,16 @@
         </is>
       </c>
       <c r="E6" s="18" t="n">
-        <v>0.08092105263157889</v>
+        <v>0.06631648063033491</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.8738595151394408</v>
+        <v>0.8513451634753439</v>
       </c>
       <c r="G6" s="18" t="n">
-        <v>0.7100333273047776</v>
+        <v>0.6881496881496882</v>
       </c>
       <c r="H6" s="18" t="n">
-        <v>0.0057801718763421</v>
+        <v>-0.0018603499106882</v>
       </c>
       <c r="I6" s="16" t="inlineStr">
         <is>
@@ -1922,53 +1922,53 @@
         </is>
       </c>
       <c r="J6" s="18" t="n">
-        <v>0.0270134881240675</v>
+        <v>0.0271268884677411</v>
       </c>
       <c r="K6" s="18" t="n">
-        <v>0.0228858964847257</v>
+        <v>0.0195381889719499</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="19" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="21" t="n">
-        <v>0.08803168877804519</v>
-      </c>
-      <c r="F7" s="21" t="n">
-        <v>0.1235955099960948</v>
-      </c>
-      <c r="G7" s="21" t="n">
-        <v>0.1476264951717811</v>
-      </c>
-      <c r="H7" s="21" t="n">
-        <v>0.2149767695184756</v>
-      </c>
-      <c r="I7" s="19" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0603290676416818</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>-0.0749601275917065</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.0366398570151922</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-0.0251433240548861</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="21" t="n">
-        <v>0.0379119403918964</v>
-      </c>
-      <c r="K7" s="21" t="n">
-        <v>-0.0031957788743339</v>
+      <c r="J7" s="15" t="n">
+        <v>0.0233916577859975</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0440718553247694</v>
       </c>
     </row>
     <row r="8">
@@ -1982,7 +1982,7 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D8" s="13" t="inlineStr">
@@ -1991,16 +1991,16 @@
         </is>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0270270451715765</v>
+        <v>-0.0210324277969439</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>-0.1026086779608242</v>
+        <v>-0.1012287209527198</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>-0.2463485508681538</v>
+        <v>-0.2601155992889228</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>0.0294478279074266</v>
+        <v>0.0229567002920754</v>
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
@@ -2008,10 +2008,10 @@
         </is>
       </c>
       <c r="J8" s="15" t="n">
-        <v>0.0186115303364236</v>
+        <v>0.0186023142151574</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>0.0955196579070878</v>
+        <v>0.0436874311853043</v>
       </c>
     </row>
     <row r="9">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2034,27 +2034,27 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0196382977066574</v>
+        <v>-0.0240601274303924</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.099240275668942</v>
+        <v>-0.0546249077443409</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.429586242960047</v>
+        <v>0.0675521339407823</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>-0.0463635917944209</v>
+        <v>0.0466086873881392</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.026040629859347</v>
+        <v>0.0213699592605512</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.012842734528077</v>
+        <v>0.0171547181631014</v>
       </c>
     </row>
     <row r="10">
@@ -2063,7 +2063,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2077,27 +2077,27 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>-0.0292573823404875</v>
+        <v>-0.0222797106127056</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0650289046019142</v>
+        <v>-0.08398055874758679</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0625823294254592</v>
+        <v>0.371080762650305</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>0.07447914883926041</v>
+        <v>-0.0635463784701541</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0213838784267613</v>
+        <v>0.0259133640359863</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.01715475009491</v>
+        <v>0.0245096604354778</v>
       </c>
     </row>
     <row r="11">
@@ -2106,127 +2106,127 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>0.0593561546775376</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>0.0968749285986054</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>0.0968749285986054</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>0.2248945580867938</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.038242188177953</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.002557432846991</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.034176349252919</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.0854368734514057</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0.050557643507493</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.1951579618097842</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="E12" s="23" t="n">
+        <v>-0.02676728880008</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.0816061615467036</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.0597907310727441</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>0.17897104086832</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0246367814914131</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0246437220862215</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.0111110916693351</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.07391538980894299</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.1695485281901001</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.2232704889680876</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>0.1048848031430502</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E13" s="21" t="n">
+        <v>-0.0867482082088227</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.1555117683036949</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>-0.223529384146988</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>0.1003856692808642</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0147205548238684</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>-0.0062980681240358</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>-0.0612027694175204</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-0.0949204750094849</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-0.0037021562789459</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>0.0172722110388683</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0202362846087154</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0444883459564573</v>
+      <c r="J13" s="21" t="n">
+        <v>0.0144825594088848</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>-0.0176822004387343</v>
       </c>
     </row>
     <row r="14">
@@ -2249,16 +2249,16 @@
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.0495760336087512</v>
+        <v>-0.0316831884604476</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.1910050415850703</v>
+        <v>-0.171654478303657</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.1796171624942414</v>
+        <v>-0.1711864579195356</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.0408610500281017</v>
+        <v>0.0216553996269717</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
@@ -2266,10 +2266,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0180696158519192</v>
+        <v>0.0180299757870784</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>0.0290598638376957</v>
+        <v>0.0063456596971369</v>
       </c>
     </row>
     <row r="15">
@@ -2292,16 +2292,16 @@
         </is>
       </c>
       <c r="E15" s="25" t="n">
-        <v>-0.0391304642681913</v>
+        <v>-0.0277237939582618</v>
       </c>
       <c r="F15" s="25" t="n">
-        <v>-0.1032462075752523</v>
+        <v>-0.0880474604035462</v>
       </c>
       <c r="G15" s="25" t="n">
-        <v>-0.0617924816203565</v>
+        <v>-0.0606203429054268</v>
       </c>
       <c r="H15" s="25" t="n">
-        <v>0.1755718149091731</v>
+        <v>0.1258996931118607</v>
       </c>
       <c r="I15" s="24" t="inlineStr">
         <is>
@@ -2309,10 +2309,10 @@
         </is>
       </c>
       <c r="J15" s="25" t="n">
-        <v>0.0205927546794307</v>
+        <v>0.0205669732511004</v>
       </c>
       <c r="K15" s="25" t="n">
-        <v>0.0138761110298255</v>
+        <v>0.0122719965535019</v>
       </c>
     </row>
     <row r="16">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B16" s="24" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C16" s="24" t="inlineStr">
@@ -2335,27 +2335,27 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>0.0154405086285194</v>
+        <v>-0.0586666666666666</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.14</v>
+        <v>-0.0948717948717948</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>0.0256880733944953</v>
+        <v>0.0063725333676007</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>-0.038674221596768</v>
+        <v>0.0099768134882742</v>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0232585633457885</v>
+        <v>0.0202363669454623</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.0218373705587808</v>
+        <v>0.0607735410264971</v>
       </c>
     </row>
     <row r="17">
@@ -2378,16 +2378,16 @@
         </is>
       </c>
       <c r="E17" s="25" t="n">
-        <v>-0.0648298217179902</v>
+        <v>-0.0537021969080553</v>
       </c>
       <c r="F17" s="25" t="n">
-        <v>-0.127739984882842</v>
+        <v>-0.1162613981762917</v>
       </c>
       <c r="G17" s="25" t="n">
-        <v>-0.0170357751277683</v>
+        <v>-0.0110544217687075</v>
       </c>
       <c r="H17" s="25" t="n">
-        <v>-0.0373764328753959</v>
+        <v>-0.0636907097647794</v>
       </c>
       <c r="I17" s="24" t="inlineStr">
         <is>
@@ -2395,10 +2395,10 @@
         </is>
       </c>
       <c r="J17" s="25" t="n">
-        <v>0.0198777168655203</v>
+        <v>0.019910855344003</v>
       </c>
       <c r="K17" s="25" t="n">
-        <v>0.0383031418515351</v>
+        <v>0.012312990332685</v>
       </c>
     </row>
     <row r="18">
@@ -2421,16 +2421,16 @@
         </is>
       </c>
       <c r="E18" s="25" t="n">
-        <v>-0.0372168554468483</v>
+        <v>-0.0293001034501172</v>
       </c>
       <c r="F18" s="25" t="n">
-        <v>-0.1219871889593315</v>
+        <v>-0.1072855003820407</v>
       </c>
       <c r="G18" s="25" t="n">
-        <v>0.0759493801864303</v>
+        <v>0.0783604113986555</v>
       </c>
       <c r="H18" s="25" t="n">
-        <v>0.0510324769608887</v>
+        <v>0.0269559867655238</v>
       </c>
       <c r="I18" s="24" t="inlineStr">
         <is>
@@ -2438,10 +2438,10 @@
         </is>
       </c>
       <c r="J18" s="25" t="n">
-        <v>0.0265240406867316</v>
+        <v>0.0264796048332912</v>
       </c>
       <c r="K18" s="25" t="n">
-        <v>0.0505952630994552</v>
+        <v>0.0492106566855715</v>
       </c>
     </row>
     <row r="19">
@@ -2464,16 +2464,16 @@
         </is>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0765850596359071</v>
+        <v>-0.0780185758513931</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.0172890733056707</v>
+        <v>0.0412587412587412</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>0.0880177514792899</v>
+        <v>0.1254724111866969</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>-0.1618223652309838</v>
+        <v>-0.1764974921360816</v>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0297793875768886</v>
+        <v>0.0297755297019779</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.1070430290873052</v>
+        <v>0.0657663918867637</v>
       </c>
     </row>
     <row r="20">
@@ -2507,16 +2507,16 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.0273360398343868</v>
+        <v>-0.019980000468739</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.136363644015681</v>
+        <v>-0.1268357170098918</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1251391122396601</v>
+        <v>-0.114304907742561</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.3618103710149756</v>
+        <v>0.3663174846425323</v>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
@@ -2524,10 +2524,10 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.0269738111759092</v>
+        <v>0.0269670382266868</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0303867688593402</v>
+        <v>0.0328525399081489</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2552,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2560,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2585,7 +2585,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
+          <t>BIMAS.IS, TOASO.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2597,7 +2597,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2609,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PETKM.IS, ARCLK.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, GARAN.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TCELL.IS, TOASO.IS, THYAO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>GARAN.IS, EREGL.IS, PETKM.IS, AKBNK.IS, PGSUS.IS, TCELL.IS, SAHOL.IS, THYAO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2671,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2872,7 +2872,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2922,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2930,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12899.400390625</v>
+        <v>12592.7998046875</v>
       </c>
     </row>
     <row r="5">
@@ -2964,7 +2964,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13553.55952148437</v>
+        <v>13560.57602050781</v>
       </c>
     </row>
     <row r="6">
@@ -2998,7 +2998,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>61.27</v>
+        <v>66.09999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3032,16 +3032,16 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-24</t>
+          <t>Rapor Tarihi: 2026-09-25</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3055,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-28 07:50</t>
+          <t>Son Güncelleme: 2026-09-29 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3123,19 +3123,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="26" t="n">
-        <v>367.75</v>
+        <v>372.25</v>
       </c>
       <c r="E4" s="27" t="n">
-        <v>-0.07947434292866085</v>
+        <v>-0.06821026282853571</v>
       </c>
       <c r="F4" s="26" t="n">
-        <v>-55988.06464167603</v>
+        <v>-48052.74839324958</v>
       </c>
       <c r="G4" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H4" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="5">
@@ -3153,19 +3153,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="26" t="n">
-        <v>216</v>
+        <v>216.5</v>
       </c>
       <c r="E5" s="27" t="n">
-        <v>0.09644670050761417</v>
+        <v>0.09898477157360408</v>
       </c>
       <c r="F5" s="26" t="n">
-        <v>280307.3606860545</v>
+        <v>287683.8701777929</v>
       </c>
       <c r="G5" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H5" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="6">
@@ -3183,19 +3183,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="26" t="n">
-        <v>88.19999694824219</v>
+        <v>88.25</v>
       </c>
       <c r="E6" s="27" t="n">
-        <v>-0.08601039431873381</v>
+        <v>-0.08549222797927458</v>
       </c>
       <c r="F6" s="26" t="n">
-        <v>-7552.958009776936</v>
+        <v>-7507.455502376353</v>
       </c>
       <c r="G6" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H6" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="7">
@@ -3213,19 +3213,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="26" t="n">
-        <v>129.3999938964844</v>
+        <v>129.8000030517578</v>
       </c>
       <c r="E7" s="27" t="n">
-        <v>-0.02998500886817068</v>
+        <v>-0.02698643935111478</v>
       </c>
       <c r="F7" s="26" t="n">
-        <v>-145208.4468539497</v>
+        <v>-130687.2698127953</v>
       </c>
       <c r="G7" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H7" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="8">
@@ -3243,19 +3243,19 @@
         <v>38.86000061035156</v>
       </c>
       <c r="D8" s="26" t="n">
-        <v>37.93999862670898</v>
+        <v>37.7400016784668</v>
       </c>
       <c r="E8" s="27" t="n">
-        <v>-0.0236747804733054</v>
+        <v>-0.02882138225150777</v>
       </c>
       <c r="F8" s="26" t="n">
-        <v>-5153.556888308318</v>
+        <v>-6273.875831723271</v>
       </c>
       <c r="G8" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H8" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="9">
@@ -3273,19 +3273,19 @@
         <v>405.5</v>
       </c>
       <c r="D9" s="26" t="n">
-        <v>422.75</v>
+        <v>424.75</v>
       </c>
       <c r="E9" s="27" t="n">
-        <v>0.04254007398273729</v>
+        <v>0.04747225647348952</v>
       </c>
       <c r="F9" s="26" t="n">
-        <v>120631.6665780433</v>
+        <v>134617.9467610051</v>
       </c>
       <c r="G9" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H9" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="10">
@@ -3303,19 +3303,19 @@
         <v>417.25</v>
       </c>
       <c r="D10" s="26" t="n">
-        <v>410.75</v>
+        <v>406</v>
       </c>
       <c r="E10" s="27" t="n">
-        <v>-0.01557819053325349</v>
+        <v>-0.02696225284601561</v>
       </c>
       <c r="F10" s="26" t="n">
-        <v>-71119.78273489885</v>
+        <v>-123091.9316565571</v>
       </c>
       <c r="G10" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H10" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
     <row r="11">
@@ -3333,19 +3333,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D11" s="26" t="n">
-        <v>77.40000152587891</v>
+        <v>76.80000305175781</v>
       </c>
       <c r="E11" s="27" t="n">
-        <v>0</v>
+        <v>-0.007751918117475554</v>
       </c>
       <c r="F11" s="26" t="n">
-        <v>0</v>
+        <v>-34705.99654011708</v>
       </c>
       <c r="G11" s="26" t="n">
-        <v>20753084.26775555</v>
+        <v>20709150.58882204</v>
       </c>
       <c r="H11" s="27" t="n">
-        <v>-0.0595227813275321</v>
+        <v>-0.05871275608399</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +158,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -610,7 +618,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +635,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +686,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 66.10/100</t>
+          <t>Güven Puanı: 70.51/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -738,7 +746,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, TOASO.IS, FROTO.IS</t>
+          <t>AL: BIMAS.IS, TOASO.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -772,7 +780,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: ARCLK.IS</t>
+          <t>ÇIK: AKBNK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,29 +966,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2395979348997341</v>
+        <v>0.258254054258822</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23959.79348997341</v>
+        <v>25825.4054258822</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232721257482955</v>
+        <v>0.048593625281839</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>557.5953270018532</v>
+        <v>1254.950074016891</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>434.6348354115885</v>
+        <v>447.2251811827044</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>403.5125</v>
+        <v>405.175</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.465442514965911</v>
-      </c>
-      <c r="K20" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.9718725056367798</v>
+      </c>
+      <c r="K20" s="6" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
     </row>
@@ -1001,25 +1009,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.182910266005868</v>
+        <v>0.1849929358065573</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18291.0266005868</v>
+        <v>18499.29358065573</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0440718553247694</v>
+        <v>0.0635007618651324</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>806.1194780825703</v>
+        <v>1174.719236338392</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>302.7808380441832</v>
+        <v>296.4508373699057</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>265.8793125755992</v>
+        <v>264.8125</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5298703896495865</v>
+        <v>1.27001523730265</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1033,7 +1041,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1042,62 +1050,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1774917990943978</v>
+        <v>0.1567530099346208</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17749.17990943978</v>
+        <v>15675.30099346208</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0436874311853043</v>
+        <v>0.0233118944998451</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>775.4160758892361</v>
+        <v>365.420963012905</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>80.15519790011265</v>
+        <v>132.4165529024798</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>72.96000289916992</v>
+        <v>119.8362837058763</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.8737486237060891</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.3154172330480927</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>39999.99999999999</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1138,7 +1146,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1167,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1339,344 +1347,344 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>424.75</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.031423347761997</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0232721257482955</v>
-      </c>
-      <c r="G8" s="15" t="n">
+      <c r="D8" s="15" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0314232904294908</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.048593625281839</v>
+      </c>
+      <c r="G8" s="16" t="n">
         <v>0.0814231940286049</v>
       </c>
-      <c r="H8" s="14" t="n">
-        <v>411.4029330380918</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>434.6348354115885</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>459.33450166365</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>403.5125</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="H8" s="15" t="n">
+        <v>413.0979666318222</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>447.2251811827044</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>461.2269922532</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>405.175</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>214</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0674845571666603</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0185279555776163</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0466707658152421</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>199.5583047663347</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>217.9649824936099</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>223.9875438844618</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>199.5583047663347</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M9" s="17" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>398.25</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.08640226646425481</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0073026269510195</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.1262860185683387</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>363.8402973806105</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>401.1582711832435</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>448.5434068948409</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>363.8402973806105</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="15" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0739081193331332</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0233118944998451</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.06601745255810321</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>119.8362837058763</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>132.4165529024798</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>137.9426518545644</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>119.8362837058763</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>278.75</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0008697116948598</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.0635007618651324</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.1307693764463149</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>278.5075678650578</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>296.4508373699057</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>315.2019636844103</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>264.8125</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="16" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="16" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>216.5</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0674846665340597</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.0185277170790933</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0914169657590902</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>201.8895696953761</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>220.5112507476237</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>236.291773086843</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>201.8895696953761</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="16" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>406</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.08576801418596321</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.0195381889719499</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1467398346446296</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>371.1781862404989</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>413.9325047226117</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>465.5763728657196</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>371.1781862404989</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="21" t="n">
+        <v>70.09999847412109</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.057659407092476</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.0243562983599827</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.0665740665489882</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>66.0580741249198</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>68.39262199625107</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>74.7668404376212</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>66.0580741249198</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="13" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>290</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.08317478422207179</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0440718553247694</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1217073782813475</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>265.8793125755992</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>302.7808380441832</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>325.2951397015908</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>265.8793125755992</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="13" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="14" t="n">
-        <v>76.80000305175781</v>
-      </c>
-      <c r="E12" s="15" t="n">
-        <v>-0.0181828709961684</v>
-      </c>
-      <c r="F12" s="15" t="n">
-        <v>0.0436874311853043</v>
-      </c>
-      <c r="G12" s="15" t="n">
-        <v>0.1388396415680386</v>
-      </c>
-      <c r="H12" s="14" t="n">
-        <v>75.40355850376235</v>
-      </c>
-      <c r="I12" s="14" t="n">
-        <v>80.15519790011265</v>
-      </c>
-      <c r="J12" s="14" t="n">
-        <v>87.46288794788813</v>
-      </c>
-      <c r="K12" s="14" t="n">
-        <v>72.96000289916992</v>
-      </c>
-      <c r="L12" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="13" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N12" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="n">
-        <v>85.80000305175781</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0535024643406818</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.0176822004387343</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.1080537552156288</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>81.20949144805074</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>84.28287020015262</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>95.07101557901267</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>81.20949144805074</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="19" t="n">
-        <v>66.09999999999999</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M13" s="20" t="n">
+        <v>70.51000000000001</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1711,7 +1719,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1728,7 +1736,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1800,734 +1808,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0.0327965513213854</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.1518047346924724</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.2578190477481508</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.07205546430306629</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E4" s="16" t="n">
+        <v>0.0326839122625022</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1747574064163009</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.2520027445324579</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.0667260011589796</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.01932078417901</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0232721257482955</v>
+      <c r="J4" s="16" t="n">
+        <v>0.0191848061055832</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.048593625281839</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>0.0107376427849041</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.1062851475529602</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.124091345478146</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.1356084928899614</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1059431524547802</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.1030927835051547</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.1288570661208279</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0208190671400168</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.0185277170790933</v>
+      <c r="J5" s="19" t="n">
+        <v>0.0208221950310057</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0185279555776163</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>0.06631648063033491</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.8513451634753439</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.6881496881496882</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.0018603499106882</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="n">
+        <v>0.0056818181818181</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.7505494505494505</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.6123481781376519</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.012653952518295</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.0271268884677411</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>0.0195381889719499</v>
+      <c r="J6" s="19" t="n">
+        <v>0.027146504684067</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.0073026269510195</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="16" t="n">
+        <v>-0.0328849705150707</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>-0.0623188848080842</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.0727423995045353</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>0.0387055294657465</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.0213591968255307</v>
+      </c>
+      <c r="K7" s="16" t="n">
+        <v>0.0233118944998451</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0603290676416818</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>-0.0749601275917065</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.0366398570151922</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>-0.0251433240548861</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0233916577859975</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0440718553247694</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="13" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="E8" s="16" t="n">
+        <v>0.0248161764705883</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>-0.0949675324675324</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.0267034990791896</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.0158727084928328</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0237844226265886</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.0635007618651324</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>-0.0429009272656267</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>-0.0741106727748314</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0.3774335409451175</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>-0.0910798605635072</v>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0.0258393895793461</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0.008960632080292101</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>-0.06716818694270769</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.1263210429301852</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.1962962680392794</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>0.1352091522236986</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>0.014371534326613</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.0423497076962041</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.0896104094269988</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.0685975625712129</v>
+      </c>
+      <c r="H11" s="22" t="n">
+        <v>0.1720121375609908</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="22" t="n">
+        <v>0.0246767774360878</v>
+      </c>
+      <c r="K11" s="22" t="n">
+        <v>-0.0243562983599827</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0210324277969439</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>-0.1012287209527198</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>-0.2601155992889228</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>0.0229567002920754</v>
-      </c>
-      <c r="I8" s="13" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>-0.0440051595725787</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>-0.1135423507630025</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>-0.2505000305175781</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.034416471445952</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="15" t="n">
-        <v>0.0186023142151574</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>0.0436874311853043</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="J12" s="24" t="n">
+        <v>0.0187857116755223</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.0417061954400697</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0240601274303924</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.0546249077443409</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0.0675521339407823</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>0.0466086873881392</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="E13" s="24" t="n">
+        <v>-0.0470822676381429</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>-0.1793261454069303</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>-0.1769759912663099</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>0.0257819842186814</v>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0213699592605512</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0171547181631014</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="J13" s="24" t="n">
+        <v>0.0181359438794645</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0.0293749779565115</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D14" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.0222797106127056</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-0.08398055874758679</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0.371080762650305</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.0635463784701541</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="E14" s="26" t="n">
+        <v>-0.0497584688490715</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.08426445924749019</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.0597514349060559</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>0.1301916561897569</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.0205132764659884</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.0122719055930224</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.0666666666666666</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.1196319018404907</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-0.0060606060606061</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>-0.0712361116745953</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.0199390407087947</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0.019818305116646</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.0720768808330956</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.1087179330679086</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.0067929542392483</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>0.0162522834983966</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0.0203111892988181</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.0483515622718333</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.0456743876191452</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.11509713508058</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0.085574545617342</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.0161450783703462</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0259133640359863</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.0245096604354778</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="J17" s="26" t="n">
+        <v>0.026486852660048</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.0523180466794031</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C18" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D18" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>0.0593561546775376</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>0.0968749285986054</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>0.0968749285986054</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>0.2248945580867938</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0.038242188177953</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.002557432846991</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
+      <c r="E18" s="26" t="n">
+        <v>0.007984023957211501</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>0.0570382060583218</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>-0.0146341091249047</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.249435085959637</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0386162426723168</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.0688776102278674</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="22" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E12" s="23" t="n">
-        <v>-0.02676728880008</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.0816061615467036</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.0597907310727441</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>0.17897104086832</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
+      <c r="E19" s="26" t="n">
+        <v>-0.09096534653465339</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>0.0644927536231885</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>0.1458658346333854</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.1716971575653025</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0246437220862215</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0.0111110916693351</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="J19" s="26" t="n">
+        <v>0.0294772299234431</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.07234284902876199</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0867482082088227</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.1555117683036949</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>-0.223529384146988</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>0.1003856692808642</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>-0.0438464959714743</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1336342724808165</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.0979392290114437</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>0.3765566762420678</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="21" t="n">
-        <v>0.0144825594088848</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>-0.0176822004387343</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.0316831884604476</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.171654478303657</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.1711864579195356</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.0216553996269717</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0180299757870784</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0063456596971369</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.0277237939582618</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0880474604035462</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.0606203429054268</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.1258996931118607</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0205669732511004</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0122719965535019</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.0586666666666666</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.0948717948717948</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0.0063725333676007</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0.0099768134882742</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0202363669454623</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0607735410264971</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0537021969080553</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.1162613981762917</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.0110544217687075</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.0636907097647794</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0.019910855344003</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.012312990332685</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0293001034501172</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.1072855003820407</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0783604113986555</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>0.0269559867655238</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0264796048332912</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0492106566855715</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0780185758513931</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>0.0412587412587412</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0.1254724111866969</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.1764974921360816</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0297755297019779</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0657663918867637</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.019980000468739</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1268357170098918</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.114304907742561</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>0.3663174846425323</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0269670382266868</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0328525399081489</v>
+      <c r="J20" s="26" t="n">
+        <v>0.0270414178348575</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.0512217880135596</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2560,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2560,7 +2568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2585,7 +2593,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TOASO.IS, FROTO.IS</t>
+          <t>BIMAS.IS, GARAN.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2617,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2629,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, EREGL.IS, PETKM.IS, AKBNK.IS, PGSUS.IS, TCELL.IS, SAHOL.IS, THYAO.IS, YKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>EREGL.IS, ARCLK.IS, FROTO.IS, PGSUS.IS, TCELL.IS, THYAO.IS, SAHOL.IS, YKBNK.IS, PETKM.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2679,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,7 +2687,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2764,7 +2772,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2784,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2922,7 +2930,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2930,7 +2938,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2954,7 +2962,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12592.7998046875</v>
+        <v>12290.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -2964,7 +2972,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13560.57602050781</v>
+        <v>13565.83701660156</v>
       </c>
     </row>
     <row r="6">
@@ -2998,7 +3006,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>66.09999999999999</v>
+        <v>70.51000000000001</v>
       </c>
     </row>
     <row r="9">
@@ -3032,7 +3040,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="20" customWidth="1" min="8" max="8"/>
@@ -3041,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-25</t>
+          <t>Rapor Tarihi: 2026-09-28</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3055,7 +3063,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-29 07:35</t>
+          <t>Son Güncelleme: 2026-09-30 07:35</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,23 +3127,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="27" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>372.25</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>-0.06821026282853571</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>-48052.74839324958</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D4" s="27" t="n">
+        <v>367.25</v>
+      </c>
+      <c r="E4" s="28" t="n">
+        <v>-0.08072590738423024</v>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>-56869.76644705678</v>
+      </c>
+      <c r="G4" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H4" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="5">
@@ -3149,23 +3157,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="27" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>216.5</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>0.09898477157360408</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>287683.8701777929</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D5" s="27" t="n">
+        <v>214</v>
+      </c>
+      <c r="E5" s="28" t="n">
+        <v>0.08629441624365475</v>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>250801.3227191013</v>
+      </c>
+      <c r="G5" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H5" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="6">
@@ -3179,23 +3187,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="27" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>88.25</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.08549222797927458</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-7507.455502376353</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D6" s="27" t="n">
+        <v>86.90000152587891</v>
+      </c>
+      <c r="E6" s="28" t="n">
+        <v>-0.0994818494727574</v>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>-8735.946832405461</v>
+      </c>
+      <c r="G6" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H6" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="7">
@@ -3209,23 +3217,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="27" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>129.8000030517578</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-0.02698643935111478</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>-130687.2698127953</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D7" s="27" t="n">
+        <v>129.3999938964844</v>
+      </c>
+      <c r="E7" s="28" t="n">
+        <v>-0.02998500886817068</v>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>-145208.4468539497</v>
+      </c>
+      <c r="G7" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H7" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="8">
@@ -3239,23 +3247,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="27" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>37.7400016784668</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.02882138225150777</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-6273.875831723271</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D8" s="27" t="n">
+        <v>37.47999954223633</v>
+      </c>
+      <c r="E8" s="28" t="n">
+        <v>-0.03551212162738948</v>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>-7730.324648105336</v>
+      </c>
+      <c r="G8" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H8" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="9">
@@ -3269,23 +3277,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="27" t="n">
         <v>405.5</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>424.75</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>0.04747225647348952</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>134617.9467610051</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D9" s="27" t="n">
+        <v>426.5</v>
+      </c>
+      <c r="E9" s="28" t="n">
+        <v>0.05178791615289757</v>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>146855.9419210963</v>
+      </c>
+      <c r="G9" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H9" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="10">
@@ -3299,23 +3307,23 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C10" s="26" t="n">
+      <c r="C10" s="27" t="n">
         <v>417.25</v>
       </c>
-      <c r="D10" s="26" t="n">
-        <v>406</v>
-      </c>
-      <c r="E10" s="27" t="n">
-        <v>-0.02696225284601561</v>
-      </c>
-      <c r="F10" s="26" t="n">
-        <v>-123091.9316565571</v>
-      </c>
-      <c r="G10" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H10" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D10" s="27" t="n">
+        <v>398.25</v>
+      </c>
+      <c r="E10" s="28" t="n">
+        <v>-0.04553624925104849</v>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>-207888.5956866294</v>
+      </c>
+      <c r="G10" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H10" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
     <row r="11">
@@ -3329,23 +3337,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C11" s="26" t="n">
+      <c r="C11" s="27" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D11" s="26" t="n">
-        <v>76.80000305175781</v>
-      </c>
-      <c r="E11" s="27" t="n">
-        <v>-0.007751918117475554</v>
-      </c>
-      <c r="F11" s="26" t="n">
-        <v>-34705.99654011708</v>
-      </c>
-      <c r="G11" s="26" t="n">
-        <v>20709150.58882204</v>
-      </c>
-      <c r="H11" s="27" t="n">
-        <v>-0.05871275608399</v>
+      <c r="D11" s="27" t="n">
+        <v>74.94999694824219</v>
+      </c>
+      <c r="E11" s="28" t="n">
+        <v>-0.03165380528858974</v>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>-141716.7777289534</v>
+      </c>
+      <c r="G11" s="27" t="n">
+        <v>20466675.45606316</v>
+      </c>
+      <c r="H11" s="28" t="n">
+        <v>-0.081085828612996</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,11 +99,6 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -158,9 +153,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,6 +201,12 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -618,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -635,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -686,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 70.51/100</t>
+          <t>Güven Puanı: 67.95/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -780,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: AKBNK.IS</t>
+          <t>ÇIK: AKBNK.IS, PGSUS.IS, THYAO.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -966,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.258254054258822</v>
+        <v>0.250611702418947</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>25825.4054258822</v>
+        <v>25061.1702418947</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.048593625281839</v>
+        <v>0.0485934089511839</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1254.950074016891</v>
+        <v>1217.80769435963</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>447.2251811827044</v>
+        <v>442.2442702251618</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>405.175</v>
+        <v>400.6625</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9718725056367798</v>
+        <v>0.9718681790236766</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1009,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1849929358065573</v>
+        <v>0.1777766291512752</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18499.29358065573</v>
+        <v>17777.66291512752</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0635007618651324</v>
+        <v>0.0521797150691485</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>1174.719236338392</v>
+        <v>927.6333855067217</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>296.4508373699057</v>
+        <v>291.4537810741542</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>264.8125</v>
+        <v>263.15</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.27001523730265</v>
+        <v>1.04359430138297</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1050,62 +1048,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1567530099346208</v>
+        <v>0.1716116684297777</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>15675.30099346208</v>
+        <v>17161.16684297777</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0233118944998451</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>365.420963012905</v>
+        <v>568.3338464273503</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>132.4165529024798</v>
+        <v>133.3754673069377</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>119.8362837058763</v>
+        <v>122.6450057983398</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3154172330480927</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.662348722120731</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>39999.99999999999</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000.00000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1123,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1146,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1167,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1209,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1347,349 +1345,520 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>426.5</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0314232904294908</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.048593625281839</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0814231940286049</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>413.0979666318222</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>447.2251811827044</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>461.2269922532</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>405.175</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D8" s="14" t="n">
+        <v>421.75</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0314232827399248</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0485934089511839</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.08142280530855769</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>408.4972305044367</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>442.2442702251618</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>456.0900681388842</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>400.6625</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M8" s="13" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>214</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0674845571666603</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0185279555776163</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0466707658152421</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>199.5583047663347</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>217.9649824936099</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>223.9875438844618</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>199.5583047663347</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D9" s="17" t="n">
+        <v>214.1000061035156</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0654616378591889</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.020897898080708</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.0578573960996917</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>200.0846690383171</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>218.5742462101458</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>226.4872749615932</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>200.0846690383171</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="16" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O9" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="n">
+      <c r="A10" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>129.1000061035156</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0137508623139599</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.0795559387098858</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>127.3247696948548</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>133.3754673069377</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>139.3706782765328</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>122.6450057983398</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>277</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0458660455809996</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0521797150691485</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1296241265638341</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>264.2951053740631</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>291.4537810741542</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>312.905883058182</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>263.15</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>398.25</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.08640226646425481</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0073026269510195</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1262860185683387</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>363.8402973806105</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>401.1582711832435</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>448.5434068948409</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>363.8402973806105</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="D12" s="17" t="n">
+        <v>376.5030517578125</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0506137967402887</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0177982164043262</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.1114567362745178</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>357.4468028240442</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>383.2041345498873</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>418.4668531041341</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>355.7842705664092</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>129.3999938964844</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0739081193331332</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0233118944998451</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.06601745255810321</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>119.8362837058763</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>132.4165529024798</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>137.9426518545644</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>119.8362837058763</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>69.90000152587891</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0525384307623365</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0126939113464409</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.0665740665489882</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>66.2275651354243</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>69.01269710339331</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>74.55352887923715</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>66.2275651354243</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="M13" s="19" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>142.3999938964844</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.0444858411315781</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0171127424349814</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.0615545291580976</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>136.0652103908677</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>139.9631394781909</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>151.1653584728984</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>135.2799942016601</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="n">
+        <v>291.5</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.0573248422045384</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>-0.0407844352132465</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.0475785896346643</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>274.7898084973771</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>279.6113371353387</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>305.3691588785047</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>274.7898084973771</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="19" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>278.75</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0008697116948598</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.0635007618651324</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.1307693764463149</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>278.5075678650578</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>296.4508373699057</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>315.2019636844103</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>264.8125</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
-        <v>70.09999847412109</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.057659407092476</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0243562983599827</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.0665740665489882</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>66.0580741249198</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>68.39262199625107</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>74.7668404376212</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>66.0580741249198</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="D16" s="20" t="n">
+        <v>19.44000053405762</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>-0.1344322197940816</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>-0.0316827048008266</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.0308602711215918</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>16.82663810946612</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>18.82408873580916</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>20.03992422114252</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>16.82663810946612</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n">
-        <v>70.51000000000001</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+      <c r="M16" s="19" t="n">
+        <v>67.95</v>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1719,7 +1888,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1736,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1808,734 +1977,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.0326839122625022</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1747574064163009</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.2520027445324579</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.0667260011589796</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="n">
+        <v>0.046365995624918</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.1640641958067286</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.2125410606368623</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>-0.1060680391706845</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0191848061055832</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.048593625281839</v>
+      <c r="J4" s="15" t="n">
+        <v>0.019255416782264</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0485934089511839</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.0037226050055362</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.097948749248798</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.0990759894733157</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.111890212897965</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0208089041979225</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.020897898080708</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0137508623139599</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>-0.0678699920323782</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>0.0617949442776202</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.0223846752596001</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0.021352470283261</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0211981566820276</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>-0.0918032786885245</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.0118721461187214</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-0.0385477520346346</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0237686135775877</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0521797150691485</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1059431524547802</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.1030927835051547</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.1288570661208279</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E8" s="18" t="n">
+        <v>-0.0424734337790807</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.6218789459119614</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.4840271562881915</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.0355937760498206</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0208221950310057</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0185279555776163</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="J8" s="18" t="n">
+        <v>0.0275147586383055</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.0177982164043262</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>0.0056818181818181</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.7505494505494505</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.6123481781376519</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.012653952518295</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="19" t="n">
-        <v>0.027146504684067</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>0.0073026269510195</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>0.0336664581325649</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.0961361291777954</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.0722379737077668</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.0042457255168696</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="23" t="n">
+        <v>0.0204426527018122</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0124594158070348</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="19" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0328849705150707</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>-0.0623188848080842</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.0727423995045353</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>0.0387055294657465</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.0271398328413957</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.1021194233020431</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>0.0590909322102863</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0.1609790406909332</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>0.0246277386173225</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>-0.0126939113464409</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="19" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0312925585273171</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.1936580465743846</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.1886040233818554</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>0.0031783365504038</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.0213591968255307</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0233118944998451</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J11" s="21" t="n">
+        <v>0.0180909416875128</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>-0.0171127424349814</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>0.0248161764705883</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>-0.0949675324675324</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0267034990791896</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.0158727084928328</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0355665839536807</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.1126331811263318</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.0093457943925233</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.0704534431987032</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.0200259118267082</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>-0.0407844352132465</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>-0.0722559618478099</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.1573146703161367</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-0.22559852987326</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.0805125554218029</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0148036254000479</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>-0.0331383433852303</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1267605141925548</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.2640949292900006</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0008159835443355</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0187594786664026</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.07589889957388091</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>-0.052088718962056</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0909990215169119</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.3203340263556753</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.1175827719478029</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0237844226265886</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.0635007618651324</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="J15" s="25" t="n">
+        <v>0.0259423111487782</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0190703728875496</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.0429009272656267</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.0741106727748314</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0.3774335409451175</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.0910798605635072</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.0142387856310425</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.1133004592858096</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>0.0902483192284653</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0.0007316226435329</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="24" t="n">
-        <v>0.0258393895793461</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0.008960632080292101</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0265044380231435</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0653044418346088</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
-        <v>-0.06716818694270769</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>-0.1263210429301852</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.1962962680392794</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>0.1352091522236986</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="E17" s="25" t="n">
+        <v>-0.068669464657156</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.1151885382072073</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.0134843446281089</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.0165947083620279</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="24" t="n">
-        <v>0.014371534326613</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.0007363095911598</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="J17" s="25" t="n">
+        <v>0.020286919497638</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0394097661969332</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.0423497076962041</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.0896104094269988</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.0685975625712129</v>
-      </c>
-      <c r="H11" s="22" t="n">
-        <v>0.1720121375609908</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J11" s="22" t="n">
-        <v>0.0246767774360878</v>
-      </c>
-      <c r="K11" s="22" t="n">
-        <v>-0.0243562983599827</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
+      <c r="E18" s="27" t="n">
+        <v>-0.0309072257423232</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>0.0231579228451377</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.0838830743117252</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>0.2443317137253151</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="27" t="n">
+        <v>0.0389217489272056</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>-0.0316827048008266</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E12" s="24" t="n">
-        <v>-0.0440051595725787</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>-0.1135423507630025</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.2505000305175781</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.034416471445952</v>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.1236245954692556</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.08821548821548809</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>0.0569867291178767</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.1574279537758144</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="24" t="n">
-        <v>0.0187857116755223</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>0.0417061954400697</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.0295861436658756</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0288487046828432</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
-        <v>-0.0470822676381429</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>-0.1793261454069303</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>-0.1769759912663099</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>0.0257819842186814</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.0353356322292823</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1480160343135671</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1196739457634159</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.3628996403778135</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="24" t="n">
-        <v>0.0181359438794645</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0.0293749779565115</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.0497584688490715</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.08426445924749019</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>-0.0597514349060559</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.1301916561897569</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0205132764659884</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0122719055930224</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>-0.0666666666666666</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.1196319018404907</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.0060606060606061</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>-0.0712361116745953</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>0.0199390407087947</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.019818305116646</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.0720768808330956</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.1087179330679086</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.0067929542392483</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>0.0162522834983966</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0203111892988181</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0.0483515622718333</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0456743876191452</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.11509713508058</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>0.085574545617342</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.0161450783703462</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.026486852660048</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.0523180466794031</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>0.007984023957211501</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>0.0570382060583218</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>-0.0146341091249047</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.249435085959637</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0386162426723168</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.0688776102278674</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.09096534653465339</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>0.0644927536231885</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>0.1458658346333854</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.1716971575653025</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0294772299234431</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.07234284902876199</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.0438464959714743</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1336342724808165</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.0979392290114437</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>0.3765566762420678</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0270414178348575</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0512217880135596</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0269783360128968</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0288487046828432</v>
       </c>
     </row>
   </sheetData>
@@ -2560,7 +2729,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2568,7 +2737,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2617,7 +2786,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>AKBNK.IS, PGSUS.IS, THYAO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2629,7 +2798,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, ARCLK.IS, FROTO.IS, PGSUS.IS, TCELL.IS, THYAO.IS, SAHOL.IS, YKBNK.IS, PETKM.IS, ASELS.IS, SISE.IS</t>
+          <t>TCELL.IS, ARCLK.IS, FROTO.IS, EREGL.IS, YKBNK.IS, SAHOL.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2641,7 +2810,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.31 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2679,7 +2848,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2687,7 +2856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2930,7 +3099,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2938,7 +3107,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2962,7 +3131,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12290.599609375</v>
+        <v>11947.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -2972,7 +3141,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13565.83701660156</v>
+        <v>13569.603515625</v>
       </c>
     </row>
     <row r="6">
@@ -3006,7 +3175,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70.51000000000001</v>
+        <v>67.95</v>
       </c>
     </row>
     <row r="9">
@@ -3042,14 +3211,14 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-28</t>
+          <t>Rapor Tarihi: 2026-09-29</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3063,7 +3232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-09-30 07:35</t>
+          <t>Son Güncelleme: 2026-10-01 07:54</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3127,23 +3296,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="27" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="27" t="n">
-        <v>367.25</v>
-      </c>
-      <c r="E4" s="28" t="n">
-        <v>-0.08072590738423024</v>
-      </c>
-      <c r="F4" s="27" t="n">
-        <v>-56869.76644705678</v>
-      </c>
-      <c r="G4" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H4" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D4" s="28" t="n">
+        <v>338.5</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>-0.1526908635794744</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>-107567.6202564484</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="5">
@@ -3157,23 +3326,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="27" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="27" t="n">
-        <v>214</v>
-      </c>
-      <c r="E5" s="28" t="n">
-        <v>0.08629441624365475</v>
-      </c>
-      <c r="F5" s="27" t="n">
-        <v>250801.3227191013</v>
-      </c>
-      <c r="G5" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H5" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D5" s="28" t="n">
+        <v>214.1000061035156</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>0.08680206143916558</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>252276.7146627312</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="6">
@@ -3187,23 +3356,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="27" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="27" t="n">
-        <v>86.90000152587891</v>
-      </c>
-      <c r="E6" s="28" t="n">
-        <v>-0.0994818494727574</v>
-      </c>
-      <c r="F6" s="27" t="n">
-        <v>-8735.946832405461</v>
-      </c>
-      <c r="G6" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H6" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D6" s="28" t="n">
+        <v>86.80000305175781</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.1005181030905926</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-8826.944904498756</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="7">
@@ -3217,23 +3386,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="27" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="27" t="n">
-        <v>129.3999938964844</v>
-      </c>
-      <c r="E7" s="28" t="n">
-        <v>-0.02998500886817068</v>
-      </c>
-      <c r="F7" s="27" t="n">
-        <v>-145208.4468539497</v>
-      </c>
-      <c r="G7" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H7" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D7" s="28" t="n">
+        <v>129.1000061035156</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.03223379302629847</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-156098.6372269839</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="8">
@@ -3247,23 +3416,23 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="C8" s="27" t="n">
+      <c r="C8" s="28" t="n">
         <v>38.86000061035156</v>
       </c>
-      <c r="D8" s="27" t="n">
-        <v>37.47999954223633</v>
-      </c>
-      <c r="E8" s="28" t="n">
-        <v>-0.03551212162738948</v>
-      </c>
-      <c r="F8" s="27" t="n">
-        <v>-7730.324648105336</v>
-      </c>
-      <c r="G8" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H8" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D8" s="28" t="n">
+        <v>36.7599983215332</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.05404020215735561</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-11763.54122428445</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="9">
@@ -3277,23 +3446,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <v>405.5</v>
       </c>
-      <c r="D9" s="27" t="n">
-        <v>426.5</v>
-      </c>
-      <c r="E9" s="28" t="n">
-        <v>0.05178791615289757</v>
-      </c>
-      <c r="F9" s="27" t="n">
-        <v>146855.9419210963</v>
-      </c>
-      <c r="G9" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H9" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D9" s="28" t="n">
+        <v>421.75</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0.04007398273736129</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>113638.5264865626</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="10">
@@ -3307,23 +3476,23 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="C10" s="27" t="n">
+      <c r="C10" s="28" t="n">
         <v>417.25</v>
       </c>
-      <c r="D10" s="27" t="n">
-        <v>398.25</v>
-      </c>
-      <c r="E10" s="28" t="n">
-        <v>-0.04553624925104849</v>
-      </c>
-      <c r="F10" s="27" t="n">
-        <v>-207888.5956866294</v>
-      </c>
-      <c r="G10" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H10" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D10" s="28" t="n">
+        <v>376.5030517578125</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.09765595744083289</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-445832.9393991656</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
     <row r="11">
@@ -3337,23 +3506,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D11" s="27" t="n">
-        <v>74.94999694824219</v>
-      </c>
-      <c r="E11" s="28" t="n">
-        <v>-0.03165380528858974</v>
-      </c>
-      <c r="F11" s="27" t="n">
-        <v>-141716.7777289534</v>
-      </c>
-      <c r="G11" s="27" t="n">
-        <v>20466675.45606316</v>
-      </c>
-      <c r="H11" s="28" t="n">
-        <v>-0.081085828612996</v>
+      <c r="D11" s="28" t="n">
+        <v>74.40000152587891</v>
+      </c>
+      <c r="E11" s="29" t="n">
+        <v>-0.03875968915836447</v>
+      </c>
+      <c r="F11" s="28" t="n">
+        <v>-173530.4240112733</v>
+      </c>
+      <c r="G11" s="28" t="n">
+        <v>20099463.1837467</v>
+      </c>
+      <c r="H11" s="29" t="n">
+        <v>-0.1031377984986136</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,22 +185,13 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 67.95/100</t>
+          <t>Güven Puanı: 72.61/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +735,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, TOASO.IS, GARAN.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +752,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, TUPRS.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: AKBNK.IS, PGSUS.IS, THYAO.IS, PETKM.IS</t>
+          <t>ÇIK: TUPRS.IS, EREGL.IS, THYAO.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -964,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.250611702418947</v>
+        <v>0.2370015689047132</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>25061.1702418947</v>
+        <v>23700.15689047132</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0485934089511839</v>
+        <v>0.0485935221290569</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1217.80769435963</v>
+        <v>1151.674098319239</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>442.2442702251618</v>
+        <v>438.8363890110103</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>400.6625</v>
+        <v>397.575</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9718681790236766</v>
+        <v>0.9718704425811387</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -998,7 +989,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1777766291512752</v>
+        <v>0.1891968267277309</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>17777.66291512752</v>
+        <v>18919.68267277309</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0521797150691485</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>927.6333855067217</v>
+        <v>440.2246726425386</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>291.4537810741542</v>
+        <v>213.2490614352234</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>263.15</v>
+        <v>194.617255911677</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>1.04359430138297</v>
+        <v>0.3518217892616216</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1030,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,25 +1039,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1716116684297777</v>
+        <v>0.1738016043675558</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17161.16684297777</v>
+        <v>17380.16043675558</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0315183238607393</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>568.3338464273503</v>
+        <v>547.7935253972706</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>133.3754673069377</v>
+        <v>75.86817586790147</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>122.6450057983398</v>
+        <v>69.87250289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.662348722120731</v>
+        <v>0.6303664772147827</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1089,10 +1080,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000.00000000001</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1121,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1135,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1156,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1198,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,28 +1350,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>421.75</v>
+        <v>418.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0314232827399248</v>
+        <v>-0.0314234662717713</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0485934089511839</v>
+        <v>0.0485935221290569</v>
       </c>
       <c r="G8" s="15" t="n">
         <v>0.08142280530855769</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>408.4972305044367</v>
+        <v>405.3492793652637</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>442.2442702251618</v>
+        <v>438.8363890110103</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>456.0900681388842</v>
+        <v>452.5754440216314</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>400.6625</v>
+        <v>397.575</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1388,7 +1379,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>67.95</v>
+        <v>72.61</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1402,57 +1393,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>214.1000061035156</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0654616378591889</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.020897898080708</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0578573960996917</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>200.0846690383171</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>218.5742462101458</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>226.4872749615932</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>200.0846690383171</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.06613598075081251</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.06904391931949121</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>194.617255911677</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>213.2490614352234</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>222.7887462612557</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>194.617255911677</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="M9" s="13" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
@@ -1464,7 +1455,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1473,28 +1464,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>129.1000061035156</v>
+        <v>73.55000305175781</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0137508623139599</v>
+        <v>-0.0475011878622574</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0315183238607393</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.0795559387098858</v>
+        <v>0.0961031584456031</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>127.3247696948548</v>
+        <v>70.05629053952666</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>133.3754673069377</v>
+        <v>75.86817586790147</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>139.3706782765328</v>
+        <v>80.61839064871549</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>122.6450057983398</v>
+        <v>69.87250289916992</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1502,11 +1493,11 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>67.95</v>
+        <v>72.61</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; hacim artışı var; volatilite görece düşük</t>
+          <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O10" s="13" t="inlineStr">
@@ -1516,59 +1507,59 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>277</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0458660455809996</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0521797150691485</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1296241265638341</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>264.2951053740631</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>291.4537810741542</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>312.905883058182</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>263.15</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>376.25</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0751524029661248</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.0049329293972443</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.1104291354757626</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>347.9739083839955</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>374.3939853142869</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>417.7989622227556</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>347.9739083839955</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1578,37 +1569,37 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>376.5030517578125</v>
+        <v>35.93999862670898</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-0.0506137967402887</v>
+        <v>-0.0653061001718057</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>0.0177982164043262</v>
+        <v>-0.0210280210184544</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.1114567362745178</v>
+        <v>0.0348675647128589</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>357.4468028240442</v>
+        <v>33.59289747621857</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>383.2041345498873</v>
+        <v>35.18425158018333</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>418.4668531041341</v>
+        <v>37.19313885460582</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>355.7842705664092</v>
+        <v>33.59289747621857</v>
       </c>
       <c r="L12" s="16" t="inlineStr">
         <is>
@@ -1616,11 +1607,11 @@
         </is>
       </c>
       <c r="M12" s="16" t="n">
-        <v>67.95</v>
+        <v>72.61</v>
       </c>
       <c r="N12" s="16" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var</t>
         </is>
       </c>
       <c r="O12" s="16" t="inlineStr">
@@ -1630,235 +1621,178 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="A13" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>69.90000152587891</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0525384307623365</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.0126939113464409</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.0665740665489882</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>66.2275651354243</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>69.01269710339331</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>74.55352887923715</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>66.2275651354243</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="D13" s="17" t="n">
+        <v>283.25</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.06308392033297271</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0407844352132465</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0454073760257329</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>265.3814795656855</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>271.6978087258479</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>296.1116392592888</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>265.3814795656855</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+      <c r="M13" s="16" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="A14" s="16" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>142.3999938964844</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.0444858411315781</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.0171127424349814</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.0615545291580976</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>136.0652103908677</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>139.9631394781909</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>151.1653584728984</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>135.2799942016601</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="D14" s="17" t="n">
+        <v>136.1000061035156</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0462686718992926</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.0194552529182879</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.0673149458156319</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>129.8028395756203</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>133.4521460625912</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>145.2615706398809</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>129.2950057983398</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="19" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="M14" s="16" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="A15" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D15" s="20" t="n">
-        <v>291.5</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.0573248422045384</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>-0.0407844352132465</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0475785896346643</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>274.7898084973771</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>279.6113371353387</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>305.3691588785047</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>274.7898084973771</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
+      <c r="D15" s="17" t="n">
+        <v>18.90999984741211</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.1344322197940816</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.0316827048008266</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.0308602711215918</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>16.36788659161876</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>18.31087990446288</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>19.49356756961251</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>16.36788659161876</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M15" s="19" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>19.44000053405762</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>-0.1344322197940816</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>-0.0316827048008266</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.0308602711215918</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>16.82663810946612</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>18.82408873580916</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>20.03992422114252</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>16.82663810946612</v>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>67.95</v>
-      </c>
-      <c r="N16" s="19" t="inlineStr">
+      <c r="M15" s="16" t="n">
+        <v>72.61</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
         <is>
           <t>3A momentum destekli; hacim artışı var</t>
         </is>
       </c>
-      <c r="O16" s="19" t="inlineStr">
+      <c r="O15" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1888,7 +1822,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1905,7 +1839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1996,16 +1930,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.046365995624918</v>
+        <v>0.0313086453325817</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1640641958067286</v>
+        <v>0.1777111843078196</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2125410606368623</v>
+        <v>0.22496277119014</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.1060680391706845</v>
+        <v>-0.1054473269412359</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -2013,53 +1947,53 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.019255416782264</v>
+        <v>0.0190993116381614</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0485934089511839</v>
+        <v>0.0485935221290569</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>-0.0037226050055362</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.097948749248798</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.0990759894733157</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.111890212897965</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0208089041979225</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.020897898080708</v>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0293432843097644</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.0758905378412067</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.0643513311968431</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.0756018134192069</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>0.0210882991743487</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0232680790823229</v>
       </c>
     </row>
     <row r="6">
@@ -2068,7 +2002,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -2082,16 +2016,16 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.0137508623139599</v>
+        <v>-0.0478964006244942</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.0678699920323782</v>
+        <v>-0.1212663592181593</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.0617949442776202</v>
+        <v>-0.2824389946169969</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0223846752596001</v>
+        <v>0.0102352037947996</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -2099,53 +2033,53 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.021352470283261</v>
+        <v>0.0186924647901297</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0315183238607393</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0211981566820276</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>-0.0918032786885245</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.0118721461187214</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>-0.0385477520346346</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0237686135775877</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0521797150691485</v>
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>-0.0490566934200201</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.5971327429661775</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.5093297423027483</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.0480105104047176</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0275227730050399</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>-0.0049329293972443</v>
       </c>
     </row>
     <row r="8">
@@ -2154,7 +2088,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -2164,74 +2098,74 @@
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>-0.0424734337790807</v>
+        <v>-0.0487030230820493</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0.6218789459119614</v>
+        <v>-0.119117664245861</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>0.4840271562881915</v>
+        <v>0.2657635096700415</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-0.0355937760498206</v>
+        <v>-0.1150367419711329</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0275147586383055</v>
+        <v>0.0260445109248329</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>0.0177982164043262</v>
+        <v>-0.0210280210184544</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>0.0336664581325649</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.0961361291777954</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-0.0722379737077668</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.0042457255168696</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="n">
+        <v>-0.0046608447790051</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>-0.1134686612418669</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>-0.103544764833159</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.0667237892711047</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0204426527018122</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0124594158070348</v>
+      <c r="J9" s="20" t="n">
+        <v>0.0206045904356744</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0124595339704571</v>
       </c>
     </row>
     <row r="10">
@@ -2240,7 +2174,7 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
@@ -2250,74 +2184,74 @@
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n">
+        <v>-0.0752444908191226</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>-0.1132756413149861</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>-0.0072475937442743</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>0.0232494182650186</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="20" t="n">
+        <v>0.0221609022696276</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.0233118944998451</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.0271398328413957</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>-0.1021194233020431</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>0.0590909322102863</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>0.1609790406909332</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>0.0246277386173225</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>-0.0126939113464409</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0312925585273171</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.1936580465743846</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.1886040233818554</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>0.0031783365504038</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="E11" s="18" t="n">
+        <v>-0.060530679933665</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.1500375093773444</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>-0.0494966442953019</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>-0.060616712968899</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0180909416875128</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>-0.0171127424349814</v>
+      <c r="J11" s="18" t="n">
+        <v>0.0201934249564709</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>-0.0407844352132465</v>
       </c>
     </row>
     <row r="12">
@@ -2326,7 +2260,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
@@ -2336,375 +2270,375 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.1058172083297264</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-0.1909774742030858</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-0.2676951072317661</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>0.0879624110588572</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0.0155480620918477</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0.0462427745664739</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.0901286928276321</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>-0.1307021999090573</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>-0.063500826131539</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.0146618521552636</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0.0204587359533638</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.0483517688336121</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0355665839536807</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.1126331811263318</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.0093457943925233</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.0704534431987032</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E14" s="22" t="n">
+        <v>-0.104015723685519</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.2310734118445444</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.2413600293540326</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>-0.0288769351755694</v>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0200259118267082</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>-0.0407844352132465</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="J14" s="22" t="n">
+        <v>0.0187973585994814</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>-0.0194552529182879</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>-0.0722559618478099</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-0.1573146703161367</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-0.22559852987326</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>0.0805125554218029</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="E15" s="24" t="n">
+        <v>-0.0223880597014924</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.1444897959183673</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.038532110091743</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.0325460006251897</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0148036254000479</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0007363095911598</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="J15" s="24" t="n">
+        <v>0.0246729486580986</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>0.0355140318659195</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="23" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.0331383433852303</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.1267605141925548</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.2640949292900006</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0008159835443355</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E16" s="24" t="n">
+        <v>-0.06879773673657</v>
+      </c>
+      <c r="F16" s="24" t="n">
+        <v>-0.1404746295950831</v>
+      </c>
+      <c r="G16" s="24" t="n">
+        <v>-0.0183150183150183</v>
+      </c>
+      <c r="H16" s="24" t="n">
+        <v>0.1519405211493802</v>
+      </c>
+      <c r="I16" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0187594786664026</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.07589889957388091</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="J16" s="24" t="n">
+        <v>0.0251364935844182</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <v>0.0377795542969727</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.052088718962056</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0909990215169119</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.3203340263556753</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.1175827719478029</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0259423111487782</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0190703728875496</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="E17" s="24" t="n">
+        <v>-0.0755024117962623</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.1595061502338927</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.0064214073783998</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.0039801755863774</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0273291602426887</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>0.0423504428390855</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>-0.073947121608233</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>0.0026510729290805</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>-0.07030483256873719</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>0.2325193659505331</v>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="22" t="n">
+        <v>0.0390719900862105</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>-0.0316827048008266</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="23" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.0142387856310425</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.1133004592858096</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>0.0902483192284653</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0.0007316226435329</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0265044380231435</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0653044418346088</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="E19" s="24" t="n">
+        <v>-0.0722952606438102</v>
+      </c>
+      <c r="F19" s="24" t="n">
+        <v>-0.1752808817316976</v>
+      </c>
+      <c r="G19" s="24" t="n">
+        <v>-0.1668089139555892</v>
+      </c>
+      <c r="H19" s="24" t="n">
+        <v>0.3685019271262522</v>
+      </c>
+      <c r="I19" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="24" t="n">
+        <v>0.0273826627349781</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <v>0.0316196947808986</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="23" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D20" s="23" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.068669464657156</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.1151885382072073</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.0134843446281089</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.0165947083620279</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="E20" s="24" t="n">
+        <v>-0.1248374512353706</v>
+      </c>
+      <c r="F20" s="24" t="n">
+        <v>-0.1254061078622482</v>
+      </c>
+      <c r="G20" s="24" t="n">
+        <v>0.0507416081186573</v>
+      </c>
+      <c r="H20" s="24" t="n">
+        <v>-0.1324804890646602</v>
+      </c>
+      <c r="I20" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.020286919497638</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.0394097661969332</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.0309072257423232</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>0.0231579228451377</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>-0.0838830743117252</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>0.2443317137253151</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0389217489272056</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>-0.0316827048008266</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.1236245954692556</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.08821548821548809</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>0.0569867291178767</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.1574279537758144</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0295861436658756</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0288487046828432</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0353356322292823</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1480160343135671</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1196739457634159</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>0.3628996403778135</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0269783360128968</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0288487046828432</v>
+      <c r="J20" s="24" t="n">
+        <v>0.029201204559906</v>
+      </c>
+      <c r="K20" s="24" t="n">
+        <v>0.0378562565940547</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2663,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2737,7 +2671,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2762,7 +2696,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, GARAN.IS, TOASO.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2708,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TUPRS.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2720,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>AKBNK.IS, PGSUS.IS, THYAO.IS, PETKM.IS</t>
+          <t>TUPRS.IS, EREGL.IS, THYAO.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2732,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ARCLK.IS, FROTO.IS, EREGL.IS, YKBNK.IS, SAHOL.IS, ASELS.IS, SISE.IS</t>
+          <t>TCELL.IS, GARAN.IS, ARCLK.IS, SAHOL.IS, TOASO.IS, AKBNK.IS, YKBNK.IS, SISE.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2744,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.31 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2782,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2856,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2941,7 +2875,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2953,7 +2887,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2965,7 +2899,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3049,7 +2983,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3099,7 +3033,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3107,7 +3041,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3131,7 +3065,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11947.2001953125</v>
+        <v>12249</v>
       </c>
     </row>
     <row r="5">
@@ -3141,7 +3075,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13569.603515625</v>
+        <v>13574.68001464844</v>
       </c>
     </row>
     <row r="6">
@@ -3175,7 +3109,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>67.95</v>
+        <v>72.61</v>
       </c>
     </row>
     <row r="9">
@@ -3202,7 +3136,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3211,14 +3145,14 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-29</t>
+          <t>Rapor Tarihi: 2026-09-30</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3232,7 +3166,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-01 07:54</t>
+          <t>Son Güncelleme: 2026-10-02 07:37</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3296,23 +3230,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>338.5</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>-0.1526908635794744</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>-107567.6202564484</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.1031377984986136</v>
+      <c r="D4" s="25" t="n">
+        <v>336.5</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>-0.1576971214017522</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>-111094.4274779713</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
     <row r="5">
@@ -3326,23 +3260,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>214.1000061035156</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.08680206143916558</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>252276.7146627312</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.1031377984986136</v>
+      <c r="D5" s="25" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>0.05786798932225579</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>168184.326366351</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
     <row r="6">
@@ -3356,23 +3290,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>86.80000305175781</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.1005181030905926</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-8826.944904498756</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.1031377984986136</v>
+      <c r="D6" s="25" t="n">
+        <v>84.80000305175781</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.1212434916916288</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-10646.93411719606</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
     <row r="7">
@@ -3386,147 +3320,87 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>129.1000061035156</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.03223379302629847</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-156098.6372269839</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.1031377984986136</v>
+      <c r="D7" s="25" t="n">
+        <v>122.9000015258789</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.07871059108708245</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-381171.8960284851</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="C8" s="28" t="n">
-        <v>38.86000061035156</v>
-      </c>
-      <c r="D8" s="28" t="n">
-        <v>36.7599983215332</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.05404020215735561</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-11763.54122428445</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.1031377984986136</v>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="C8" s="25" t="n">
+        <v>405.5</v>
+      </c>
+      <c r="D8" s="25" t="n">
+        <v>418.5</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>0.03205918618988912</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>90910.82118924987</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>421.75</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0.04007398273736129</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>113638.5264865626</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.1031377984986136</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="C10" s="28" t="n">
-        <v>417.25</v>
-      </c>
-      <c r="D10" s="28" t="n">
-        <v>376.5030517578125</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.09765595744083289</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-445832.9393991656</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>-0.1031377984986136</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n">
+      <c r="C9" s="25" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D11" s="28" t="n">
-        <v>74.40000152587891</v>
-      </c>
-      <c r="E11" s="29" t="n">
-        <v>-0.03875968915836447</v>
-      </c>
-      <c r="F11" s="28" t="n">
-        <v>-173530.4240112733</v>
-      </c>
-      <c r="G11" s="28" t="n">
-        <v>20099463.1837467</v>
-      </c>
-      <c r="H11" s="29" t="n">
-        <v>-0.1031377984986136</v>
+      <c r="D9" s="25" t="n">
+        <v>73.55000305175781</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>-0.04974158137237028</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>-222697.2892189957</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>19705694.02657917</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>-0.1281961328581071</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H11"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,7 +86,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -96,7 +96,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -150,6 +150,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -186,12 +189,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -607,7 +604,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +672,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 72.61/100</t>
+          <t>Güven Puanı: 75.77/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +732,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, FROTO.IS</t>
+          <t>AL: BIMAS.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -752,7 +749,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -769,7 +766,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: TUPRS.IS, EREGL.IS, THYAO.IS, PGSUS.IS, PETKM.IS</t>
+          <t>ÇIK: -</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -955,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2370015689047132</v>
+        <v>0.2569227197998707</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23700.15689047132</v>
+        <v>25692.27197998708</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0485935221290569</v>
+        <v>0.0438354098267489</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1151.674098319239</v>
+        <v>1126.231271623031</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>438.8363890110103</v>
+        <v>425.8848472093135</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>397.575</v>
+        <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.9718704425811387</v>
+        <v>0.8767081965349757</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -989,7 +986,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -998,25 +995,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1891968267277309</v>
+        <v>0.1847809963640967</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18919.68267277309</v>
+        <v>18478.09963640967</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0285714285714284</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>440.2246726425386</v>
+        <v>527.945703897416</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>213.2490614352234</v>
+        <v>398.0571428571428</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>194.617255911677</v>
+        <v>365.767852694762</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3518217892616216</v>
+        <v>0.5207736503606034</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1030,7 +1027,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1039,62 +1036,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1738016043675558</v>
+        <v>0.1582962838360325</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17380.16043675558</v>
+        <v>15829.62838360325</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0315183238607393</v>
+        <v>0.0265059178623019</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>547.7935253972706</v>
+        <v>419.5788297265506</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>75.86817586790147</v>
+        <v>129.5450437015751</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>69.87250289916992</v>
+        <v>116.8727931447235</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6303664772147827</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.3586333936512622</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>39999.99999999999</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1112,7 +1109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1120,7 +1117,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1135,7 +1132,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1156,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1198,7 +1195,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 5</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1336,463 +1333,292 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0314234662717713</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0485935221290569</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.08142280530855769</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>405.3492793652637</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>438.8363890110103</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>452.5754440216314</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>397.575</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="D8" s="15" t="n">
+        <v>408</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.02667302642785</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0438354098267489</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.0795481196044297</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>397.1174052174372</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>425.8848472093135</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>440.4556327986073</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>387.6</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M8" s="14" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>209.8999938964844</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0166358032889645</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0869050204659417</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>206.4081388876676</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>214.7839635538469</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>228.1413571618594</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>199.4049942016601</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>208.3999938964844</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.06613598075081251</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.06904391931949121</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>194.617255911677</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>213.2490614352234</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>222.7887462612557</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>194.617255911677</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>387</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.0431169977013468</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0285714285714284</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1756283386431509</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>370.3137218895788</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>398.0571428571428</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>454.9681670548994</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>365.767852694762</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="13" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="M10" s="14" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>Risk sinyali sınırlı</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>75.44999694824219</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.047717796601708</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.009999865017208299</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.0961029988959161</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>71.84968934026648</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>76.2044867332734</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>82.70096792165599</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>71.67749710083008</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
-        <v>73.55000305175781</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0475011878622574</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0315183238607393</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.0961031584456031</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>70.05629053952666</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>75.86817586790147</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>80.61839064871549</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>69.87250289916992</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0739081143349315</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.0265059178623019</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.0826997649837511</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>116.8727931447235</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>129.5450437015751</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>136.6367070368119</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>116.8727931447235</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>75.77</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>376.25</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0751524029661248</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.0049329293972443</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.1104291354757626</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>347.9739083839955</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>374.3939853142869</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>417.7989622227556</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>347.9739083839955</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>35.93999862670898</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.0348675647128589</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>33.59289747621857</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>35.18425158018333</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>37.19313885460582</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>33.59289747621857</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="16" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="17" t="n">
-        <v>283.25</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.06308392033297271</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0407844352132465</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.0454073760257329</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>265.3814795656855</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>271.6978087258479</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>296.1116392592888</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>265.3814795656855</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="16" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
+      <c r="O12" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>136.1000061035156</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0462686718992926</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.0194552529182879</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0673149458156319</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>129.8028395756203</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>133.4521460625912</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>145.2615706398809</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>129.2950057983398</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>18.90999984741211</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.1344322197940816</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.0316827048008266</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.0308602711215918</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>16.36788659161876</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>18.31087990446288</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>19.49356756961251</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>16.36788659161876</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>72.61</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1812,7 +1638,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
+    <col width="24" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1822,7 +1648,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1839,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1911,734 +1737,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>0.0313086453325817</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.1777111843078196</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.22496277119014</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.1054473269412359</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E4" s="16" t="n">
+        <v>0.0103833508464963</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.1497709977233934</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.1942289382212119</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.0860738353190809</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0190993116381614</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0485935221290569</v>
+      <c r="J4" s="16" t="n">
+        <v>0.0194135163494683</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.0438354098267489</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.0145540192653316</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1070674427187814</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.0870014876331113</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>0.0617187790758331</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0209011161906187</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0293432843097644</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.0758905378412067</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.0643513311968431</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.0756018134192069</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="E6" s="16" t="n">
+        <v>0.0042958834469577</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.5871679016310591</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>0.5388088480305013</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.06495109374227059</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J6" s="16" t="n">
+        <v>0.0274317148646485</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0285714285714284</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.0104918433017417</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>-0.0991045140508395</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-0.2507447940934695</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>0.0145514515489975</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0190139916779236</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.009999865017208299</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0439394170587713</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>-0.054681670799684</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-1.088185066944192e-06</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>0.0278214528154485</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0219836810151661</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.0265059178623019</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="21" t="n">
+        <v>-0.0260638186703872</v>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>-0.0867830342807164</v>
+      </c>
+      <c r="G9" s="21" t="n">
+        <v>0.3162383142651317</v>
+      </c>
+      <c r="H9" s="21" t="n">
+        <v>-0.1351999089132836</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0210882991743487</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="J9" s="21" t="n">
+        <v>0.0260951348532902</v>
+      </c>
+      <c r="K9" s="21" t="n">
+        <v>0.016724655661642</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0478964006244942</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>-0.1212663592181593</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>-0.2824389946169969</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.0102352037947996</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="21" t="n">
+        <v>-0.1024930747922437</v>
+      </c>
+      <c r="F10" s="21" t="n">
+        <v>-0.1916167418464079</v>
+      </c>
+      <c r="G10" s="21" t="n">
+        <v>-0.2689530887272393</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>0.1155858520987549</v>
+      </c>
+      <c r="I10" s="20" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0186924647901297</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0315183238607393</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="J10" s="21" t="n">
+        <v>0.0155420014820778</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.0490566934200201</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.5971327429661775</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.5093297423027483</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.0480105104047176</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0275227730050399</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>-0.0049329293972443</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>0.0051440330833163</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.0886194055078821</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.0860617815371082</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>-0.1002489595618008</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.0206969776313607</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.0047016180666799</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>-0.0487030230820493</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>-0.119117664245861</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.2657635096700415</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.1150367419711329</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.06918920568517729</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0888889050357556</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.0443951172890296</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.0168211059368003</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.0202251259166578</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.0394096913634611</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0171526586620925</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.1422155688622755</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>-0.0442035029190992</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>-0.09208993124339759</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0.020260833495684</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>0.0114739629302735</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>-0.0552447125628278</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>-0.0840677552304025</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>-0.0245486923933889</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>0.1761557752373423</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>0.0242756658707128</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <v>0.0096600462209198</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>-0.0570469798657717</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>-0.1929925613186818</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>-0.2146450263084049</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-0.0511380232457066</v>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>0.0192750337456335</v>
+      </c>
+      <c r="K15" s="23" t="n">
+        <v>0.0218960101593786</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="22" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="22" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="n">
+        <v>0.0182341650671784</v>
+      </c>
+      <c r="F16" s="23" t="n">
+        <v>-0.1216887417218542</v>
+      </c>
+      <c r="G16" s="23" t="n">
+        <v>-0.0157699443413729</v>
+      </c>
+      <c r="H16" s="23" t="n">
+        <v>-0.0483402259237579</v>
+      </c>
+      <c r="I16" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="23" t="n">
+        <v>0.0246940729390698</v>
+      </c>
+      <c r="K16" s="23" t="n">
+        <v>0.0124045801526717</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="22" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="22" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="n">
+        <v>-0.0282337491792514</v>
+      </c>
+      <c r="F17" s="23" t="n">
+        <v>-0.07384230287859821</v>
+      </c>
+      <c r="G17" s="23" t="n">
+        <v>0.099554234769688</v>
+      </c>
+      <c r="H17" s="23" t="n">
+        <v>-0.0798065338682971</v>
+      </c>
+      <c r="I17" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0260445109248329</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="J17" s="23" t="n">
+        <v>0.031484362145451</v>
+      </c>
+      <c r="K17" s="23" t="n">
+        <v>0.0414962223049317</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>-0.0046608447790051</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>-0.1134686612418669</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>-0.103544764833159</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.0667237892711047</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E18" s="23" t="n">
+        <v>-0.0349224521143445</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>-0.0841662473543188</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>0.0057770297258805</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.0251416593757456</v>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0206045904356744</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.0124595339704571</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="J18" s="23" t="n">
+        <v>0.0264489111327368</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>0.0523180466794031</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="22" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D19" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.0752444908191226</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>-0.1132756413149861</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>-0.0072475937442743</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>0.0232494182650186</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
+      <c r="E19" s="23" t="n">
+        <v>-0.0350877561989784</v>
+      </c>
+      <c r="F19" s="23" t="n">
+        <v>0.0169043681809517</v>
+      </c>
+      <c r="G19" s="23" t="n">
+        <v>-0.0374999999999999</v>
+      </c>
+      <c r="H19" s="23" t="n">
+        <v>0.2308682295438795</v>
+      </c>
+      <c r="I19" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="20" t="n">
-        <v>0.0221609022696276</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0.0233118944998451</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="J19" s="23" t="n">
+        <v>0.0391305386923763</v>
+      </c>
+      <c r="K19" s="23" t="n">
+        <v>0.0030632507027809</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.060530679933665</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.1500375093773444</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>-0.0494966442953019</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>-0.060616712968899</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>-0.0450127465528696</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>-0.1578709962992962</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>-0.1534175667167142</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>0.371326606622486</v>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
-        <v>0.0201934249564709</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>-0.0407844352132465</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.1058172083297264</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>-0.1909774742030858</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-0.2676951072317661</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>0.0879624110588572</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0.0155480620918477</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0.0462427745664739</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.0901286928276321</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>-0.1307021999090573</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>-0.063500826131539</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.0146618521552636</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>0.0204587359533638</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.0483517688336121</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.104015723685519</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.2310734118445444</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.2413600293540326</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>-0.0288769351755694</v>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0187973585994814</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>-0.0194552529182879</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.0223880597014924</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.1444897959183673</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.038532110091743</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.0325460006251897</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0246729486580986</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>0.0355140318659195</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="23" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="23" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="24" t="n">
-        <v>-0.06879773673657</v>
-      </c>
-      <c r="F16" s="24" t="n">
-        <v>-0.1404746295950831</v>
-      </c>
-      <c r="G16" s="24" t="n">
-        <v>-0.0183150183150183</v>
-      </c>
-      <c r="H16" s="24" t="n">
-        <v>0.1519405211493802</v>
-      </c>
-      <c r="I16" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="24" t="n">
-        <v>0.0251364935844182</v>
-      </c>
-      <c r="K16" s="24" t="n">
-        <v>0.0377795542969727</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.0755024117962623</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.1595061502338927</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.0064214073783998</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.0039801755863774</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0273291602426887</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>0.0423504428390855</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.073947121608233</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>0.0026510729290805</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-0.07030483256873719</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>0.2325193659505331</v>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.0390719900862105</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>-0.0316827048008266</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="23" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="23" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="24" t="n">
-        <v>-0.0722952606438102</v>
-      </c>
-      <c r="F19" s="24" t="n">
-        <v>-0.1752808817316976</v>
-      </c>
-      <c r="G19" s="24" t="n">
-        <v>-0.1668089139555892</v>
-      </c>
-      <c r="H19" s="24" t="n">
-        <v>0.3685019271262522</v>
-      </c>
-      <c r="I19" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="24" t="n">
-        <v>0.0273826627349781</v>
-      </c>
-      <c r="K19" s="24" t="n">
-        <v>0.0316196947808986</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="23" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="23" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="24" t="n">
-        <v>-0.1248374512353706</v>
-      </c>
-      <c r="F20" s="24" t="n">
-        <v>-0.1254061078622482</v>
-      </c>
-      <c r="G20" s="24" t="n">
-        <v>0.0507416081186573</v>
-      </c>
-      <c r="H20" s="24" t="n">
-        <v>-0.1324804890646602</v>
-      </c>
-      <c r="I20" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="24" t="n">
-        <v>0.029201204559906</v>
-      </c>
-      <c r="K20" s="24" t="n">
-        <v>0.0378562565940547</v>
+      <c r="J20" s="23" t="n">
+        <v>0.0274993725325908</v>
+      </c>
+      <c r="K20" s="23" t="n">
+        <v>0.0328525399081489</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2489,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2671,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2696,7 +2522,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
+          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2708,7 +2534,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2546,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, EREGL.IS, THYAO.IS, PGSUS.IS, PETKM.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2558,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, GARAN.IS, ARCLK.IS, SAHOL.IS, TOASO.IS, AKBNK.IS, YKBNK.IS, SISE.IS, ASELS.IS</t>
+          <t>EREGL.IS, ARCLK.IS, TCELL.IS, SAHOL.IS, THYAO.IS, AKBNK.IS, PGSUS.IS, TOASO.IS, ASELS.IS, YKBNK.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2570,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.65 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2608,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2790,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2839,7 +2665,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2677,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2875,7 +2701,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2887,7 +2713,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2899,7 +2725,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2785,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2995,7 +2821,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3007,7 +2833,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3033,7 +2859,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3041,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3065,7 +2891,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12249</v>
+        <v>12270.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3075,7 +2901,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13574.68001464844</v>
+        <v>13579.47451660156</v>
       </c>
     </row>
     <row r="6">
@@ -3109,7 +2935,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>72.61</v>
+        <v>75.77</v>
       </c>
     </row>
     <row r="9">
@@ -3136,7 +2962,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3152,7 +2978,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-09-30</t>
+          <t>Rapor Tarihi: 2026-10-01</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3166,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-02 07:37</t>
+          <t>Son Güncelleme: 2026-10-03 07:11</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3230,23 +3056,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="24" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>336.5</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>-0.1576971214017522</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>-111094.4274779713</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D4" s="24" t="n">
+        <v>370</v>
+      </c>
+      <c r="E4" s="25" t="n">
+        <v>-0.07384230287859828</v>
+      </c>
+      <c r="F4" s="24" t="n">
+        <v>-52020.4065174628</v>
+      </c>
+      <c r="G4" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H4" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="5">
@@ -3260,23 +3086,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="24" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>208.3999938964844</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>0.05786798932225579</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>168184.326366351</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D5" s="24" t="n">
+        <v>209.8999938964844</v>
+      </c>
+      <c r="E5" s="25" t="n">
+        <v>0.0654822025202253</v>
+      </c>
+      <c r="F5" s="24" t="n">
+        <v>190313.8548415657</v>
+      </c>
+      <c r="G5" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H5" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="6">
@@ -3290,23 +3116,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="24" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>84.80000305175781</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.1212434916916288</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-10646.93411719606</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D6" s="24" t="n">
+        <v>86.09999847412109</v>
+      </c>
+      <c r="E6" s="25" t="n">
+        <v>-0.1077720365376053</v>
+      </c>
+      <c r="F6" s="24" t="n">
+        <v>-9463.945294567529</v>
+      </c>
+      <c r="G6" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H6" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="7">
@@ -3320,23 +3146,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="24" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>122.9000015258789</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.07871059108708245</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-381171.8960284851</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D7" s="24" t="n">
+        <v>126.1999969482422</v>
+      </c>
+      <c r="E7" s="25" t="n">
+        <v>-0.05397299308596093</v>
+      </c>
+      <c r="F7" s="24" t="n">
+        <v>-261375.0935518565</v>
+      </c>
+      <c r="G7" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H7" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="8">
@@ -3350,23 +3176,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="24" t="n">
         <v>405.5</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>418.5</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>0.03205918618988912</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>90910.82118924987</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D8" s="24" t="n">
+        <v>408</v>
+      </c>
+      <c r="E8" s="25" t="n">
+        <v>0.006165228113440113</v>
+      </c>
+      <c r="F8" s="24" t="n">
+        <v>17482.85022870218</v>
+      </c>
+      <c r="G8" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H8" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
     <row r="9">
@@ -3380,27 +3206,57 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C9" s="25" t="n">
+      <c r="C9" s="24" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D9" s="25" t="n">
-        <v>73.55000305175781</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>-0.04974158137237028</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>-222697.2892189957</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>19705694.02657917</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>-0.1281961328581071</v>
+      <c r="D9" s="24" t="n">
+        <v>75.44999694824219</v>
+      </c>
+      <c r="E9" s="25" t="n">
+        <v>-0.02519385709552902</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>-112795.0403937409</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H9" s="25" t="n">
+        <v>-0.1061733800350263</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C10" s="24" t="n">
+        <v>387</v>
+      </c>
+      <c r="D10" s="24" t="n">
+        <v>387</v>
+      </c>
+      <c r="E10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>19944351.64517885</v>
+      </c>
+      <c r="H10" s="25" t="n">
+        <v>-0.1061733800350263</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -952,25 +952,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2569227197998707</v>
+        <v>0.2569227197998708</v>
       </c>
       <c r="E20" s="8" t="n">
         <v>25692.27197998708</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1126.231271623031</v>
+        <v>1126.231271623034</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8767081965349757</v>
+        <v>0.8767081965349784</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -995,16 +995,16 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1847809963640967</v>
+        <v>0.1847809963640966</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18478.09963640967</v>
+        <v>18478.09963640966</v>
       </c>
       <c r="F21" s="7" t="n">
         <v>0.0285714285714284</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>527.945703897416</v>
+        <v>527.9457038974157</v>
       </c>
       <c r="H21" s="8" t="n">
         <v>398.0571428571428</v>
@@ -1013,7 +1013,7 @@
         <v>365.767852694762</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5207736503606034</v>
+        <v>0.5207736503606021</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1045,7 +1045,7 @@
         <v>0.0265059178623019</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>419.5788297265506</v>
+        <v>419.5788297265505</v>
       </c>
       <c r="H22" s="8" t="n">
         <v>129.5450437015751</v>
@@ -1054,7 +1054,7 @@
         <v>116.8727931447235</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3586333936512622</v>
+        <v>0.3586333936512606</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1077,10 +1077,10 @@
         </is>
       </c>
       <c r="D23" s="12" t="n">
-        <v>0.4</v>
+        <v>0.4000000000000001</v>
       </c>
       <c r="E23" s="13" t="n">
-        <v>40000</v>
+        <v>40000.00000000001</v>
       </c>
       <c r="F23" s="12" t="n">
         <v>0</v>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1353,19 +1353,19 @@
         <v>-0.02667302642785</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0795481196044297</v>
+        <v>0.0795481196044298</v>
       </c>
       <c r="H8" s="15" t="n">
         <v>397.1174052174372</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>425.8848472093135</v>
+        <v>425.8848472093136</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>440.4556327986073</v>
+        <v>440.4556327986074</v>
       </c>
       <c r="K8" s="15" t="n">
         <v>387.6</v>
@@ -1410,22 +1410,22 @@
         <v>-0.0166358032889645</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0869050204659417</v>
+        <v>0.08690502046594149</v>
       </c>
       <c r="H9" s="18" t="n">
         <v>206.4081388876676</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>214.7839635538469</v>
+        <v>214.783963553847</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>228.1413571618594</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>199.4049942016601</v>
+        <v>199.4049942016602</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1776,7 +1776,7 @@
         <v>0.0194135163494683</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0438354098267489</v>
+        <v>0.043835409826749</v>
       </c>
     </row>
     <row r="5">
@@ -1799,13 +1799,13 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0145540192653316</v>
+        <v>-0.0145540192653313</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1070674427187814</v>
+        <v>0.1070674427187816</v>
       </c>
       <c r="G5" s="19" t="n">
-        <v>0.0870014876331113</v>
+        <v>0.0870014876331117</v>
       </c>
       <c r="H5" s="19" t="n">
         <v>0.0617187790758331</v>
@@ -1816,10 +1816,10 @@
         </is>
       </c>
       <c r="J5" s="19" t="n">
-        <v>0.0209011161906187</v>
+        <v>0.0209011161906186</v>
       </c>
       <c r="K5" s="19" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0232680790823232</v>
       </c>
     </row>
     <row r="6">
@@ -1859,7 +1859,7 @@
         </is>
       </c>
       <c r="J6" s="16" t="n">
-        <v>0.0274317148646485</v>
+        <v>0.0274317148646486</v>
       </c>
       <c r="K6" s="16" t="n">
         <v>0.0285714285714284</v>
@@ -1891,7 +1891,7 @@
         <v>-0.0991045140508395</v>
       </c>
       <c r="G7" s="19" t="n">
-        <v>-0.2507447940934695</v>
+        <v>-0.2507447940934696</v>
       </c>
       <c r="H7" s="19" t="n">
         <v>0.0145514515489975</v>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0439394170587713</v>
+        <v>-0.0439394170587712</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.054681670799684</v>
+        <v>-0.0546816707996838</v>
       </c>
       <c r="G8" s="16" t="n">
         <v>-1.088185066944192e-06</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="E9" s="21" t="n">
-        <v>-0.0260638186703872</v>
+        <v>-0.0260638186703869</v>
       </c>
       <c r="F9" s="21" t="n">
-        <v>-0.0867830342807164</v>
+        <v>-0.08678303428071631</v>
       </c>
       <c r="G9" s="21" t="n">
         <v>0.3162383142651317</v>
@@ -2017,7 +2017,7 @@
         <v>-0.1024930747922437</v>
       </c>
       <c r="F10" s="21" t="n">
-        <v>-0.1916167418464079</v>
+        <v>-0.1916167418464081</v>
       </c>
       <c r="G10" s="21" t="n">
         <v>-0.2689530887272393</v>
@@ -2031,7 +2031,7 @@
         </is>
       </c>
       <c r="J10" s="21" t="n">
-        <v>0.0155420014820778</v>
+        <v>0.0155420014820779</v>
       </c>
       <c r="K10" s="21" t="n">
         <v>0.0007363095911598</v>
@@ -2060,10 +2060,10 @@
         <v>0.0051440330833163</v>
       </c>
       <c r="F11" s="21" t="n">
-        <v>-0.0886194055078821</v>
+        <v>-0.088619405507882</v>
       </c>
       <c r="G11" s="21" t="n">
-        <v>-0.0860617815371082</v>
+        <v>-0.0860617815371079</v>
       </c>
       <c r="H11" s="21" t="n">
         <v>-0.1002489595618008</v>
@@ -2120,7 +2120,7 @@
         <v>0.0202251259166578</v>
       </c>
       <c r="K12" s="21" t="n">
-        <v>0.0394096913634611</v>
+        <v>0.0394096913634612</v>
       </c>
     </row>
     <row r="13">
@@ -2203,7 +2203,7 @@
         </is>
       </c>
       <c r="J14" s="23" t="n">
-        <v>0.0242756658707128</v>
+        <v>0.0242756658707127</v>
       </c>
       <c r="K14" s="23" t="n">
         <v>0.0096600462209198</v>
@@ -2332,7 +2332,7 @@
         </is>
       </c>
       <c r="J17" s="23" t="n">
-        <v>0.031484362145451</v>
+        <v>0.0314843621454511</v>
       </c>
       <c r="K17" s="23" t="n">
         <v>0.0414962223049317</v>
@@ -2375,7 +2375,7 @@
         </is>
       </c>
       <c r="J18" s="23" t="n">
-        <v>0.0264489111327368</v>
+        <v>0.0264489111327367</v>
       </c>
       <c r="K18" s="23" t="n">
         <v>0.0523180466794031</v>
@@ -2444,7 +2444,7 @@
         </is>
       </c>
       <c r="E20" s="23" t="n">
-        <v>-0.0450127465528696</v>
+        <v>-0.0450127465528694</v>
       </c>
       <c r="F20" s="23" t="n">
         <v>-0.1578709962992962</v>
@@ -2461,7 +2461,7 @@
         </is>
       </c>
       <c r="J20" s="23" t="n">
-        <v>0.0274993725325908</v>
+        <v>0.0274993725325907</v>
       </c>
       <c r="K20" s="23" t="n">
         <v>0.0328525399081489</v>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-03 07:11</t>
+          <t>Son Güncelleme: 2026-10-04 07:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3069,7 +3069,7 @@
         <v>-52020.4065174628</v>
       </c>
       <c r="G4" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H4" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3096,10 +3096,10 @@
         <v>0.0654822025202253</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>190313.8548415657</v>
+        <v>190313.8548415662</v>
       </c>
       <c r="G5" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H5" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3129,7 +3129,7 @@
         <v>-9463.945294567529</v>
       </c>
       <c r="G6" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H6" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3153,13 +3153,13 @@
         <v>126.1999969482422</v>
       </c>
       <c r="E7" s="25" t="n">
-        <v>-0.05397299308596093</v>
+        <v>-0.05397299308596082</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>-261375.0935518565</v>
+        <v>-261375.0935518555</v>
       </c>
       <c r="G7" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H7" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3189,7 +3189,7 @@
         <v>17482.85022870218</v>
       </c>
       <c r="G8" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H8" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3219,7 +3219,7 @@
         <v>-112795.0403937409</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H9" s="25" t="n">
         <v>-0.1061733800350263</v>
@@ -3249,7 +3249,7 @@
         <v>0</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>19944351.64517885</v>
+        <v>19944351.64517886</v>
       </c>
       <c r="H10" s="25" t="n">
         <v>-0.1061733800350263</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -621,7 +621,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1153,7 +1153,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1665,7 +1665,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2497,7 +2497,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2616,7 +2616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2867,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2992,7 +2992,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-04 07:30</t>
+          <t>Son Güncelleme: 2026-10-05 07:47</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$12</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -87,6 +87,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,10 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -188,7 +190,22 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -604,7 +621,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -621,7 +638,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -672,7 +689,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 75.77/100</t>
+          <t>Güven Puanı: 68.99/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -732,7 +749,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, TUPRS.IS, GARAN.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -749,7 +766,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, FROTO.IS</t>
+          <t>AZALT: TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -766,7 +783,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: -</t>
+          <t>ÇIK: THYAO.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -952,25 +969,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2569227197998708</v>
+        <v>0.2599858817138774</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>25692.27197998708</v>
+        <v>25998.58817138774</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.043835409826749</v>
+        <v>0.0480373342181153</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1126.231271623034</v>
+        <v>1248.902869188092</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>425.8848472093136</v>
+        <v>433.8874563662997</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>387.6</v>
+        <v>393.3</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8767081965349784</v>
+        <v>0.960746684362303</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -986,7 +1003,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -995,29 +1012,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1847809963640966</v>
+        <v>0.1822394667326065</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18478.09963640966</v>
+        <v>18223.94667326065</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0285714285714284</v>
+        <v>0.0175710278888081</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>527.9457038974157</v>
+        <v>320.2134752400145</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>398.0571428571428</v>
+        <v>210.4336916727859</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>365.767852694762</v>
+        <v>196.4600028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5207736503606021</v>
+        <v>0.3514205577761639</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1044,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1036,62 +1053,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1582962838360325</v>
+        <v>0.1577746515535162</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>15829.62838360325</v>
+        <v>15777.46515535162</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0265059178623019</v>
+        <v>0.0081576947549393</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>419.5788297265505</v>
+        <v>128.7077447440494</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>129.5450437015751</v>
+        <v>74.75489460440531</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>116.8727931447235</v>
+        <v>70.44250144958495</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3586333936512606</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
+        <v>0.1631538950987852</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.4000000000000001</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>40000.00000000001</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>39999.99999999999</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1109,7 +1126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O12"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1117,7 +1134,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1132,7 +1149,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1153,7 +1170,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1195,7 +1212,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 5</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1333,292 +1350,349 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>408</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.02667302642785</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.043835409826749</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0795481196044298</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>397.1174052174372</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>425.8848472093136</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>440.4556327986074</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>387.6</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D8" s="14" t="n">
+        <v>414</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>0.0187532125021777</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0480373342181153</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.08658758396009129</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>421.7638299759016</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>433.8874563662997</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>449.8472597594778</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>393.3</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>HIGH</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M8" s="13" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>Risk sinyali sınırlı</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>206.8000030517578</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0175710278888081</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.0535160660679254</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>200.5450004551365</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>210.4336916727859</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>217.8671256779229</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>196.4600028991699</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="13" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>74.15000152587891</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0477178908449019</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0081576947549393</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.0961029912293149</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>70.61171984691771</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>74.75489460440531</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>81.27603847217414</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>70.44250144958495</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>209.8999938964844</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0166358032889645</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0232680790823232</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.08690502046594149</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>206.4081388876676</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>214.783963553847</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>228.1413571618594</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>199.4049942016602</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="D11" s="17" t="n">
+        <v>377</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.06474817369495731</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0019933554817275</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.1094016557937762</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>352.5899385170011</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>377.7514950166113</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>418.2444242342536</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>352.5899385170011</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="15" t="n">
-        <v>387</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.0431169977013468</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0285714285714284</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1756283386431509</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>370.3137218895788</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>398.0571428571428</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>454.9681670548994</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>365.767852694762</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>Risk sinyali sınırlı</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>75.44999694824219</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.047717796601708</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.009999865017208299</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.0961029988959161</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>71.84968934026648</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>76.2044867332734</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>82.70096792165599</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>71.67749710083008</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>292</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0608602533895163</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0059141356137313</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.0475785896346643</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>274.2288060102612</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>290.2730724007905</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>305.892948173322</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>274.2288060102612</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>126.1999969482422</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0739081143349315</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.0265059178623019</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0826997649837511</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>116.8727931447235</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>129.5450437015751</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>136.6367070368119</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>116.8727931447235</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+      <c r="M12" s="19" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>259.25</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0829261006515727</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0068635274969548</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.1059738126207166</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>237.7514084060798</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>257.4706304964145</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>286.7237109219208</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>237.7514084060798</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>75.77</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="M13" s="19" t="n">
+        <v>68.98999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O12"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1638,7 +1712,7 @@
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="21" customWidth="1" min="5" max="5"/>
     <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="24" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
@@ -1648,7 +1722,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1665,7 +1739,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1737,734 +1811,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>0.0103833508464963</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.1497709977233934</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.1942289382212119</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.0860738353190809</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="n">
+        <v>0.0090964047521868</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.1226537025607616</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.2215137369457347</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>-0.0771765910537707</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0194135163494683</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.043835409826749</v>
+      <c r="J4" s="15" t="n">
+        <v>0.0189027431918166</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0480373342181153</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0443622509958052</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.1000000162327543</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.0810245674476353</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.0553077848966356</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>0.0209663935284886</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0175710278888081</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.019828155581555</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>-0.0957316887087937</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-0.2555220616278907</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>0.0341666180106403</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="15" t="n">
+        <v>0.0189591428141435</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0081576947549393</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.0145540192653313</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1070674427187816</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.0870014876331117</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>0.0617187790758331</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E7" s="18" t="n">
+        <v>-0.0185272063846909</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.5511555249403384</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.5034510145785096</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.1021696941251346</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0277237702974423</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0019933554817275</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>0.0017152658662091</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.1585014409221902</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-0.0135135135135134</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.1145747265739567</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.0197608845538712</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-0.0059141356137313</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>0.0120283926923001</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.1083815016952525</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0.2850465937708701</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.1480337378864555</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0209011161906186</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0232680790823232</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
+      <c r="J9" s="23" t="n">
+        <v>0.0257222202511619</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0178975596031467</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0042958834469577</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.5871679016310591</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>0.5388088480305013</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>-0.06495109374227059</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0274317148646486</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0285714285714284</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>-0.0418568693004529</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-0.0583395332864727</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>-0.0091698516561644</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>0.0180717821465905</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>0.0219829746451994</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.0244100892005951</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.0104918433017417</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.0991045140508395</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-0.2507447940934696</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>0.0145514515489975</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>0.0124224078322132</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.09944747305808541</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.09023252975109</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-0.1063482771459283</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0190139916779236</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.009999865017208299</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J11" s="23" t="n">
+        <v>0.0206180855749656</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0124595325163139</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0439394170587712</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>-0.0546816707996838</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>-1.088185066944192e-06</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>0.0278214528154485</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>-0.06774196829847109</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.0737179662218332</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>-0.0258427309186271</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>-0.0248600098346968</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0219836810151661</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.0265059178623019</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="20" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="20" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0202233716553744</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.0444882765564661</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="20" t="inlineStr">
+      <c r="D13" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="21" t="n">
-        <v>-0.0260638186703869</v>
-      </c>
-      <c r="F9" s="21" t="n">
-        <v>-0.08678303428071631</v>
-      </c>
-      <c r="G9" s="21" t="n">
-        <v>0.3162383142651317</v>
-      </c>
-      <c r="H9" s="21" t="n">
-        <v>-0.1351999089132836</v>
-      </c>
-      <c r="I9" s="20" t="inlineStr">
+      <c r="E13" s="23" t="n">
+        <v>-0.0872256627247698</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>-0.1857429747331455</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-0.2600364999706588</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>0.1038579346379695</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0155481234976726</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>-0.04453435209605</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1899313293399186</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.1981879886203653</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0497477258349482</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0193040415237895</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0073660782405308</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>-0.0267410266954416</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0672717704045066</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.0151075097451001</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.0516228777912411</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.0263964057649921</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0540408302593511</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>-0.0621943310668718</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.08707485069222989</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.0240000221946022</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>0.1617320186239779</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="25" t="n">
+        <v>0.0242841291778718</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0391830585858164</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0047984644913627</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.1401326699834162</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>-0.0189214758751182</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.0496255841926664</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0248335343605494</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>-0.0068635274969548</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.0460223537146614</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0970752955818294</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0975794251134645</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.0501570897509607</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="21" t="n">
-        <v>0.0260951348532902</v>
-      </c>
-      <c r="K9" s="21" t="n">
-        <v>0.016724655661642</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="20" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="20" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0315624463004209</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0723427667211422</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="20" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="21" t="n">
-        <v>-0.1024930747922437</v>
-      </c>
-      <c r="F10" s="21" t="n">
-        <v>-0.1916167418464081</v>
-      </c>
-      <c r="G10" s="21" t="n">
-        <v>-0.2689530887272393</v>
-      </c>
-      <c r="H10" s="21" t="n">
-        <v>0.1155858520987549</v>
-      </c>
-      <c r="I10" s="20" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.0331355142950691</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0.0376857260468297</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.0165995944485406</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0.233441474653725</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="21" t="n">
-        <v>0.0155420014820779</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>0.0007363095911598</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.0391660876761456</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0338444947018876</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="20" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="21" t="n">
-        <v>0.0051440330833163</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.088619405507882</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.0860617815371079</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>-0.1002489595618008</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.0377455809967326</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1439742039429477</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1430967781598141</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.3767394794125525</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="21" t="n">
-        <v>0.0206969776313607</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0047016180666799</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.06918920568517729</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0888889050357556</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.0443951172890296</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.0168211059368003</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0202251259166578</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>0.0394096913634612</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0171526586620925</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.1422155688622755</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>-0.0442035029190992</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>-0.09208993124339759</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0.020260833495684</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>0.0114739629302735</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="23" t="n">
-        <v>-0.0552447125628278</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>-0.0840677552304025</v>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>-0.0245486923933889</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <v>0.1761557752373423</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="23" t="n">
-        <v>0.0242756658707127</v>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>0.0096600462209198</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="23" t="n">
-        <v>-0.0570469798657717</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>-0.1929925613186818</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>-0.2146450263084049</v>
-      </c>
-      <c r="H15" s="23" t="n">
-        <v>-0.0511380232457066</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="23" t="n">
-        <v>0.0192750337456335</v>
-      </c>
-      <c r="K15" s="23" t="n">
-        <v>0.0218960101593786</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="22" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="22" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="23" t="n">
-        <v>0.0182341650671784</v>
-      </c>
-      <c r="F16" s="23" t="n">
-        <v>-0.1216887417218542</v>
-      </c>
-      <c r="G16" s="23" t="n">
-        <v>-0.0157699443413729</v>
-      </c>
-      <c r="H16" s="23" t="n">
-        <v>-0.0483402259237579</v>
-      </c>
-      <c r="I16" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="23" t="n">
-        <v>0.0246940729390698</v>
-      </c>
-      <c r="K16" s="23" t="n">
-        <v>0.0124045801526717</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="22" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="22" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="23" t="n">
-        <v>-0.0282337491792514</v>
-      </c>
-      <c r="F17" s="23" t="n">
-        <v>-0.07384230287859821</v>
-      </c>
-      <c r="G17" s="23" t="n">
-        <v>0.099554234769688</v>
-      </c>
-      <c r="H17" s="23" t="n">
-        <v>-0.0798065338682971</v>
-      </c>
-      <c r="I17" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="23" t="n">
-        <v>0.0314843621454511</v>
-      </c>
-      <c r="K17" s="23" t="n">
-        <v>0.0414962223049317</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="23" t="n">
-        <v>-0.0349224521143445</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>-0.0841662473543188</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>0.0057770297258805</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>-0.0251416593757456</v>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="23" t="n">
-        <v>0.0264489111327367</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>0.0523180466794031</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="22" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="22" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="23" t="n">
-        <v>-0.0350877561989784</v>
-      </c>
-      <c r="F19" s="23" t="n">
-        <v>0.0169043681809517</v>
-      </c>
-      <c r="G19" s="23" t="n">
-        <v>-0.0374999999999999</v>
-      </c>
-      <c r="H19" s="23" t="n">
-        <v>0.2308682295438795</v>
-      </c>
-      <c r="I19" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="23" t="n">
-        <v>0.0391305386923763</v>
-      </c>
-      <c r="K19" s="23" t="n">
-        <v>0.0030632507027809</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>-0.0450127465528694</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>-0.1578709962992962</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <v>-0.1534175667167142</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <v>0.371326606622486</v>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>0.0274993725325907</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>0.0328525399081489</v>
+      <c r="J20" s="25" t="n">
+        <v>0.027413043337168</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0325454537156234</v>
       </c>
     </row>
   </sheetData>
@@ -2489,7 +2563,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2497,7 +2571,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2522,7 +2596,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2534,7 +2608,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2546,7 +2620,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>THYAO.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2558,7 +2632,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, ARCLK.IS, TCELL.IS, SAHOL.IS, THYAO.IS, AKBNK.IS, PGSUS.IS, TOASO.IS, ASELS.IS, YKBNK.IS, PETKM.IS, SISE.IS</t>
+          <t>EREGL.IS, GARAN.IS, TCELL.IS, SAHOL.IS, ARCLK.IS, PGSUS.IS, YKBNK.IS, AKBNK.IS, ASELS.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2570,7 +2644,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.65 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.82 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2682,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2616,7 +2690,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2701,7 +2775,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2787,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2799,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2821,7 +2895,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2933,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2867,7 +2941,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2891,7 +2965,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12270.2001953125</v>
+        <v>12443.900390625</v>
       </c>
     </row>
     <row r="5">
@@ -2901,7 +2975,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13579.47451660156</v>
+        <v>13584.41251953125</v>
       </c>
     </row>
     <row r="6">
@@ -2935,7 +3009,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>75.77</v>
+        <v>68.98999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2978,7 +3052,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-01</t>
+          <t>Rapor Tarihi: 2026-10-02</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2992,7 +3066,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-05 07:47</t>
+          <t>Son Güncelleme: 2026-10-06 08:14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3056,23 +3130,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n">
+      <c r="C4" s="28" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="24" t="n">
-        <v>370</v>
-      </c>
-      <c r="E4" s="25" t="n">
-        <v>-0.07384230287859828</v>
-      </c>
-      <c r="F4" s="24" t="n">
-        <v>-52020.4065174628</v>
-      </c>
-      <c r="G4" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H4" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D4" s="28" t="n">
+        <v>362.75</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>-0.0919899874843555</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>-64805.08269548335</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="5">
@@ -3086,23 +3160,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="24" t="n">
+      <c r="C5" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="24" t="n">
-        <v>209.8999938964844</v>
-      </c>
-      <c r="E5" s="25" t="n">
-        <v>0.0654822025202253</v>
-      </c>
-      <c r="F5" s="24" t="n">
-        <v>190313.8548415662</v>
-      </c>
-      <c r="G5" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H5" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D5" s="28" t="n">
+        <v>206.8000030517578</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>0.04974620838455746</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>144579.6310607111</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="6">
@@ -3116,23 +3190,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n">
+      <c r="C6" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="24" t="n">
-        <v>86.09999847412109</v>
-      </c>
-      <c r="E6" s="25" t="n">
-        <v>-0.1077720365376053</v>
-      </c>
-      <c r="F6" s="24" t="n">
-        <v>-9463.945294567529</v>
-      </c>
-      <c r="G6" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H6" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D6" s="28" t="n">
+        <v>86.69999694824219</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.1015544357695111</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-8917.949919299906</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="7">
@@ -3146,23 +3220,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="24" t="n">
+      <c r="C7" s="28" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="24" t="n">
-        <v>126.1999969482422</v>
-      </c>
-      <c r="E7" s="25" t="n">
-        <v>-0.05397299308596082</v>
-      </c>
-      <c r="F7" s="24" t="n">
-        <v>-261375.0935518555</v>
-      </c>
-      <c r="G7" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H7" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D7" s="28" t="n">
+        <v>125.9000015258789</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.05622183443595441</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-272265.5608880231</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="8">
@@ -3176,23 +3250,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n">
+      <c r="C8" s="28" t="n">
         <v>405.5</v>
       </c>
-      <c r="D8" s="24" t="n">
-        <v>408</v>
-      </c>
-      <c r="E8" s="25" t="n">
-        <v>0.006165228113440113</v>
-      </c>
-      <c r="F8" s="24" t="n">
-        <v>17482.85022870218</v>
-      </c>
-      <c r="G8" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H8" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D8" s="28" t="n">
+        <v>414</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>0.02096177558569656</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>59441.69077758677</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="9">
@@ -3206,23 +3280,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n">
+      <c r="C9" s="28" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D9" s="24" t="n">
-        <v>75.44999694824219</v>
-      </c>
-      <c r="E9" s="25" t="n">
-        <v>-0.02519385709552902</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-112795.0403937409</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H9" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D9" s="28" t="n">
+        <v>74.15000152587891</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>-0.04198966325489484</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>-187991.2926788786</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
     <row r="10">
@@ -3236,23 +3310,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n">
+      <c r="C10" s="28" t="n">
         <v>387</v>
       </c>
-      <c r="D10" s="24" t="n">
-        <v>387</v>
-      </c>
-      <c r="E10" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>19944351.64517886</v>
-      </c>
-      <c r="H10" s="25" t="n">
-        <v>-0.1061733800350263</v>
+      <c r="D10" s="28" t="n">
+        <v>377</v>
+      </c>
+      <c r="E10" s="29" t="n">
+        <v>-0.02583979328165376</v>
+      </c>
+      <c r="F10" s="28" t="n">
+        <v>-111577.9237274509</v>
+      </c>
+      <c r="G10" s="28" t="n">
+        <v>19730672.93779538</v>
+      </c>
+      <c r="H10" s="29" t="n">
+        <v>-0.1046263722042833</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -97,11 +97,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
       </patternFill>
     </fill>
   </fills>
@@ -157,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -621,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -638,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -689,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 68.99/100</t>
+          <t>Güven Puanı: 74.86/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -749,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, FROTO.IS</t>
+          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -766,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS</t>
+          <t>AZALT: KCHOL.IS, EREGL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -783,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, TOASO.IS</t>
+          <t>ÇIK: PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -969,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2599858817138774</v>
+        <v>0.2496192428796928</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>25998.58817138774</v>
+        <v>24961.92428796928</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0480373342181153</v>
+        <v>0.0432795011507813</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1248.902869188092</v>
+        <v>1080.339630946882</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>433.8874563662997</v>
+        <v>431.3960737258481</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>393.3</v>
+        <v>392.825</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.960746684362303</v>
+        <v>0.8655900230156277</v>
       </c>
       <c r="K20" s="6" t="inlineStr">
         <is>
@@ -1003,7 +998,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1012,29 +1007,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1822394667326065</v>
+        <v>0.1771987150724769</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18223.94667326065</v>
+        <v>17719.87150724769</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0175710278888081</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>320.2134752400145</v>
+        <v>586.8367124484538</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>210.4336916727859</v>
+        <v>134.7185073625788</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>196.4600028991699</v>
+        <v>123.8799942016602</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3514205577761639</v>
+        <v>0.6623487221207344</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1044,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1053,29 +1048,29 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1577746515535162</v>
+        <v>0.1731820420478303</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>15777.46515535162</v>
+        <v>17318.20420478303</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0081576947549393</v>
+        <v>0.0398671096345515</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>128.7077447440494</v>
+        <v>690.4267457056359</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>74.75489460440531</v>
+        <v>406.8480066445183</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>70.44250144958495</v>
+        <v>357.7760386066882</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1631538950987852</v>
+        <v>0.465974327365833</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -1094,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>39999.99999999999</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1126,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1149,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1170,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1212,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1364,28 +1359,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>414</v>
+        <v>413.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>0.0187532125021777</v>
+        <v>-0.0168164405252459</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0480373342181153</v>
+        <v>0.0432795011507813</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.08658758396009129</v>
+        <v>0.0795480343837232</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>421.7638299759016</v>
+        <v>406.5464018428108</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>433.8874563662997</v>
+        <v>431.3960737258481</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>449.8472597594778</v>
+        <v>446.3931122176695</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>393.3</v>
+        <v>392.825</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1393,7 +1388,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>68.98999999999999</v>
+        <v>74.86</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1407,57 +1402,57 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="13" t="n">
+      <c r="A9" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="13" t="inlineStr">
+      <c r="B9" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>206.8000030517578</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0302466271968858</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0175710278888081</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.0535160660679254</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>200.5450004551365</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>210.4336916727859</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>217.8671256779229</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>196.4600028991699</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="C9" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="n">
+        <v>214.8999938964844</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0475169610822255</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.025967427052516</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.06904386578716611</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>204.6885992499346</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>220.4803938115775</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>229.7375202327361</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>204.1549942016601</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="16" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
@@ -1469,7 +1464,7 @@
       </c>
       <c r="B10" s="13" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="13" t="inlineStr">
@@ -1478,221 +1473,278 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>74.15000152587891</v>
+        <v>130.3999938964844</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0477178908449019</v>
+        <v>-0.0446735827301302</v>
       </c>
       <c r="F10" s="15" t="n">
-        <v>0.0081576947549393</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.0961029912293149</v>
+        <v>0.0795559387098858</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>70.61171984691771</v>
+        <v>124.5745589811413</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>74.75489460440531</v>
+        <v>134.7185073625788</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>81.27603847217414</v>
+        <v>140.7740878186826</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>70.44250144958495</v>
+        <v>123.8799942016602</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="13" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="14" t="n">
+        <v>391.25</v>
+      </c>
+      <c r="E11" s="15" t="n">
+        <v>-0.0855564508455252</v>
+      </c>
+      <c r="F11" s="15" t="n">
+        <v>0.0398671096345515</v>
+      </c>
+      <c r="G11" s="15" t="n">
+        <v>0.1268436896227545</v>
+      </c>
+      <c r="H11" s="14" t="n">
+        <v>357.7760386066882</v>
+      </c>
+      <c r="I11" s="14" t="n">
+        <v>406.8480066445183</v>
+      </c>
+      <c r="J11" s="14" t="n">
+        <v>440.8775935649027</v>
+      </c>
+      <c r="K11" s="14" t="n">
+        <v>357.7760386066882</v>
+      </c>
+      <c r="L11" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N11" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="13" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>37.63999938964844</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.06569465539051229</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>0.0167247463187438</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0473010803533</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>35.16725260084639</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>38.26951883087798</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>39.42041202527636</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>35.16725260084639</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="13" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>377</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.06474817369495731</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.0019933554817275</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.1094016557937762</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>352.5899385170011</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>377.7514950166113</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>418.2444242342536</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>352.5899385170011</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>292</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0608602533895163</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0059141356137313</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.0475785896346643</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>274.2288060102612</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>290.2730724007905</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>305.892948173322</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>274.2288060102612</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="19" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M12" s="16" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="n">
+        <v>142.8999938964844</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0601762081116165</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.0097276264591439</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.129632824695417</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>134.3008141246208</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>141.5099161348454</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>161.4245237542435</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>134.3008141246208</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="19" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0829261006515727</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.0068635274969548</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.1059738126207166</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>237.7514084060798</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>257.4706304964145</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>286.7237109219208</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>237.7514084060798</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="D14" s="20" t="n">
+        <v>264.75</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.0887776816785481</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0216207187319253</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.0581759305162942</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>241.2461087756044</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>259.0259147157228</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>280.1520776041889</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>241.2461087756044</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>68.98999999999999</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
+      <c r="M14" s="19" t="n">
+        <v>74.86</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="O14" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1722,7 +1774,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1739,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1830,16 +1882,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0090964047521868</v>
+        <v>0.0006049606775559</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1226537025607616</v>
+        <v>0.1115605076129555</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.2215137369457347</v>
+        <v>0.1511856570777916</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0771765910537707</v>
+        <v>-0.0685757287095444</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1847,53 +1899,53 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0189027431918166</v>
+        <v>0.0188870682374456</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0480373342181153</v>
+        <v>0.0432795011507813</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="13" t="n">
+      <c r="A5" s="16" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="13" t="inlineStr">
+      <c r="B5" s="16" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0443622509958052</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.1000000162327543</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.0810245674476353</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.0553077848966356</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0209663935284886</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0175710278888081</v>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="18" t="n">
+        <v>-0.000929856817089</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.1358350811986151</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.1054526782079838</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.0479962500987813</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0214842246840753</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.025967427052516</v>
       </c>
     </row>
     <row r="6">
@@ -1902,7 +1954,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C6" s="13" t="inlineStr">
@@ -1916,113 +1968,113 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.019828155581555</v>
+        <v>-0.0076103504296034</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.0957316887087937</v>
+        <v>-0.029761906113484</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.2555220616278907</v>
+        <v>0.000513141059</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0341666180106403</v>
+        <v>0.0178849701902401</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0189591428141435</v>
+        <v>0.0224473481797315</v>
       </c>
       <c r="K6" s="15" t="n">
-        <v>0.0081576947549393</v>
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="13" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C7" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D7" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="15" t="n">
+        <v>0.0251254272362109</v>
+      </c>
+      <c r="F7" s="15" t="n">
+        <v>0.5436481167927154</v>
+      </c>
+      <c r="G7" s="15" t="n">
+        <v>0.5526753550658163</v>
+      </c>
+      <c r="H7" s="15" t="n">
+        <v>-0.1130716993750996</v>
+      </c>
+      <c r="I7" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J7" s="15" t="n">
+        <v>0.0276267189827164</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.0398671096345515</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.0185272063846909</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.5511555249403384</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.5034510145785096</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.1021696941251346</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0277237702974423</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.0019933554817275</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>0.0017152658662091</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1585014409221902</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0135135135135134</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.1145747265739567</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0197608845538712</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-0.0059141356137313</v>
+      <c r="E8" s="18" t="n">
+        <v>0.0118279198302417</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>-0.0877362840316821</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>0.2691880423812154</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.140788131432354</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0258165350177656</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>0.0167247463187438</v>
       </c>
     </row>
     <row r="9">
@@ -2031,7 +2083,7 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
@@ -2045,27 +2097,27 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>0.0120283926923001</v>
+        <v>-0.0343263471663222</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.1083815016952525</v>
+        <v>-0.1018071921474962</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>0.2850465937708701</v>
+        <v>-0.2574701004108854</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>-0.1480337378864555</v>
+        <v>0.0422829153016697</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0257222202511619</v>
+        <v>0.0188996417659717</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.0178975596031467</v>
+        <v>0.0203423204102901</v>
       </c>
     </row>
     <row r="10">
@@ -2074,7 +2126,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2088,16 +2140,16 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>-0.0418568693004529</v>
+        <v>-0.0410366683043225</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0583395332864727</v>
+        <v>-0.0431034468583914</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>-0.0091698516561644</v>
+        <v>-0.0321525552941928</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>0.0180717821465905</v>
+        <v>-0.0234315238855641</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
@@ -2105,10 +2157,10 @@
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0219829746451994</v>
+        <v>0.0204466472257388</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.0244100892005951</v>
+        <v>0.0471698096232213</v>
       </c>
     </row>
     <row r="11">
@@ -2117,7 +2169,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -2131,16 +2183,16 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>0.0124224078322132</v>
+        <v>-0.0977485033231647</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>-0.09944747305808541</v>
+        <v>-0.1685222774452401</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-0.09023252975109</v>
+        <v>-0.2558876776227028</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>-0.1063482771459283</v>
+        <v>0.1021016887639982</v>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
@@ -2148,10 +2200,10 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0206180855749656</v>
+        <v>0.0156657923401147</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>0.0124595325163139</v>
+        <v>0.0007363095911598</v>
       </c>
     </row>
     <row r="12">
@@ -2160,7 +2212,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2174,16 +2226,16 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>-0.06774196829847109</v>
+        <v>-0.0126689189189189</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.0737179662218332</v>
+        <v>-0.1608040201005025</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>-0.0258427309186271</v>
+        <v>-0.016820857863751</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>-0.0248600098346968</v>
+        <v>-0.1225059234796297</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
@@ -2191,10 +2243,10 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0202233716553744</v>
+        <v>0.0197501361683288</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>0.0444882765564661</v>
+        <v>0.0317740511915269</v>
       </c>
     </row>
     <row r="13">
@@ -2203,7 +2255,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2217,16 +2269,16 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0872256627247698</v>
+        <v>0.0239429285541221</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.1857429747331455</v>
+        <v>-0.0711644839687519</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-0.2600364999706588</v>
+        <v>-0.0745856223566272</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>0.1038579346379695</v>
+        <v>-0.1381962403630893</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
@@ -2234,10 +2286,10 @@
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0155481234976726</v>
+        <v>0.0209377966832188</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0007363095911598</v>
+        <v>0.0047015865685376</v>
       </c>
     </row>
     <row r="14">
@@ -2246,84 +2298,84 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.0452126866284913</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>0.0216278357834676</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0617809749780328</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.026630102357745</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0576923532547533</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.04453435209605</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.1899313293399186</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.1981879886203653</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0497477258349482</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.0390047287881022</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.1792074159289832</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.1989910381981217</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-0.0484163572712402</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0193040415237895</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0073660782405308</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.0267410266954416</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0672717704045066</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.0151075097451001</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.0516228777912411</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0263964057649921</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0540408302593511</v>
+      <c r="J15" s="27" t="n">
+        <v>0.0193660446130582</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>-0.0097276264591439</v>
       </c>
     </row>
     <row r="16">
@@ -2346,16 +2398,16 @@
         </is>
       </c>
       <c r="E16" s="25" t="n">
-        <v>-0.0621943310668718</v>
+        <v>-0.0403618870906925</v>
       </c>
       <c r="F16" s="25" t="n">
-        <v>-0.08707485069222989</v>
+        <v>-0.0631793698679752</v>
       </c>
       <c r="G16" s="25" t="n">
-        <v>-0.0240000221946022</v>
+        <v>-0.019203499927613</v>
       </c>
       <c r="H16" s="25" t="n">
-        <v>0.1617320186239779</v>
+        <v>0.1600771369091091</v>
       </c>
       <c r="I16" s="24" t="inlineStr">
         <is>
@@ -2363,96 +2415,96 @@
         </is>
       </c>
       <c r="J16" s="25" t="n">
-        <v>0.0242841291778718</v>
+        <v>0.0245510230622174</v>
       </c>
       <c r="K16" s="25" t="n">
-        <v>0.0391830585858164</v>
+        <v>0.0477419817054558</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="26" t="n">
+      <c r="A17" s="24" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="26" t="inlineStr">
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.0431423052157114</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.0300261096605743</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>0.1023738872403561</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.0357516465713041</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0311727846302145</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.0564292419222857</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="26" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C17" s="26" t="inlineStr">
+      <c r="C18" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="26" t="inlineStr">
+      <c r="D18" s="26" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.0047984644913627</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.1401326699834162</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.0189214758751182</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.0496255841926664</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
+      <c r="E18" s="27" t="n">
+        <v>-0.0346399270738377</v>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>-0.1145484949832775</v>
+      </c>
+      <c r="G18" s="27" t="n">
+        <v>-0.0046992481203007</v>
+      </c>
+      <c r="H18" s="27" t="n">
+        <v>-0.0818796613502346</v>
+      </c>
+      <c r="I18" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0248335343605494</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>-0.0068635274969548</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0460223537146614</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0970752955818294</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0975794251134645</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.0501570897509607</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0315624463004209</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0723427667211422</v>
+      <c r="J18" s="27" t="n">
+        <v>0.0249924370188186</v>
+      </c>
+      <c r="K18" s="27" t="n">
+        <v>-0.0216207187319253</v>
       </c>
     </row>
     <row r="19">
@@ -2475,16 +2527,16 @@
         </is>
       </c>
       <c r="E19" s="25" t="n">
-        <v>-0.0331355142950691</v>
+        <v>0.0019940636386983</v>
       </c>
       <c r="F19" s="25" t="n">
-        <v>0.0376857260468297</v>
+        <v>0.0490605710617779</v>
       </c>
       <c r="G19" s="25" t="n">
-        <v>-0.0165995944485406</v>
+        <v>-0.0364333751986897</v>
       </c>
       <c r="H19" s="25" t="n">
-        <v>0.233441474653725</v>
+        <v>0.2407167199401134</v>
       </c>
       <c r="I19" s="24" t="inlineStr">
         <is>
@@ -2492,10 +2544,10 @@
         </is>
       </c>
       <c r="J19" s="25" t="n">
-        <v>0.0391660876761456</v>
+        <v>0.0392630023399694</v>
       </c>
       <c r="K19" s="25" t="n">
-        <v>0.0338444947018876</v>
+        <v>0.0166223768740767</v>
       </c>
     </row>
     <row r="20">
@@ -2518,16 +2570,16 @@
         </is>
       </c>
       <c r="E20" s="25" t="n">
-        <v>-0.0377455809967326</v>
+        <v>-0.0250768503330733</v>
       </c>
       <c r="F20" s="25" t="n">
-        <v>-0.1439742039429477</v>
+        <v>-0.1172382157363333</v>
       </c>
       <c r="G20" s="25" t="n">
-        <v>-0.1430967781598141</v>
+        <v>-0.1385004917464062</v>
       </c>
       <c r="H20" s="25" t="n">
-        <v>0.3767394794125525</v>
+        <v>0.382997481507219</v>
       </c>
       <c r="I20" s="24" t="inlineStr">
         <is>
@@ -2535,10 +2587,10 @@
         </is>
       </c>
       <c r="J20" s="25" t="n">
-        <v>0.027413043337168</v>
+        <v>0.0275946765368713</v>
       </c>
       <c r="K20" s="25" t="n">
-        <v>0.0325454537156234</v>
+        <v>0.046011499209606</v>
       </c>
     </row>
   </sheetData>
@@ -2563,7 +2615,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2571,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2596,7 +2648,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, FROTO.IS</t>
+          <t>BIMAS.IS, GARAN.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2608,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>KCHOL.IS, EREGL.IS</t>
         </is>
       </c>
     </row>
@@ -2620,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, TOASO.IS</t>
+          <t>PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2632,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, GARAN.IS, TCELL.IS, SAHOL.IS, ARCLK.IS, PGSUS.IS, YKBNK.IS, AKBNK.IS, ASELS.IS, PETKM.IS, SISE.IS</t>
+          <t>FROTO.IS, SAHOL.IS, ARCLK.IS, THYAO.IS, TCELL.IS, YKBNK.IS, AKBNK.IS, ASELS.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.82 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %3.31 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2682,7 +2734,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2690,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2775,7 +2827,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2839,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2851,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2947,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2933,7 +2985,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2941,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2965,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12443.900390625</v>
+        <v>12374.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -2975,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13584.41251953125</v>
+        <v>13589.54001953125</v>
       </c>
     </row>
     <row r="6">
@@ -3009,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>68.98999999999999</v>
+        <v>74.86</v>
       </c>
     </row>
     <row r="9">
@@ -3052,7 +3104,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-02</t>
+          <t>Rapor Tarihi: 2026-10-05</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3066,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-06 08:14</t>
+          <t>Son Güncelleme: 2026-10-07 07:48</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3134,19 +3186,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>362.75</v>
+        <v>371.5</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>-0.0919899874843555</v>
+        <v>-0.07008760951188986</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>-64805.08269548335</v>
+        <v>-49375.30110132066</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="5">
@@ -3164,19 +3216,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>206.8000030517578</v>
+        <v>214.8999938964844</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>0.04974620838455746</v>
+        <v>0.09086291318012374</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>144579.6310607111</v>
+        <v>264078.9497589483</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="6">
@@ -3194,19 +3246,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>86.69999694824219</v>
+        <v>88.80000305175781</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.1015544357695111</v>
+        <v>-0.07979271448955638</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-8917.949919299906</v>
+        <v>-7006.955691801457</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="7">
@@ -3224,19 +3276,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>125.9000015258789</v>
+        <v>130.3999938964844</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.05622183443595441</v>
+        <v>-0.02248875665112804</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>-272265.5608880231</v>
+        <v>-108906.335140462</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="8">
@@ -3254,19 +3306,19 @@
         <v>405.5</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>414</v>
+        <v>413.5</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.02096177558569656</v>
+        <v>0.01972872996300867</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>59441.69077758677</v>
+        <v>55945.12073184643</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="9">
@@ -3284,19 +3336,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>74.15000152587891</v>
+        <v>74.55000305175781</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.04198966325489484</v>
+        <v>-0.03682168498624883</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-187991.2926788786</v>
+        <v>-164853.8145485716</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
     <row r="10">
@@ -3314,19 +3366,19 @@
         <v>387</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>377</v>
+        <v>391.25</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>-0.02583979328165376</v>
+        <v>0.01098191214470279</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>-111577.9237274509</v>
+        <v>47420.61758416705</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>19730672.93779538</v>
+        <v>20209511.70745903</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>-0.1046263722042833</v>
+        <v>-0.09195122660354629</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -197,16 +197,16 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 74.86/100</t>
+          <t>Güven Puanı: 72.20/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS, EREGL.IS</t>
+          <t>AZALT: TUPRS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PGSUS.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS, PGSUS.IS, TOASO.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -964,29 +964,29 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2496192428796928</v>
+        <v>0.2251318590885242</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>24961.92428796928</v>
+        <v>22513.18590885242</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0432795011507813</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1080.339630946882</v>
+        <v>879.7591085788063</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>431.3960737258481</v>
+        <v>425.2424684424298</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>392.825</v>
+        <v>388.7875</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8655900230156277</v>
-      </c>
-      <c r="K20" s="6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+        <v>0.7815500766001089</v>
+      </c>
+      <c r="K20" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
@@ -998,7 +998,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1771987150724769</v>
+        <v>0.1999698056869224</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>17719.87150724769</v>
+        <v>19996.98056869224</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0241100768715995</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>586.8367124484538</v>
+        <v>482.1287387110515</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>134.7185073625788</v>
+        <v>218.7499186704455</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>123.8799942016602</v>
+        <v>202.9200057983398</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6623487221207344</v>
+        <v>0.4822015374319927</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1731820420478303</v>
+        <v>0.1748983352245534</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17318.20420478303</v>
+        <v>17489.83352245534</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0398671096345515</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>690.4267457056359</v>
+        <v>579.2184441851317</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>406.8480066445183</v>
+        <v>135.5450044642878</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>357.7760386066882</v>
+        <v>124.6399971008301</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.465974327365833</v>
+        <v>0.6623487221207344</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4</v>
+        <v>0.3999999999999999</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000</v>
+        <v>39999.99999999999</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,36 +1359,36 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>413.5</v>
+        <v>409.25</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0168164405252459</v>
+        <v>-0.0213304009125906</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0432795011507813</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0795480343837232</v>
+        <v>0.08353716053812341</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>406.5464018428108</v>
+        <v>400.5205334265223</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>431.3960737258481</v>
+        <v>425.2424684424298</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>446.3931122176695</v>
+        <v>443.437582950227</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>392.825</v>
+        <v>388.7875</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>74.86</v>
+        <v>72.2</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1397,62 +1397,62 @@
       </c>
       <c r="O8" s="13" t="inlineStr">
         <is>
-          <t>Risk sinyali sınırlı</t>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>214.8999938964844</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0475169610822255</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.025967427052516</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.06904386578716611</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>204.6885992499346</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>220.4803938115775</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>229.7375202327361</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>204.1549942016601</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="14" t="n">
+        <v>213.6000061035156</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0388817941395556</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0241100768715995</v>
+      </c>
+      <c r="G9" s="15" t="n">
+        <v>0.0578573158012041</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>205.2948546379909</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>218.7499186704455</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>225.9583291117858</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>202.9200057983398</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="M9" s="13" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
@@ -1473,28 +1473,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>130.3999938964844</v>
+        <v>131.1999969482422</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0446735827301302</v>
+        <v>-0.0492384381057878</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.0795559387098858</v>
+        <v>0.0795560183272892</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>124.5745589811413</v>
+        <v>124.7399140190266</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>134.7185073625788</v>
+        <v>135.5450044642878</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>140.7740878186826</v>
+        <v>141.6377463099968</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>123.8799942016602</v>
+        <v>124.6399971008301</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1502,11 +1502,11 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>74.86</v>
+        <v>72.2</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; hacim artışı var</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O10" s="13" t="inlineStr">
@@ -1516,126 +1516,126 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="13" t="n">
+      <c r="A11" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B11" s="13" t="inlineStr">
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C11" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="14" t="n">
-        <v>391.25</v>
-      </c>
-      <c r="E11" s="15" t="n">
-        <v>-0.0855564508455252</v>
-      </c>
-      <c r="F11" s="15" t="n">
-        <v>0.0398671096345515</v>
-      </c>
-      <c r="G11" s="15" t="n">
-        <v>0.1268436896227545</v>
-      </c>
-      <c r="H11" s="14" t="n">
-        <v>357.7760386066882</v>
-      </c>
-      <c r="I11" s="14" t="n">
-        <v>406.8480066445183</v>
-      </c>
-      <c r="J11" s="14" t="n">
-        <v>440.8775935649027</v>
-      </c>
-      <c r="K11" s="14" t="n">
-        <v>357.7760386066882</v>
-      </c>
-      <c r="L11" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="13" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="N11" s="13" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>379.25</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0647481693898728</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0079734219269103</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.1094015224928461</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>354.6942567588907</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>382.2739202657808</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>420.7405274054119</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>354.6942567588907</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O11" s="13" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="17" t="n">
-        <v>37.63999938964844</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.06569465539051229</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>0.0167247463187438</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.0473010803533</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>35.16725260084639</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>38.26951883087798</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>39.42041202527636</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>35.16725260084639</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>290.5</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.062935886319979</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0281832350218385</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.0410649488078702</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>272.2171250240461</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>282.3127702261559</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>302.4293676286863</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>272.2171250240461</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="M12" s="19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1644,28 +1644,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>142.8999938964844</v>
+        <v>80.80000305175781</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0601762081116165</v>
+        <v>-0.0538623427796313</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.0097276264591439</v>
+        <v>-0.016938908556182</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.129632824695417</v>
+        <v>0.1065267096092228</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>134.3008141246208</v>
+        <v>76.44792559078877</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>141.5099161348454</v>
+        <v>79.43133918872486</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>161.4245237542435</v>
+        <v>89.40736151327674</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>134.3008141246208</v>
+        <v>76.44792559078877</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>74.86</v>
+        <v>72.2</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
@@ -1688,63 +1688,177 @@
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>140.1999969482422</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.0476752666070049</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0102648816912705</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.06299463332248111</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>133.5159247154335</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>138.760860566452</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>149.0318443478097</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>133.1899971008301</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
         <v>15</v>
       </c>
-      <c r="B14" s="19" t="inlineStr">
+      <c r="B15" s="19" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="20" t="n">
-        <v>264.75</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.0887776816785481</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.0216207187319253</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.0581759305162942</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>241.2461087756044</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>259.0259147157228</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>280.1520776041889</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>241.2461087756044</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
+      <c r="D15" s="20" t="n">
+        <v>271.25</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.1106174583284473</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>-0.0216206407595431</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.0248325055186346</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>241.2450144284087</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>265.385401193974</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>277.9858171219296</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>241.2450144284087</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="19" t="n">
-        <v>74.86</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
+      <c r="M15" s="19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" s="19" t="n">
+        <v>16</v>
+      </c>
+      <c r="B16" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="n">
+        <v>19.78000068664551</v>
+      </c>
+      <c r="E16" s="21" t="n">
+        <v>-0.0406728066800316</v>
+      </c>
+      <c r="F16" s="21" t="n">
+        <v>-0.000244900869758</v>
+      </c>
+      <c r="G16" s="21" t="n">
+        <v>0.0397132319205291</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>18.97549254258668</v>
+      </c>
+      <c r="I16" s="20" t="n">
+        <v>19.77515654727353</v>
+      </c>
+      <c r="J16" s="20" t="n">
+        <v>20.56552844130249</v>
+      </c>
+      <c r="K16" s="20" t="n">
+        <v>18.2243572978558</v>
+      </c>
+      <c r="L16" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M16" s="19" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N16" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1774,7 +1888,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,7 +1905,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1882,16 +1996,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>0.0006049606775559</v>
+        <v>-0.0150100689249625</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.1115605076129555</v>
+        <v>0.0957439524230754</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1511856570777916</v>
+        <v>0.120081826762767</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0685757287095444</v>
+        <v>-0.0627271358981496</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1899,53 +2013,53 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0188870682374456</v>
+        <v>0.0189464677182626</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0432795011507813</v>
+        <v>0.0390775038300055</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="18" t="n">
-        <v>-0.000929856817089</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.1358350811986151</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.1054526782079838</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.0479962500987813</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0277650929879785</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.1608695983886718</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.1236191438479148</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.0354639231400832</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0214842246840753</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.025967427052516</v>
+      <c r="J5" s="15" t="n">
+        <v>0.0211732108594615</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0241100768715995</v>
       </c>
     </row>
     <row r="6">
@@ -1968,16 +2082,16 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.0076103504296034</v>
+        <v>-0.0172284872790847</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>-0.029761906113484</v>
+        <v>0.0061349930153591</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>0.000513141059</v>
+        <v>0.0322580528980565</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>0.0178849701902401</v>
+        <v>0.0044668838896742</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -1985,96 +2099,96 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0224473481797315</v>
+        <v>0.0221392296866459</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="13" t="n">
+      <c r="A7" s="16" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="13" t="inlineStr">
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C7" s="13" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="15" t="n">
-        <v>0.0251254272362109</v>
-      </c>
-      <c r="F7" s="15" t="n">
-        <v>0.5436481167927154</v>
-      </c>
-      <c r="G7" s="15" t="n">
-        <v>0.5526753550658163</v>
-      </c>
-      <c r="H7" s="15" t="n">
-        <v>-0.1130716993750996</v>
-      </c>
-      <c r="I7" s="13" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>-0.0208086544587756</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>0.5050533633449479</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>0.4847930232101063</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.1206398509852128</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="15" t="n">
-        <v>0.0276267189827164</v>
-      </c>
-      <c r="K7" s="15" t="n">
-        <v>0.0398671096345515</v>
+      <c r="J7" s="18" t="n">
+        <v>0.0279919446755963</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0079734219269103</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="16" t="n">
+      <c r="A8" s="19" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.0118279198302417</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>-0.0877362840316821</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>0.2691880423812154</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.140788131432354</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0258165350177656</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>0.0167247463187438</v>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>-0.02106149957877</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.125</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-0.0051369863013698</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.1141001298325837</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.0189340480388195</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-0.0281832350218385</v>
       </c>
     </row>
     <row r="9">
@@ -2088,7 +2202,7 @@
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -2097,16 +2211,16 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0343263471663222</v>
+        <v>-0.0634024225362636</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.1018071921474962</v>
+        <v>-0.0767327270231066</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-0.2574701004108854</v>
+        <v>-0.2285418735426633</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>0.0422829153016697</v>
+        <v>0.0189300855603316</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
@@ -2114,10 +2228,10 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.0188996417659717</v>
+        <v>0.01862852867487</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.0203423204102901</v>
+        <v>0.0955198460494279</v>
       </c>
     </row>
     <row r="10">
@@ -2126,7 +2240,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2140,27 +2254,27 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>-0.0410366683043225</v>
+        <v>0.0055157410975577</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>-0.0431034468583914</v>
+        <v>0.0066261141822476</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>-0.0321525552941928</v>
+        <v>0.0617355539448067</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>-0.0234315238855641</v>
+        <v>-0.06840226865997211</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0204466472257388</v>
+        <v>0.0262928620970792</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.0471698096232213</v>
+        <v>0.004261373601285</v>
       </c>
     </row>
     <row r="11">
@@ -2169,7 +2283,7 @@
       </c>
       <c r="B11" s="22" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C11" s="22" t="inlineStr">
@@ -2183,16 +2297,16 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>-0.0977485033231647</v>
+        <v>-0.0558213697995395</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>-0.1685222774452401</v>
+        <v>-0.0133332994249132</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-0.2558876776227028</v>
+        <v>-0.005599103951992</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>0.1021016887639982</v>
+        <v>-0.0227977640742474</v>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
@@ -2200,10 +2314,10 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0156657923401147</v>
+        <v>0.0200905164968222</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>0.0007363095911598</v>
+        <v>0.0588821519160343</v>
       </c>
     </row>
     <row r="12">
@@ -2212,7 +2326,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2226,16 +2340,16 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>-0.0126689189189189</v>
+        <v>0.016658191273575</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.1608040201005025</v>
+        <v>-0.0445920731460589</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>-0.016820857863751</v>
+        <v>-0.0400381746095644</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>-0.1225059234796297</v>
+        <v>-0.1594274954404007</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
@@ -2243,10 +2357,10 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0197501361683288</v>
+        <v>0.0206956804308002</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>0.0317740511915269</v>
+        <v>0.0120845772999691</v>
       </c>
     </row>
     <row r="13">
@@ -2255,7 +2369,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2269,27 +2383,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>0.0239429285541221</v>
+        <v>-0.0323590259301859</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0711644839687519</v>
+        <v>-0.0716073333498248</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>-0.0745856223566272</v>
+        <v>0.3031961978413329</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.1381962403630893</v>
+        <v>-0.1459287355992151</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0209377966832188</v>
+        <v>0.0255753923991939</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0047015865685376</v>
+        <v>0.0190703728875496</v>
       </c>
     </row>
     <row r="14">
@@ -2298,7 +2412,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2308,203 +2422,203 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E14" s="25" t="n">
+        <v>-0.1349036217160011</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1652892509873681</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.2441533966470774</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>0.0870630526756557</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.0156046233478215</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>-0.0615796340300832</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.1554217051310711</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.1988571602957589</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.0379250029154167</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.0186632822272146</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>-0.0102648816912705</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>0</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.0452126866284913</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.0216278357834676</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0617809749780328</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E16" s="27" t="n">
+        <v>-0.0485968912176847</v>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>-0.0162774451669001</v>
+      </c>
+      <c r="G16" s="27" t="n">
+        <v>0.0036101083032491</v>
+      </c>
+      <c r="H16" s="27" t="n">
+        <v>0.1593230295967795</v>
+      </c>
+      <c r="I16" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="27" t="n">
+        <v>0.024050494948932</v>
+      </c>
+      <c r="K16" s="27" t="n">
+        <v>0.0153848487787879</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.0420382165605095</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.0026525198938992</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>0.0994152046783625</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.0208151595531934</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.026630102357745</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0576923532547533</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="J17" s="27" t="n">
+        <v>0.0311441885678829</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>0.0485096508933775</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.0390047287881022</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.1792074159289832</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.1989910381981217</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.0484163572712402</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="E18" s="25" t="n">
+        <v>-0.0581597222222222</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0890008396305626</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0763888888888888</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.1140776898543125</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0193660446130582</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>-0.0097276264591439</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.0403618870906925</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.0631793698679752</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.019203499927613</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>0.1600771369091091</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0245510230622174</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0477419817054558</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0431423052157114</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.0300261096605743</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>0.1023738872403561</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.0357516465713041</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0311727846302145</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.0564292419222857</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="26" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="26" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="27" t="n">
-        <v>-0.0346399270738377</v>
-      </c>
-      <c r="F18" s="27" t="n">
-        <v>-0.1145484949832775</v>
-      </c>
-      <c r="G18" s="27" t="n">
-        <v>-0.0046992481203007</v>
-      </c>
-      <c r="H18" s="27" t="n">
-        <v>-0.0818796613502346</v>
-      </c>
-      <c r="I18" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="27" t="n">
-        <v>0.0249924370188186</v>
-      </c>
-      <c r="K18" s="27" t="n">
-        <v>-0.0216207187319253</v>
+      <c r="J18" s="25" t="n">
+        <v>0.0252062390704968</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>-0.0216206407595431</v>
       </c>
     </row>
     <row r="19">
@@ -2523,74 +2637,74 @@
       </c>
       <c r="D19" s="24" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.1033544349272029</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>0.0291363888292084</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.09762770904197229</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0.2330352574805372</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0393236434475962</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>-0.000244900869758</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="26" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D20" s="26" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
-        <v>0.0019940636386983</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>0.0490605710617779</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.0364333751986897</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0.2407167199401134</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="E20" s="27" t="n">
+        <v>-0.0878540533081511</v>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>-0.0869773912731053</v>
+      </c>
+      <c r="G20" s="27" t="n">
+        <v>-0.1211442704647621</v>
+      </c>
+      <c r="H20" s="27" t="n">
+        <v>0.3166121870564984</v>
+      </c>
+      <c r="I20" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0392630023399694</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0166223768740767</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.0250768503330733</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1172382157363333</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1385004917464062</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>0.382997481507219</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0275946765368713</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.046011499209606</v>
+      <c r="J20" s="27" t="n">
+        <v>0.0272483344683138</v>
+      </c>
+      <c r="K20" s="27" t="n">
+        <v>0.0512218227370565</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2729,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2623,7 +2737,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2648,7 +2762,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, GARAN.IS, TUPRS.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2774,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, EREGL.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2786,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, TOASO.IS</t>
+          <t>THYAO.IS, ARCLK.IS, PGSUS.IS, TOASO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2798,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, SAHOL.IS, ARCLK.IS, THYAO.IS, TCELL.IS, YKBNK.IS, AKBNK.IS, ASELS.IS, PETKM.IS, SISE.IS</t>
+          <t>FROTO.IS, YKBNK.IS, SAHOL.IS, TCELL.IS, EREGL.IS, AKBNK.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2810,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %3.31 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.41 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2848,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2742,7 +2856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2851,7 +2965,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2947,7 +3061,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2985,7 +3099,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2993,7 +3107,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3017,7 +3131,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12374.2998046875</v>
+        <v>12122.900390625</v>
       </c>
     </row>
     <row r="5">
@@ -3027,7 +3141,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13589.54001953125</v>
+        <v>13593.72052246094</v>
       </c>
     </row>
     <row r="6">
@@ -3061,7 +3175,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>74.86</v>
+        <v>72.2</v>
       </c>
     </row>
     <row r="9">
@@ -3104,7 +3218,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-05</t>
+          <t>Rapor Tarihi: 2026-10-06</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3118,7 +3232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-07 07:48</t>
+          <t>Son Güncelleme: 2026-10-08 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3186,19 +3300,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>371.5</v>
+        <v>376</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>-0.07008760951188986</v>
+        <v>-0.05882352941176472</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>-49375.30110132066</v>
+        <v>-41439.98485289409</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="5">
@@ -3216,19 +3330,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>214.8999938964844</v>
+        <v>213.6000061035156</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>0.09086291318012374</v>
+        <v>0.08426399037317567</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>264078.9497589483</v>
+        <v>244900.2051709928</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="6">
@@ -3255,10 +3369,10 @@
         <v>-7006.955691801457</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="7">
@@ -3276,19 +3390,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>130.3999938964844</v>
+        <v>131.1999969482422</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.02248875665112804</v>
+        <v>-0.01649173200074761</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>-108906.335140462</v>
+        <v>-79864.53498441912</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="8">
@@ -3306,19 +3420,19 @@
         <v>405.5</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>413.5</v>
+        <v>409.25</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.01972872996300867</v>
+        <v>0.009247842170160281</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>55945.12073184643</v>
+        <v>26224.27534305304</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="9">
@@ -3336,19 +3450,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>74.55000305175781</v>
+        <v>74.59999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.03682168498624883</v>
+        <v>-0.03617574930953493</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-164853.8145485716</v>
+        <v>-161961.9056014642</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
     <row r="10">
@@ -3366,19 +3480,19 @@
         <v>387</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>391.25</v>
+        <v>379.25</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>0.01098191214470279</v>
+        <v>-0.02002583979328165</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>47420.61758416705</v>
+        <v>-86472.89088877384</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>20209511.70745903</v>
+        <v>20066587.63436091</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>-0.09195122660354629</v>
+        <v>-0.0970300784670533</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -164,6 +164,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -171,15 +180,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -197,16 +197,16 @@
     <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 72.20/100</t>
+          <t>Güven Puanı: 71.85/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>AL: KCHOL.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: TUPRS.IS</t>
+          <t>AZALT: BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS, PGSUS.IS, TOASO.IS, PETKM.IS</t>
+          <t>ÇIK: YKBNK.IS, TOASO.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -955,7 +955,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -964,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2251318590885242</v>
+        <v>0.2194814243017508</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22513.18590885242</v>
+        <v>21948.14243017508</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>879.7591085788063</v>
+        <v>510.6911137754004</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>425.2424684424298</v>
+        <v>214.4769956211876</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>388.7875</v>
+        <v>199.1200057983398</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.7815500766001089</v>
+        <v>0.4653615816464584</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +1007,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1999698056869224</v>
+        <v>0.195184292701372</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19996.98056869224</v>
+        <v>19518.4292701372</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0241100768715995</v>
+        <v>0.0389899779259399</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>482.1287387110515</v>
+        <v>761.0231263916688</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>218.7499186704455</v>
+        <v>394.5564441173757</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>202.9200057983398</v>
+        <v>351.2890081116944</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4822015374319927</v>
+        <v>0.5202364055154228</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1048,25 +1048,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1748983352245534</v>
+        <v>0.1853342829968772</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17489.83352245534</v>
+        <v>18533.42829968772</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>579.2184441851317</v>
+        <v>613.7796275407186</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>135.5450044642878</v>
+        <v>134.2019486445257</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>124.6399971008301</v>
+        <v>123.4049942016601</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6623487221207344</v>
+        <v>0.6623487221207311</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1089,10 +1089,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.3999999999999999</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>39999.99999999999</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 7</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1355,163 +1355,163 @@
       </c>
       <c r="C8" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="n">
+        <v>394.25</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0181177116532006</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0190287675853519</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0761517645004781</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>387.1070921807257</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>401.7520916205251</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>424.2728331543135</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>374.5375</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="13" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="16" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>409.25</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0213304009125906</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0390775038300055</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.08353716053812341</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>400.5205334265223</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>425.2424684424298</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>443.437582950227</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>388.7875</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="D9" s="17" t="n">
+        <v>209.6000061035156</v>
+      </c>
+      <c r="E9" s="18" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F9" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G9" s="18" t="n">
+        <v>0.0914169657590902</v>
+      </c>
+      <c r="H9" s="17" t="n">
+        <v>203.2603128584376</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <v>214.4769956211876</v>
+      </c>
+      <c r="J9" s="17" t="n">
+        <v>228.7610026845858</v>
+      </c>
+      <c r="K9" s="17" t="n">
+        <v>199.1200057983398</v>
+      </c>
+      <c r="L9" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M9" s="16" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="N9" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O9" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>213.6000061035156</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0388817941395556</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0241100768715995</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.0578573158012041</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>205.2948546379909</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>218.7499186704455</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>225.9583291117858</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>202.9200057983398</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
+      <c r="D10" s="17" t="n">
+        <v>379.75</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.07494665408375401</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>0.0389899779259399</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1865322622170305</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>351.2890081116944</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>394.5564441173757</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>450.5856265769173</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>351.2890081116944</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="13" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
+      <c r="M10" s="16" t="n">
+        <v>71.84999999999999</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>131.1999969482422</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0492384381057878</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>124.7399140190266</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>135.5450044642878</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>141.6377463099968</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>124.6399971008301</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1521,54 +1521,54 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>379.25</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0647481693898728</v>
+        <v>-0.0219137721740656</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.0079734219269103</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.1094015224928461</v>
+        <v>0.0795559387098858</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>354.6942567588907</v>
+        <v>127.0533950248243</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>382.2739202657808</v>
+        <v>134.2019486445257</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>420.7405274054119</v>
+        <v>140.2343098493276</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>354.6942567588907</v>
+        <v>123.4049942016601</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>72.2</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C12" s="19" t="inlineStr">
@@ -1587,28 +1587,28 @@
         </is>
       </c>
       <c r="D12" s="20" t="n">
-        <v>290.5</v>
+        <v>36.59999847412109</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>-0.062935886319979</v>
+        <v>-0.0660887705377549</v>
       </c>
       <c r="F12" s="21" t="n">
-        <v>-0.0281832350218385</v>
+        <v>-0.0089743807627755</v>
       </c>
       <c r="G12" s="21" t="n">
-        <v>0.0410649488078702</v>
+        <v>0.0618296226277728</v>
       </c>
       <c r="H12" s="20" t="n">
-        <v>272.2171250240461</v>
+        <v>34.18114957328272</v>
       </c>
       <c r="I12" s="20" t="n">
-        <v>282.3127702261559</v>
+        <v>36.27153615189733</v>
       </c>
       <c r="J12" s="20" t="n">
-        <v>302.4293676286863</v>
+        <v>38.86296256795306</v>
       </c>
       <c r="K12" s="20" t="n">
-        <v>272.2171250240461</v>
+        <v>34.18114957328272</v>
       </c>
       <c r="L12" s="19" t="inlineStr">
         <is>
@@ -1616,26 +1616,26 @@
         </is>
       </c>
       <c r="M12" s="19" t="n">
-        <v>72.2</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="N12" s="19" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O12" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="19" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="B13" s="19" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1644,28 +1644,28 @@
         </is>
       </c>
       <c r="D13" s="20" t="n">
-        <v>80.80000305175781</v>
+        <v>262.5</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>-0.0538623427796313</v>
+        <v>-0.1062914431538463</v>
       </c>
       <c r="F13" s="21" t="n">
-        <v>-0.016938908556182</v>
+        <v>-0.0341013824884792</v>
       </c>
       <c r="G13" s="21" t="n">
-        <v>0.1065267096092228</v>
+        <v>0.0748476932760191</v>
       </c>
       <c r="H13" s="20" t="n">
-        <v>76.44792559078877</v>
+        <v>234.5984961721153</v>
       </c>
       <c r="I13" s="20" t="n">
-        <v>79.43133918872486</v>
+        <v>253.5483870967742</v>
       </c>
       <c r="J13" s="20" t="n">
-        <v>89.40736151327674</v>
+        <v>282.147519484955</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>76.44792559078877</v>
+        <v>234.5984961721153</v>
       </c>
       <c r="L13" s="19" t="inlineStr">
         <is>
@@ -1673,11 +1673,11 @@
         </is>
       </c>
       <c r="M13" s="19" t="n">
-        <v>72.2</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="N13" s="19" t="inlineStr">
         <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
+          <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
       <c r="O13" s="19" t="inlineStr">
@@ -1688,11 +1688,11 @@
     </row>
     <row r="14">
       <c r="A14" s="19" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B14" s="19" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -1701,28 +1701,28 @@
         </is>
       </c>
       <c r="D14" s="20" t="n">
-        <v>140.1999969482422</v>
+        <v>20.10000038146973</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>-0.0476752666070049</v>
+        <v>-0.1119199378692978</v>
       </c>
       <c r="F14" s="21" t="n">
-        <v>-0.0102648816912705</v>
+        <v>-0.013086137901929</v>
       </c>
       <c r="G14" s="21" t="n">
-        <v>0.06299463332248111</v>
+        <v>0.0471306356513333</v>
       </c>
       <c r="H14" s="20" t="n">
-        <v>133.5159247154335</v>
+        <v>17.85040958760277</v>
       </c>
       <c r="I14" s="20" t="n">
-        <v>138.760860566452</v>
+        <v>19.83696900464899</v>
       </c>
       <c r="J14" s="20" t="n">
-        <v>149.0318443478097</v>
+        <v>21.04732617604044</v>
       </c>
       <c r="K14" s="20" t="n">
-        <v>133.1899971008301</v>
+        <v>17.85040958760277</v>
       </c>
       <c r="L14" s="19" t="inlineStr">
         <is>
@@ -1730,135 +1730,21 @@
         </is>
       </c>
       <c r="M14" s="19" t="n">
-        <v>72.2</v>
+        <v>71.84999999999999</v>
       </c>
       <c r="N14" s="19" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; hacim artışı var</t>
         </is>
       </c>
       <c r="O14" s="19" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>271.25</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.1106174583284473</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>-0.0216206407595431</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0248325055186346</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>241.2450144284087</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>265.385401193974</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>277.9858171219296</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>241.2450144284087</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif</t>
-        </is>
-      </c>
-      <c r="O15" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="n">
-        <v>19.78000068664551</v>
-      </c>
-      <c r="E16" s="21" t="n">
-        <v>-0.0406728066800316</v>
-      </c>
-      <c r="F16" s="21" t="n">
-        <v>-0.000244900869758</v>
-      </c>
-      <c r="G16" s="21" t="n">
-        <v>0.0397132319205291</v>
-      </c>
-      <c r="H16" s="20" t="n">
-        <v>18.97549254258668</v>
-      </c>
-      <c r="I16" s="20" t="n">
-        <v>19.77515654727353</v>
-      </c>
-      <c r="J16" s="20" t="n">
-        <v>20.56552844130249</v>
-      </c>
-      <c r="K16" s="20" t="n">
-        <v>18.2243572978558</v>
-      </c>
-      <c r="L16" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="19" t="n">
-        <v>72.2</v>
-      </c>
-      <c r="N16" s="19" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="19" t="inlineStr">
-        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O14"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1888,7 +1774,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1905,7 +1791,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1992,117 +1878,117 @@
       </c>
       <c r="D4" s="13" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E4" s="15" t="n">
+        <v>-0.0567537241291089</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.08667137714074211</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.1539822521904725</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>-0.0586366762905714</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>0.0191791703215786</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0190287675853519</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="16" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="16" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.0150100689249625</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.0957439524230754</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.120081826762767</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.0627271358981496</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E5" s="18" t="n">
+        <v>-0.0676156438696424</v>
+      </c>
+      <c r="F5" s="18" t="n">
+        <v>0.1323608816430757</v>
+      </c>
+      <c r="G5" s="18" t="n">
+        <v>0.0956612794554248</v>
+      </c>
+      <c r="H5" s="18" t="n">
+        <v>0.0020527105616958</v>
+      </c>
+      <c r="I5" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="18" t="n">
+        <v>0.0213375970732259</v>
+      </c>
+      <c r="K5" s="18" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="16" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>-0.0201390585162986</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.4628387421535067</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>0.5144178323241086</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>-0.1616524183240336</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0189464677182626</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0390775038300055</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D5" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0277650929879785</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>0.1608695983886718</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>0.1236191438479148</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>0.0354639231400832</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0211732108594615</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0241100768715995</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0172284872790847</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0061349930153591</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>0.0322580528980565</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>0.0044668838896742</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0221392296866459</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0331174361060366</v>
+      <c r="J6" s="18" t="n">
+        <v>0.0278399849202571</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>0.0389899779259399</v>
       </c>
     </row>
     <row r="7">
@@ -2111,7 +1997,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2121,31 +2007,31 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.0208086544587756</v>
+        <v>-0.044852986055262</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>0.5050533633449479</v>
+        <v>-0.0015373727720819</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>0.4847930232101063</v>
+        <v>0.0223099973184723</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.1206398509852128</v>
+        <v>-0.0452343141914926</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0279919446755963</v>
+        <v>0.0221745607907126</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0.0079734219269103</v>
+        <v>0.0331174361060366</v>
       </c>
     </row>
     <row r="8">
@@ -2154,7 +2040,7 @@
       </c>
       <c r="B8" s="19" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
@@ -2168,27 +2054,27 @@
         </is>
       </c>
       <c r="E8" s="21" t="n">
-        <v>-0.02106149957877</v>
+        <v>-0.027113250577452</v>
       </c>
       <c r="F8" s="21" t="n">
-        <v>-0.125</v>
+        <v>0.020635745989249</v>
       </c>
       <c r="G8" s="21" t="n">
-        <v>-0.0051369863013698</v>
+        <v>0.0633352824272559</v>
       </c>
       <c r="H8" s="21" t="n">
-        <v>-0.1141001298325837</v>
+        <v>-0.1157031395432498</v>
       </c>
       <c r="I8" s="19" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J8" s="21" t="n">
-        <v>0.0189340480388195</v>
+        <v>0.0262624035886349</v>
       </c>
       <c r="K8" s="21" t="n">
-        <v>-0.0281832350218385</v>
+        <v>-0.0089743807627755</v>
       </c>
     </row>
     <row r="9">
@@ -2197,12 +2083,12 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="22" t="inlineStr">
@@ -2211,16 +2097,16 @@
         </is>
       </c>
       <c r="E9" s="23" t="n">
-        <v>-0.0634024225362636</v>
+        <v>-0.0614754098360655</v>
       </c>
       <c r="F9" s="23" t="n">
-        <v>-0.0767327270231066</v>
+        <v>-0.1537324464153732</v>
       </c>
       <c r="G9" s="23" t="n">
-        <v>-0.2285418735426633</v>
+        <v>-0.0329391891891891</v>
       </c>
       <c r="H9" s="23" t="n">
-        <v>0.0189300855603316</v>
+        <v>-0.1307349837883297</v>
       </c>
       <c r="I9" s="22" t="inlineStr">
         <is>
@@ -2228,10 +2114,10 @@
         </is>
       </c>
       <c r="J9" s="23" t="n">
-        <v>0.01862852867487</v>
+        <v>0.0188109839137912</v>
       </c>
       <c r="K9" s="23" t="n">
-        <v>0.0955198460494279</v>
+        <v>0.003753763602968</v>
       </c>
     </row>
     <row r="10">
@@ -2240,7 +2126,7 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
@@ -2254,27 +2140,27 @@
         </is>
       </c>
       <c r="E10" s="23" t="n">
-        <v>0.0055157410975577</v>
+        <v>-0.1080918387411425</v>
       </c>
       <c r="F10" s="23" t="n">
-        <v>0.0066261141822476</v>
+        <v>-0.0865800882141092</v>
       </c>
       <c r="G10" s="23" t="n">
-        <v>0.0617355539448067</v>
+        <v>-0.2585341405069457</v>
       </c>
       <c r="H10" s="23" t="n">
-        <v>-0.06840226865997211</v>
+        <v>-0.0261517673424205</v>
       </c>
       <c r="I10" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J10" s="23" t="n">
-        <v>0.0262928620970792</v>
+        <v>0.0186611788812665</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>0.004261373601285</v>
+        <v>0.0417059852961161</v>
       </c>
     </row>
     <row r="11">
@@ -2297,16 +2183,16 @@
         </is>
       </c>
       <c r="E11" s="23" t="n">
-        <v>-0.0558213697995395</v>
+        <v>-0.092227995086828</v>
       </c>
       <c r="F11" s="23" t="n">
-        <v>-0.0133332994249132</v>
+        <v>-0.0173864613037372</v>
       </c>
       <c r="G11" s="23" t="n">
-        <v>-0.005599103951992</v>
+        <v>-0.0157303542233584</v>
       </c>
       <c r="H11" s="23" t="n">
-        <v>-0.0227977640742474</v>
+        <v>-0.0462642981536363</v>
       </c>
       <c r="I11" s="22" t="inlineStr">
         <is>
@@ -2314,10 +2200,10 @@
         </is>
       </c>
       <c r="J11" s="23" t="n">
-        <v>0.0200905164968222</v>
+        <v>0.0201278290500201</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>0.0588821519160343</v>
+        <v>0.0588820371511202</v>
       </c>
     </row>
     <row r="12">
@@ -2326,7 +2212,7 @@
       </c>
       <c r="B12" s="22" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C12" s="22" t="inlineStr">
@@ -2340,16 +2226,16 @@
         </is>
       </c>
       <c r="E12" s="23" t="n">
-        <v>0.016658191273575</v>
+        <v>-0.1568421213250411</v>
       </c>
       <c r="F12" s="23" t="n">
-        <v>-0.0445920731460589</v>
+        <v>-0.169948202340714</v>
       </c>
       <c r="G12" s="23" t="n">
-        <v>-0.0400381746095644</v>
+        <v>-0.2691605876889276</v>
       </c>
       <c r="H12" s="23" t="n">
-        <v>-0.1594274954404007</v>
+        <v>0.0691039374001909</v>
       </c>
       <c r="I12" s="22" t="inlineStr">
         <is>
@@ -2357,10 +2243,10 @@
         </is>
       </c>
       <c r="J12" s="23" t="n">
-        <v>0.0206956804308002</v>
+        <v>0.0156224090698621</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>0.0120845772999691</v>
+        <v>0.0007363095911598</v>
       </c>
     </row>
     <row r="13">
@@ -2369,7 +2255,7 @@
       </c>
       <c r="B13" s="22" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C13" s="22" t="inlineStr">
@@ -2383,27 +2269,27 @@
         </is>
       </c>
       <c r="E13" s="23" t="n">
-        <v>-0.0323590259301859</v>
+        <v>-0.0216535135953034</v>
       </c>
       <c r="F13" s="23" t="n">
-        <v>-0.0716073333498248</v>
+        <v>-0.0524308857959658</v>
       </c>
       <c r="G13" s="23" t="n">
-        <v>0.3031961978413329</v>
+        <v>-0.0753488230150799</v>
       </c>
       <c r="H13" s="23" t="n">
-        <v>-0.1459287355992151</v>
+        <v>-0.192574200190126</v>
       </c>
       <c r="I13" s="22" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J13" s="23" t="n">
-        <v>0.0255753923991939</v>
+        <v>0.0207481298970322</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>0.0190703728875496</v>
+        <v>0.0124594158070348</v>
       </c>
     </row>
     <row r="14">
@@ -2412,7 +2298,7 @@
       </c>
       <c r="B14" s="24" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">
@@ -2422,20 +2308,20 @@
       </c>
       <c r="D14" s="24" t="inlineStr">
         <is>
-          <t>SAT</t>
+          <t>PORTFOY_DISI</t>
         </is>
       </c>
       <c r="E14" s="25" t="n">
-        <v>-0.1349036217160011</v>
+        <v>-0.0760506628463028</v>
       </c>
       <c r="F14" s="25" t="n">
-        <v>-0.1652892509873681</v>
+        <v>-0.013532720648729</v>
       </c>
       <c r="G14" s="25" t="n">
-        <v>-0.2441533966470774</v>
+        <v>0.0072727272727273</v>
       </c>
       <c r="H14" s="25" t="n">
-        <v>0.0870630526756557</v>
+        <v>0.1005149493281738</v>
       </c>
       <c r="I14" s="24" t="inlineStr">
         <is>
@@ -2443,10 +2329,10 @@
         </is>
       </c>
       <c r="J14" s="25" t="n">
-        <v>0.0156046233478215</v>
+        <v>0.0240411483060092</v>
       </c>
       <c r="K14" s="25" t="n">
-        <v>-0.016938908556182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -2455,84 +2341,84 @@
       </c>
       <c r="B15" s="24" t="inlineStr">
         <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="25" t="n">
+        <v>-0.085170287252833</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0883674686513502</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>0.2676904811576761</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>-0.1835639267290416</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J15" s="25" t="n">
+        <v>0.0256330343630821</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.029948947983406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C16" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.0615796340300832</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.1554217051310711</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.1988571602957589</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.0379250029154167</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="25" t="n">
+        <v>-0.1221864951768488</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.1841004332930537</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.2270668443805752</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.0679367814359703</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0186632822272146</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>-0.0102648816912705</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="26" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="26" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="27" t="n">
-        <v>-0.0485968912176847</v>
-      </c>
-      <c r="F16" s="27" t="n">
-        <v>-0.0162774451669001</v>
-      </c>
-      <c r="G16" s="27" t="n">
-        <v>0.0036101083032491</v>
-      </c>
-      <c r="H16" s="27" t="n">
-        <v>0.1593230295967795</v>
-      </c>
-      <c r="I16" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="27" t="n">
-        <v>0.024050494948932</v>
-      </c>
-      <c r="K16" s="27" t="n">
-        <v>0.0153848487787879</v>
+      <c r="J16" s="25" t="n">
+        <v>0.0188546078295222</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2541,7 +2427,7 @@
       </c>
       <c r="B17" s="26" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>TOASO.IS</t>
         </is>
       </c>
       <c r="C17" s="26" t="inlineStr">
@@ -2551,31 +2437,31 @@
       </c>
       <c r="D17" s="26" t="inlineStr">
         <is>
-          <t>PORTFOY_DISI</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E17" s="27" t="n">
-        <v>-0.0420382165605095</v>
+        <v>-0.1002570694087403</v>
       </c>
       <c r="F17" s="27" t="n">
-        <v>-0.0026525198938992</v>
+        <v>-0.1101694915254237</v>
       </c>
       <c r="G17" s="27" t="n">
-        <v>0.0994152046783625</v>
+        <v>-0.0066225165562914</v>
       </c>
       <c r="H17" s="27" t="n">
-        <v>-0.0208151595531934</v>
+        <v>-0.1360240018729415</v>
       </c>
       <c r="I17" s="26" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J17" s="27" t="n">
-        <v>0.0311441885678829</v>
+        <v>0.0254903982304084</v>
       </c>
       <c r="K17" s="27" t="n">
-        <v>0.0485096508933775</v>
+        <v>-0.0341013824884792</v>
       </c>
     </row>
     <row r="18">
@@ -2584,7 +2470,7 @@
       </c>
       <c r="B18" s="24" t="inlineStr">
         <is>
-          <t>TOASO.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C18" s="24" t="inlineStr">
@@ -2594,117 +2480,117 @@
       </c>
       <c r="D18" s="24" t="inlineStr">
         <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.1057692307692307</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0278745644599303</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>0.0552193645990923</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>0.0036937573522548</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="25" t="n">
+        <v>0.0318914991346351</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0478184256278046</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D19" s="26" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.0581597222222222</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0890008396305626</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0763888888888888</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.1140776898543125</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="E19" s="27" t="n">
+        <v>-0.1714756722244205</v>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>0.0567823290070015</v>
+      </c>
+      <c r="G19" s="27" t="n">
+        <v>0.0110664602610899</v>
+      </c>
+      <c r="H19" s="27" t="n">
+        <v>0.1486342474882058</v>
+      </c>
+      <c r="I19" s="26" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0252062390704968</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>-0.0216206407595431</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="J19" s="27" t="n">
+        <v>0.0393396303804498</v>
+      </c>
+      <c r="K19" s="27" t="n">
+        <v>-0.013086137901929</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.1033544349272029</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>0.0291363888292084</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.09762770904197229</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0.2330352574805372</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="25" t="n">
+        <v>-0.1802705887504893</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1103742234172892</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1352690721785295</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>0.1692058921210597</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0393236434475962</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>-0.000244900869758</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="26" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="26" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="26" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="27" t="n">
-        <v>-0.0878540533081511</v>
-      </c>
-      <c r="F20" s="27" t="n">
-        <v>-0.0869773912731053</v>
-      </c>
-      <c r="G20" s="27" t="n">
-        <v>-0.1211442704647621</v>
-      </c>
-      <c r="H20" s="27" t="n">
-        <v>0.3166121870564984</v>
-      </c>
-      <c r="I20" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="27" t="n">
-        <v>0.0272483344683138</v>
-      </c>
-      <c r="K20" s="27" t="n">
-        <v>0.0512218227370565</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0272067141705221</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0905550350972887</v>
       </c>
     </row>
   </sheetData>
@@ -2729,7 +2615,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2737,7 +2623,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2762,7 +2648,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>KCHOL.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2774,7 +2660,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2786,7 +2672,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS, PGSUS.IS, TOASO.IS, PETKM.IS</t>
+          <t>YKBNK.IS, TOASO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2684,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, YKBNK.IS, SAHOL.IS, TCELL.IS, EREGL.IS, AKBNK.IS, ASELS.IS, SISE.IS</t>
+          <t>THYAO.IS, FROTO.IS, SAHOL.IS, ARCLK.IS, TCELL.IS, AKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2696,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.41 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2848,7 +2734,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2856,7 +2742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2917,7 +2803,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -3061,7 +2947,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3099,7 +2985,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3107,7 +2993,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3131,7 +3017,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12122.900390625</v>
+        <v>12213.599609375</v>
       </c>
     </row>
     <row r="5">
@@ -3141,7 +3027,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13593.72052246094</v>
+        <v>13598.11302246094</v>
       </c>
     </row>
     <row r="6">
@@ -3175,7 +3061,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>72.2</v>
+        <v>71.84999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -3218,7 +3104,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-06</t>
+          <t>Rapor Tarihi: 2026-10-07</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3232,7 +3118,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-08 08:05</t>
+          <t>Son Güncelleme: 2026-10-09 08:05</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3300,19 +3186,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="28" t="n">
-        <v>376</v>
+        <v>348.75</v>
       </c>
       <c r="E4" s="29" t="n">
-        <v>-0.05882352941176472</v>
+        <v>-0.1270337922403004</v>
       </c>
       <c r="F4" s="28" t="n">
-        <v>-41439.98485289409</v>
+        <v>-89492.73324614356</v>
       </c>
       <c r="G4" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H4" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="5">
@@ -3330,19 +3216,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="28" t="n">
-        <v>213.6000061035156</v>
+        <v>209.6000061035156</v>
       </c>
       <c r="E5" s="29" t="n">
-        <v>0.08426399037317567</v>
+        <v>0.06395942184525705</v>
       </c>
       <c r="F5" s="28" t="n">
-        <v>244900.2051709928</v>
+        <v>185888.1292370865</v>
       </c>
       <c r="G5" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H5" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="6">
@@ -3360,19 +3246,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="28" t="n">
-        <v>88.80000305175781</v>
+        <v>87.59999847412109</v>
       </c>
       <c r="E6" s="29" t="n">
-        <v>-0.07979271448955638</v>
+        <v>-0.092227995086828</v>
       </c>
       <c r="F6" s="28" t="n">
-        <v>-7006.955691801457</v>
+        <v>-8098.953385044559</v>
       </c>
       <c r="G6" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H6" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="7">
@@ -3390,19 +3276,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="28" t="n">
-        <v>131.1999969482422</v>
+        <v>129.8999938964844</v>
       </c>
       <c r="E7" s="29" t="n">
-        <v>-0.01649173200074761</v>
+        <v>-0.0262368827596493</v>
       </c>
       <c r="F7" s="28" t="n">
-        <v>-79864.53498441912</v>
+        <v>-127057.3909972059</v>
       </c>
       <c r="G7" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H7" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="8">
@@ -3420,19 +3306,19 @@
         <v>405.5</v>
       </c>
       <c r="D8" s="28" t="n">
-        <v>409.25</v>
+        <v>394.25</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.009247842170160281</v>
+        <v>-0.02774352651048084</v>
       </c>
       <c r="F8" s="28" t="n">
-        <v>26224.27534305304</v>
+        <v>-78672.82602915866</v>
       </c>
       <c r="G8" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="9">
@@ -3450,19 +3336,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>74.59999847412109</v>
+        <v>73.84999847412109</v>
       </c>
       <c r="E9" s="29" t="n">
-        <v>-0.03617574930953493</v>
+        <v>-0.04586567159912602</v>
       </c>
       <c r="F9" s="28" t="n">
-        <v>-161961.9056014642</v>
+        <v>-205344.5116042821</v>
       </c>
       <c r="G9" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H9" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
     <row r="10">
@@ -3480,19 +3366,19 @@
         <v>387</v>
       </c>
       <c r="D10" s="28" t="n">
-        <v>379.25</v>
+        <v>379.75</v>
       </c>
       <c r="E10" s="29" t="n">
-        <v>-0.02002583979328165</v>
+        <v>-0.01873385012919893</v>
       </c>
       <c r="F10" s="28" t="n">
-        <v>-86472.89088877384</v>
+        <v>-80893.99470240157</v>
       </c>
       <c r="G10" s="28" t="n">
-        <v>20066587.63436091</v>
+        <v>19768537.14513906</v>
       </c>
       <c r="H10" s="29" t="n">
-        <v>-0.0970300784670533</v>
+        <v>-0.1153750444669439</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +158,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -616,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 71.85/100</t>
+          <t>Güven Puanı: 70.95/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, TUPRS.IS, GARAN.IS</t>
+          <t>AL: KCHOL.IS, FROTO.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS</t>
+          <t>AZALT: BIMAS.IS, THYAO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: YKBNK.IS, TOASO.IS, PETKM.IS</t>
+          <t>ÇIK: PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -964,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2194814243017508</v>
+        <v>0.2211403098513339</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21948.14243017508</v>
+        <v>22114.03098513339</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0191938585275912</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>510.6911137754004</v>
+        <v>424.4535822034185</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>214.4769956211876</v>
+        <v>216.4767693305947</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>199.1200057983398</v>
+        <v>198.3527119886738</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.4653615816464584</v>
+        <v>0.2902180977690499</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -998,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.195184292701372</v>
+        <v>0.1958022278387909</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19518.4292701372</v>
+        <v>19580.22278387909</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0389899779259399</v>
+        <v>0.0417061216022127</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>761.0231263916688</v>
+        <v>816.6151524228771</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>394.5564441173757</v>
+        <v>77.50293703672203</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>351.2890081116944</v>
+        <v>70.68000144958496</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.5202364055154228</v>
+        <v>0.834122432044257</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1039,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1048,62 +1056,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1853342829968772</v>
+        <v>0.1830574623098753</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18533.42829968772</v>
+        <v>18305.74623098753</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
+        <v>0.0195381803197951</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>613.7796275407186</v>
+        <v>357.6609707494438</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>134.2019486445257</v>
+        <v>399.9138512304397</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>123.4049942016601</v>
+        <v>358.5245988394586</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.6623487221207311</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.227242700359821</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="10" t="n">
+      <c r="A23" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.3999999999999999</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>39999.99999999999</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1144,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1345,401 +1353,401 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C8" s="14" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>394.25</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0181177116532006</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0190287675853519</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.0761517645004781</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>387.1070921807257</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>401.7520916205251</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>424.2728331543135</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>374.5375</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="D8" s="15" t="n">
+        <v>401</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0205580539159817</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.019028938484348</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.06844627048378669</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>392.7562203796913</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>408.6306043322236</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>428.4469544639985</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>380.95</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
+      <c r="M8" s="14" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="13" t="inlineStr">
+      <c r="O8" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="n">
+      <c r="A9" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="16" t="inlineStr">
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="16" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
-        <v>209.6000061035156</v>
-      </c>
-      <c r="E9" s="18" t="n">
-        <v>-0.0302466271968858</v>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.0232680790823229</v>
-      </c>
-      <c r="G9" s="18" t="n">
-        <v>0.0914169657590902</v>
-      </c>
-      <c r="H9" s="17" t="n">
-        <v>203.2603128584376</v>
-      </c>
-      <c r="I9" s="17" t="n">
-        <v>214.4769956211876</v>
-      </c>
-      <c r="J9" s="17" t="n">
-        <v>228.7610026845858</v>
-      </c>
-      <c r="K9" s="17" t="n">
-        <v>199.1200057983398</v>
-      </c>
-      <c r="L9" s="16" t="inlineStr">
+      <c r="D9" s="18" t="n">
+        <v>212.3999938964844</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.06613598075081251</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0191938585275912</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.06904391931949121</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>198.3527119886738</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>216.4767693305947</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>227.0649219385337</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>198.3527119886738</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="16" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N9" s="16" t="inlineStr">
+      <c r="M9" s="17" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>379.75</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.07494665408375401</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>0.0389899779259399</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1865322622170305</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>351.2890081116944</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>394.5564441173757</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>450.5856265769173</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>351.2890081116944</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="D10" s="18" t="n">
+        <v>392.25</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.08597935286307549</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.0195381803197951</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.1188713720805591</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>358.5245988394586</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>399.9138512304397</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>438.8772956985994</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>358.5245988394586</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>74.40000152587891</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.030662695557949</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.0417061216022127</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.1388396310918183</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>72.11869692957994</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>77.50293703672203</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>84.72967029096264</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>70.68000144958496</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>129.8999938964844</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0219137721740656</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.0795559387098858</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>127.0533950248243</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>134.2019486445257</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>140.2343098493276</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>123.4049942016601</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="16" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="M11" s="17" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>284.25</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.052434175232511</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.003753763602968</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.0701777996871968</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>269.3455856901587</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>285.3170073041437</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>304.1980395610857</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>269.3455856901587</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>13</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>36.59999847412109</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0660887705377549</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.0618296226277728</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.18114957328272</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>36.27153615189733</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>38.86296256795306</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.18114957328272</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="D13" s="21" t="n">
+        <v>135.6000061035156</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.0537067277155769</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.0194552529182879</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.1090029643218295</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>128.3173734974835</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>132.9618736890503</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>150.380808730857</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>128.3173734974835</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
+      <c r="M13" s="20" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C14" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>262.5</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.1062914431538463</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.0341013824884792</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.0748476932760191</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>234.5984961721153</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>253.5483870967742</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>282.147519484955</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>234.5984961721153</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="D14" s="21" t="n">
+        <v>269</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.07126395669746011</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.0091399766450234</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0.0415042015350602</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>249.8299956483832</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>266.5413462824887</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>280.1646302129312</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>249.8299956483832</v>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
+      <c r="M14" s="20" t="n">
+        <v>70.95</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>16</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>20.10000038146973</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.1119199378692978</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.013086137901929</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.0471306356513333</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>17.85040958760277</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>19.83696900464899</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>21.04732617604044</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>17.85040958760277</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>71.84999999999999</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
@@ -1774,7 +1782,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1791,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1863,734 +1871,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C4" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D4" s="14" t="inlineStr">
         <is>
           <t>TUT</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.0567537241291089</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>0.08667137714074211</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>0.1539822521904725</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.0586366762905714</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E4" s="16" t="n">
+        <v>-0.0563137182802316</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.08302253368216519</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.1737397162419263</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.0605774813729588</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0191791703215786</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0190287675853519</v>
+      <c r="J4" s="16" t="n">
+        <v>0.0191290724367972</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.019028938484348</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="16" t="n">
+      <c r="A5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="16" t="inlineStr">
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="16" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="16" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>-0.0676156438696424</v>
-      </c>
-      <c r="F5" s="18" t="n">
-        <v>0.1323608816430757</v>
-      </c>
-      <c r="G5" s="18" t="n">
-        <v>0.0956612794554248</v>
-      </c>
-      <c r="H5" s="18" t="n">
-        <v>0.0020527105616958</v>
-      </c>
-      <c r="I5" s="16" t="inlineStr">
+      <c r="E5" s="19" t="n">
+        <v>-0.0505140956902753</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.1016597019423535</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.09259259549969311</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.0485430687963439</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="18" t="n">
-        <v>0.0213375970732259</v>
-      </c>
-      <c r="K5" s="18" t="n">
-        <v>0.0232680790823229</v>
+      <c r="J5" s="19" t="n">
+        <v>0.0207860298554876</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0191938585275912</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>-0.0201390585162986</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.4628387421535067</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>0.5144178323241086</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.1616524183240336</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="E6" s="19" t="n">
+        <v>-0.036139677786054</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.4954275911945411</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>0.5566438543758887</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.1962484737015959</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.0278399849202571</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>0.0389899779259399</v>
+      <c r="J6" s="19" t="n">
+        <v>0.0280355349385904</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.0195381803197951</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="16" t="n">
+      <c r="A7" s="17" t="n">
         <v>4</v>
       </c>
-      <c r="B7" s="16" t="inlineStr">
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.1137581390056649</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>-0.09046456295602651</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-0.2589641394905586</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.0586189602200157</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0186206047020004</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>0.0417061216022127</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0556478405315614</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>-0.1748911465892597</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-0.0437342304457527</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.1639114710894957</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0186262496527776</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.003753763602968</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="23" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n">
+        <v>-0.0256830236584199</v>
+      </c>
+      <c r="F9" s="24" t="n">
+        <v>0.0147979643368136</v>
+      </c>
+      <c r="G9" s="24" t="n">
+        <v>0.0147979643368136</v>
+      </c>
+      <c r="H9" s="24" t="n">
+        <v>-0.1384289250641028</v>
+      </c>
+      <c r="I9" s="23" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J9" s="24" t="n">
+        <v>0.0263431621899088</v>
+      </c>
+      <c r="K9" s="24" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>-0.07600211160664</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.0193370165745856</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>-0.0326975476839237</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.07408657888789739</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="24" t="n">
+        <v>0.0201048370906429</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0.0588821519160343</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.044852986055262</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>-0.0015373727720819</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>0.0223099973184723</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.0452343141914926</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.0431869167532524</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.003875968992248</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.0140648416890173</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.1007340676179966</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0221745607907126</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="19" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="J11" s="24" t="n">
+        <v>0.0221911300146039</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.0265059178623019</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>-0.1561844998696046</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>-0.1860465241859903</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>-0.2708333434114132</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>0.0268120563432003</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="24" t="n">
+        <v>0.0152502117516968</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.0007363095911598</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="23" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n">
+        <v>-0.0157171518226982</v>
+      </c>
+      <c r="F13" s="24" t="n">
+        <v>-0.0635514303902599</v>
+      </c>
+      <c r="G13" s="24" t="n">
+        <v>-0.07734808143556821</v>
+      </c>
+      <c r="H13" s="24" t="n">
+        <v>-0.2330852114160289</v>
+      </c>
+      <c r="I13" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="24" t="n">
+        <v>0.0206102435815252</v>
+      </c>
+      <c r="K13" s="24" t="n">
+        <v>0.0124594158070348</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>-0.0634596530382676</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.094059477926595</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>0.2341201160407111</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.222405128083297</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.0256071566045418</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.0190703728875496</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="25" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>-0.06579843212013919</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>-0.0087272505326704</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>-0.0305832351713553</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>0.0331064851884299</v>
+      </c>
+      <c r="I15" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>0.0239822715859189</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0.0111110916693351</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="27" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="27" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.027113250577452</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0.020635745989249</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>0.0633352824272559</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.1157031395432498</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0262624035886349</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="E16" s="28" t="n">
+        <v>-0.1234647137783514</v>
+      </c>
+      <c r="F16" s="28" t="n">
+        <v>-0.2032901966223208</v>
+      </c>
+      <c r="G16" s="28" t="n">
+        <v>-0.2399102536842193</v>
+      </c>
+      <c r="H16" s="28" t="n">
+        <v>-0.102048370776654</v>
+      </c>
+      <c r="I16" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J16" s="28" t="n">
+        <v>0.0186775555598611</v>
+      </c>
+      <c r="K16" s="28" t="n">
+        <v>-0.0194552529182879</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0614754098360655</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.1537324464153732</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-0.0329391891891891</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.1307349837883297</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="E17" s="26" t="n">
+        <v>-0.2030888149171456</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>0.0672181606413582</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.010546558689646</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.0260650374925286</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0394224350412246</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.07582576484113181</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>-0.081127241673783</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1114781172584641</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>0.0112781954887217</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.1670440637480758</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0188109839137912</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.003753763602968</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="J18" s="28" t="n">
+        <v>0.0254645426742394</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>-0.0091399766450234</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.1080918387411425</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-0.0865800882141092</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>-0.2585341405069457</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.0261517673424205</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="E19" s="26" t="n">
+        <v>-0.1330018645121193</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.0574324324324324</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>0.03486646884273</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.0046009331250927</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0186611788812665</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.0417059852961161</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="J19" s="26" t="n">
+        <v>0.0316386844276283</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.0478184312002618</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.092227995086828</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.0173864613037372</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.0157303542233584</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.0462642981536363</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="E20" s="26" t="n">
+        <v>-0.1569326977205356</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1293738284887817</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.1448316943799105</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>-0.0441114367350677</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0201278290500201</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0588820371511202</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>-0.1568421213250411</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.169948202340714</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>-0.2691605876889276</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>0.0691039374001909</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0156224090698621</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0.0007363095911598</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="23" t="n">
-        <v>-0.0216535135953034</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>-0.0524308857959658</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-0.0753488230150799</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>-0.192574200190126</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0207481298970322</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0124594158070348</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.0760506628463028</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.013532720648729</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>0.0072727272727273</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>0.1005149493281738</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0240411483060092</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="24" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.085170287252833</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0883674686513502</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>0.2676904811576761</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>-0.1835639267290416</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0256330343630821</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.029948947983406</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.1221864951768488</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.1841004332930537</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.2270668443805752</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.0679367814359703</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0188546078295222</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.1002570694087403</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.1101694915254237</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.0066225165562914</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.1360240018729415</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0254903982304084</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>-0.0341013824884792</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.1057692307692307</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0278745644599303</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>0.0552193645990923</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>0.0036937573522548</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0318914991346351</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0478184256278046</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="26" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="27" t="n">
-        <v>-0.1714756722244205</v>
-      </c>
-      <c r="F19" s="27" t="n">
-        <v>0.0567823290070015</v>
-      </c>
-      <c r="G19" s="27" t="n">
-        <v>0.0110664602610899</v>
-      </c>
-      <c r="H19" s="27" t="n">
-        <v>0.1486342474882058</v>
-      </c>
-      <c r="I19" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="27" t="n">
-        <v>0.0393396303804498</v>
-      </c>
-      <c r="K19" s="27" t="n">
-        <v>-0.013086137901929</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1802705887504893</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1103742234172892</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1352690721785295</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>0.1692058921210597</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0272067141705221</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0905550350972887</v>
+      <c r="J20" s="26" t="n">
+        <v>0.0269505186174669</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.0809523100911218</v>
       </c>
     </row>
   </sheetData>
@@ -2615,7 +2623,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2623,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2648,7 +2656,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TUPRS.IS, GARAN.IS</t>
+          <t>KCHOL.IS, TUPRS.IS, FROTO.IS</t>
         </is>
       </c>
     </row>
@@ -2660,7 +2668,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>BIMAS.IS, THYAO.IS</t>
         </is>
       </c>
     </row>
@@ -2672,7 +2680,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, TOASO.IS, PETKM.IS</t>
+          <t>PGSUS.IS, TOASO.IS</t>
         </is>
       </c>
     </row>
@@ -2684,7 +2692,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, FROTO.IS, SAHOL.IS, ARCLK.IS, TCELL.IS, AKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, SISE.IS</t>
+          <t>YKBNK.IS, SAHOL.IS, GARAN.IS, ARCLK.IS, TCELL.IS, EREGL.IS, AKBNK.IS, PETKM.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2696,7 +2704,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %2.33 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.92 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2734,7 +2742,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2742,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2827,7 +2835,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2839,7 +2847,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2993,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2993,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3017,7 +3025,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12213.599609375</v>
+        <v>12266</v>
       </c>
     </row>
     <row r="5">
@@ -3027,7 +3035,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13598.11302246094</v>
+        <v>13602.73352050781</v>
       </c>
     </row>
     <row r="6">
@@ -3061,7 +3069,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>71.84999999999999</v>
+        <v>70.95</v>
       </c>
     </row>
     <row r="9">
@@ -3104,7 +3112,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-07</t>
+          <t>Rapor Tarihi: 2026-10-08</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3118,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-09 08:05</t>
+          <t>Son Güncelleme: 2026-10-10 07:49</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3182,23 +3190,23 @@
           <t>2026-07-03</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="29" t="n">
         <v>399.5</v>
       </c>
-      <c r="D4" s="28" t="n">
+      <c r="D4" s="29" t="n">
         <v>348.75</v>
       </c>
-      <c r="E4" s="29" t="n">
+      <c r="E4" s="30" t="n">
         <v>-0.1270337922403004</v>
       </c>
-      <c r="F4" s="28" t="n">
+      <c r="F4" s="29" t="n">
         <v>-89492.73324614356</v>
       </c>
-      <c r="G4" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="G4" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="5">
@@ -3212,23 +3220,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="29" t="n">
         <v>197</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>209.6000061035156</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>0.06395942184525705</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>185888.1292370865</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D5" s="29" t="n">
+        <v>212.3999938964844</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>0.07817255785017441</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>227196.4023002572</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="6">
@@ -3242,23 +3250,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="29" t="n">
         <v>96.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>87.59999847412109</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.092227995086828</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-8098.953385044559</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D6" s="29" t="n">
+        <v>88.75</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>-0.0803108808290155</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-7052.458199202025</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="7">
@@ -3272,23 +3280,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="29" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>129.8999938964844</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.0262368827596493</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-127057.3909972059</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D7" s="29" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>-0.03673159011001659</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-177880.1258255821</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="8">
@@ -3302,23 +3310,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>405.5</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>394.25</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.02774352651048084</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-78672.82602915866</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D8" s="29" t="n">
+        <v>401</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>-0.01109741060419234</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>-31469.13041166309</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="9">
@@ -3332,23 +3340,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n">
+      <c r="C9" s="29" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D9" s="28" t="n">
-        <v>73.84999847412109</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>-0.04586567159912602</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>-205344.5116042821</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D9" s="29" t="n">
+        <v>74.40000152587891</v>
+      </c>
+      <c r="E9" s="30" t="n">
+        <v>-0.03875968915836447</v>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>-173530.4240112733</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H9" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
     <row r="10">
@@ -3362,23 +3370,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n">
+      <c r="C10" s="29" t="n">
         <v>387</v>
       </c>
-      <c r="D10" s="28" t="n">
-        <v>379.75</v>
-      </c>
-      <c r="E10" s="29" t="n">
-        <v>-0.01873385012919893</v>
-      </c>
-      <c r="F10" s="28" t="n">
-        <v>-80893.99470240157</v>
-      </c>
-      <c r="G10" s="28" t="n">
-        <v>19768537.14513906</v>
-      </c>
-      <c r="H10" s="29" t="n">
-        <v>-0.1153750444669439</v>
+      <c r="D10" s="29" t="n">
+        <v>392.25</v>
+      </c>
+      <c r="E10" s="30" t="n">
+        <v>0.01356589147286824</v>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>58578.40995691251</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>19978559.36642952</v>
+      </c>
+      <c r="H10" s="30" t="n">
+        <v>-0.1087565959300204</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -972,10 +972,10 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2211403098513339</v>
+        <v>0.2211403098513338</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22114.03098513339</v>
+        <v>22114.03098513338</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0191938585275912</v>
@@ -984,13 +984,13 @@
         <v>424.4535822034185</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="I20" s="8" t="n">
         <v>198.3527119886738</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2902180977690499</v>
+        <v>0.2902180977690493</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1370,7 +1370,7 @@
         <v>401</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0205580539159817</v>
+        <v>-0.0205580539159813</v>
       </c>
       <c r="F8" s="16" t="n">
         <v>0.019028938484348</v>
@@ -1379,7 +1379,7 @@
         <v>0.06844627048378669</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>392.7562203796913</v>
+        <v>392.7562203796915</v>
       </c>
       <c r="I8" s="15" t="n">
         <v>408.6306043322236</v>
@@ -1439,7 +1439,7 @@
         <v>198.3527119886738</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>216.4767693305947</v>
+        <v>216.4767693305948</v>
       </c>
       <c r="J9" s="18" t="n">
         <v>227.0649219385337</v>
@@ -1484,7 +1484,7 @@
         <v>392.25</v>
       </c>
       <c r="E10" s="19" t="n">
-        <v>-0.08597935286307549</v>
+        <v>-0.0859793528630754</v>
       </c>
       <c r="F10" s="19" t="n">
         <v>0.0195381803197951</v>
@@ -1547,7 +1547,7 @@
         <v>0.0417061216022127</v>
       </c>
       <c r="G11" s="19" t="n">
-        <v>0.1388396310918183</v>
+        <v>0.1388396310918185</v>
       </c>
       <c r="H11" s="18" t="n">
         <v>72.11869692957994</v>
@@ -1556,7 +1556,7 @@
         <v>77.50293703672203</v>
       </c>
       <c r="J11" s="18" t="n">
-        <v>84.72967029096264</v>
+        <v>84.72967029096267</v>
       </c>
       <c r="K11" s="18" t="n">
         <v>70.68000144958496</v>
@@ -1601,10 +1601,10 @@
         <v>-0.052434175232511</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0701777996871968</v>
+        <v>0.0701777996871966</v>
       </c>
       <c r="H12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1613,7 +1613,7 @@
         <v>285.3170073041437</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>304.1980395610857</v>
+        <v>304.1980395610856</v>
       </c>
       <c r="K12" s="15" t="n">
         <v>269.3455856901587</v>
@@ -1655,13 +1655,13 @@
         <v>135.6000061035156</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0537067277155769</v>
+        <v>-0.0537067277155768</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.0194552529182879</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1090029643218295</v>
+        <v>0.1090029643218296</v>
       </c>
       <c r="H13" s="21" t="n">
         <v>128.3173734974835</v>
@@ -1715,7 +1715,7 @@
         <v>-0.07126395669746011</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
       <c r="G14" s="22" t="n">
         <v>0.0415042015350602</v>
@@ -1724,7 +1724,7 @@
         <v>249.8299956483832</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>266.5413462824887</v>
+        <v>266.5413462824886</v>
       </c>
       <c r="J14" s="21" t="n">
         <v>280.1646302129312</v>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1893,7 +1893,7 @@
         <v>-0.0563137182802316</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.08302253368216519</v>
+        <v>0.083022533682165</v>
       </c>
       <c r="G4" s="16" t="n">
         <v>0.1737397162419263</v>
@@ -1933,10 +1933,10 @@
         </is>
       </c>
       <c r="E5" s="19" t="n">
-        <v>-0.0505140956902753</v>
+        <v>-0.0505140956902752</v>
       </c>
       <c r="F5" s="19" t="n">
-        <v>0.1016597019423535</v>
+        <v>0.1016597019423537</v>
       </c>
       <c r="G5" s="19" t="n">
         <v>0.09259259549969311</v>
@@ -2079,10 +2079,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.0186262496527776</v>
+        <v>0.0186262496527777</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.003753763602968</v>
+        <v>0.0037537636029683</v>
       </c>
     </row>
     <row r="9">
@@ -2105,7 +2105,7 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.0256830236584199</v>
+        <v>-0.0256830236584196</v>
       </c>
       <c r="F9" s="24" t="n">
         <v>0.0147979643368136</v>
@@ -2148,7 +2148,7 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.07600211160664</v>
+        <v>-0.0760021116066399</v>
       </c>
       <c r="F10" s="24" t="n">
         <v>-0.0193370165745856</v>
@@ -2168,7 +2168,7 @@
         <v>0.0201048370906429</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.0588821519160343</v>
+        <v>0.058882151916034</v>
       </c>
     </row>
     <row r="11">
@@ -2251,7 +2251,7 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.0152502117516968</v>
+        <v>0.0152502117516969</v>
       </c>
       <c r="K12" s="24" t="n">
         <v>0.0007363095911598</v>
@@ -2277,13 +2277,13 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.0157171518226982</v>
+        <v>-0.0157171518226979</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.0635514303902599</v>
+        <v>-0.06355143039025971</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.07734808143556821</v>
+        <v>-0.07734808143556809</v>
       </c>
       <c r="H13" s="24" t="n">
         <v>-0.2330852114160289</v>
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0634596530382676</v>
+        <v>-0.0634596530382678</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.094059477926595</v>
+        <v>-0.09405947792659509</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.2341201160407111</v>
+        <v>0.2341201160407109</v>
       </c>
       <c r="H14" s="26" t="n">
         <v>-0.222405128083297</v>
@@ -2423,7 +2423,7 @@
         </is>
       </c>
       <c r="J16" s="28" t="n">
-        <v>0.0186775555598611</v>
+        <v>0.018677555559861</v>
       </c>
       <c r="K16" s="28" t="n">
         <v>-0.0194552529182879</v>
@@ -2452,10 +2452,10 @@
         <v>-0.2030888149171456</v>
       </c>
       <c r="F17" s="26" t="n">
-        <v>0.0672181606413582</v>
+        <v>0.0672181606413584</v>
       </c>
       <c r="G17" s="26" t="n">
-        <v>-0.010546558689646</v>
+        <v>-0.0105465586896457</v>
       </c>
       <c r="H17" s="26" t="n">
         <v>0.0260650374925286</v>
@@ -2512,7 +2512,7 @@
         <v>0.0254645426742394</v>
       </c>
       <c r="K18" s="28" t="n">
-        <v>-0.0091399766450234</v>
+        <v>-0.0091399766450236</v>
       </c>
     </row>
     <row r="19">
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="J19" s="26" t="n">
-        <v>0.0316386844276283</v>
+        <v>0.0316386844276284</v>
       </c>
       <c r="K19" s="26" t="n">
         <v>0.0478184312002618</v>
@@ -2581,7 +2581,7 @@
         <v>-0.1569326977205356</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1293738284887817</v>
+        <v>-0.1293738284887816</v>
       </c>
       <c r="G20" s="26" t="n">
         <v>-0.1448316943799105</v>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-10 07:49</t>
+          <t>Son Güncelleme: 2026-10-11 07:56</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3227,7 +3227,7 @@
         <v>212.3999938964844</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.07817255785017441</v>
+        <v>0.07817255785017463</v>
       </c>
       <c r="F5" s="29" t="n">
         <v>227196.4023002572</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1799,7 +1799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2631,7 +2631,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2750,7 +2750,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3001,7 +3001,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3126,7 +3126,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-11 07:56</t>
+          <t>Son Güncelleme: 2026-10-12 08:10</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$14</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 70.95/100</t>
+          <t>Güven Puanı: 72.16/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: KCHOL.IS, FROTO.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS, THYAO.IS</t>
+          <t>AZALT: KCHOL.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: PGSUS.IS, TOASO.IS</t>
+          <t>ÇIK: THYAO.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,7 +963,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2211403098513338</v>
+        <v>0.2386068933315149</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22114.03098513338</v>
+        <v>23860.68933315149</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0191938585275912</v>
+        <v>0.0190288554508686</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>424.4535822034185</v>
+        <v>454.0416082786219</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>216.4767693305948</v>
+        <v>410.4138715328373</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>198.3527119886738</v>
+        <v>382.6125</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.2902180977690493</v>
+        <v>0.3805771090173714</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1958022278387909</v>
+        <v>0.1842085690247992</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19580.22278387909</v>
+        <v>18420.85690247992</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0417061216022127</v>
+        <v>0.0345887193676873</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>816.6151524228771</v>
+        <v>637.1538499122036</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>77.50293703672203</v>
+        <v>133.7723245715562</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>70.68000144958496</v>
+        <v>122.8350028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.834122432044257</v>
+        <v>0.6917743873537451</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1830574623098753</v>
+        <v>0.177184537643686</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18305.74623098753</v>
+        <v>17718.4537643686</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0195381803197951</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>357.6609707494438</v>
+        <v>346.1863446361859</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>399.9138512304397</v>
+        <v>393.7966221485209</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>358.5245988394586</v>
+        <v>361.2410949552292</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.227242700359821</v>
+        <v>0.3017573994147673</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O14"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 7</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1363,32 +1363,32 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>401</v>
+        <v>402.75</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0205580539159813</v>
+        <v>-0.0181176605991072</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0190288554508686</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.06844627048378669</v>
+        <v>0.0761518731697465</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>392.7562203796915</v>
+        <v>395.4531121937096</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>408.6306043322236</v>
+        <v>410.4138715328373</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>428.4469544639985</v>
+        <v>433.4201669191154</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>380.95</v>
+        <v>382.6125</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1420,163 +1420,163 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>208</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0647872949675653</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.0185279533884517</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0466707608184535</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>194.5242426467464</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>211.853814304798</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>217.7075182502383</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>194.5242426467464</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="n">
+        <v>287.5</v>
+      </c>
+      <c r="E10" s="22" t="n">
+        <v>-0.0514324059862513</v>
+      </c>
+      <c r="F10" s="22" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+      <c r="G10" s="22" t="n">
+        <v>0.1281139375574904</v>
+      </c>
+      <c r="H10" s="21" t="n">
+        <v>272.7131832789527</v>
+      </c>
+      <c r="I10" s="21" t="n">
+        <v>283.4648862956888</v>
+      </c>
+      <c r="J10" s="21" t="n">
+        <v>324.3327570477785</v>
+      </c>
+      <c r="K10" s="21" t="n">
+        <v>272.7131832789527</v>
+      </c>
+      <c r="L10" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="20" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N10" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="14" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>212.3999938964844</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.06613598075081251</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0191938585275912</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.06904391931949121</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>198.3527119886738</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>216.4767693305948</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>227.0649219385337</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>198.3527119886738</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>386.25</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.0647479742259439</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.0195381803197951</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.1094018425999727</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>361.2410949552292</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>393.7966221485209</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>428.5064617042395</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>361.2410949552292</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="14" t="n">
+        <v>72.16</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O11" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="n">
-        <v>392.25</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0859793528630754</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.0195381803197951</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1188713720805591</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>358.5245988394586</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>399.9138512304397</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>438.8772956985994</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>358.5245988394586</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="n">
-        <v>74.40000152587891</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.030662695557949</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>0.0417061216022127</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.1388396310918185</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>72.11869692957994</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>77.50293703672203</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>84.72967029096267</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>70.68000144958496</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M11" s="17" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O11" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1586,64 +1586,64 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D12" s="15" t="n">
-        <v>284.25</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="E12" s="16" t="n">
-        <v>-0.052434175232511</v>
+        <v>-0.0492384989131554</v>
       </c>
       <c r="F12" s="16" t="n">
-        <v>0.0037537636029683</v>
+        <v>0.0345887193676873</v>
       </c>
       <c r="G12" s="16" t="n">
-        <v>0.0701777996871966</v>
+        <v>0.0882606294604084</v>
       </c>
       <c r="H12" s="15" t="n">
-        <v>269.3455856901587</v>
+        <v>122.9334649920228</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>285.3170073041437</v>
+        <v>133.7723245715562</v>
       </c>
       <c r="J12" s="15" t="n">
-        <v>304.1980395610856</v>
+        <v>140.7121027103387</v>
       </c>
       <c r="K12" s="15" t="n">
-        <v>269.3455856901587</v>
+        <v>122.8350028991699</v>
       </c>
       <c r="L12" s="14" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="M12" s="14" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N12" s="14" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O12" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="20" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>PETKM.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>135.6000061035156</v>
+        <v>20.55999946594238</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.0537067277155768</v>
+        <v>-0.0668953740197302</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>-0.0194552529182879</v>
+        <v>-0.0118534116209535</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.1090029643218296</v>
+        <v>0.0872554009436483</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>128.3173734974835</v>
+        <v>19.18463061182271</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>132.9618736890503</v>
+        <v>20.31629332934598</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>150.380808730857</v>
+        <v>22.35397046274438</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>128.3173734974835</v>
+        <v>18.94285522134967</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,78 +1681,21 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O13" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="20" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" s="20" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="n">
-        <v>269</v>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.07126395669746011</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.0091399766450236</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>0.0415042015350602</v>
-      </c>
-      <c r="H14" s="21" t="n">
-        <v>249.8299956483832</v>
-      </c>
-      <c r="I14" s="21" t="n">
-        <v>266.5413462824886</v>
-      </c>
-      <c r="J14" s="21" t="n">
-        <v>280.1646302129312</v>
-      </c>
-      <c r="K14" s="21" t="n">
-        <v>249.8299956483832</v>
-      </c>
-      <c r="L14" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="20" t="n">
-        <v>70.95</v>
-      </c>
-      <c r="N14" s="20" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif</t>
-        </is>
-      </c>
-      <c r="O14" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O14"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1782,7 +1725,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1799,7 +1742,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1886,20 +1829,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0563137182802316</v>
+        <v>-0.0577058518103443</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.083022533682165</v>
+        <v>0.0826626225903697</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1737397162419263</v>
+        <v>0.1883204288765572</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.0605774813729588</v>
+        <v>-0.06586916356473491</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -1907,10 +1850,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0191290724367972</v>
+        <v>0.0191282031761057</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0190288554508686</v>
       </c>
     </row>
     <row r="5">
@@ -1929,117 +1872,117 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.0726705431564196</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.0861618798955614</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.0941609327815446</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.0526104301604252</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0209519991267496</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.0185279533884517</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="22" t="n">
+        <v>-0.039264828738513</v>
+      </c>
+      <c r="F6" s="22" t="n">
+        <v>-0.1379310344827586</v>
+      </c>
+      <c r="G6" s="22" t="n">
+        <v>-0.0154109589041095</v>
+      </c>
+      <c r="H6" s="22" t="n">
+        <v>-0.1744791215756487</v>
+      </c>
+      <c r="I6" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J6" s="22" t="n">
+        <v>0.0183342111248289</v>
+      </c>
+      <c r="K6" s="22" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="14" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.0505140956902752</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.1016597019423537</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.09259259549969311</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0485430687963439</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0207860298554876</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0191938585275912</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.036139677786054</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>0.4954275911945411</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>0.5566438543758887</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.1962484737015959</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="E7" s="16" t="n">
+        <v>-0.0565768126863727</v>
+      </c>
+      <c r="F7" s="16" t="n">
+        <v>0.4656911172793534</v>
+      </c>
+      <c r="G7" s="16" t="n">
+        <v>0.5121985635198514</v>
+      </c>
+      <c r="H7" s="16" t="n">
+        <v>-0.2247959256692422</v>
+      </c>
+      <c r="I7" s="14" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.0280355349385904</v>
-      </c>
-      <c r="K6" s="19" t="n">
+      <c r="J7" s="16" t="n">
+        <v>0.0281724471412737</v>
+      </c>
+      <c r="K7" s="16" t="n">
         <v>0.0195381803197951</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.1137581390056649</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.09046456295602651</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-0.2589641394905586</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.0586189602200157</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0186206047020004</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>0.0417061216022127</v>
       </c>
     </row>
     <row r="8">
@@ -2048,7 +1991,7 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
@@ -2058,20 +2001,20 @@
       </c>
       <c r="D8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0556478405315614</v>
+        <v>-0.0307345654596361</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>-0.1748911465892597</v>
+        <v>0.0205209642157904</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>-0.0437342304457527</v>
+        <v>0.0173092415739459</v>
       </c>
       <c r="H8" s="16" t="n">
-        <v>-0.1639114710894957</v>
+        <v>-0.1191133144180434</v>
       </c>
       <c r="I8" s="14" t="inlineStr">
         <is>
@@ -2079,10 +2022,10 @@
         </is>
       </c>
       <c r="J8" s="16" t="n">
-        <v>0.0186262496527777</v>
+        <v>0.0220829823689621</v>
       </c>
       <c r="K8" s="16" t="n">
-        <v>0.0037537636029683</v>
+        <v>0.0345887193676873</v>
       </c>
     </row>
     <row r="9">
@@ -2091,12 +2034,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MEDIUM</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -2105,27 +2048,27 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.0256830236584196</v>
+        <v>-0.08852258687332409</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>0.0147979643368136</v>
+        <v>-0.08461068384632239</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>0.0147979643368136</v>
+        <v>-0.2280247788856223</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.1384289250641028</v>
+        <v>-0.0749760335276649</v>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.0263431621899088</v>
+        <v>0.0186285784449945</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.0012391857819089</v>
+        <v>0.1028056950580804</v>
       </c>
     </row>
     <row r="10">
@@ -2134,7 +2077,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -2148,27 +2091,27 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.0760021116066399</v>
+        <v>-0.0425859380940586</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>-0.0193370165745856</v>
+        <v>-0.0866373192033314</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>-0.0326975476839237</v>
+        <v>0.3116310491927303</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.07408657888789739</v>
+        <v>-0.2316984786697485</v>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.0201048370906429</v>
+        <v>0.0256941804933773</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.058882151916034</v>
+        <v>0.019070255160478</v>
       </c>
     </row>
     <row r="11">
@@ -2177,7 +2120,7 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -2191,16 +2134,16 @@
         </is>
       </c>
       <c r="E11" s="24" t="n">
-        <v>-0.0431869167532524</v>
+        <v>-0.0300196404347403</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>-0.003875968992248</v>
+        <v>-0.0958715316352494</v>
       </c>
       <c r="G11" s="24" t="n">
-        <v>-0.0140648416890173</v>
+        <v>-0.060533826327491</v>
       </c>
       <c r="H11" s="24" t="n">
-        <v>-0.1007340676179966</v>
+        <v>-0.2407365854282926</v>
       </c>
       <c r="I11" s="23" t="inlineStr">
         <is>
@@ -2208,10 +2151,10 @@
         </is>
       </c>
       <c r="J11" s="24" t="n">
-        <v>0.0221911300146039</v>
+        <v>0.020549051226188</v>
       </c>
       <c r="K11" s="24" t="n">
-        <v>0.0265059178623019</v>
+        <v>0.0034066979194351</v>
       </c>
     </row>
     <row r="12">
@@ -2234,16 +2177,16 @@
         </is>
       </c>
       <c r="E12" s="24" t="n">
-        <v>-0.1561844998696046</v>
+        <v>-0.1491043340185853</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>-0.1860465241859903</v>
+        <v>-0.1717948717948717</v>
       </c>
       <c r="G12" s="24" t="n">
-        <v>-0.2708333434114132</v>
+        <v>-0.244621152035703</v>
       </c>
       <c r="H12" s="24" t="n">
-        <v>0.0268120563432003</v>
+        <v>0.0108941768229855</v>
       </c>
       <c r="I12" s="23" t="inlineStr">
         <is>
@@ -2251,10 +2194,10 @@
         </is>
       </c>
       <c r="J12" s="24" t="n">
-        <v>0.0152502117516969</v>
+        <v>0.0152042217780923</v>
       </c>
       <c r="K12" s="24" t="n">
-        <v>0.0007363095911598</v>
+        <v>0.0318627708566732</v>
       </c>
     </row>
     <row r="13">
@@ -2263,7 +2206,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2277,16 +2220,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.0157171518226979</v>
+        <v>-0.020994533707539</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>-0.06355143039025971</v>
+        <v>0.0392961939163964</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>-0.07734808143556809</v>
+        <v>0.0320325704494266</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.2330852114160289</v>
+        <v>-0.1457413007169843</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2294,10 +2237,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.0206102435815252</v>
+        <v>0.0260744241772801</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.0124594158070348</v>
+        <v>0.0653045409271195</v>
       </c>
     </row>
     <row r="14">
@@ -2306,7 +2249,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2320,27 +2263,27 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0634596530382678</v>
+        <v>-0.0589459097079656</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>-0.09405947792659509</v>
+        <v>0.0029563480226335</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>0.2341201160407109</v>
+        <v>-0.0202166285325473</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>-0.222405128083297</v>
+        <v>0.0018435798894262</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.0256071566045418</v>
+        <v>0.0239007500913969</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.0190703728875496</v>
+        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="15">
@@ -2349,7 +2292,7 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -2363,16 +2306,16 @@
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>-0.06579843212013919</v>
+        <v>-0.1191983405906471</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>-0.0087272505326704</v>
+        <v>-0.063901313265174</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>-0.0305832351713553</v>
+        <v>-0.0649496400173262</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.0331064851884299</v>
+        <v>0.0009450280090033001</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -2380,53 +2323,53 @@
         </is>
       </c>
       <c r="J15" s="26" t="n">
-        <v>0.0239822715859189</v>
+        <v>0.0213692066505879</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>0.0111110916693351</v>
+        <v>0.048351558995445</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n">
+      <c r="A16" s="25" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="27" t="inlineStr">
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C16" s="27" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E16" s="28" t="n">
-        <v>-0.1234647137783514</v>
-      </c>
-      <c r="F16" s="28" t="n">
-        <v>-0.2032901966223208</v>
-      </c>
-      <c r="G16" s="28" t="n">
-        <v>-0.2399102536842193</v>
-      </c>
-      <c r="H16" s="28" t="n">
-        <v>-0.102048370776654</v>
-      </c>
-      <c r="I16" s="27" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>-0.123287728499864</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.1874244325510758</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.2320000348772322</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.09256794568438829</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="28" t="n">
-        <v>0.018677555559861</v>
-      </c>
-      <c r="K16" s="28" t="n">
-        <v>-0.0194552529182879</v>
+      <c r="J16" s="26" t="n">
+        <v>0.0184209265016707</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2435,127 +2378,127 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.0885640584694754</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.12106135986733</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>0.0515873015873016</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.1698261549468688</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0255179500222131</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.009805545465515699</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="25" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>-0.1185696361355082</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>-0.00354609929078</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>0.027046783625731</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>0.0102367776137011</v>
+      </c>
+      <c r="I18" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>0.0310769985189652</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0.1070429210315777</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="27" t="inlineStr">
+        <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C19" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.2030888149171456</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>0.0672181606413584</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0105465586896457</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>0.0260650374925286</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0394224350412246</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.07582576484113181</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
+      <c r="D19" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.081127241673783</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.1114781172584641</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>0.0112781954887217</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.1670440637480758</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>0.0254645426742394</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>-0.0091399766450236</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="25" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="26" t="n">
-        <v>-0.1330018645121193</v>
-      </c>
-      <c r="F19" s="26" t="n">
-        <v>-0.0574324324324324</v>
-      </c>
-      <c r="G19" s="26" t="n">
-        <v>0.03486646884273</v>
-      </c>
-      <c r="H19" s="26" t="n">
-        <v>-0.0046009331250927</v>
-      </c>
-      <c r="I19" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="26" t="n">
-        <v>0.0316386844276284</v>
-      </c>
-      <c r="K19" s="26" t="n">
-        <v>0.0478184312002618</v>
+      <c r="E19" s="28" t="n">
+        <v>-0.1769415595392859</v>
+      </c>
+      <c r="F19" s="28" t="n">
+        <v>0.0383838514225449</v>
+      </c>
+      <c r="G19" s="28" t="n">
+        <v>-0.062043823248996</v>
+      </c>
+      <c r="H19" s="28" t="n">
+        <v>-0.07030959147250811</v>
+      </c>
+      <c r="I19" s="27" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J19" s="28" t="n">
+        <v>0.0393274388764336</v>
+      </c>
+      <c r="K19" s="28" t="n">
+        <v>-0.0118534116209535</v>
       </c>
     </row>
     <row r="20">
@@ -2578,16 +2521,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1569326977205356</v>
+        <v>-0.1366318717686869</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1293738284887816</v>
+        <v>-0.1182197159544896</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.1448316943799105</v>
+        <v>-0.1202191379963973</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.0441114367350677</v>
+        <v>-0.0841787164039297</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2595,10 +2538,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0269505186174669</v>
+        <v>0.0269596069705385</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.0809523100911218</v>
+        <v>0.1001577768561146</v>
       </c>
     </row>
   </sheetData>
@@ -2623,7 +2566,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2631,7 +2574,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2656,7 +2599,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS, TUPRS.IS, FROTO.IS</t>
+          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2668,7 +2611,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, THYAO.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2680,7 +2623,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>PGSUS.IS, TOASO.IS</t>
+          <t>THYAO.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2692,7 +2635,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS, SAHOL.IS, GARAN.IS, ARCLK.IS, TCELL.IS, EREGL.IS, AKBNK.IS, PETKM.IS, ASELS.IS, SISE.IS</t>
+          <t>FROTO.IS, EREGL.IS, TCELL.IS, ARCLK.IS, YKBNK.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2647,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.92 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2742,7 +2685,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2750,7 +2693,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2811,7 +2754,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2835,7 +2778,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REMOVED</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2790,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2802,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2993,7 +2936,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3001,7 +2944,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3025,7 +2968,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12266</v>
+        <v>12150.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3035,7 +2978,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13602.73352050781</v>
+        <v>13606.9315234375</v>
       </c>
     </row>
     <row r="6">
@@ -3069,7 +3012,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>70.95</v>
+        <v>72.16</v>
       </c>
     </row>
     <row r="9">
@@ -3103,7 +3046,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3112,7 +3055,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-08</t>
+          <t>Rapor Tarihi: 2026-10-09</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3126,7 +3069,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-12 08:10</t>
+          <t>Son Güncelleme: 2026-10-13 08:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3194,19 +3137,19 @@
         <v>399.5</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>348.75</v>
+        <v>351.25</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>-0.1270337922403004</v>
+        <v>-0.1207759699624531</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-89492.73324614356</v>
+        <v>-85084.2242192399</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="5">
@@ -3224,19 +3167,19 @@
         <v>197</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>212.3999938964844</v>
+        <v>208</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.07817255785017463</v>
+        <v>0.05583756345177671</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>227196.4023002572</v>
+        <v>162283.208818242</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="6">
@@ -3254,19 +3197,19 @@
         <v>96.5</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>88.75</v>
+        <v>83.5</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.0803108808290155</v>
+        <v>-0.1347150259067358</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-7052.458199202025</v>
+        <v>-11829.92988253244</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="7">
@@ -3284,19 +3227,19 @@
         <v>133.3999938964844</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>128.5</v>
+        <v>129.3000030517578</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.03673159011001659</v>
+        <v>-0.03073456545963615</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-177880.1258255821</v>
+        <v>-148838.3256695392</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="8">
@@ -3314,19 +3257,19 @@
         <v>405.5</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>401</v>
+        <v>402.75</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.01109741060419234</v>
+        <v>-0.006781750924784169</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-31469.13041166309</v>
+        <v>-19231.13525157189</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="9">
@@ -3344,19 +3287,19 @@
         <v>77.40000152587891</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>74.40000152587891</v>
+        <v>74.65000152587891</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.03875968915836447</v>
+        <v>-0.03552971506183411</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-173530.4240112733</v>
+        <v>-159069.555343667</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
     <row r="10">
@@ -3374,19 +3317,19 @@
         <v>387</v>
       </c>
       <c r="D10" s="29" t="n">
-        <v>392.25</v>
+        <v>386.25</v>
       </c>
       <c r="E10" s="30" t="n">
-        <v>0.01356589147286824</v>
+        <v>-0.001937984496124034</v>
       </c>
       <c r="F10" s="29" t="n">
-        <v>58578.40995691251</v>
+        <v>-8368.344279558398</v>
       </c>
       <c r="G10" s="29" t="n">
-        <v>19978559.36642952</v>
+        <v>19902071.12003835</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>-0.1087565959300204</v>
+        <v>-0.1049328663164039</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,12 +17,12 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,12 +86,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F4CCCC"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -157,7 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -211,10 +211,10 @@
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 72.16/100</t>
+          <t>Güven Puanı: 76.06/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, GARAN.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: KCHOL.IS</t>
+          <t>AZALT: YKBNK.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, PETKM.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2386068933315149</v>
+        <v>0.2224992347307692</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>23860.68933315149</v>
+        <v>22249.92347307692</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>454.0416082786219</v>
+        <v>423.3924250506313</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>410.4138715328373</v>
+        <v>404.044974109044</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>382.6125</v>
+        <v>376.675</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805771090173714</v>
+        <v>0.3805787696869603</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1842085690247992</v>
+        <v>0.2084179173556735</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18420.85690247992</v>
+        <v>20841.79173556735</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0345887193676873</v>
+        <v>0.018527596735292</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>637.1538499122036</v>
+        <v>386.1483125175334</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>133.7723245715562</v>
+        <v>210.7333535479328</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>122.8350028991699</v>
+        <v>193.4955029631254</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.6917743873537451</v>
+        <v>0.2859757726351672</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.177184537643686</v>
+        <v>0.1690828479135573</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>17718.4537643686</v>
+        <v>16908.28479135573</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>346.1863446361859</v>
+        <v>330.3588004488608</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>393.7966221485209</v>
+        <v>392.2673531816593</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.3017573994147673</v>
+        <v>0.2283666196330747</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1367,28 +1367,28 @@
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>402.75</v>
+        <v>396.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0181176605991072</v>
+        <v>-0.0339317012120768</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0761518731697465</v>
+        <v>0.07229912231651719</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>395.4531121937096</v>
+        <v>383.0460804694115</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>410.4138715328373</v>
+        <v>404.044974109044</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>433.4201669191154</v>
+        <v>425.1666019984991</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>382.6125</v>
+        <v>376.675</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,7 +1396,7 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1410,114 +1410,114 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="17" t="n">
+      <c r="A9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="n">
-        <v>208</v>
-      </c>
-      <c r="E9" s="19" t="n">
+      <c r="C9" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="15" t="n">
+        <v>206.8999938964844</v>
+      </c>
+      <c r="E9" s="16" t="n">
         <v>-0.0647872949675653</v>
       </c>
-      <c r="F9" s="19" t="n">
-        <v>0.0185279533884517</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0466707608184535</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>194.5242426467464</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>211.853814304798</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>217.7075182502383</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>194.5242426467464</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="F9" s="16" t="n">
+        <v>0.018527596735292</v>
+      </c>
+      <c r="G9" s="16" t="n">
+        <v>0.0466708728798923</v>
+      </c>
+      <c r="H9" s="15" t="n">
+        <v>193.4955029631254</v>
+      </c>
+      <c r="I9" s="15" t="n">
+        <v>210.7333535479328</v>
+      </c>
+      <c r="J9" s="15" t="n">
+        <v>216.5561972104777</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>193.4955029631254</v>
+      </c>
+      <c r="L9" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
+      <c r="M9" s="14" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N9" s="14" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="O9" s="14" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="20" t="n">
+      <c r="A10" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C10" s="20" t="inlineStr">
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="21" t="n">
-        <v>287.5</v>
-      </c>
-      <c r="E10" s="22" t="n">
-        <v>-0.0514324059862513</v>
-      </c>
-      <c r="F10" s="22" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-      <c r="G10" s="22" t="n">
+      <c r="D10" s="18" t="n">
+        <v>285.75</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0628618693134822</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-0.0241174841137557</v>
+      </c>
+      <c r="G10" s="19" t="n">
         <v>0.1281139375574904</v>
       </c>
-      <c r="H10" s="21" t="n">
-        <v>272.7131832789527</v>
-      </c>
-      <c r="I10" s="21" t="n">
-        <v>283.4648862956888</v>
-      </c>
-      <c r="J10" s="21" t="n">
-        <v>324.3327570477785</v>
-      </c>
-      <c r="K10" s="21" t="n">
-        <v>272.7131832789527</v>
-      </c>
-      <c r="L10" s="20" t="inlineStr">
+      <c r="H10" s="18" t="n">
+        <v>267.7872208436725</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>278.8584289144943</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>322.3585576570529</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>267.7872208436725</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="20" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N10" s="20" t="inlineStr">
+      <c r="M10" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="20" t="inlineStr">
+      <c r="O10" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
@@ -1538,28 +1538,28 @@
         </is>
       </c>
       <c r="D11" s="15" t="n">
-        <v>386.25</v>
+        <v>384.75</v>
       </c>
       <c r="E11" s="16" t="n">
-        <v>-0.0647479742259439</v>
+        <v>-0.0855566365423768</v>
       </c>
       <c r="F11" s="16" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
       <c r="G11" s="16" t="n">
-        <v>0.1094018425999727</v>
+        <v>0.1009766152812969</v>
       </c>
       <c r="H11" s="15" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>393.7966221485209</v>
+        <v>392.2673531816593</v>
       </c>
       <c r="J11" s="15" t="n">
-        <v>428.5064617042395</v>
+        <v>423.600752729479</v>
       </c>
       <c r="K11" s="15" t="n">
-        <v>361.2410949552292</v>
+        <v>351.8320840903206</v>
       </c>
       <c r="L11" s="14" t="inlineStr">
         <is>
@@ -1567,7 +1567,7 @@
         </is>
       </c>
       <c r="M11" s="14" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
       <c r="N11" s="14" t="inlineStr">
         <is>
@@ -1581,121 +1581,235 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="14" t="n">
+      <c r="A12" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>129.3000030517578</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0492384989131554</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.0345887193676873</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.0882606294604084</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>122.9334649920228</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>133.7723245715562</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>140.7121027103387</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>122.8350028991699</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M12" s="14" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="21" t="n">
+        <v>35.70000076293945</v>
+      </c>
+      <c r="E12" s="22" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F12" s="22" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+      <c r="G12" s="22" t="n">
+        <v>0.0895632063722737</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>33.79405057778999</v>
+      </c>
+      <c r="I12" s="21" t="n">
+        <v>35.74423969629903</v>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>38.89740729876093</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>33.79405057778999</v>
+      </c>
+      <c r="L12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="20" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N12" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="n">
+        <v>79.69999694824219</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.0476629979133642</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0123915741984644</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.1088380129700114</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>75.90125616000299</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>78.71238852244066</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>88.37438624980484</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>75.71499710083008</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="20" t="n">
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="n">
+        <v>259.25</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.1122727836453332</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-0.0351689285600669</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.0835562048104195</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>230.1432808399474</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>250.1324552708026</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>280.9119460971012</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>230.1432808399474</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
         <v>16</v>
       </c>
-      <c r="B13" s="20" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="20" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="21" t="n">
-        <v>20.55999946594238</v>
-      </c>
-      <c r="E13" s="22" t="n">
-        <v>-0.0668953740197302</v>
-      </c>
-      <c r="F13" s="22" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G13" s="22" t="n">
-        <v>0.0872554009436483</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>19.18463061182271</v>
-      </c>
-      <c r="I13" s="21" t="n">
-        <v>20.31629332934598</v>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>22.35397046274438</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>18.94285522134967</v>
-      </c>
-      <c r="L13" s="20" t="inlineStr">
+      <c r="D15" s="18" t="n">
+        <v>341.75</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0977678549854652</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.005529134834197</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1083753514763447</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>308.3378355587172</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>339.8604181704131</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>378.7872763670408</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>308.3378355587172</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="20" t="n">
-        <v>72.16</v>
-      </c>
-      <c r="N13" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; volatilite yüksek; alt bant riski belirgin</t>
+      <c r="M15" s="17" t="n">
+        <v>76.06</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1725,7 +1839,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1742,7 +1856,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1833,16 +1947,16 @@
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0577058518103443</v>
+        <v>-0.0824642322042362</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.0826626225903697</v>
+        <v>0.0374477363977292</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.1883204288765572</v>
+        <v>0.103857588951256</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.06586916356473491</v>
+        <v>-0.06741185359372349</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -1850,96 +1964,96 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0191282031761057</v>
+        <v>0.0189524792403736</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0190288554508686</v>
+        <v>0.019028938484348</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="17" t="n">
+      <c r="A5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="B5" s="17" t="inlineStr">
+      <c r="B5" s="14" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C5" s="17" t="inlineStr">
+      <c r="C5" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="17" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.0726705431564196</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>0.0861618798955614</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.0941609327815446</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0526104301604252</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="16" t="n">
+        <v>-0.0824833973548364</v>
+      </c>
+      <c r="F5" s="16" t="n">
+        <v>0.082679159017976</v>
+      </c>
+      <c r="G5" s="16" t="n">
+        <v>0.0273088389606748</v>
+      </c>
+      <c r="H5" s="16" t="n">
+        <v>-0.0597960627732419</v>
+      </c>
+      <c r="I5" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0209519991267496</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>0.0185279533884517</v>
+      <c r="J5" s="16" t="n">
+        <v>0.0209647836935707</v>
+      </c>
+      <c r="K5" s="16" t="n">
+        <v>0.018527596735292</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="20" t="n">
+      <c r="A6" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="17" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C6" s="20" t="inlineStr">
+      <c r="C6" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
+      <c r="D6" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="22" t="n">
-        <v>-0.039264828738513</v>
-      </c>
-      <c r="F6" s="22" t="n">
-        <v>-0.1379310344827586</v>
-      </c>
-      <c r="G6" s="22" t="n">
-        <v>-0.0154109589041095</v>
-      </c>
-      <c r="H6" s="22" t="n">
-        <v>-0.1744791215756487</v>
-      </c>
-      <c r="I6" s="20" t="inlineStr">
+      <c r="E6" s="19" t="n">
+        <v>-0.048293089092423</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>-0.1234662576687116</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.0985804416403786</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.1838035473419896</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="22" t="n">
-        <v>0.0183342111248289</v>
-      </c>
-      <c r="K6" s="22" t="n">
-        <v>-0.0140351781019522</v>
+      <c r="J6" s="19" t="n">
+        <v>0.018156884273008</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="7">
@@ -1962,16 +2076,16 @@
         </is>
       </c>
       <c r="E7" s="16" t="n">
-        <v>-0.0565768126863727</v>
+        <v>-0.0528542750964556</v>
       </c>
       <c r="F7" s="16" t="n">
-        <v>0.4656911172793534</v>
+        <v>0.4465180215722137</v>
       </c>
       <c r="G7" s="16" t="n">
-        <v>0.5121985635198514</v>
+        <v>0.5603375976000915</v>
       </c>
       <c r="H7" s="16" t="n">
-        <v>-0.2247959256692422</v>
+        <v>-0.2244550284745238</v>
       </c>
       <c r="I7" s="14" t="inlineStr">
         <is>
@@ -1979,53 +2093,53 @@
         </is>
       </c>
       <c r="J7" s="16" t="n">
-        <v>0.0281724471412737</v>
+        <v>0.028200042319893</v>
       </c>
       <c r="K7" s="16" t="n">
-        <v>0.0195381803197951</v>
+        <v>0.0195382798743581</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="20" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="B8" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0307345654596361</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0205209642157904</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.0173092415739459</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.1191133144180434</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0220829823689621</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.0345887193676873</v>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="22" t="n">
+        <v>-0.0272479558368244</v>
+      </c>
+      <c r="F8" s="22" t="n">
+        <v>0.0512367999227174</v>
+      </c>
+      <c r="G8" s="22" t="n">
+        <v>-0.0490143875256759</v>
+      </c>
+      <c r="H8" s="22" t="n">
+        <v>-0.1525930514087783</v>
+      </c>
+      <c r="I8" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="22" t="n">
+        <v>0.0260785342604604</v>
+      </c>
+      <c r="K8" s="22" t="n">
+        <v>0.0012391857819089</v>
       </c>
     </row>
     <row r="9">
@@ -2034,12 +2148,12 @@
       </c>
       <c r="B9" s="23" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C9" s="23" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D9" s="23" t="inlineStr">
@@ -2048,27 +2162,27 @@
         </is>
       </c>
       <c r="E9" s="24" t="n">
-        <v>-0.08852258687332409</v>
+        <v>-0.0456853548743018</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>-0.08461068384632239</v>
+        <v>-0.1021968119588387</v>
       </c>
       <c r="G9" s="24" t="n">
-        <v>-0.2280247788856223</v>
+        <v>0.2884126747282864</v>
       </c>
       <c r="H9" s="24" t="n">
-        <v>-0.0749760335276649</v>
+        <v>-0.246774969672824</v>
       </c>
       <c r="I9" s="23" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="24" t="n">
-        <v>0.0186285784449945</v>
+        <v>0.0255018791340404</v>
       </c>
       <c r="K9" s="24" t="n">
-        <v>0.1028056950580804</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2077,7 +2191,7 @@
       </c>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -2091,27 +2205,27 @@
         </is>
       </c>
       <c r="E10" s="24" t="n">
-        <v>-0.0425859380940586</v>
+        <v>-0.0327868405107442</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>-0.0866373192033314</v>
+        <v>0.0069822280674132</v>
       </c>
       <c r="G10" s="24" t="n">
-        <v>0.3116310491927303</v>
+        <v>-0.0559999778053977</v>
       </c>
       <c r="H10" s="24" t="n">
-        <v>-0.2316984786697485</v>
+        <v>-0.1419483389452992</v>
       </c>
       <c r="I10" s="23" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J10" s="24" t="n">
-        <v>0.0256941804933773</v>
+        <v>0.021982568542005</v>
       </c>
       <c r="K10" s="24" t="n">
-        <v>0.019070255160478</v>
+        <v>0.0426715939840771</v>
       </c>
     </row>
     <row r="11">
@@ -2120,84 +2234,84 @@
       </c>
       <c r="B11" s="23" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
         <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.1086300563157068</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.0888341061879893</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.2745579935142653</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.0764441679740844</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="24" t="n">
+        <v>0.0186569658567114</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.102805642445124</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
+        <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="24" t="n">
-        <v>-0.0300196404347403</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.0958715316352494</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-0.060533826327491</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>-0.2407365854282926</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="D12" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.1680585134722519</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>-0.1863195565962446</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>-0.2877569628110316</v>
+      </c>
+      <c r="H12" s="19" t="n">
+        <v>-0.0044326364510109</v>
+      </c>
+      <c r="I12" s="17" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.020549051226188</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.0034066979194351</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="23" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="23" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="24" t="n">
-        <v>-0.1491043340185853</v>
-      </c>
-      <c r="F12" s="24" t="n">
-        <v>-0.1717948717948717</v>
-      </c>
-      <c r="G12" s="24" t="n">
-        <v>-0.244621152035703</v>
-      </c>
-      <c r="H12" s="24" t="n">
-        <v>0.0108941768229855</v>
-      </c>
-      <c r="I12" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="24" t="n">
-        <v>0.0152042217780923</v>
-      </c>
-      <c r="K12" s="24" t="n">
-        <v>0.0318627708566732</v>
+      <c r="J12" s="19" t="n">
+        <v>0.0152262854483399</v>
+      </c>
+      <c r="K12" s="19" t="n">
+        <v>-0.0123915741984644</v>
       </c>
     </row>
     <row r="13">
@@ -2206,7 +2320,7 @@
       </c>
       <c r="B13" s="23" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -2220,16 +2334,16 @@
         </is>
       </c>
       <c r="E13" s="24" t="n">
-        <v>-0.020994533707539</v>
+        <v>-0.0598349196247974</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>0.0392961939163964</v>
+        <v>-0.010853835261384</v>
       </c>
       <c r="G13" s="24" t="n">
-        <v>0.0320325704494266</v>
+        <v>-0.0976897891205136</v>
       </c>
       <c r="H13" s="24" t="n">
-        <v>-0.1457413007169843</v>
+        <v>-0.0288025021689304</v>
       </c>
       <c r="I13" s="23" t="inlineStr">
         <is>
@@ -2237,10 +2351,10 @@
         </is>
       </c>
       <c r="J13" s="24" t="n">
-        <v>0.0260744241772801</v>
+        <v>0.0237657020847789</v>
       </c>
       <c r="K13" s="24" t="n">
-        <v>0.0653045409271195</v>
+        <v>0.0111110916693351</v>
       </c>
     </row>
     <row r="14">
@@ -2249,7 +2363,7 @@
       </c>
       <c r="B14" s="25" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C14" s="25" t="inlineStr">
@@ -2263,16 +2377,16 @@
         </is>
       </c>
       <c r="E14" s="26" t="n">
-        <v>-0.0589459097079656</v>
+        <v>-0.1149003591499333</v>
       </c>
       <c r="F14" s="26" t="n">
-        <v>0.0029563480226335</v>
+        <v>-0.0570150771170184</v>
       </c>
       <c r="G14" s="26" t="n">
-        <v>-0.0202166285325473</v>
+        <v>-0.12454592828274</v>
       </c>
       <c r="H14" s="26" t="n">
-        <v>0.0018435798894262</v>
+        <v>0.0117628907218287</v>
       </c>
       <c r="I14" s="25" t="inlineStr">
         <is>
@@ -2280,10 +2394,10 @@
         </is>
       </c>
       <c r="J14" s="26" t="n">
-        <v>0.0239007500913969</v>
+        <v>0.0214095607902122</v>
       </c>
       <c r="K14" s="26" t="n">
-        <v>0.0111110916693351</v>
+        <v>0.0483517655572096</v>
       </c>
     </row>
     <row r="15">
@@ -2292,7 +2406,7 @@
       </c>
       <c r="B15" s="25" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C15" s="25" t="inlineStr">
@@ -2306,16 +2420,16 @@
         </is>
       </c>
       <c r="E15" s="26" t="n">
-        <v>-0.1191983405906471</v>
+        <v>-0.0621986223534939</v>
       </c>
       <c r="F15" s="26" t="n">
-        <v>-0.063901313265174</v>
+        <v>-0.1175135871766351</v>
       </c>
       <c r="G15" s="26" t="n">
-        <v>-0.0649496400173262</v>
+        <v>-0.1254496162867269</v>
       </c>
       <c r="H15" s="26" t="n">
-        <v>0.0009450280090033001</v>
+        <v>-0.28242131227121</v>
       </c>
       <c r="I15" s="25" t="inlineStr">
         <is>
@@ -2323,10 +2437,10 @@
         </is>
       </c>
       <c r="J15" s="26" t="n">
-        <v>0.0213692066505879</v>
+        <v>0.0205397708069739</v>
       </c>
       <c r="K15" s="26" t="n">
-        <v>0.048351558995445</v>
+        <v>0.0124595339704571</v>
       </c>
     </row>
     <row r="16">
@@ -2349,16 +2463,16 @@
         </is>
       </c>
       <c r="E16" s="26" t="n">
-        <v>-0.123287728499864</v>
+        <v>-0.1381323182445148</v>
       </c>
       <c r="F16" s="26" t="n">
-        <v>-0.1874244325510758</v>
+        <v>-0.1993976271296121</v>
       </c>
       <c r="G16" s="26" t="n">
-        <v>-0.2320000348772322</v>
+        <v>-0.2854839037823421</v>
       </c>
       <c r="H16" s="26" t="n">
-        <v>-0.09256794568438829</v>
+        <v>-0.1118784227705204</v>
       </c>
       <c r="I16" s="25" t="inlineStr">
         <is>
@@ -2366,7 +2480,7 @@
         </is>
       </c>
       <c r="J16" s="26" t="n">
-        <v>0.0184209265016707</v>
+        <v>0.0184277553287016</v>
       </c>
       <c r="K16" s="26" t="n">
         <v>0</v>
@@ -2378,84 +2492,84 @@
       </c>
       <c r="B17" s="25" t="inlineStr">
         <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D17" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>-0.1782819920633277</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>0.0346938924459749</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.0249999312254073</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>-0.1010948896538656</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>0.0393464526538943</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.0706630475858574</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C17" s="25" t="inlineStr">
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.0885640584694754</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>-0.12106135986733</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>0.0515873015873016</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.1698261549468688</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="28" t="n">
+        <v>-0.1351125938281902</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1211864406779661</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.0442396313364055</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.2157061124078084</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0255179500222131</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.009805545465515699</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="25" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="25" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="26" t="n">
-        <v>-0.1185696361355082</v>
-      </c>
-      <c r="F18" s="26" t="n">
-        <v>-0.00354609929078</v>
-      </c>
-      <c r="G18" s="26" t="n">
-        <v>0.027046783625731</v>
-      </c>
-      <c r="H18" s="26" t="n">
-        <v>0.0102367776137011</v>
-      </c>
-      <c r="I18" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="26" t="n">
-        <v>0.0310769985189652</v>
-      </c>
-      <c r="K18" s="26" t="n">
-        <v>0.1070429210315777</v>
+      <c r="J18" s="28" t="n">
+        <v>0.0255197014582361</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>-0.0351689285600669</v>
       </c>
     </row>
     <row r="19">
@@ -2464,7 +2578,7 @@
       </c>
       <c r="B19" s="27" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>ASELS.IS</t>
         </is>
       </c>
       <c r="C19" s="27" t="inlineStr">
@@ -2478,27 +2592,27 @@
         </is>
       </c>
       <c r="E19" s="28" t="n">
-        <v>-0.1769415595392859</v>
+        <v>-0.1320634920634921</v>
       </c>
       <c r="F19" s="28" t="n">
-        <v>0.0383838514225449</v>
+        <v>-0.0193687230989957</v>
       </c>
       <c r="G19" s="28" t="n">
-        <v>-0.062043823248996</v>
+        <v>-0.0565907522429262</v>
       </c>
       <c r="H19" s="28" t="n">
-        <v>-0.07030959147250811</v>
+        <v>0.0129751276111689</v>
       </c>
       <c r="I19" s="27" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J19" s="28" t="n">
-        <v>0.0393274388764336</v>
+        <v>0.0312353919675467</v>
       </c>
       <c r="K19" s="28" t="n">
-        <v>-0.0118534116209535</v>
+        <v>-0.005529134834197</v>
       </c>
     </row>
     <row r="20">
@@ -2521,16 +2635,16 @@
         </is>
       </c>
       <c r="E20" s="26" t="n">
-        <v>-0.1366318717686869</v>
+        <v>-0.1640729467145814</v>
       </c>
       <c r="F20" s="26" t="n">
-        <v>-0.1182197159544896</v>
+        <v>-0.1376146837152142</v>
       </c>
       <c r="G20" s="26" t="n">
-        <v>-0.1202191379963973</v>
+        <v>-0.1843966326020115</v>
       </c>
       <c r="H20" s="26" t="n">
-        <v>-0.0841787164039297</v>
+        <v>-0.1831940100157078</v>
       </c>
       <c r="I20" s="25" t="inlineStr">
         <is>
@@ -2538,10 +2652,10 @@
         </is>
       </c>
       <c r="J20" s="26" t="n">
-        <v>0.0269596069705385</v>
+        <v>0.0269414901477214</v>
       </c>
       <c r="K20" s="26" t="n">
-        <v>0.1001577768561146</v>
+        <v>0.0597309519640328</v>
       </c>
     </row>
   </sheetData>
@@ -2566,7 +2680,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2574,7 +2688,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2599,7 +2713,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, TUPRS.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2725,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
     </row>
@@ -2623,7 +2737,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, PETKM.IS</t>
+          <t>THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2635,7 +2749,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS, EREGL.IS, TCELL.IS, ARCLK.IS, YKBNK.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>EREGL.IS, GARAN.IS, FROTO.IS, AKBNK.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2647,7 +2761,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2685,7 +2799,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2693,7 +2807,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2790,7 +2904,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2916,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>REDUCED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -2936,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2944,7 +3058,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2968,7 +3082,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12150.7001953125</v>
+        <v>12250.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -2978,7 +3092,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13606.9315234375</v>
+        <v>13611.73302246094</v>
       </c>
     </row>
     <row r="6">
@@ -3012,7 +3126,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>72.16</v>
+        <v>76.06</v>
       </c>
     </row>
     <row r="9">
@@ -3039,7 +3153,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3049,13 +3163,13 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-09</t>
+          <t>Rapor Tarihi: 2026-10-12</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3069,7 +3183,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-13 08:36</t>
+          <t>Son Güncelleme: 2026-10-14 06:50</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3125,215 +3239,185 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASELS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>2026-07-03</t>
+          <t>2026-07-16</t>
         </is>
       </c>
       <c r="C4" s="29" t="n">
-        <v>399.5</v>
+        <v>197</v>
       </c>
       <c r="D4" s="29" t="n">
-        <v>351.25</v>
+        <v>206.8999938964844</v>
       </c>
       <c r="E4" s="30" t="n">
-        <v>-0.1207759699624531</v>
+        <v>0.05025377612428628</v>
       </c>
       <c r="F4" s="29" t="n">
-        <v>-85084.2242192399</v>
+        <v>146054.7978911358</v>
       </c>
       <c r="G4" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>2026-07-16</t>
+          <t>2026-09-08</t>
         </is>
       </c>
       <c r="C5" s="29" t="n">
-        <v>197</v>
+        <v>96.5</v>
       </c>
       <c r="D5" s="29" t="n">
-        <v>208</v>
+        <v>84.34999847412109</v>
       </c>
       <c r="E5" s="30" t="n">
-        <v>0.05583756345177671</v>
+        <v>-0.1259067515635119</v>
       </c>
       <c r="F5" s="29" t="n">
-        <v>162283.208818242</v>
+        <v>-11056.43585567767</v>
       </c>
       <c r="G5" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-10</t>
         </is>
       </c>
       <c r="C6" s="29" t="n">
-        <v>96.5</v>
+        <v>133.3999938964844</v>
       </c>
       <c r="D6" s="29" t="n">
-        <v>83.5</v>
+        <v>129.8000030517578</v>
       </c>
       <c r="E6" s="30" t="n">
-        <v>-0.1347150259067358</v>
+        <v>-0.02698643935111478</v>
       </c>
       <c r="F6" s="29" t="n">
-        <v>-11829.92988253244</v>
+        <v>-130687.2698127953</v>
       </c>
       <c r="G6" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C7" s="29" t="n">
-        <v>133.3999938964844</v>
+        <v>405.5</v>
       </c>
       <c r="D7" s="29" t="n">
-        <v>129.3000030517578</v>
+        <v>396.5</v>
       </c>
       <c r="E7" s="30" t="n">
-        <v>-0.03073456545963615</v>
+        <v>-0.02219482120838467</v>
       </c>
       <c r="F7" s="29" t="n">
-        <v>-148838.3256695392</v>
+        <v>-62938.26082332665</v>
       </c>
       <c r="G7" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H7" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C8" s="29" t="n">
-        <v>405.5</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>402.75</v>
+        <v>73.84999847412109</v>
       </c>
       <c r="E8" s="30" t="n">
-        <v>-0.006781750924784169</v>
+        <v>-0.04586567159912602</v>
       </c>
       <c r="F8" s="29" t="n">
-        <v>-19231.13525157189</v>
+        <v>-205344.5116042821</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H8" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C9" s="29" t="n">
-        <v>77.40000152587891</v>
+        <v>387</v>
       </c>
       <c r="D9" s="29" t="n">
-        <v>74.65000152587891</v>
+        <v>384.75</v>
       </c>
       <c r="E9" s="30" t="n">
-        <v>-0.03552971506183411</v>
+        <v>-0.005813953488372103</v>
       </c>
       <c r="F9" s="29" t="n">
-        <v>-159069.555343667</v>
+        <v>-25105.03283867612</v>
       </c>
       <c r="G9" s="29" t="n">
-        <v>19902071.12003835</v>
+        <v>19781296.15430112</v>
       </c>
       <c r="H9" s="30" t="n">
-        <v>-0.1049328663164039</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C10" s="29" t="n">
-        <v>387</v>
-      </c>
-      <c r="D10" s="29" t="n">
-        <v>386.25</v>
-      </c>
-      <c r="E10" s="30" t="n">
-        <v>-0.001937984496124034</v>
-      </c>
-      <c r="F10" s="29" t="n">
-        <v>-8368.344279558398</v>
-      </c>
-      <c r="G10" s="29" t="n">
-        <v>19902071.12003835</v>
-      </c>
-      <c r="H10" s="30" t="n">
-        <v>-0.1049328663164039</v>
+        <v>-0.113346453932246</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H10"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -99,11 +99,6 @@
         <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -131,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -158,9 +153,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -209,12 +201,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -599,7 +585,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="18" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -624,7 +610,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +627,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +678,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 76.06/100</t>
+          <t>Güven Puanı: 80.91/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +738,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -786,7 +772,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
+          <t>ÇIK: THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +958,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2224992347307692</v>
+        <v>0.2298474453949678</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22249.92347307692</v>
+        <v>22984.74453949678</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.019028938484348</v>
+        <v>0.0390775038300055</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>423.3924250506313</v>
+        <v>898.1864427738836</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>404.044974109044</v>
+        <v>427.3206234500898</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>376.675</v>
+        <v>390.6875</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805787696869603</v>
+        <v>0.781550076600111</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1015,25 +1001,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2084179173556735</v>
+        <v>0.1890962006107245</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20841.79173556735</v>
+        <v>18909.62006107245</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.018527596735292</v>
+        <v>0.0185277170790933</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>386.1483125175334</v>
+        <v>350.3520905646974</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>210.7333535479328</v>
+        <v>216.4371398793074</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>193.4955029631254</v>
+        <v>201.875</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.2859757726351672</v>
+        <v>0.3705543415818685</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1047,7 +1033,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,62 +1042,62 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1690828479135573</v>
+        <v>0.1810563539943076</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16908.28479135573</v>
+        <v>18105.63539943076</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.0195382798743581</v>
+        <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>330.3588004488608</v>
+        <v>599.6122234998426</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>392.2673531816593</v>
+        <v>135.6483225135468</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>351.8320840903206</v>
+        <v>123.815263377019</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.2283666196330747</v>
-      </c>
-      <c r="K22" s="10" t="inlineStr">
-        <is>
-          <t>LOW</t>
+        <v>0.5809580093299256</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
         </is>
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="11" t="n">
+      <c r="A23" s="10" t="n">
         <v>4</v>
       </c>
-      <c r="B23" s="11" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="11" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="12" t="n">
-        <v>0.3999999999999999</v>
-      </c>
-      <c r="E23" s="13" t="n">
-        <v>39999.99999999999</v>
-      </c>
-      <c r="F23" s="12" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000.00000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="13" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="13" t="inlineStr"/>
-      <c r="I23" s="13" t="inlineStr"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="11" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
@@ -1129,7 +1115,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1152,7 +1138,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1159,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1215,7 +1201,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1353,463 +1339,349 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="14" t="n">
+      <c r="A8" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="14" t="inlineStr">
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="C8" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="15" t="n">
-        <v>396.5</v>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0339317012120768</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.019028938484348</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>0.07229912231651719</v>
-      </c>
-      <c r="H8" s="15" t="n">
-        <v>383.0460804694115</v>
-      </c>
-      <c r="I8" s="15" t="n">
-        <v>404.044974109044</v>
-      </c>
-      <c r="J8" s="15" t="n">
-        <v>425.1666019984991</v>
-      </c>
-      <c r="K8" s="15" t="n">
-        <v>376.675</v>
-      </c>
-      <c r="L8" s="14" t="inlineStr">
+      <c r="D8" s="14" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="E8" s="15" t="n">
+        <v>-0.0205581560241685</v>
+      </c>
+      <c r="F8" s="15" t="n">
+        <v>0.0390775038300055</v>
+      </c>
+      <c r="G8" s="15" t="n">
+        <v>0.0814230337123209</v>
+      </c>
+      <c r="H8" s="14" t="n">
+        <v>402.7954583350607</v>
+      </c>
+      <c r="I8" s="14" t="n">
+        <v>427.3206234500898</v>
+      </c>
+      <c r="J8" s="14" t="n">
+        <v>444.735222614192</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>390.6875</v>
+      </c>
+      <c r="L8" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N8" s="14" t="inlineStr">
+      <c r="M8" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N8" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O8" s="14" t="inlineStr">
+      <c r="O8" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="14" t="n">
+      <c r="A9" s="13" t="n">
         <v>2</v>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C9" s="14" t="inlineStr">
+      <c r="C9" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
-        <v>206.8999938964844</v>
-      </c>
-      <c r="E9" s="16" t="n">
-        <v>-0.0647872949675653</v>
-      </c>
-      <c r="F9" s="16" t="n">
-        <v>0.018527596735292</v>
-      </c>
-      <c r="G9" s="16" t="n">
+      <c r="D9" s="14" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E9" s="15" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F9" s="15" t="n">
+        <v>0.0185277170790933</v>
+      </c>
+      <c r="G9" s="15" t="n">
         <v>0.0466708728798923</v>
       </c>
-      <c r="H9" s="15" t="n">
-        <v>193.4955029631254</v>
-      </c>
-      <c r="I9" s="15" t="n">
-        <v>210.7333535479328</v>
-      </c>
-      <c r="J9" s="15" t="n">
-        <v>216.5561972104777</v>
-      </c>
-      <c r="K9" s="15" t="n">
-        <v>193.4955029631254</v>
-      </c>
-      <c r="L9" s="14" t="inlineStr">
+      <c r="H9" s="14" t="n">
+        <v>206.0725917206618</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>216.4371398793074</v>
+      </c>
+      <c r="J9" s="14" t="n">
+        <v>222.4175604869771</v>
+      </c>
+      <c r="K9" s="14" t="n">
+        <v>201.875</v>
+      </c>
+      <c r="L9" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M9" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N9" s="14" t="inlineStr">
+      <c r="M9" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N9" s="13" t="inlineStr">
         <is>
           <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O9" s="14" t="inlineStr">
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>131.3000030517578</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0570048705314075</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.0795559387098858</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>123.815263377019</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>135.6483225135468</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>141.7456980471513</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>123.815263377019</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="13" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>285.75</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0628618693134822</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1281139375574904</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>267.7872208436725</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>278.8584289144943</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>322.3585576570529</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>267.7872208436725</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="D11" s="17" t="n">
+        <v>286.25</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0553651563181906</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.0341997901255592</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.1114960523971878</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>270.4017240039179</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>276.4603100765587</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>318.165744998695</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>270.4017240039179</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
+      <c r="M11" s="16" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="17" t="inlineStr">
+      <c r="O11" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="14" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D11" s="15" t="n">
-        <v>384.75</v>
-      </c>
-      <c r="E11" s="16" t="n">
-        <v>-0.0855566365423768</v>
-      </c>
-      <c r="F11" s="16" t="n">
-        <v>0.0195382798743581</v>
-      </c>
-      <c r="G11" s="16" t="n">
-        <v>0.1009766152812969</v>
-      </c>
-      <c r="H11" s="15" t="n">
-        <v>351.8320840903206</v>
-      </c>
-      <c r="I11" s="15" t="n">
-        <v>392.2673531816593</v>
-      </c>
-      <c r="J11" s="15" t="n">
-        <v>423.600752729479</v>
-      </c>
-      <c r="K11" s="15" t="n">
-        <v>351.8320840903206</v>
-      </c>
-      <c r="L11" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="n">
+        <v>36.41999816894531</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.1033217154246511</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>34.47560879164018</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>36.46512931285342</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>40.18297485552339</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>34.47560879164018</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="14" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N11" s="14" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="14" t="inlineStr">
+      <c r="M12" s="19" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="21" t="n">
-        <v>35.70000076293945</v>
-      </c>
-      <c r="E12" s="22" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F12" s="22" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-      <c r="G12" s="22" t="n">
-        <v>0.0895632063722737</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>33.79405057778999</v>
-      </c>
-      <c r="I12" s="21" t="n">
-        <v>35.74423969629903</v>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>38.89740729876093</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>33.79405057778999</v>
-      </c>
-      <c r="L12" s="20" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>78.40000152587891</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.0445633254802306</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0772325318535918</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>74.9062367402306</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>77.07198604420731</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>84.45503214104799</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>74.48000144958496</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="20" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N12" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D13" s="18" t="n">
-        <v>79.69999694824219</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.0476629979133642</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0123915741984644</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.1088380129700114</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>75.90125616000299</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>78.71238852244066</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>88.37438624980484</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>75.71499710083008</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M13" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
+      <c r="M13" s="16" t="n">
+        <v>80.91</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>15</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="18" t="n">
-        <v>259.25</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.1122727836453332</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.0351689285600669</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.0835562048104195</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>230.1432808399474</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>250.1324552708026</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>280.9119460971012</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>230.1432808399474</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>341.75</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0977678549854652</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.005529134834197</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1083753514763447</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>308.3378355587172</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>339.8604181704131</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>378.7872763670408</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>308.3378355587172</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>76.06</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1839,7 +1711,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1856,7 +1728,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1928,734 +1800,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="14" t="n">
+      <c r="A4" s="13" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="14" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="14" t="inlineStr">
+      <c r="C4" s="13" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D4" s="14" t="inlineStr">
+      <c r="D4" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="16" t="n">
-        <v>-0.0824642322042362</v>
-      </c>
-      <c r="F4" s="16" t="n">
-        <v>0.0374477363977292</v>
-      </c>
-      <c r="G4" s="16" t="n">
-        <v>0.103857588951256</v>
-      </c>
-      <c r="H4" s="16" t="n">
-        <v>-0.06741185359372349</v>
-      </c>
-      <c r="I4" s="14" t="inlineStr">
+      <c r="E4" s="15" t="n">
+        <v>-0.0372591422531518</v>
+      </c>
+      <c r="F4" s="15" t="n">
+        <v>0.0441335285670299</v>
+      </c>
+      <c r="G4" s="15" t="n">
+        <v>0.1255556536498179</v>
+      </c>
+      <c r="H4" s="15" t="n">
+        <v>-0.0492395802835036</v>
+      </c>
+      <c r="I4" s="13" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J4" s="15" t="n">
+        <v>0.0191384637845102</v>
+      </c>
+      <c r="K4" s="15" t="n">
+        <v>0.0390775038300055</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="13" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C5" s="13" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D5" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="n">
+        <v>-0.0576496674057649</v>
+      </c>
+      <c r="F5" s="15" t="n">
+        <v>0.0786802030456852</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.06462922596201839</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>-0.0576587433953539</v>
+      </c>
+      <c r="I5" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="16" t="n">
-        <v>0.0189524792403736</v>
-      </c>
-      <c r="K4" s="16" t="n">
-        <v>0.019028938484348</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="14" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="14" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="14" t="inlineStr">
+      <c r="J5" s="15" t="n">
+        <v>0.0208840053323224</v>
+      </c>
+      <c r="K5" s="15" t="n">
+        <v>0.0185277170790933</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="13" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="13" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="14" t="inlineStr">
+      <c r="D6" s="13" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="16" t="n">
-        <v>-0.0824833973548364</v>
-      </c>
-      <c r="F5" s="16" t="n">
-        <v>0.082679159017976</v>
-      </c>
-      <c r="G5" s="16" t="n">
-        <v>0.0273088389606748</v>
-      </c>
-      <c r="H5" s="16" t="n">
-        <v>-0.0597960627732419</v>
-      </c>
-      <c r="I5" s="14" t="inlineStr">
+      <c r="E6" s="15" t="n">
+        <v>-0.0194174082392906</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0202020681054191</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-0.039502516584027</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-0.1369664216105703</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="16" t="n">
-        <v>0.0209647836935707</v>
-      </c>
-      <c r="K5" s="16" t="n">
-        <v>0.018527596735292</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="17" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="J6" s="15" t="n">
+        <v>0.0220263134795572</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0331174361060366</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="16" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="16" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C6" s="17" t="inlineStr">
+      <c r="C7" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="D7" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="19" t="n">
-        <v>-0.048293089092423</v>
-      </c>
-      <c r="F6" s="19" t="n">
-        <v>-0.1234662576687116</v>
-      </c>
-      <c r="G6" s="19" t="n">
-        <v>-0.0985804416403786</v>
-      </c>
-      <c r="H6" s="19" t="n">
-        <v>-0.1838035473419896</v>
-      </c>
-      <c r="I6" s="17" t="inlineStr">
+      <c r="E7" s="18" t="n">
+        <v>-0.0313028764805414</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.1325757575757575</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-0.1040688575899843</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.1936358141344232</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J6" s="19" t="n">
-        <v>0.018156884273008</v>
-      </c>
-      <c r="K6" s="19" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="14" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="14" t="inlineStr">
+      <c r="J7" s="18" t="n">
+        <v>0.0180723854988791</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>-0.0341997901255592</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E8" s="21" t="n">
+        <v>-0.0060044002283821</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>0.08651544366282859</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>-0.0324123602679612</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.1255658644328388</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="21" t="n">
+        <v>0.0261239227485806</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C7" s="14" t="inlineStr">
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="n">
-        <v>-0.0528542750964556</v>
-      </c>
-      <c r="F7" s="16" t="n">
-        <v>0.4465180215722137</v>
-      </c>
-      <c r="G7" s="16" t="n">
-        <v>0.5603375976000915</v>
-      </c>
-      <c r="H7" s="16" t="n">
-        <v>-0.2244550284745238</v>
-      </c>
-      <c r="I7" s="14" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0555317409253494</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>0.3717472667621082</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>0.539853563379223</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.2309781767799872</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J7" s="16" t="n">
-        <v>0.028200042319893</v>
-      </c>
-      <c r="K7" s="16" t="n">
-        <v>0.0195382798743581</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="20" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="20" t="inlineStr">
+      <c r="J9" s="23" t="n">
+        <v>0.0274366815632304</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0195382818194833</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D10" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="23" t="n">
+        <v>-0.1113149660442947</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>-0.139218006961732</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>-0.2891389070914403</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>-0.0627516685691355</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J10" s="23" t="n">
+        <v>0.0179308105833148</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.102805769808545</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="22" t="n">
-        <v>-0.0272479558368244</v>
-      </c>
-      <c r="F8" s="22" t="n">
-        <v>0.0512367999227174</v>
-      </c>
-      <c r="G8" s="22" t="n">
-        <v>-0.0490143875256759</v>
-      </c>
-      <c r="H8" s="22" t="n">
-        <v>-0.1525930514087783</v>
-      </c>
-      <c r="I8" s="20" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="n">
+        <v>-0.0288086380242014</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.1136363667271895</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1306818564530771</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-0.2821456295959658</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="23" t="n">
+        <v>0.0206173299279643</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0124595339704571</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="22" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="n">
+        <v>-0.0411735013815761</v>
+      </c>
+      <c r="F12" s="23" t="n">
+        <v>-0.1543350621836327</v>
+      </c>
+      <c r="G12" s="23" t="n">
+        <v>0.2547050709559768</v>
+      </c>
+      <c r="H12" s="23" t="n">
+        <v>-0.2495341591699014</v>
+      </c>
+      <c r="I12" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="22" t="n">
-        <v>0.0260785342604604</v>
-      </c>
-      <c r="K8" s="22" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="23" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="23" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="23" t="inlineStr">
+      <c r="J12" s="23" t="n">
+        <v>0.0245820513339388</v>
+      </c>
+      <c r="K12" s="23" t="n">
+        <v>0.029948947983406</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="23" t="inlineStr">
+      <c r="D13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.1690513747344368</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.2068790820831018</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>-0.3086419711556413</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>0.0004404513674984</v>
+      </c>
+      <c r="I13" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>0.0152318656113831</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="24" t="n">
-        <v>-0.0456853548743018</v>
-      </c>
-      <c r="F9" s="24" t="n">
-        <v>-0.1021968119588387</v>
-      </c>
-      <c r="G9" s="24" t="n">
-        <v>0.2884126747282864</v>
-      </c>
-      <c r="H9" s="24" t="n">
-        <v>-0.246774969672824</v>
-      </c>
-      <c r="I9" s="23" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J9" s="24" t="n">
-        <v>0.0255018791340404</v>
-      </c>
-      <c r="K9" s="24" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="23" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="23" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="23" t="inlineStr">
+      <c r="E14" s="25" t="n">
+        <v>-0.0523777104329941</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>0.0021866112130526</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.0869854287689156</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.0241364620182464</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="25" t="n">
+        <v>0.023757732105983</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0111110916693351</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="24" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="23" t="inlineStr">
+      <c r="D15" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="24" t="n">
-        <v>-0.0327868405107442</v>
-      </c>
-      <c r="F10" s="24" t="n">
-        <v>0.0069822280674132</v>
-      </c>
-      <c r="G10" s="24" t="n">
-        <v>-0.0559999778053977</v>
-      </c>
-      <c r="H10" s="24" t="n">
-        <v>-0.1419483389452992</v>
-      </c>
-      <c r="I10" s="23" t="inlineStr">
+      <c r="E15" s="25" t="n">
+        <v>-0.09794624245678241</v>
+      </c>
+      <c r="F15" s="25" t="n">
+        <v>-0.0514950317688653</v>
+      </c>
+      <c r="G15" s="25" t="n">
+        <v>-0.1219887355571381</v>
+      </c>
+      <c r="H15" s="25" t="n">
+        <v>0.0276953346162978</v>
+      </c>
+      <c r="I15" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="24" t="n">
-        <v>0.021982568542005</v>
-      </c>
-      <c r="K10" s="24" t="n">
-        <v>0.0426715939840771</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="23" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="23" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="23" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D11" s="23" t="inlineStr">
+      <c r="J15" s="25" t="n">
+        <v>0.0214678685986214</v>
+      </c>
+      <c r="K15" s="25" t="n">
+        <v>0.0483516300336255</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E11" s="24" t="n">
-        <v>-0.1086300563157068</v>
-      </c>
-      <c r="F11" s="24" t="n">
-        <v>-0.0888341061879893</v>
-      </c>
-      <c r="G11" s="24" t="n">
-        <v>-0.2745579935142653</v>
-      </c>
-      <c r="H11" s="24" t="n">
-        <v>-0.0764441679740844</v>
-      </c>
-      <c r="I11" s="23" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.153256699007633</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.2093022747970567</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.2844036485715657</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.1628946465915355</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="24" t="n">
-        <v>0.0186569658567114</v>
-      </c>
-      <c r="K11" s="24" t="n">
-        <v>0.102805642445124</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0183461054684322</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0073660782405308</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.1680585134722519</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>-0.1863195565962446</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>-0.2877569628110316</v>
-      </c>
-      <c r="H12" s="19" t="n">
-        <v>-0.0044326364510109</v>
-      </c>
-      <c r="I12" s="17" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E17" s="25" t="n">
+        <v>-0.1174979165077881</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>0.0126090354486556</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.0242990872445344</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>-0.1072208885749907</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Güçlü trend</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0389793391056107</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>0.07582576484113181</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="25" t="n">
+        <v>-0.08355321020228661</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.1459016393442622</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.0612612612612613</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.2255174654706502</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="19" t="n">
-        <v>0.0152262854483399</v>
-      </c>
-      <c r="K12" s="19" t="n">
-        <v>-0.0123915741984644</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="23" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="23" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="23" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0251248630786822</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0532805395405533</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="24" t="n">
-        <v>-0.0598349196247974</v>
-      </c>
-      <c r="F13" s="24" t="n">
-        <v>-0.010853835261384</v>
-      </c>
-      <c r="G13" s="24" t="n">
-        <v>-0.0976897891205136</v>
-      </c>
-      <c r="H13" s="24" t="n">
-        <v>-0.0288025021689304</v>
-      </c>
-      <c r="I13" s="23" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.0583892617449663</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.0049645390070921</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.0690112806901127</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>0.0091218873182385</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="24" t="n">
-        <v>0.0237657020847789</v>
-      </c>
-      <c r="K13" s="24" t="n">
-        <v>0.0111110916693351</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="25" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="25" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.031377917776001</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0478181869880385</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="25" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="26" t="n">
-        <v>-0.1149003591499333</v>
-      </c>
-      <c r="F14" s="26" t="n">
-        <v>-0.0570150771170184</v>
-      </c>
-      <c r="G14" s="26" t="n">
-        <v>-0.12454592828274</v>
-      </c>
-      <c r="H14" s="26" t="n">
-        <v>0.0117628907218287</v>
-      </c>
-      <c r="I14" s="25" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.1295955728475251</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1582221984863281</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.1733665773215752</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.1990612037864825</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="26" t="n">
-        <v>0.0214095607902122</v>
-      </c>
-      <c r="K14" s="26" t="n">
-        <v>0.0483517655572096</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="25" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="25" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="26" t="n">
-        <v>-0.0621986223534939</v>
-      </c>
-      <c r="F15" s="26" t="n">
-        <v>-0.1175135871766351</v>
-      </c>
-      <c r="G15" s="26" t="n">
-        <v>-0.1254496162867269</v>
-      </c>
-      <c r="H15" s="26" t="n">
-        <v>-0.28242131227121</v>
-      </c>
-      <c r="I15" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="26" t="n">
-        <v>0.0205397708069739</v>
-      </c>
-      <c r="K15" s="26" t="n">
-        <v>0.0124595339704571</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="25" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="25" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="26" t="n">
-        <v>-0.1381323182445148</v>
-      </c>
-      <c r="F16" s="26" t="n">
-        <v>-0.1993976271296121</v>
-      </c>
-      <c r="G16" s="26" t="n">
-        <v>-0.2854839037823421</v>
-      </c>
-      <c r="H16" s="26" t="n">
-        <v>-0.1118784227705204</v>
-      </c>
-      <c r="I16" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="26" t="n">
-        <v>0.0184277553287016</v>
-      </c>
-      <c r="K16" s="26" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="25" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="25" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="26" t="n">
-        <v>-0.1782819920633277</v>
-      </c>
-      <c r="F17" s="26" t="n">
-        <v>0.0346938924459749</v>
-      </c>
-      <c r="G17" s="26" t="n">
-        <v>-0.0249999312254073</v>
-      </c>
-      <c r="H17" s="26" t="n">
-        <v>-0.1010948896538656</v>
-      </c>
-      <c r="I17" s="25" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="26" t="n">
-        <v>0.0393464526538943</v>
-      </c>
-      <c r="K17" s="26" t="n">
-        <v>0.0706630475858574</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="27" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="27" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="28" t="n">
-        <v>-0.1351125938281902</v>
-      </c>
-      <c r="F18" s="28" t="n">
-        <v>-0.1211864406779661</v>
-      </c>
-      <c r="G18" s="28" t="n">
-        <v>-0.0442396313364055</v>
-      </c>
-      <c r="H18" s="28" t="n">
-        <v>-0.2157061124078084</v>
-      </c>
-      <c r="I18" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="28" t="n">
-        <v>0.0255197014582361</v>
-      </c>
-      <c r="K18" s="28" t="n">
-        <v>-0.0351689285600669</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="27" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="27" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="27" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="27" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="28" t="n">
-        <v>-0.1320634920634921</v>
-      </c>
-      <c r="F19" s="28" t="n">
-        <v>-0.0193687230989957</v>
-      </c>
-      <c r="G19" s="28" t="n">
-        <v>-0.0565907522429262</v>
-      </c>
-      <c r="H19" s="28" t="n">
-        <v>0.0129751276111689</v>
-      </c>
-      <c r="I19" s="27" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="28" t="n">
-        <v>0.0312353919675467</v>
-      </c>
-      <c r="K19" s="28" t="n">
-        <v>-0.005529134834197</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="25" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="25" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="25" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="25" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="26" t="n">
-        <v>-0.1640729467145814</v>
-      </c>
-      <c r="F20" s="26" t="n">
-        <v>-0.1376146837152142</v>
-      </c>
-      <c r="G20" s="26" t="n">
-        <v>-0.1843966326020115</v>
-      </c>
-      <c r="H20" s="26" t="n">
-        <v>-0.1831940100157078</v>
-      </c>
-      <c r="I20" s="25" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="26" t="n">
-        <v>0.0269414901477214</v>
-      </c>
-      <c r="K20" s="26" t="n">
-        <v>0.0597309519640328</v>
+      <c r="J20" s="25" t="n">
+        <v>0.026615207399564</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0190112247110776</v>
       </c>
     </row>
   </sheetData>
@@ -2680,7 +2552,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2688,7 +2560,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2713,7 +2585,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, TUPRS.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2737,7 +2609,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS, TOASO.IS, ASELS.IS</t>
+          <t>THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2749,7 +2621,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, GARAN.IS, FROTO.IS, AKBNK.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, SISE.IS</t>
+          <t>TUPRS.IS, FROTO.IS, TCELL.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2671,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2807,7 +2679,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2904,7 +2776,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3012,7 +2884,7 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3050,7 +2922,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3058,7 +2930,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,7 +2954,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12250.7001953125</v>
+        <v>12118.2998046875</v>
       </c>
     </row>
     <row r="5">
@@ -3092,7 +2964,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13611.73302246094</v>
+        <v>13615.6240234375</v>
       </c>
     </row>
     <row r="6">
@@ -3126,7 +2998,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>76.06</v>
+        <v>80.91</v>
       </c>
     </row>
     <row r="9">
@@ -3163,13 +3035,13 @@
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-12</t>
+          <t>Rapor Tarihi: 2026-10-13</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3183,7 +3055,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-14 06:50</t>
+          <t>Son Güncelleme: 2026-10-15 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3247,23 +3119,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="29" t="n">
+      <c r="C4" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="29" t="n">
-        <v>206.8999938964844</v>
-      </c>
-      <c r="E4" s="30" t="n">
-        <v>0.05025377612428628</v>
-      </c>
-      <c r="F4" s="29" t="n">
-        <v>146054.7978911358</v>
-      </c>
-      <c r="G4" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H4" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D4" s="26" t="n">
+        <v>212.5</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>0.07868020304568524</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>228671.7942438866</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="5">
@@ -3277,23 +3149,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="29" t="n">
+      <c r="C5" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="29" t="n">
-        <v>84.34999847412109</v>
-      </c>
-      <c r="E5" s="30" t="n">
-        <v>-0.1259067515635119</v>
-      </c>
-      <c r="F5" s="29" t="n">
-        <v>-11056.43585567767</v>
-      </c>
-      <c r="G5" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H5" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D5" s="26" t="n">
+        <v>85.65000152587891</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>-0.1124352173484051</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>-9873.440090341275</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="6">
@@ -3307,23 +3179,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C6" s="29" t="n">
+      <c r="C6" s="26" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D6" s="29" t="n">
-        <v>129.8000030517578</v>
-      </c>
-      <c r="E6" s="30" t="n">
-        <v>-0.02698643935111478</v>
-      </c>
-      <c r="F6" s="29" t="n">
-        <v>-130687.2698127953</v>
-      </c>
-      <c r="G6" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H6" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D6" s="26" t="n">
+        <v>131.3000030517578</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.01574206102555076</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-76234.10224256478</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="7">
@@ -3337,23 +3209,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C7" s="29" t="n">
+      <c r="C7" s="26" t="n">
         <v>405.5</v>
       </c>
-      <c r="D7" s="29" t="n">
-        <v>396.5</v>
-      </c>
-      <c r="E7" s="30" t="n">
-        <v>-0.02219482120838467</v>
-      </c>
-      <c r="F7" s="29" t="n">
-        <v>-62938.26082332665</v>
-      </c>
-      <c r="G7" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H7" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D7" s="26" t="n">
+        <v>411.25</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>0.0141800246609125</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>40210.55552601442</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="8">
@@ -3367,23 +3239,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C8" s="29" t="n">
+      <c r="C8" s="26" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D8" s="29" t="n">
-        <v>73.84999847412109</v>
-      </c>
-      <c r="E8" s="30" t="n">
-        <v>-0.04586567159912602</v>
-      </c>
-      <c r="F8" s="29" t="n">
-        <v>-205344.5116042821</v>
-      </c>
-      <c r="G8" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H8" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D8" s="26" t="n">
+        <v>72.65000152587891</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>-0.06136950783407702</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>-274756.5046845153</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
     <row r="9">
@@ -3397,23 +3269,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C9" s="29" t="n">
+      <c r="C9" s="26" t="n">
         <v>387</v>
       </c>
-      <c r="D9" s="29" t="n">
-        <v>384.75</v>
-      </c>
-      <c r="E9" s="30" t="n">
-        <v>-0.005813953488372103</v>
-      </c>
-      <c r="F9" s="29" t="n">
-        <v>-25105.03283867612</v>
-      </c>
-      <c r="G9" s="29" t="n">
-        <v>19781296.15430112</v>
-      </c>
-      <c r="H9" s="30" t="n">
-        <v>-0.113346453932246</v>
+      <c r="D9" s="26" t="n">
+        <v>385.75</v>
+      </c>
+      <c r="E9" s="27" t="n">
+        <v>-0.003229974160206761</v>
+      </c>
+      <c r="F9" s="26" t="n">
+        <v>-13947.24046593066</v>
+      </c>
+      <c r="G9" s="26" t="n">
+        <v>19964443.92963129</v>
+      </c>
+      <c r="H9" s="27" t="n">
+        <v>-0.1060493144109383</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -91,12 +91,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
+        <fgColor rgb="00E7E6E6"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E7E6E6"/>
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,22 +185,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -585,7 +582,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="18" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -610,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -627,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -678,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.91/100</t>
+          <t>Güven Puanı: 80.75/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -755,7 +752,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: YKBNK.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -772,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, ARCLK.IS</t>
+          <t>ÇIK: THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -958,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2298474453949678</v>
+        <v>0.2155269052313723</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22984.74453949678</v>
+        <v>21552.69052313723</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>898.1864427738836</v>
+        <v>410.1248568516434</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>427.3206234500898</v>
+        <v>415.763807558775</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>390.6875</v>
+        <v>387.6</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.781550076600111</v>
+        <v>0.3805788019007346</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1001,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1890962006107245</v>
+        <v>0.1994846123862184</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>18909.62006107245</v>
+        <v>19948.46123862184</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>350.3520905646974</v>
+        <v>464.1623736709059</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>216.4371398793074</v>
+        <v>216.1142151794203</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>201.875</v>
+        <v>200.6399971008301</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705543415818685</v>
+        <v>0.4653615816464591</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1042,25 +1039,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1810563539943076</v>
+        <v>0.1849884823824094</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>18105.63539943076</v>
+        <v>18498.84823824093</v>
       </c>
       <c r="F22" s="7" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>599.6122234998426</v>
+        <v>612.6344245652119</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>135.6483225135468</v>
+        <v>134.8218254118378</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.5809580093299256</v>
+        <v>0.5418845397997932</v>
       </c>
       <c r="K22" s="9" t="inlineStr">
         <is>
@@ -1083,10 +1080,10 @@
         </is>
       </c>
       <c r="D23" s="11" t="n">
-        <v>0.4000000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>40000.00000000001</v>
+        <v>40000</v>
       </c>
       <c r="F23" s="11" t="n">
         <v>0</v>
@@ -1115,7 +1112,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1138,7 +1135,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1159,7 +1156,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1201,7 +1198,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1353,28 +1350,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>411.25</v>
+        <v>408</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205581560241685</v>
+        <v>-0.0205577496905355</v>
       </c>
       <c r="F8" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0814230337123209</v>
+        <v>0.0542750535284166</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>402.7954583350607</v>
+        <v>399.6124381262615</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>427.3206234500898</v>
+        <v>415.763807558775</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>444.735222614192</v>
+        <v>430.144221839594</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>390.6875</v>
+        <v>387.6</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1382,7 +1379,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1410,28 +1407,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>212.5</v>
+        <v>211.1999969482422</v>
       </c>
       <c r="E9" s="15" t="n">
         <v>-0.0302466271968858</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.0466708728798923</v>
+        <v>0.0914169657590902</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>206.0725917206618</v>
+        <v>204.8119093765653</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>216.4371398793074</v>
+        <v>216.1142151794203</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>222.4175604869771</v>
+        <v>230.5072598375796</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>201.875</v>
+        <v>200.6399971008301</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1439,7 +1436,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1467,28 +1464,28 @@
         </is>
       </c>
       <c r="D10" s="14" t="n">
-        <v>131.3000030517578</v>
+        <v>130.5</v>
       </c>
       <c r="E10" s="15" t="n">
-        <v>-0.0570048705314075</v>
+        <v>-0.0611152997985</v>
       </c>
       <c r="F10" s="15" t="n">
         <v>0.0331174361060366</v>
       </c>
       <c r="G10" s="15" t="n">
-        <v>0.0795559387098858</v>
+        <v>0.0795560183272892</v>
       </c>
       <c r="H10" s="14" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="I10" s="14" t="n">
-        <v>135.6483225135468</v>
+        <v>134.8218254118378</v>
       </c>
       <c r="J10" s="14" t="n">
-        <v>141.7456980471513</v>
+        <v>140.8820603917112</v>
       </c>
       <c r="K10" s="14" t="n">
-        <v>123.815263377019</v>
+        <v>122.5244533762957</v>
       </c>
       <c r="L10" s="13" t="inlineStr">
         <is>
@@ -1496,7 +1493,7 @@
         </is>
       </c>
       <c r="M10" s="13" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N10" s="13" t="inlineStr">
         <is>
@@ -1505,7 +1502,7 @@
       </c>
       <c r="O10" s="13" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1524,28 +1521,28 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>286.25</v>
+        <v>279.25</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0553651563181906</v>
+        <v>-0.0628618693134822</v>
       </c>
       <c r="F11" s="18" t="n">
         <v>-0.0341997901255592</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.1114960523971878</v>
+        <v>0.051230381576059</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>270.4017240039179</v>
+        <v>261.6958229942101</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>276.4603100765587</v>
+        <v>269.6997086074376</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>318.165744998695</v>
+        <v>293.5560840551145</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>270.4017240039179</v>
+        <v>261.6958229942101</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1553,7 +1550,7 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
@@ -1567,121 +1564,235 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="19" t="n">
+      <c r="A12" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B12" s="19" t="inlineStr">
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="n">
-        <v>36.41999816894531</v>
-      </c>
-      <c r="E12" s="21" t="n">
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>35.93999862670898</v>
+      </c>
+      <c r="E12" s="18" t="n">
         <v>-0.053387959227386</v>
       </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.1033217154246511</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>34.47560879164018</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>36.46512931285342</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>40.18297485552339</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>34.47560879164018</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="F12" s="18" t="n">
+        <v>-0.0095238891213882</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.0919881126195933</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>34.02123544539393</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>35.59771006476537</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>39.24605126793072</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>34.02123544539393</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
+      <c r="M12" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>98.30000305175781</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.039929164947756</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0056461366774436</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0253202830653163</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>94.37496601553926</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>97.74498779913446</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>100.7889869543498</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>93.38500289916992</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
+      <c r="B14" s="16" t="inlineStr">
         <is>
           <t>ARCLK.IS</t>
         </is>
       </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="C14" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>78.40000152587891</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0445633254802306</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.0772325318535918</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>74.9062367402306</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>77.07198604420731</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>84.45503214104799</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>74.48000144958496</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D14" s="17" t="n">
+        <v>76.55000305175781</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0514249572914607</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.1080537552156288</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>72.61342241415998</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>75.25332955008864</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>84.8215183432681</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>72.61342241415998</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>80.91</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
+      <c r="M14" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
         <is>
           <t>hacim artışı var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="17" t="n">
+        <v>348</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.097767991594519</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.0055291931010313</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.1083753223429276</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>313.9767389251074</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>346.0758408008411</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>385.7146121753388</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>313.9767389251074</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="16" t="n">
+        <v>80.75</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1711,7 +1822,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1728,7 +1839,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1819,27 +1930,27 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0372591422531518</v>
+        <v>-0.012704174228675</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0441335285670299</v>
+        <v>0.0633892203471258</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.1255556536498179</v>
+        <v>0.0988178293379029</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0492395802835036</v>
+        <v>-0.0462534110402206</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0191384637845102</v>
+        <v>0.0188656249393633</v>
       </c>
       <c r="K4" s="15" t="n">
-        <v>0.0390775038300055</v>
+        <v>0.0190289400950367</v>
       </c>
     </row>
     <row r="5">
@@ -1862,16 +1973,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.0576496674057649</v>
+        <v>-0.0347349451440264</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0786802030456852</v>
+        <v>0.0720812027829551</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.06462922596201839</v>
+        <v>0.0352941026874618</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.0576587433953539</v>
+        <v>-0.0799832003221837</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1879,10 +1990,10 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208840053323224</v>
+        <v>0.0209049144524068</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185277170790933</v>
+        <v>0.0232680790823229</v>
       </c>
     </row>
     <row r="6">
@@ -1905,16 +2016,16 @@
         </is>
       </c>
       <c r="E6" s="15" t="n">
-        <v>-0.0194174082392906</v>
+        <v>0.0211267361797222</v>
       </c>
       <c r="F6" s="15" t="n">
-        <v>0.0202020681054191</v>
+        <v>0.0291797859557771</v>
       </c>
       <c r="G6" s="15" t="n">
-        <v>-0.039502516584027</v>
+        <v>-0.070512780105842</v>
       </c>
       <c r="H6" s="15" t="n">
-        <v>-0.1369664216105703</v>
+        <v>-0.1541701320588953</v>
       </c>
       <c r="I6" s="13" t="inlineStr">
         <is>
@@ -1922,7 +2033,7 @@
         </is>
       </c>
       <c r="J6" s="15" t="n">
-        <v>0.0220263134795572</v>
+        <v>0.0219560472301172</v>
       </c>
       <c r="K6" s="15" t="n">
         <v>0.0331174361060366</v>
@@ -1948,16 +2059,16 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.0313028764805414</v>
+        <v>-0.021034180543383</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1325757575757575</v>
+        <v>-0.1525037936267071</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1040688575899843</v>
+        <v>-0.1361175560711524</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.1936358141344232</v>
+        <v>-0.202007399453498</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -1965,225 +2076,225 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0180723854988791</v>
+        <v>0.0182902909452241</v>
       </c>
       <c r="K7" s="18" t="n">
         <v>-0.0341997901255592</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
         <is>
           <t>YKBNK.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
-        <is>
-          <t>TUT</t>
-        </is>
-      </c>
-      <c r="E8" s="21" t="n">
-        <v>-0.0060044002283821</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>0.08651544366282859</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>-0.0324123602679612</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.1255658644328388</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>0.0363321312123852</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.081878305420131</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.0703569899492693</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.1410192860246872</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0261239227485806</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>0.0012391857819089</v>
+      <c r="J8" s="18" t="n">
+        <v>0.0261570210933936</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>-0.0095238891213882</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="22" t="n">
+      <c r="A9" s="19" t="n">
         <v>6</v>
       </c>
-      <c r="B9" s="22" t="inlineStr">
+      <c r="B9" s="19" t="inlineStr">
         <is>
           <t>TUPRS.IS</t>
         </is>
       </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
+      <c r="D9" s="19" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0555317409253494</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>0.3717472667621082</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>0.539853563379223</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.2309781767799872</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="E9" s="20" t="n">
+        <v>-0.0351351420553087</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>0.3759956869540564</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>0.5638771539369436</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.2403921002344196</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0274366815632304</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0195382818194833</v>
+      <c r="J9" s="20" t="n">
+        <v>0.0274488615475791</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0266028003670319</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="22" t="n">
+      <c r="A10" s="19" t="n">
         <v>7</v>
       </c>
-      <c r="B10" s="22" t="inlineStr">
+      <c r="B10" s="19" t="inlineStr">
         <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C10" s="22" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="D10" s="22" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.1113149660442947</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>-0.139218006961732</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>-0.2891389070914403</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.0627516685691355</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
+      <c r="E10" s="20" t="n">
+        <v>-0.0835459556667959</v>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>-0.1405502417997924</v>
+      </c>
+      <c r="G10" s="20" t="n">
+        <v>-0.3176638519297585</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>-0.07722106603181431</v>
+      </c>
+      <c r="I10" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0179308105833148</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.102805769808545</v>
+      <c r="J10" s="20" t="n">
+        <v>0.0179418586662416</v>
+      </c>
+      <c r="K10" s="20" t="n">
+        <v>0.0955199358563398</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="22" t="n">
+      <c r="A11" s="19" t="n">
         <v>8</v>
       </c>
-      <c r="B11" s="22" t="inlineStr">
+      <c r="B11" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n">
+        <v>-0.0303188682253351</v>
+      </c>
+      <c r="F11" s="20" t="n">
+        <v>-0.1237600769858882</v>
+      </c>
+      <c r="G11" s="20" t="n">
+        <v>0.2014201044256922</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>-0.2707792314346859</v>
+      </c>
+      <c r="I11" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J11" s="20" t="n">
+        <v>0.0241314061543816</v>
+      </c>
+      <c r="K11" s="20" t="n">
+        <v>0.0190703728875496</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
         <is>
           <t>TCELL.IS</t>
         </is>
       </c>
-      <c r="C11" s="22" t="inlineStr">
+      <c r="C12" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0288086380242014</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.1136363667271895</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.1306818564530771</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.2821456295959658</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0110663828695687</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>-0.0940091884630616</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>-0.1619778303979786</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>-0.2987318037968683</v>
+      </c>
+      <c r="I12" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0206173299279643</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0124595339704571</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="22" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="22" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="23" t="n">
-        <v>-0.0411735013815761</v>
-      </c>
-      <c r="F12" s="23" t="n">
-        <v>-0.1543350621836327</v>
-      </c>
-      <c r="G12" s="23" t="n">
-        <v>0.2547050709559768</v>
-      </c>
-      <c r="H12" s="23" t="n">
-        <v>-0.2495341591699014</v>
-      </c>
-      <c r="I12" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J12" s="23" t="n">
-        <v>0.0245820513339388</v>
-      </c>
-      <c r="K12" s="23" t="n">
-        <v>0.029948947983406</v>
+      <c r="J12" s="18" t="n">
+        <v>0.0202669303577498</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>-0.0056461366774436</v>
       </c>
     </row>
     <row r="13">
@@ -2206,16 +2317,16 @@
         </is>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-0.1690513747344368</v>
+        <v>-0.1606359033630071</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.2068790820831018</v>
+        <v>-0.2156761859780638</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>-0.3086419711556413</v>
+        <v>-0.3473998204588225</v>
       </c>
       <c r="H13" s="18" t="n">
-        <v>0.0004404513674984</v>
+        <v>0.0167865251532108</v>
       </c>
       <c r="I13" s="16" t="inlineStr">
         <is>
@@ -2223,311 +2334,311 @@
         </is>
       </c>
       <c r="J13" s="18" t="n">
-        <v>0.0152318656113831</v>
+        <v>0.015398835227913</v>
       </c>
       <c r="K13" s="18" t="n">
-        <v>-0.0169389726508262</v>
+        <v>-0.016938908556182</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n">
+      <c r="A14" s="21" t="n">
         <v>11</v>
       </c>
-      <c r="B14" s="24" t="inlineStr">
+      <c r="B14" s="21" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D14" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.0523777104329941</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>0.0021866112130526</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.0869854287689156</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.0241364620182464</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E14" s="22" t="n">
+        <v>-0.0352265200594379</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>0.009022533445429901</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.1441326891814895</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>-0.0324538470874489</v>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.023757732105983</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0111110916693351</v>
+      <c r="J14" s="22" t="n">
+        <v>0.0236332051822288</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>0.0132478544110439</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="24" t="n">
+      <c r="A15" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="24" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>SAHOL.IS</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="24" t="inlineStr">
+      <c r="D15" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n">
-        <v>-0.09794624245678241</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>-0.0514950317688653</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>-0.1219887355571381</v>
-      </c>
-      <c r="H15" s="25" t="n">
-        <v>0.0276953346162978</v>
-      </c>
-      <c r="I15" s="24" t="inlineStr">
+      <c r="E15" s="22" t="n">
+        <v>-0.0614618257385515</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.0412896093085516</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>-0.1691176470588234</v>
+      </c>
+      <c r="H15" s="22" t="n">
+        <v>0.0103087844515024</v>
+      </c>
+      <c r="I15" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="25" t="n">
-        <v>0.0214678685986214</v>
-      </c>
-      <c r="K15" s="25" t="n">
-        <v>0.0483516300336255</v>
+      <c r="J15" s="22" t="n">
+        <v>0.0213468675694466</v>
+      </c>
+      <c r="K15" s="22" t="n">
+        <v>0.0540671532455347</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n">
+      <c r="A16" s="21" t="n">
         <v>13</v>
       </c>
-      <c r="B16" s="24" t="inlineStr">
+      <c r="B16" s="21" t="inlineStr">
         <is>
           <t>PGSUS.IS</t>
         </is>
       </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.153256699007633</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.2093022747970567</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.2844036485715657</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.1628946465915355</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E16" s="22" t="n">
+        <v>-0.1353333536783854</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.2210210393498968</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>-0.3115711191609415</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-0.1814248975650475</v>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0183461054684322</v>
-      </c>
-      <c r="K16" s="25" t="n">
+      <c r="J16" s="22" t="n">
+        <v>0.0184858230413237</v>
+      </c>
+      <c r="K16" s="22" t="n">
         <v>0.0073660782405308</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="n">
+      <c r="A17" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="B17" s="24" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>PETKM.IS</t>
         </is>
       </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
+      <c r="D17" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.1174979165077881</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>0.0126090354486556</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.0242990872445344</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>-0.1072208885749907</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="E17" s="22" t="n">
+        <v>-0.08377423249402149</v>
+      </c>
+      <c r="F17" s="22" t="n">
+        <v>-0.0076408712192667</v>
+      </c>
+      <c r="G17" s="22" t="n">
+        <v>-0.027153553704721</v>
+      </c>
+      <c r="H17" s="22" t="n">
+        <v>-0.1247594319985501</v>
+      </c>
+      <c r="I17" s="21" t="inlineStr">
         <is>
           <t>Güçlü trend</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0389793391056107</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>0.07582576484113181</v>
+      <c r="J17" s="22" t="n">
+        <v>0.0389407713074076</v>
+      </c>
+      <c r="K17" s="22" t="n">
+        <v>0.0827739194543963</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n">
+      <c r="A18" s="23" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="24" t="inlineStr">
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n">
+        <v>-0.0769230769230768</v>
+      </c>
+      <c r="F18" s="24" t="n">
+        <v>-0.0099573257467994</v>
+      </c>
+      <c r="G18" s="24" t="n">
+        <v>-0.1267252195734002</v>
+      </c>
+      <c r="H18" s="24" t="n">
+        <v>0.011602209270932</v>
+      </c>
+      <c r="I18" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J18" s="24" t="n">
+        <v>0.0313925821554888</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <v>-0.0055291931010313</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>TOASO.IS</t>
         </is>
       </c>
-      <c r="C18" s="24" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="24" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.08355321020228661</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.1459016393442622</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.0612612612612613</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.2255174654706502</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
+      <c r="E19" s="22" t="n">
+        <v>-0.119613016710642</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>-0.1868399675060925</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>-0.1211589113257243</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>-0.2339115262360762</v>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0251248630786822</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0532805395405533</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
+      <c r="J19" s="22" t="n">
+        <v>0.0255128092543047</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>0.0369101913701237</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D19" s="24" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0583892617449663</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.0049645390070921</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.0690112806901127</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>0.0091218873182385</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
+      <c r="E20" s="22" t="n">
+        <v>-0.1174529051347802</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>-0.1533937211982809</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>-0.2009624849968089</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-0.2354993133065573</v>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J19" s="25" t="n">
-        <v>0.031377917776001</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0478181869880385</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1295955728475251</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1582221984863281</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.1733665773215752</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.1990612037864825</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.026615207399564</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0190112247110776</v>
+      <c r="J20" s="22" t="n">
+        <v>0.0265720710599121</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>0.1001577768561146</v>
       </c>
     </row>
   </sheetData>
@@ -2552,7 +2663,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2560,7 +2671,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2597,7 +2708,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2720,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, ARCLK.IS</t>
+          <t>THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
         </is>
       </c>
     </row>
@@ -2621,7 +2732,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, FROTO.IS, TCELL.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>TUPRS.IS, FROTO.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2744,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2671,7 +2782,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2679,7 +2790,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2922,7 +3033,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2930,7 +3041,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2954,7 +3065,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12118.2998046875</v>
+        <v>12070.2001953125</v>
       </c>
     </row>
     <row r="5">
@@ -2964,7 +3075,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13615.6240234375</v>
+        <v>13619.50302246094</v>
       </c>
     </row>
     <row r="6">
@@ -2998,7 +3109,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.91</v>
+        <v>80.75</v>
       </c>
     </row>
     <row r="9">
@@ -3032,7 +3143,7 @@
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3041,7 +3152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-13</t>
+          <t>Rapor Tarihi: 2026-10-14</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3055,7 +3166,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-15 06:36</t>
+          <t>Son Güncelleme: 2026-10-16 06:30</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3119,23 +3230,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>0.07868020304568524</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>228671.7942438866</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D4" s="25" t="n">
+        <v>211.1999969482422</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.07208120278295516</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>209492.8245427259</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="5">
@@ -3149,23 +3260,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>85.65000152587891</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-0.1124352173484051</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>-9873.440090341275</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D5" s="25" t="n">
+        <v>84.75</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.1217616580310881</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-10692.43662459664</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="6">
@@ -3179,23 +3290,23 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="25" t="n">
         <v>133.3999938964844</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>131.3000030517578</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.01574206102555076</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-76234.10224256478</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D6" s="25" t="n">
+        <v>130.5</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.02173908567593119</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-105275.9023986077</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="7">
@@ -3209,23 +3320,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="25" t="n">
         <v>405.5</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>411.25</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>0.0141800246609125</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>40210.55552601442</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D7" s="25" t="n">
+        <v>408</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>0.006165228113440113</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>17482.85022870218</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="8">
@@ -3239,23 +3350,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="25" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>72.65000152587891</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>-0.06136950783407702</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>-274756.5046845153</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D8" s="25" t="n">
+        <v>71.84999847412109</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.07170546437136893</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-321031.4609451308</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
     <row r="9">
@@ -3269,23 +3380,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C9" s="26" t="n">
+      <c r="C9" s="25" t="n">
         <v>387</v>
       </c>
-      <c r="D9" s="26" t="n">
-        <v>385.75</v>
-      </c>
-      <c r="E9" s="27" t="n">
-        <v>-0.003229974160206761</v>
-      </c>
-      <c r="F9" s="26" t="n">
-        <v>-13947.24046593066</v>
-      </c>
-      <c r="G9" s="26" t="n">
-        <v>19964443.92963129</v>
-      </c>
-      <c r="H9" s="27" t="n">
-        <v>-0.1060493144109383</v>
+      <c r="D9" s="25" t="n">
+        <v>391</v>
+      </c>
+      <c r="E9" s="26" t="n">
+        <v>0.01033591731266159</v>
+      </c>
+      <c r="F9" s="25" t="n">
+        <v>44631.16949098092</v>
+      </c>
+      <c r="G9" s="25" t="n">
+        <v>19904979.91163881</v>
+      </c>
+      <c r="H9" s="26" t="n">
+        <v>-0.1157107556416009</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -571,7 +571,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -582,7 +582,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="19" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -607,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.75/100</t>
+          <t>Güven Puanı: 81.06/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +735,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
+          <t>ÇIK: GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %40</t>
+          <t>NAKIT: %60</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +884,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 3</t>
+          <t>Qualified opportunities count: 2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,7 +941,7 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 2</t>
+          <t>Rejected opportunities count: 3</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
@@ -955,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2155269052313723</v>
+        <v>0.2077980275017419</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>21552.69052313723</v>
+        <v>20779.80275017419</v>
       </c>
       <c r="F20" s="7" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>410.1248568516434</v>
+        <v>395.4176217197435</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>415.763807558775</v>
+        <v>409.1401194481572</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>387.6</v>
+        <v>381.425</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007346</v>
+        <v>0.3805788019007332</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,7 +984,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %40</t>
+          <t>Cash allocation %: %60</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -998,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.1994846123862184</v>
+        <v>0.1922019724982581</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19948.46123862184</v>
+        <v>19220.19724982581</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>464.1623736709059</v>
+        <v>356.1109187616202</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>216.1142151794203</v>
+        <v>214.8075391530232</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>200.6399971008301</v>
+        <v>196.9519159598</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4653615816464591</v>
+        <v>0.2801493707073222</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1025,83 +1025,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.1849884823824094</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>18498.84823824093</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>612.6344245652119</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>134.8218254118378</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.5418845397997932</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D22" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K23"/>
+  <autoFilter ref="A19:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1112,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1135,7 +1094,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1156,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1198,7 +1157,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 6</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1350,28 +1309,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>408</v>
+        <v>401.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0205577496905355</v>
+        <v>-0.0339316023388089</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0542750535284166</v>
+        <v>0.0722991184716234</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>399.6124381262615</v>
+        <v>387.8764616609682</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>415.763807558775</v>
+        <v>409.1401194481572</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>430.144221839594</v>
+        <v>430.5280960663567</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>387.6</v>
+        <v>381.425</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1379,7 +1338,7 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
@@ -1407,28 +1366,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>211.1999969482422</v>
+        <v>210.8999938964844</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0302466271968858</v>
+        <v>-0.06613598075081251</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.0914169657590902</v>
+        <v>0.06904391931949121</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>204.8119093765653</v>
+        <v>196.9519159598</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>216.1142151794203</v>
+        <v>214.8075391530232</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>230.5072598375796</v>
+        <v>225.4613560595544</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>200.6399971008301</v>
+        <v>196.9519159598</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1436,7 +1395,7 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
@@ -1445,62 +1404,62 @@
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="n">
+      <c r="A10" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="13" t="inlineStr">
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>130.5</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0611152997985</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0331174361060366</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.0795560183272892</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>134.8218254118378</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>140.8820603917112</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>122.5244533762957</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>133.8999938964844</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0597515338203614</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.008288919948726801</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1264267348706023</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>125.8992638826324</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>132.7901075659414</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>150.8285329240105</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>125.8992638826324</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>81.06</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="13" t="inlineStr">
+      <c r="O10" s="16" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
@@ -1512,7 +1471,7 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1521,28 +1480,28 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>279.25</v>
+        <v>36.29999923706055</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0628618693134822</v>
+        <v>-0.053387959227386</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>-0.0341997901255592</v>
+        <v>-0.0095238891213882</v>
       </c>
       <c r="G11" s="18" t="n">
-        <v>0.051230381576059</v>
+        <v>0.09198805801759501</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>261.6958229942101</v>
+        <v>34.36201635783821</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>269.6997086074376</v>
+        <v>35.95428206922031</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>293.5560840551145</v>
+        <v>39.63916567291793</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>261.6958229942101</v>
+        <v>34.36201635783821</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1550,16 +1509,16 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1569,7 +1528,7 @@
       </c>
       <c r="B12" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C12" s="16" t="inlineStr">
@@ -1578,28 +1537,28 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>35.93999862670898</v>
+        <v>276.75</v>
       </c>
       <c r="E12" s="18" t="n">
-        <v>-0.053387959227386</v>
+        <v>-0.0532251759639228</v>
       </c>
       <c r="F12" s="18" t="n">
-        <v>-0.0095238891213882</v>
+        <v>-0.0241174841137557</v>
       </c>
       <c r="G12" s="18" t="n">
-        <v>0.0919881126195933</v>
+        <v>0.1059543201175193</v>
       </c>
       <c r="H12" s="17" t="n">
-        <v>34.02123544539393</v>
+        <v>262.0199325519844</v>
       </c>
       <c r="I12" s="17" t="n">
-        <v>35.59771006476537</v>
+        <v>270.0754862715181</v>
       </c>
       <c r="J12" s="17" t="n">
-        <v>39.24605126793072</v>
+        <v>306.0728580925235</v>
       </c>
       <c r="K12" s="17" t="n">
-        <v>34.02123544539393</v>
+        <v>262.0199325519844</v>
       </c>
       <c r="L12" s="16" t="inlineStr">
         <is>
@@ -1607,26 +1566,26 @@
         </is>
       </c>
       <c r="M12" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N12" s="16" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O12" s="16" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="16" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="B13" s="16" t="inlineStr">
         <is>
-          <t>TCELL.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1635,28 +1594,28 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>98.30000305175781</v>
+        <v>76.55000305175781</v>
       </c>
       <c r="E13" s="18" t="n">
-        <v>-0.039929164947756</v>
+        <v>-0.0514249572914607</v>
       </c>
       <c r="F13" s="18" t="n">
-        <v>-0.0056461366774436</v>
+        <v>-0.0169388433571329</v>
       </c>
       <c r="G13" s="18" t="n">
-        <v>0.0253202830653163</v>
+        <v>0.1080536875032713</v>
       </c>
       <c r="H13" s="17" t="n">
-        <v>94.37496601553926</v>
+        <v>72.61342241415998</v>
       </c>
       <c r="I13" s="17" t="n">
-        <v>97.74498779913446</v>
+        <v>75.25333454107604</v>
       </c>
       <c r="J13" s="17" t="n">
-        <v>100.7889869543498</v>
+        <v>84.82151315988692</v>
       </c>
       <c r="K13" s="17" t="n">
-        <v>93.38500289916992</v>
+        <v>72.61342241415998</v>
       </c>
       <c r="L13" s="16" t="inlineStr">
         <is>
@@ -1664,7 +1623,7 @@
         </is>
       </c>
       <c r="M13" s="16" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
       <c r="N13" s="16" t="inlineStr">
         <is>
@@ -1673,126 +1632,12 @@
       </c>
       <c r="O13" s="16" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>10</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>76.55000305175781</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0514249572914607</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.1080537552156288</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>75.25332955008864</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>84.8215183432681</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>15</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>348</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.097767991594519</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.0055291931010313</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.1083753223429276</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>313.9767389251074</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>346.0758408008411</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>385.7146121753388</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>313.9767389251074</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>80.75</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O13"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1822,7 +1667,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1839,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1930,16 +1775,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.012704174228675</v>
+        <v>-0.0098643649815043</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.0633892203471258</v>
+        <v>0.009822246565652301</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0988178293379029</v>
+        <v>0.09148572652625959</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0462534110402206</v>
+        <v>-0.08444800886198769</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1947,7 +1792,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0188656249393633</v>
+        <v>0.0184398313048768</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1973,16 +1818,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.0347349451440264</v>
+        <v>0.0213074764962923</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0720812027829551</v>
+        <v>0.0555555088848078</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0352941026874618</v>
+        <v>0.0333169406644697</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.0799832003221837</v>
+        <v>-0.123075695465797</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1990,53 +1835,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0209049144524068</v>
+        <v>0.0208420951766543</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.0185279533884517</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>0.0211267361797222</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0291797859557771</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>-0.070512780105842</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-0.1541701320588953</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.1075268172583339</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.0772324264604336</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0346070883732535</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>-0.1962057044093192</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0219560472301172</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0331174361060366</v>
+      <c r="J6" s="18" t="n">
+        <v>0.022027028856444</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>-0.008288919948726801</v>
       </c>
     </row>
     <row r="7">
@@ -2045,7 +1890,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>YKBNK.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -2059,27 +1904,27 @@
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.021034180543383</v>
+        <v>0.1301370001300466</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1525037936267071</v>
+        <v>0.1033433906836516</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1361175560711524</v>
+        <v>-0.0462428290258961</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.202007399453498</v>
+        <v>-0.2101215518778449</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0182902909452241</v>
+        <v>0.0261382572155817</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>-0.0341997901255592</v>
+        <v>-0.0095238891213882</v>
       </c>
     </row>
     <row r="8">
@@ -2088,7 +1933,7 @@
       </c>
       <c r="B8" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C8" s="16" t="inlineStr">
@@ -2102,27 +1947,27 @@
         </is>
       </c>
       <c r="E8" s="18" t="n">
-        <v>0.0363321312123852</v>
+        <v>0.0137362637362636</v>
       </c>
       <c r="F8" s="18" t="n">
-        <v>0.081878305420131</v>
+        <v>-0.15625</v>
       </c>
       <c r="G8" s="18" t="n">
-        <v>-0.0703569899492693</v>
+        <v>-0.1262825572217837</v>
       </c>
       <c r="H8" s="18" t="n">
-        <v>-0.1410192860246872</v>
+        <v>-0.2534142788573249</v>
       </c>
       <c r="I8" s="16" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J8" s="18" t="n">
-        <v>0.0261570210933936</v>
+        <v>0.0183068090727517</v>
       </c>
       <c r="K8" s="18" t="n">
-        <v>-0.0095238891213882</v>
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="9">
@@ -2131,7 +1976,7 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr">
@@ -2145,27 +1990,27 @@
         </is>
       </c>
       <c r="E9" s="20" t="n">
-        <v>-0.0351351420553087</v>
+        <v>0.0753307314128375</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>0.3759956869540564</v>
+        <v>-0.142201769844607</v>
       </c>
       <c r="G9" s="20" t="n">
-        <v>0.5638771539369436</v>
+        <v>0.1846415657271476</v>
       </c>
       <c r="H9" s="20" t="n">
-        <v>-0.2403921002344196</v>
+        <v>-0.3282924529445142</v>
       </c>
       <c r="I9" s="19" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J9" s="20" t="n">
-        <v>0.0274488615475791</v>
+        <v>0.0238267651578265</v>
       </c>
       <c r="K9" s="20" t="n">
-        <v>0.0266028003670319</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -2174,12 +2019,12 @@
       </c>
       <c r="B10" s="19" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
@@ -2188,27 +2033,27 @@
         </is>
       </c>
       <c r="E10" s="20" t="n">
-        <v>-0.0835459556667959</v>
+        <v>-0.0257865512061281</v>
       </c>
       <c r="F10" s="20" t="n">
-        <v>-0.1405502417997924</v>
+        <v>0.2728139134011862</v>
       </c>
       <c r="G10" s="20" t="n">
-        <v>-0.3176638519297585</v>
+        <v>0.482538893227584</v>
       </c>
       <c r="H10" s="20" t="n">
-        <v>-0.07722106603181431</v>
+        <v>-0.2597158164725923</v>
       </c>
       <c r="I10" s="19" t="inlineStr">
         <is>
-          <t>Trend altı</t>
+          <t>Güçlü trend</t>
         </is>
       </c>
       <c r="J10" s="20" t="n">
-        <v>0.0179418586662416</v>
+        <v>0.026572024756061</v>
       </c>
       <c r="K10" s="20" t="n">
-        <v>0.0955199358563398</v>
+        <v>0.0195382818194833</v>
       </c>
     </row>
     <row r="11">
@@ -2217,7 +2062,7 @@
       </c>
       <c r="B11" s="19" t="inlineStr">
         <is>
-          <t>EREGL.IS</t>
+          <t>AKBNK.IS</t>
         </is>
       </c>
       <c r="C11" s="19" t="inlineStr">
@@ -2231,113 +2076,113 @@
         </is>
       </c>
       <c r="E11" s="20" t="n">
-        <v>-0.0303188682253351</v>
+        <v>0.0429448340922553</v>
       </c>
       <c r="F11" s="20" t="n">
-        <v>-0.1237600769858882</v>
+        <v>0.0172027158134355</v>
       </c>
       <c r="G11" s="20" t="n">
-        <v>0.2014201044256922</v>
+        <v>-0.1214470457437393</v>
       </c>
       <c r="H11" s="20" t="n">
-        <v>-0.2707792314346859</v>
+        <v>-0.08903919072576209</v>
       </c>
       <c r="I11" s="19" t="inlineStr">
         <is>
-          <t>Kısmen trend üstü</t>
+          <t>Trend altı</t>
         </is>
       </c>
       <c r="J11" s="20" t="n">
-        <v>0.0241314061543816</v>
+        <v>0.0236824282904043</v>
       </c>
       <c r="K11" s="20" t="n">
-        <v>0.0190703728875496</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="16" t="n">
+      <c r="A12" s="19" t="n">
         <v>9</v>
       </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0110663828695687</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0940091884630616</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>-0.1619778303979786</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>-0.2987318037968683</v>
-      </c>
-      <c r="I12" s="16" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.0522438237931836</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>-0.1439806570620914</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-0.3255481508973484</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.1339984914720539</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="18" t="n">
-        <v>0.0202669303577498</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>-0.0056461366774436</v>
+      <c r="J12" s="20" t="n">
+        <v>0.0179810570574388</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0.0696037442997602</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="16" t="n">
+      <c r="A13" s="19" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.1606359033630071</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.2156761859780638</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>-0.3473998204588225</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>0.0167865251532108</v>
-      </c>
-      <c r="I13" s="16" t="inlineStr">
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>0.0124554612615923</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>-0.0410112530997629</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>-0.1387487407841955</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.0375289263812521</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="18" t="n">
-        <v>0.015398835227913</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>-0.016938908556182</v>
+      <c r="J13" s="20" t="n">
+        <v>0.021348496351713</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.0406249908410989</v>
       </c>
     </row>
     <row r="14">
@@ -2346,7 +2191,7 @@
       </c>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t>AKBNK.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C14" s="21" t="inlineStr">
@@ -2360,16 +2205,16 @@
         </is>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.0352265200594379</v>
+        <v>0.0219320989464344</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>0.009022533445429901</v>
+        <v>-0.1072080306896575</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.1441326891814895</v>
+        <v>-0.1542782968447803</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>-0.0324538470874489</v>
+        <v>-0.3546968211243853</v>
       </c>
       <c r="I14" s="21" t="inlineStr">
         <is>
@@ -2377,53 +2222,53 @@
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.0236332051822288</v>
+        <v>0.0202170048918636</v>
       </c>
       <c r="K14" s="22" t="n">
-        <v>0.0132478544110439</v>
+        <v>0.0124596506797498</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="21" t="n">
+      <c r="A15" s="23" t="n">
         <v>12</v>
       </c>
-      <c r="B15" s="21" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="21" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E15" s="22" t="n">
-        <v>-0.0614618257385515</v>
-      </c>
-      <c r="F15" s="22" t="n">
-        <v>-0.0412896093085516</v>
-      </c>
-      <c r="G15" s="22" t="n">
-        <v>-0.1691176470588234</v>
-      </c>
-      <c r="H15" s="22" t="n">
-        <v>0.0103087844515024</v>
-      </c>
-      <c r="I15" s="21" t="inlineStr">
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n">
+        <v>-0.1185952285932669</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.2224478880176887</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.3578019713792729</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.0237804713987</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="22" t="n">
-        <v>0.0213468675694466</v>
-      </c>
-      <c r="K15" s="22" t="n">
-        <v>0.0540671532455347</v>
+      <c r="J15" s="24" t="n">
+        <v>0.0153242689052913</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>-0.0169388433571329</v>
       </c>
     </row>
     <row r="16">
@@ -2446,16 +2291,16 @@
         </is>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1353333536783854</v>
+        <v>-0.1088154503019023</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.2210210393498968</v>
+        <v>-0.2143291056820785</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>-0.3115711191609415</v>
+        <v>-0.2955906584312952</v>
       </c>
       <c r="H16" s="22" t="n">
-        <v>-0.1814248975650475</v>
+        <v>-0.2320606108523896</v>
       </c>
       <c r="I16" s="21" t="inlineStr">
         <is>
@@ -2463,10 +2308,10 @@
         </is>
       </c>
       <c r="J16" s="22" t="n">
-        <v>0.0184858230413237</v>
+        <v>0.0184647467983716</v>
       </c>
       <c r="K16" s="22" t="n">
-        <v>0.0073660782405308</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -2489,70 +2334,70 @@
         </is>
       </c>
       <c r="E17" s="22" t="n">
-        <v>-0.08377423249402149</v>
+        <v>-0.0305052146621838</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>-0.0076408712192667</v>
+        <v>-0.1039647811027634</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>-0.027153553704721</v>
+        <v>-0.0837838083977292</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>-0.1247594319985501</v>
+        <v>-0.1681446065012396</v>
       </c>
       <c r="I17" s="21" t="inlineStr">
         <is>
-          <t>Güçlü trend</t>
+          <t>Kısmen trend üstü</t>
         </is>
       </c>
       <c r="J17" s="22" t="n">
-        <v>0.0389407713074076</v>
+        <v>0.0375357321501754</v>
       </c>
       <c r="K17" s="22" t="n">
-        <v>0.0827739194543963</v>
+        <v>0.0166223768740767</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="23" t="n">
+      <c r="A18" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="B18" s="23" t="inlineStr">
+      <c r="B18" s="21" t="inlineStr">
         <is>
           <t>ASELS.IS</t>
         </is>
       </c>
-      <c r="C18" s="23" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E18" s="24" t="n">
-        <v>-0.0769230769230768</v>
-      </c>
-      <c r="F18" s="24" t="n">
-        <v>-0.0099573257467994</v>
-      </c>
-      <c r="G18" s="24" t="n">
-        <v>-0.1267252195734002</v>
-      </c>
-      <c r="H18" s="24" t="n">
-        <v>0.011602209270932</v>
-      </c>
-      <c r="I18" s="23" t="inlineStr">
+      <c r="D18" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E18" s="22" t="n">
+        <v>-0.025</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>-0.009873060648801101</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>-0.1547260686333533</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>-0.0144960244423122</v>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="24" t="n">
-        <v>0.0313925821554888</v>
-      </c>
-      <c r="K18" s="24" t="n">
-        <v>-0.0055291931010313</v>
+      <c r="J18" s="22" t="n">
+        <v>0.0313929461035974</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>0.0401887662276918</v>
       </c>
     </row>
     <row r="19">
@@ -2575,16 +2420,16 @@
         </is>
       </c>
       <c r="E19" s="22" t="n">
-        <v>-0.119613016710642</v>
+        <v>-0.0953167931983184</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>-0.1868399675060925</v>
+        <v>-0.1837613817671655</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>-0.1211589113257243</v>
+        <v>-0.1319823680995319</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>-0.2339115262360762</v>
+        <v>-0.2413179433792739</v>
       </c>
       <c r="I19" s="21" t="inlineStr">
         <is>
@@ -2592,10 +2437,10 @@
         </is>
       </c>
       <c r="J19" s="22" t="n">
-        <v>0.0255128092543047</v>
+        <v>0.0254782595170972</v>
       </c>
       <c r="K19" s="22" t="n">
-        <v>0.0369101913701237</v>
+        <v>0.0350217789493367</v>
       </c>
     </row>
     <row r="20">
@@ -2618,16 +2463,16 @@
         </is>
       </c>
       <c r="E20" s="22" t="n">
-        <v>-0.1174529051347802</v>
+        <v>-0.0251178144560054</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>-0.1533937211982809</v>
+        <v>-0.1626966669318381</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>-0.2009624849968089</v>
+        <v>-0.2097097391095529</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>-0.2354993133065573</v>
+        <v>-0.3491513513096235</v>
       </c>
       <c r="I20" s="21" t="inlineStr">
         <is>
@@ -2635,10 +2480,10 @@
         </is>
       </c>
       <c r="J20" s="22" t="n">
-        <v>0.0265720710599121</v>
+        <v>0.0265476448629649</v>
       </c>
       <c r="K20" s="22" t="n">
-        <v>0.1001577768561146</v>
+        <v>0.0905550350972887</v>
       </c>
     </row>
   </sheetData>
@@ -2663,7 +2508,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2671,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2696,7 +2541,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2565,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS, YKBNK.IS, TCELL.IS, ARCLK.IS, ASELS.IS</t>
+          <t>GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
         </is>
       </c>
     </row>
@@ -2732,7 +2577,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS, FROTO.IS, EREGL.IS, AKBNK.IS, SAHOL.IS, PGSUS.IS, PETKM.IS, TOASO.IS, SISE.IS</t>
+          <t>EREGL.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2744,7 +2589,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.90 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2756,7 +2601,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2627,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2790,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2887,7 +2732,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3033,7 +2878,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3041,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3065,7 +2910,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>12070.2001953125</v>
+        <v>11721.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3075,7 +2920,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13619.50302246094</v>
+        <v>13622.35702148438</v>
       </c>
     </row>
     <row r="6">
@@ -3109,7 +2954,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.75</v>
+        <v>81.06</v>
       </c>
     </row>
     <row r="9">
@@ -3136,14 +2981,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
@@ -3152,7 +2997,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-14</t>
+          <t>Rapor Tarihi: 2026-10-15</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3166,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-16 06:30</t>
+          <t>Son Güncelleme: 2026-10-17 06:19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3234,19 +3079,19 @@
         <v>197</v>
       </c>
       <c r="D4" s="25" t="n">
-        <v>211.1999969482422</v>
+        <v>210.8999938964844</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.07208120278295516</v>
+        <v>0.0705583446522049</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>209492.8245427259</v>
+        <v>205066.873825042</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H4" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="5">
@@ -3264,143 +3109,113 @@
         <v>96.5</v>
       </c>
       <c r="D5" s="25" t="n">
-        <v>84.75</v>
+        <v>85.34999847412109</v>
       </c>
       <c r="E5" s="26" t="n">
-        <v>-0.1217616580310881</v>
+        <v>-0.1155440572629939</v>
       </c>
       <c r="F5" s="25" t="n">
-        <v>-10692.43662459664</v>
+        <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H5" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-10</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="C6" s="25" t="n">
-        <v>133.3999938964844</v>
+        <v>405.5</v>
       </c>
       <c r="D6" s="25" t="n">
-        <v>130.5</v>
+        <v>401.5</v>
       </c>
       <c r="E6" s="26" t="n">
-        <v>-0.02173908567593119</v>
+        <v>-0.009864364981504337</v>
       </c>
       <c r="F6" s="25" t="n">
-        <v>-105275.9023986077</v>
+        <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H6" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-24</t>
         </is>
       </c>
       <c r="C7" s="25" t="n">
-        <v>405.5</v>
+        <v>77.40000152587891</v>
       </c>
       <c r="D7" s="25" t="n">
-        <v>408</v>
+        <v>70.75</v>
       </c>
       <c r="E7" s="26" t="n">
-        <v>0.006165228113440113</v>
+        <v>-0.08591733068190521</v>
       </c>
       <c r="F7" s="25" t="n">
-        <v>17482.85022870218</v>
+        <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H7" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="C8" s="25" t="n">
-        <v>77.40000152587891</v>
+        <v>387</v>
       </c>
       <c r="D8" s="25" t="n">
-        <v>71.84999847412109</v>
+        <v>384.5</v>
       </c>
       <c r="E8" s="26" t="n">
-        <v>-0.07170546437136893</v>
+        <v>-0.006459948320413411</v>
       </c>
       <c r="F8" s="25" t="n">
-        <v>-321031.4609451308</v>
+        <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>19904979.91163881</v>
+        <v>19842918.11965895</v>
       </c>
       <c r="H8" s="26" t="n">
-        <v>-0.1157107556416009</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C9" s="25" t="n">
-        <v>387</v>
-      </c>
-      <c r="D9" s="25" t="n">
-        <v>391</v>
-      </c>
-      <c r="E9" s="26" t="n">
-        <v>0.01033591731266159</v>
-      </c>
-      <c r="F9" s="25" t="n">
-        <v>44631.16949098092</v>
-      </c>
-      <c r="G9" s="25" t="n">
-        <v>19904979.91163881</v>
-      </c>
-      <c r="H9" s="26" t="n">
-        <v>-0.1157107556416009</v>
+        <v>-0.1192206512468987</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1312,7 +1312,7 @@
         <v>401.5</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316023388089</v>
+        <v>-0.0339316023388087</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1321,7 +1321,7 @@
         <v>0.0722991184716234</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>387.8764616609682</v>
+        <v>387.8764616609683</v>
       </c>
       <c r="I8" s="14" t="n">
         <v>409.1401194481572</v>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1781,7 +1781,7 @@
         <v>0.009822246565652301</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.09148572652625959</v>
+        <v>0.0914857265262594</v>
       </c>
       <c r="H4" s="15" t="n">
         <v>-0.08444800886198769</v>
@@ -1818,13 +1818,13 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0213074764962923</v>
+        <v>0.0213074764962926</v>
       </c>
       <c r="F5" s="15" t="n">
         <v>0.0555555088848078</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0333169406644697</v>
+        <v>0.0333169406644699</v>
       </c>
       <c r="H5" s="15" t="n">
         <v>-0.123075695465797</v>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208420951766543</v>
+        <v>0.0208420951766542</v>
       </c>
       <c r="K5" s="15" t="n">
         <v>0.0185279533884517</v>
@@ -1864,7 +1864,7 @@
         <v>0.1075268172583339</v>
       </c>
       <c r="F6" s="18" t="n">
-        <v>0.0772324264604336</v>
+        <v>0.0772324264604338</v>
       </c>
       <c r="G6" s="18" t="n">
         <v>-0.0346070883732535</v>
@@ -1993,7 +1993,7 @@
         <v>0.0753307314128375</v>
       </c>
       <c r="F9" s="20" t="n">
-        <v>-0.142201769844607</v>
+        <v>-0.1422017698446069</v>
       </c>
       <c r="G9" s="20" t="n">
         <v>0.1846415657271476</v>
@@ -2136,7 +2136,7 @@
         </is>
       </c>
       <c r="J12" s="20" t="n">
-        <v>0.0179810570574388</v>
+        <v>0.0179810570574387</v>
       </c>
       <c r="K12" s="20" t="n">
         <v>0.0696037442997602</v>
@@ -2182,7 +2182,7 @@
         <v>0.021348496351713</v>
       </c>
       <c r="K13" s="20" t="n">
-        <v>0.0406249908410989</v>
+        <v>0.0406249908410991</v>
       </c>
     </row>
     <row r="14">
@@ -2211,7 +2211,7 @@
         <v>-0.1072080306896575</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>-0.1542782968447803</v>
+        <v>-0.1542782968447804</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>-0.3546968211243853</v>
@@ -2222,7 +2222,7 @@
         </is>
       </c>
       <c r="J14" s="22" t="n">
-        <v>0.0202170048918636</v>
+        <v>0.0202170048918635</v>
       </c>
       <c r="K14" s="22" t="n">
         <v>0.0124596506797498</v>
@@ -2251,10 +2251,10 @@
         <v>-0.1185952285932669</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>-0.2224478880176887</v>
+        <v>-0.2224478880176889</v>
       </c>
       <c r="G15" s="24" t="n">
-        <v>-0.3578019713792729</v>
+        <v>-0.357801971379273</v>
       </c>
       <c r="H15" s="24" t="n">
         <v>-0.0237804713987</v>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="J15" s="24" t="n">
-        <v>0.0153242689052913</v>
+        <v>0.0153242689052914</v>
       </c>
       <c r="K15" s="24" t="n">
         <v>-0.0169388433571329</v>
@@ -2308,7 +2308,7 @@
         </is>
       </c>
       <c r="J16" s="22" t="n">
-        <v>0.0184647467983716</v>
+        <v>0.0184647467983715</v>
       </c>
       <c r="K16" s="22" t="n">
         <v>0</v>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-17 06:19</t>
+          <t>Son Güncelleme: 2026-10-18 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3082,13 +3082,13 @@
         <v>210.8999938964844</v>
       </c>
       <c r="E4" s="26" t="n">
-        <v>0.0705583446522049</v>
+        <v>0.07055834465220512</v>
       </c>
       <c r="F4" s="25" t="n">
-        <v>205066.873825042</v>
+        <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>19842918.11965895</v>
+        <v>24703770.6565244</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -624,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -1115,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1684,7 +1684,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2516,7 +2516,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2635,7 +2635,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2886,7 +2886,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2990,7 +2990,7 @@
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="23" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -3011,7 +3011,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-18 06:41</t>
+          <t>Son Güncelleme: 2026-10-19 07:02</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3088,7 +3088,7 @@
         <v>205066.8738250425</v>
       </c>
       <c r="G4" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H4" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3118,7 +3118,7 @@
         <v>-10146.44124932901</v>
       </c>
       <c r="G5" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H5" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3148,7 +3148,7 @@
         <v>-27972.56036592275</v>
       </c>
       <c r="G6" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H6" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3178,7 +3178,7 @@
         <v>-384659.1948204595</v>
       </c>
       <c r="G7" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H7" s="26" t="n">
         <v>-0.1192206512468987</v>
@@ -3208,7 +3208,7 @@
         <v>-27894.48093186226</v>
       </c>
       <c r="G8" s="25" t="n">
-        <v>24703770.6565244</v>
+        <v>29564623.19338985</v>
       </c>
       <c r="H8" s="26" t="n">
         <v>-0.1192206512468987</v>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,19 +185,28 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -571,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -582,7 +591,7 @@
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="9" max="9"/>
     <col width="20" customWidth="1" min="10" max="10"/>
     <col width="12" customWidth="1" min="11" max="11"/>
   </cols>
@@ -607,7 +616,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +633,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +684,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 81.06/100</t>
+          <t>Güven Puanı: 77.21/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +744,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS</t>
+          <t>AL: GARAN.IS, BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -752,7 +761,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: THYAO.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -769,7 +778,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>ÇIK: EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +795,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %60</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +893,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 2</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,12 +950,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 3</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -955,25 +964,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2077980275017419</v>
+        <v>0.2088152294530557</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20779.80275017419</v>
+        <v>20881.52294530557</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0567878660082687</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>395.4176217197435</v>
+        <v>1185.817127066601</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>409.1401194481572</v>
+        <v>138.9676043800874</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>381.425</v>
+        <v>124.925</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007332</v>
+        <v>1.135757320165376</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,83 +993,124 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %60</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="n">
+        <v>0.2002676363786851</v>
+      </c>
+      <c r="E21" s="8" t="n">
+        <v>20026.76363786851</v>
+      </c>
+      <c r="F21" s="7" t="n">
+        <v>0.0190289400950367</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>381.0880855624591</v>
+      </c>
+      <c r="H21" s="8" t="n">
+        <v>388.250026176209</v>
+      </c>
+      <c r="I21" s="8" t="n">
+        <v>361.95</v>
+      </c>
+      <c r="J21" s="6" t="n">
+        <v>0.3805788019007357</v>
+      </c>
+      <c r="K21" s="9" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
           <t>KCHOL.IS</t>
         </is>
       </c>
-      <c r="C21" s="6" t="inlineStr">
+      <c r="C22" s="6" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D21" s="7" t="n">
-        <v>0.1922019724982581</v>
-      </c>
-      <c r="E21" s="8" t="n">
-        <v>19220.19724982581</v>
-      </c>
-      <c r="F21" s="7" t="n">
-        <v>0.0185279533884517</v>
-      </c>
-      <c r="G21" s="8" t="n">
-        <v>356.1109187616202</v>
-      </c>
-      <c r="H21" s="8" t="n">
-        <v>214.8075391530232</v>
-      </c>
-      <c r="I21" s="8" t="n">
-        <v>196.9519159598</v>
-      </c>
-      <c r="J21" s="6" t="n">
-        <v>0.2801493707073222</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
+      <c r="D22" s="7" t="n">
+        <v>0.1909171341682591</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>19091.71341682591</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.0185278352337725</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>353.7281205173542</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>207.7796783876896</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>190.5082770636984</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.2801479400025187</v>
+      </c>
+      <c r="K22" s="9" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="10" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="D23" s="11" t="n">
+        <v>0.4000000000000001</v>
+      </c>
+      <c r="E23" s="12" t="n">
+        <v>40000.00000000001</v>
+      </c>
+      <c r="F23" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="H23" s="12" t="inlineStr"/>
+      <c r="I23" s="12" t="inlineStr"/>
+      <c r="J23" s="10" t="inlineStr"/>
+      <c r="K23" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K22"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1071,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:O15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1144,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1115,7 +1165,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1157,7 +1207,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 6</t>
+          <t>Toplam önerilen/satılacak satır: 8</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1309,28 +1359,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>401.5</v>
+        <v>381</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339316023388087</v>
+        <v>-0.0339317167690779</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0722991184716234</v>
+        <v>0.0770488931257379</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>387.8764616609683</v>
+        <v>368.0720159109813</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>409.1401194481572</v>
+        <v>388.250026176209</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>430.5280960663567</v>
+        <v>410.3556282809061</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>381.425</v>
+        <v>361.95</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1338,11 +1388,11 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="13" t="inlineStr">
@@ -1366,28 +1416,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>210.8999938964844</v>
+        <v>204</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.06613598075081251</v>
+        <v>-0.0661358967465763</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.0185278352337725</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.06904391931949121</v>
+        <v>0.06904386578716611</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>196.9519159598</v>
+        <v>190.5082770636984</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>214.8075391530232</v>
+        <v>207.7796783876896</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>225.4613560595544</v>
+        <v>218.0849486205819</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>196.9519159598</v>
+        <v>190.5082770636984</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1395,73 +1445,73 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O9" s="13" t="inlineStr">
         <is>
-          <t>alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="n">
+      <c r="A10" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B10" s="16" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>133.8999938964844</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0597515338203614</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.008288919948726801</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1264267348706023</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>125.8992638826324</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>132.7901075659414</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>150.8285329240105</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>125.8992638826324</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M10" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
+      <c r="C10" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="14" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="E10" s="15" t="n">
+        <v>-0.0446735031448903</v>
+      </c>
+      <c r="F10" s="15" t="n">
+        <v>0.0567878660082687</v>
+      </c>
+      <c r="G10" s="15" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="14" t="n">
+        <v>125.6254343364469</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>138.9676043800874</v>
+      </c>
+      <c r="J10" s="14" t="n">
+        <v>147.8115010660311</v>
+      </c>
+      <c r="K10" s="14" t="n">
+        <v>124.925</v>
+      </c>
+      <c r="L10" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N10" s="13" t="inlineStr">
         <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O10" s="16" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
+      <c r="O10" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
@@ -1471,173 +1521,287 @@
       </c>
       <c r="B11" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D11" s="17" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0478683703056284</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>0.0115131578947369</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>0.128113826384147</v>
+      </c>
+      <c r="H11" s="17" t="n">
+        <v>260.4080007214106</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <v>276.6488486842106</v>
+      </c>
+      <c r="J11" s="17" t="n">
+        <v>308.5391315160642</v>
+      </c>
+      <c r="K11" s="17" t="n">
+        <v>259.825</v>
+      </c>
+      <c r="L11" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N11" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>36.29999923706055</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.0095238891213882</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.09198805801759501</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>34.36201635783821</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>35.95428206922031</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>39.63916567291793</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>34.36201635783821</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="D12" s="20" t="n">
+        <v>36.2599983215332</v>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.0210279373987021</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>0.0338076907416818</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>33.89199923891765</v>
+      </c>
+      <c r="I12" s="20" t="n">
+        <v>35.49752534675096</v>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>37.4858651310815</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>33.89199923891765</v>
+      </c>
+      <c r="L12" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="M12" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N12" s="19" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
-        <v>276.75</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0532251759639228</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.1059543201175193</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>262.0199325519844</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>270.0754862715181</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>306.0728580925235</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>262.0199325519844</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="D13" s="20" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.0627802516039144</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>-0.012693954565347</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.06657407220854521</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>62.65313875019448</v>
+      </c>
+      <c r="I13" s="20" t="n">
+        <v>66.00140763079708</v>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>71.30047509967838</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>62.65313875019448</v>
+      </c>
+      <c r="L13" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
+      <c r="M13" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N13" s="19" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="19" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="19" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="n">
+        <v>75.05000305175781</v>
+      </c>
+      <c r="E14" s="21" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F14" s="21" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+      <c r="G14" s="21" t="n">
+        <v>0.1080536875032713</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>70.77500363620553</v>
+      </c>
+      <c r="I14" s="20" t="n">
+        <v>73.77873310261967</v>
+      </c>
+      <c r="J14" s="20" t="n">
+        <v>83.15943262863202</v>
+      </c>
+      <c r="K14" s="20" t="n">
+        <v>70.77500363620553</v>
+      </c>
+      <c r="L14" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N14" s="19" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="O14" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="19" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="19" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>76.55000305175781</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0514249572914607</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0169388433571329</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.1080536875032713</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>75.25333454107604</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>84.82151315988692</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>72.61342241415998</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D15" s="20" t="n">
+        <v>19.70999908447266</v>
+      </c>
+      <c r="E15" s="21" t="n">
+        <v>-0.1036118867092948</v>
+      </c>
+      <c r="F15" s="21" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G15" s="21" t="n">
+        <v>0.0471306356513333</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>17.66780889229197</v>
+      </c>
+      <c r="I15" s="20" t="n">
+        <v>19.47636835227578</v>
+      </c>
+      <c r="J15" s="20" t="n">
+        <v>20.63894387001105</v>
+      </c>
+      <c r="K15" s="20" t="n">
+        <v>17.66780889229197</v>
+      </c>
+      <c r="L15" s="19" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>81.06</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M15" s="19" t="n">
+        <v>77.20999999999999</v>
+      </c>
+      <c r="N15" s="19" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O15" s="19" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O13"/>
+  <autoFilter ref="A7:O15"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1667,7 +1831,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1684,7 +1848,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1775,16 +1939,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0098643649815043</v>
+        <v>-0.0885167464114832</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>0.009822246565652301</v>
+        <v>-0.0246694885084334</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0914857265262594</v>
+        <v>0.0247374545953591</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.08444800886198769</v>
+        <v>-0.0713714963421137</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1792,7 +1956,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0184398313048768</v>
+        <v>0.0194215259434294</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1818,16 +1982,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>0.0213074764962926</v>
+        <v>-0.06721535049550589</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0555555088848078</v>
+        <v>0.0124069478908188</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>0.0333169406644699</v>
+        <v>-0.0111488270370058</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.123075695465797</v>
+        <v>-0.1779043813425157</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1835,53 +1999,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0208420951766542</v>
+        <v>0.0212480672808465</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185279533884517</v>
+        <v>0.0185278352337725</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="16" t="n">
+      <c r="A6" s="13" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="16" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>0.1075268172583339</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.0772324264604338</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-0.0346070883732535</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.1962057044093192</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="C6" s="13" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="13" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="15" t="n">
+        <v>-0.0075471698113207</v>
+      </c>
+      <c r="F6" s="15" t="n">
+        <v>0.0587761934873471</v>
+      </c>
+      <c r="G6" s="15" t="n">
+        <v>-0.0607142857142857</v>
+      </c>
+      <c r="H6" s="15" t="n">
+        <v>-0.2401145978594463</v>
+      </c>
+      <c r="I6" s="13" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.022027028856444</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>-0.008288919948726801</v>
+      <c r="J6" s="15" t="n">
+        <v>0.0221600754600607</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.0567878660082687</v>
       </c>
     </row>
     <row r="7">
@@ -1890,7 +2054,7 @@
       </c>
       <c r="B7" s="16" t="inlineStr">
         <is>
-          <t>YKBNK.IS</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1900,203 +2064,203 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="E7" s="18" t="n">
+        <v>-0.0544511668107173</v>
+      </c>
+      <c r="F7" s="18" t="n">
+        <v>-0.1385826771653543</v>
+      </c>
+      <c r="G7" s="18" t="n">
+        <v>-0.1558641975308642</v>
+      </c>
+      <c r="H7" s="18" t="n">
+        <v>-0.2990371871898438</v>
+      </c>
+      <c r="I7" s="16" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="18" t="n">
+        <v>0.0179550241285408</v>
+      </c>
+      <c r="K7" s="18" t="n">
+        <v>0.0115131578947369</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="19" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="19" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>0.1301370001300466</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>0.1033433906836516</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-0.0462428290258961</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.2101215518778449</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E8" s="21" t="n">
+        <v>0.0033203910877523</v>
+      </c>
+      <c r="F8" s="21" t="n">
+        <v>-0.1427896223278293</v>
+      </c>
+      <c r="G8" s="21" t="n">
+        <v>0.1682462518215937</v>
+      </c>
+      <c r="H8" s="21" t="n">
+        <v>-0.4166007613604728</v>
+      </c>
+      <c r="I8" s="19" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0261382572155817</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>-0.0095238891213882</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="J8" s="21" t="n">
+        <v>0.0238393622678929</v>
+      </c>
+      <c r="K8" s="21" t="n">
+        <v>-0.0210279373987021</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="22" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E8" s="18" t="n">
-        <v>0.0137362637362636</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>-0.15625</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>-0.1262825572217837</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.2534142788573249</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
+      <c r="D9" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="23" t="n">
+        <v>-0.0584988467066824</v>
+      </c>
+      <c r="F9" s="23" t="n">
+        <v>-0.035067855436785</v>
+      </c>
+      <c r="G9" s="23" t="n">
+        <v>-0.1512437507287779</v>
+      </c>
+      <c r="H9" s="23" t="n">
+        <v>-0.0469174948540891</v>
+      </c>
+      <c r="I9" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0183068090727517</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="J9" s="23" t="n">
+        <v>0.0213332669094879</v>
+      </c>
+      <c r="K9" s="23" t="n">
+        <v>0.0125687493441779</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D10" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>0.0753307314128375</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>-0.1422017698446069</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>0.1846415657271476</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.3282924529445142</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E10" s="23" t="n">
+        <v>-0.0722597663968105</v>
+      </c>
+      <c r="F10" s="23" t="n">
+        <v>0.2349885919682477</v>
+      </c>
+      <c r="G10" s="23" t="n">
+        <v>0.4288934039768077</v>
+      </c>
+      <c r="H10" s="23" t="n">
+        <v>-0.2797918847497309</v>
+      </c>
+      <c r="I10" s="22" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0238267651578265</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="19" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="J10" s="23" t="n">
+        <v>0.0267961516085757</v>
+      </c>
+      <c r="K10" s="23" t="n">
+        <v>0.0186683182612425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="22" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D11" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E10" s="20" t="n">
-        <v>-0.0257865512061281</v>
-      </c>
-      <c r="F10" s="20" t="n">
-        <v>0.2728139134011862</v>
-      </c>
-      <c r="G10" s="20" t="n">
-        <v>0.482538893227584</v>
-      </c>
-      <c r="H10" s="20" t="n">
-        <v>-0.2597158164725923</v>
-      </c>
-      <c r="I10" s="19" t="inlineStr">
-        <is>
-          <t>Güçlü trend</t>
-        </is>
-      </c>
-      <c r="J10" s="20" t="n">
-        <v>0.026572024756061</v>
-      </c>
-      <c r="K10" s="20" t="n">
-        <v>0.0195382818194833</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="19" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="20" t="n">
-        <v>0.0429448340922553</v>
-      </c>
-      <c r="F11" s="20" t="n">
-        <v>0.0172027158134355</v>
-      </c>
-      <c r="G11" s="20" t="n">
-        <v>-0.1214470457437393</v>
-      </c>
-      <c r="H11" s="20" t="n">
-        <v>-0.08903919072576209</v>
-      </c>
-      <c r="I11" s="19" t="inlineStr">
+      <c r="E11" s="23" t="n">
+        <v>-0.0237014466763041</v>
+      </c>
+      <c r="F11" s="23" t="n">
+        <v>-0.1318385376523962</v>
+      </c>
+      <c r="G11" s="23" t="n">
+        <v>-0.1676698150327801</v>
+      </c>
+      <c r="H11" s="23" t="n">
+        <v>-0.3947890261345917</v>
+      </c>
+      <c r="I11" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="20" t="n">
-        <v>0.0236824282904043</v>
-      </c>
-      <c r="K11" s="20" t="n">
-        <v>0</v>
+      <c r="J11" s="23" t="n">
+        <v>0.0201020435035757</v>
+      </c>
+      <c r="K11" s="23" t="n">
+        <v>0.0008189588123605</v>
       </c>
     </row>
     <row r="12">
@@ -2105,385 +2269,385 @@
       </c>
       <c r="B12" s="19" t="inlineStr">
         <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="19" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.0656883910156765</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>0.0022488985418591</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.1478648683922098</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.1463350037254664</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.023782163861295</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>-0.012693954565347</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="22" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="22" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="n">
+        <v>0.0107588072309898</v>
+      </c>
+      <c r="F13" s="23" t="n">
+        <v>0.08642727023240621</v>
+      </c>
+      <c r="G13" s="23" t="n">
+        <v>-0.0525477581263276</v>
+      </c>
+      <c r="H13" s="23" t="n">
+        <v>-0.2608541483895467</v>
+      </c>
+      <c r="I13" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="23" t="n">
+        <v>0.0262386681832899</v>
+      </c>
+      <c r="K13" s="23" t="n">
+        <v>0.0012391857819089</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="24" t="inlineStr">
+        <is>
           <t>FROTO.IS</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr">
+      <c r="C14" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="19" t="inlineStr">
+      <c r="D14" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.0522438237931836</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>-0.1439806570620914</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-0.3255481508973484</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>-0.1339984914720539</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E14" s="25" t="n">
+        <v>-0.1052291054566574</v>
+      </c>
+      <c r="F14" s="25" t="n">
+        <v>-0.1454993297703778</v>
+      </c>
+      <c r="G14" s="25" t="n">
+        <v>-0.3468425631630822</v>
+      </c>
+      <c r="H14" s="25" t="n">
+        <v>-0.184823647196279</v>
+      </c>
+      <c r="I14" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="20" t="n">
-        <v>0.0179810570574387</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0.0696037442997602</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="J14" s="25" t="n">
+        <v>0.0180080585291347</v>
+      </c>
+      <c r="K14" s="25" t="n">
+        <v>0.0417059171430678</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="26" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="19" t="inlineStr">
+      <c r="D15" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="27" t="n">
+        <v>-0.163788266832782</v>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>-0.2388437706573017</v>
+      </c>
+      <c r="G15" s="27" t="n">
+        <v>-0.3629032164049853</v>
+      </c>
+      <c r="H15" s="27" t="n">
+        <v>-0.0341178763549946</v>
+      </c>
+      <c r="I15" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="27" t="n">
+        <v>0.0154349832021613</v>
+      </c>
+      <c r="K15" s="27" t="n">
+        <v>-0.0169389726508262</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="20" t="n">
-        <v>0.0124554612615923</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>-0.0410112530997629</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>-0.1387487407841955</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.0375289263812521</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.1498002693552206</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.2180037075212559</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.3174773234502706</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.2911065832810884</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="20" t="n">
-        <v>0.021348496351713</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.0406249908410991</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0184935998639454</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>0.0147321564810616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="26" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="21" t="inlineStr">
+      <c r="D17" s="26" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="27" t="n">
+        <v>-0.08495829866634361</v>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>-0.07551597717622929</v>
+      </c>
+      <c r="G17" s="27" t="n">
+        <v>-0.1065276717299021</v>
+      </c>
+      <c r="H17" s="27" t="n">
+        <v>-0.2143560266767461</v>
+      </c>
+      <c r="I17" s="26" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="27" t="n">
+        <v>0.0369537734981878</v>
+      </c>
+      <c r="K17" s="27" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="22" t="n">
-        <v>0.0219320989464344</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.1072080306896575</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.1542782968447804</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>-0.3546968211243853</v>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
+      <c r="E18" s="25" t="n">
+        <v>-0.1040157998683344</v>
+      </c>
+      <c r="F18" s="25" t="n">
+        <v>-0.0548611111111111</v>
+      </c>
+      <c r="G18" s="25" t="n">
+        <v>-0.1736490588949605</v>
+      </c>
+      <c r="H18" s="25" t="n">
+        <v>-0.018716959054709</v>
+      </c>
+      <c r="I18" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0202170048918635</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>0.0124596506797498</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
+      <c r="J18" s="25" t="n">
+        <v>0.0315706199152426</v>
+      </c>
+      <c r="K18" s="25" t="n">
+        <v>0.0339372257730323</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.1185952285932669</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.2224478880176889</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.357801971379273</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.0237804713987</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="25" t="n">
+        <v>-0.1484320770157339</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1853333536783854</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.1798657922936766</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.2416322795488767</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0153242689052914</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.0169388433571329</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
+      <c r="J19" s="25" t="n">
+        <v>0.02548291720417</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>0.0428598924856524</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="24" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="21" t="inlineStr">
+      <c r="D20" s="24" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.1088154503019023</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.2143291056820785</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>-0.2955906584312952</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>-0.2320606108523896</v>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
+      <c r="E20" s="25" t="n">
+        <v>-0.1000497866408884</v>
+      </c>
+      <c r="F20" s="25" t="n">
+        <v>-0.1625752757792875</v>
+      </c>
+      <c r="G20" s="25" t="n">
+        <v>-0.2381455010880332</v>
+      </c>
+      <c r="H20" s="25" t="n">
+        <v>-0.4221787009784454</v>
+      </c>
+      <c r="I20" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="22" t="n">
-        <v>0.0184647467983715</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="21" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="21" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E17" s="22" t="n">
-        <v>-0.0305052146621838</v>
-      </c>
-      <c r="F17" s="22" t="n">
-        <v>-0.1039647811027634</v>
-      </c>
-      <c r="G17" s="22" t="n">
-        <v>-0.0837838083977292</v>
-      </c>
-      <c r="H17" s="22" t="n">
-        <v>-0.1681446065012396</v>
-      </c>
-      <c r="I17" s="21" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J17" s="22" t="n">
-        <v>0.0375357321501754</v>
-      </c>
-      <c r="K17" s="22" t="n">
-        <v>0.0166223768740767</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.025</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-0.009873060648801101</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-0.1547260686333533</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>-0.0144960244423122</v>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.0313929461035974</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>0.0401887662276918</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>-0.0953167931983184</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>-0.1837613817671655</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>-0.1319823680995319</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>-0.2413179433792739</v>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>0.0254782595170972</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>0.0350217789493367</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>-0.0251178144560054</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>-0.1626966669318381</v>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>-0.2097097391095529</v>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>-0.3491513513096235</v>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>0.0265476448629649</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>0.0905550350972887</v>
+      <c r="J20" s="25" t="n">
+        <v>0.0265453263368255</v>
+      </c>
+      <c r="K20" s="25" t="n">
+        <v>0.0905550690718651</v>
       </c>
     </row>
   </sheetData>
@@ -2508,7 +2672,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2516,7 +2680,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2541,7 +2705,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS</t>
+          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2717,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>THYAO.IS</t>
         </is>
       </c>
     </row>
@@ -2565,7 +2729,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, YKBNK.IS, THYAO.IS, ARCLK.IS</t>
+          <t>EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2741,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, SAHOL.IS, TCELL.IS, PGSUS.IS, PETKM.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
+          <t>SAHOL.IS, TUPRS.IS, TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2753,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2601,7 +2765,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2791,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2635,7 +2799,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2732,7 +2896,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2878,7 +3042,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2886,7 +3050,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2910,7 +3074,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11721.7001953125</v>
+        <v>11430.099609375</v>
       </c>
     </row>
     <row r="5">
@@ -2920,7 +3084,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13622.35702148438</v>
+        <v>13623.40651855469</v>
       </c>
     </row>
     <row r="6">
@@ -2954,7 +3118,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81.06</v>
+        <v>77.20999999999999</v>
       </c>
     </row>
     <row r="9">
@@ -2981,15 +3145,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -2997,7 +3161,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-15</t>
+          <t>Rapor Tarihi: 2026-10-16</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3011,7 +3175,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-19 07:02</t>
+          <t>Son Güncelleme: 2026-10-20 06:46</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3075,23 +3239,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="28" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>210.8999938964844</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.07055834465220512</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>205066.8738250425</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D4" s="28" t="n">
+        <v>204</v>
+      </c>
+      <c r="E4" s="29" t="n">
+        <v>0.03553299492385786</v>
+      </c>
+      <c r="F4" s="28" t="n">
+        <v>103271.1328843357</v>
+      </c>
+      <c r="G4" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H4" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="5">
@@ -3105,23 +3269,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="28" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>85.34999847412109</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1155440572629939</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-10146.44124932901</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D5" s="28" t="n">
+        <v>85.30000305175781</v>
+      </c>
+      <c r="E5" s="29" t="n">
+        <v>-0.1160621445413699</v>
+      </c>
+      <c r="F5" s="28" t="n">
+        <v>-10191.93681402173</v>
+      </c>
+      <c r="G5" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H5" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="6">
@@ -3135,23 +3299,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C6" s="25" t="n">
+      <c r="C6" s="28" t="n">
         <v>405.5</v>
       </c>
-      <c r="D6" s="25" t="n">
-        <v>401.5</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.009864364981504337</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-27972.56036592275</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D6" s="28" t="n">
+        <v>381</v>
+      </c>
+      <c r="E6" s="29" t="n">
+        <v>-0.06041923551171391</v>
+      </c>
+      <c r="F6" s="28" t="n">
+        <v>-171331.9322412787</v>
+      </c>
+      <c r="G6" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H6" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="7">
@@ -3165,23 +3329,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C7" s="25" t="n">
+      <c r="C7" s="28" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D7" s="25" t="n">
-        <v>70.75</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.08591733068190521</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-384659.1948204595</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D7" s="28" t="n">
+        <v>69.30000305175781</v>
+      </c>
+      <c r="E7" s="29" t="n">
+        <v>-0.1046511410133867</v>
+      </c>
+      <c r="F7" s="28" t="n">
+        <v>-468532.056568299</v>
+      </c>
+      <c r="G7" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H7" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
     <row r="8">
@@ -3195,27 +3359,57 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" s="25" t="n">
+      <c r="C8" s="28" t="n">
         <v>387</v>
       </c>
-      <c r="D8" s="25" t="n">
-        <v>384.5</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.006459948320413411</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-27894.48093186226</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>29564623.19338985</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>-0.1192206512468987</v>
+      <c r="D8" s="28" t="n">
+        <v>375.5</v>
+      </c>
+      <c r="E8" s="29" t="n">
+        <v>-0.02971576227390182</v>
+      </c>
+      <c r="F8" s="28" t="n">
+        <v>-128314.6122865686</v>
+      </c>
+      <c r="G8" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H8" s="29" t="n">
+        <v>-0.1446511824786558</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-16</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="D9" s="28" t="n">
+        <v>131.5</v>
+      </c>
+      <c r="E9" s="29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="28" t="n">
+        <v>1.862645149230957e-09</v>
+      </c>
+      <c r="G9" s="28" t="n">
+        <v>29135129.59190654</v>
+      </c>
+      <c r="H9" s="29" t="n">
+        <v>-0.1446511824786558</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H8"/>
+  <autoFilter ref="A3:H9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,13 +16,13 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PIYASA_REJIMI'!$A$3:$B$9</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$9</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'PAPER_TRADE'!$A$3:$H$8</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
   </fills>
@@ -126,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -152,7 +152,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -185,28 +185,19 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -580,14 +571,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -616,7 +607,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -633,7 +624,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -684,7 +675,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 77.21/100</t>
+          <t>Güven Puanı: 80.94/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -744,7 +735,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, BIMAS.IS, KCHOL.IS</t>
+          <t>AL: BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -761,7 +752,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: THYAO.IS</t>
+          <t>AZALT: -</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -778,7 +769,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
+          <t>ÇIK: GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -795,7 +786,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %40</t>
+          <t>NAKIT: %60</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -893,7 +884,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 3</t>
+          <t>Qualified opportunities count: 2</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -950,12 +941,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 2</t>
+          <t>Rejected opportunities count: 3</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>GARAN.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -964,25 +955,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2088152294530557</v>
+        <v>0.20384932543041</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20881.52294530557</v>
+        <v>20384.932543041</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0567878660082687</v>
+        <v>0.0190289400950367</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1185.817127066601</v>
+        <v>387.9036602028913</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>138.9676043800874</v>
+        <v>378.0597367752586</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>124.925</v>
+        <v>352.45</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.135757320165376</v>
+        <v>0.3805788019007337</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -993,12 +984,12 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %40</t>
+          <t>Cash allocation %: %60</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1007,25 +998,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2002676363786851</v>
+        <v>0.19615067456959</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20026.76363786851</v>
+        <v>19615.067456959</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0185277148899571</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>381.0880855624591</v>
+        <v>363.4223773898121</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>388.250026176209</v>
+        <v>206.6592671345725</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>361.95</v>
+        <v>192.7549942016601</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3805788019007357</v>
+        <v>0.3705542977991442</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1034,83 +1025,42 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="6" t="n">
+      <c r="A22" s="10" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="6" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C22" s="6" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D22" s="7" t="n">
-        <v>0.1909171341682591</v>
-      </c>
-      <c r="E22" s="8" t="n">
-        <v>19091.71341682591</v>
-      </c>
-      <c r="F22" s="7" t="n">
-        <v>0.0185278352337725</v>
-      </c>
-      <c r="G22" s="8" t="n">
-        <v>353.7281205173542</v>
-      </c>
-      <c r="H22" s="8" t="n">
-        <v>207.7796783876896</v>
-      </c>
-      <c r="I22" s="8" t="n">
-        <v>190.5082770636984</v>
-      </c>
-      <c r="J22" s="6" t="n">
-        <v>0.2801479400025187</v>
-      </c>
-      <c r="K22" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C23" s="10" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D23" s="11" t="n">
-        <v>0.4000000000000001</v>
-      </c>
-      <c r="E23" s="12" t="n">
-        <v>40000.00000000001</v>
-      </c>
-      <c r="F23" s="11" t="n">
+      <c r="D22" s="11" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="E22" s="12" t="n">
+        <v>60000</v>
+      </c>
+      <c r="F22" s="11" t="n">
         <v>0</v>
       </c>
-      <c r="G23" s="12" t="n">
+      <c r="G22" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="H23" s="12" t="inlineStr"/>
-      <c r="I23" s="12" t="inlineStr"/>
-      <c r="J23" s="10" t="inlineStr"/>
-      <c r="K23" s="10" t="inlineStr">
+      <c r="H22" s="12" t="inlineStr"/>
+      <c r="I22" s="12" t="inlineStr"/>
+      <c r="J22" s="10" t="inlineStr"/>
+      <c r="K22" s="10" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K23"/>
+  <autoFilter ref="A19:K22"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1121,7 +1071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O15"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1144,7 +1094,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1165,7 +1115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1207,7 +1157,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 8</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1359,28 +1309,28 @@
         </is>
       </c>
       <c r="D8" s="14" t="n">
-        <v>381</v>
+        <v>371</v>
       </c>
       <c r="E8" s="15" t="n">
-        <v>-0.0339317167690779</v>
+        <v>-0.0205581560241685</v>
       </c>
       <c r="F8" s="15" t="n">
         <v>0.0190289400950367</v>
       </c>
       <c r="G8" s="15" t="n">
-        <v>0.0770488931257379</v>
+        <v>0.06844627048378669</v>
       </c>
       <c r="H8" s="14" t="n">
-        <v>368.0720159109813</v>
+        <v>363.3729241150335</v>
       </c>
       <c r="I8" s="14" t="n">
-        <v>388.250026176209</v>
+        <v>378.0597367752586</v>
       </c>
       <c r="J8" s="14" t="n">
-        <v>410.3556282809061</v>
+        <v>396.3935663494848</v>
       </c>
       <c r="K8" s="14" t="n">
-        <v>361.95</v>
+        <v>352.45</v>
       </c>
       <c r="L8" s="13" t="inlineStr">
         <is>
@@ -1388,11 +1338,11 @@
         </is>
       </c>
       <c r="M8" s="13" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N8" s="13" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+          <t>trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="13" t="inlineStr">
@@ -1416,28 +1366,28 @@
         </is>
       </c>
       <c r="D9" s="14" t="n">
-        <v>204</v>
+        <v>202.8999938964844</v>
       </c>
       <c r="E9" s="15" t="n">
-        <v>-0.0661358967465763</v>
+        <v>-0.0302466271968858</v>
       </c>
       <c r="F9" s="15" t="n">
-        <v>0.0185278352337725</v>
+        <v>0.0185277148899571</v>
       </c>
       <c r="G9" s="15" t="n">
-        <v>0.06904386578716611</v>
+        <v>0.0466707608184535</v>
       </c>
       <c r="H9" s="14" t="n">
-        <v>190.5082770636984</v>
+        <v>196.762953422847</v>
       </c>
       <c r="I9" s="14" t="n">
-        <v>207.7796783876896</v>
+        <v>206.6592671345725</v>
       </c>
       <c r="J9" s="14" t="n">
-        <v>218.0849486205819</v>
+        <v>212.3694909816929</v>
       </c>
       <c r="K9" s="14" t="n">
-        <v>190.5082770636984</v>
+        <v>192.7549942016601</v>
       </c>
       <c r="L9" s="13" t="inlineStr">
         <is>
@@ -1445,73 +1395,73 @@
         </is>
       </c>
       <c r="M9" s="13" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
+          <t>trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="13" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D10" s="17" t="n">
+        <v>132.5</v>
+      </c>
+      <c r="E10" s="18" t="n">
+        <v>-0.0597513661055632</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.0082889988742848</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1264267348706023</v>
+      </c>
+      <c r="H10" s="17" t="n">
+        <v>124.5829439910129</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <v>131.4017076491573</v>
+      </c>
+      <c r="J10" s="17" t="n">
+        <v>149.2515423703548</v>
+      </c>
+      <c r="K10" s="17" t="n">
+        <v>124.5829439910129</v>
+      </c>
+      <c r="L10" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N10" s="16" t="inlineStr">
+        <is>
           <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="13" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="13" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="E10" s="15" t="n">
-        <v>-0.0446735031448903</v>
-      </c>
-      <c r="F10" s="15" t="n">
-        <v>0.0567878660082687</v>
-      </c>
-      <c r="G10" s="15" t="n">
-        <v>0.1240418332017574</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>125.6254343364469</v>
-      </c>
-      <c r="I10" s="14" t="n">
-        <v>138.9676043800874</v>
-      </c>
-      <c r="J10" s="14" t="n">
-        <v>147.8115010660311</v>
-      </c>
-      <c r="K10" s="14" t="n">
-        <v>124.925</v>
-      </c>
-      <c r="L10" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N10" s="13" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
+      <c r="O10" s="16" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1476,32 @@
       </c>
       <c r="C11" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>273.5</v>
+        <v>266</v>
       </c>
       <c r="E11" s="18" t="n">
-        <v>-0.0478683703056284</v>
+        <v>-0.0628618693134822</v>
       </c>
       <c r="F11" s="18" t="n">
-        <v>0.0115131578947369</v>
+        <v>-0.0241174841137557</v>
       </c>
       <c r="G11" s="18" t="n">
         <v>0.128113826384147</v>
       </c>
       <c r="H11" s="17" t="n">
-        <v>260.4080007214106</v>
+        <v>249.2787427626137</v>
       </c>
       <c r="I11" s="17" t="n">
-        <v>276.6488486842106</v>
+        <v>259.584749225741</v>
       </c>
       <c r="J11" s="17" t="n">
-        <v>308.5391315160642</v>
+        <v>300.0782778181831</v>
       </c>
       <c r="K11" s="17" t="n">
-        <v>259.825</v>
+        <v>249.2787427626137</v>
       </c>
       <c r="L11" s="16" t="inlineStr">
         <is>
@@ -1559,7 +1509,7 @@
         </is>
       </c>
       <c r="M11" s="16" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
       <c r="N11" s="16" t="inlineStr">
         <is>
@@ -1568,240 +1518,297 @@
       </c>
       <c r="O11" s="16" t="inlineStr">
         <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D12" s="17" t="n">
+        <v>36.09999847412109</v>
+      </c>
+      <c r="E12" s="18" t="n">
+        <v>-0.0432691842646411</v>
+      </c>
+      <c r="F12" s="18" t="n">
+        <v>-0.0089743807627755</v>
+      </c>
+      <c r="G12" s="18" t="n">
+        <v>0.1020406439773782</v>
+      </c>
+      <c r="H12" s="17" t="n">
+        <v>34.53798098819109</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <v>35.77602334227872</v>
+      </c>
+      <c r="J12" s="17" t="n">
+        <v>39.78366556600278</v>
+      </c>
+      <c r="K12" s="17" t="n">
+        <v>34.20459175018073</v>
+      </c>
+      <c r="L12" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N12" s="16" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O12" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D13" s="17" t="n">
+        <v>35.61999893188477</v>
+      </c>
+      <c r="E13" s="18" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F13" s="18" t="n">
+        <v>-0.0089037202852425</v>
+      </c>
+      <c r="G13" s="18" t="n">
+        <v>0.0346109210006035</v>
+      </c>
+      <c r="H13" s="17" t="n">
+        <v>33.29379571351949</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <v>35.30284842483463</v>
+      </c>
+      <c r="J13" s="17" t="n">
+        <v>36.85283990095781</v>
+      </c>
+      <c r="K13" s="17" t="n">
+        <v>33.29379571351949</v>
+      </c>
+      <c r="L13" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M13" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N13" s="16" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O13" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="17" t="n">
+        <v>96.19999694824219</v>
+      </c>
+      <c r="E14" s="18" t="n">
+        <v>-0.0435844439966387</v>
+      </c>
+      <c r="F14" s="18" t="n">
+        <v>-0.005646063733711</v>
+      </c>
+      <c r="G14" s="18" t="n">
+        <v>0.0266034411993621</v>
+      </c>
+      <c r="H14" s="17" t="n">
+        <v>92.0071735687747</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <v>95.65684563428961</v>
+      </c>
+      <c r="J14" s="17" t="n">
+        <v>98.75924791043356</v>
+      </c>
+      <c r="K14" s="17" t="n">
+        <v>91.38999710083007</v>
+      </c>
+      <c r="L14" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M14" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N14" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="16" t="inlineStr">
+        <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="16" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="16" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="20" t="n">
-        <v>36.2599983215332</v>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.0210279373987021</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>0.0338076907416818</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>33.89199923891765</v>
-      </c>
-      <c r="I12" s="20" t="n">
-        <v>35.49752534675096</v>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>37.4858651310815</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>33.89199923891765</v>
-      </c>
-      <c r="L12" s="19" t="inlineStr">
+      <c r="D15" s="17" t="n">
+        <v>72.5</v>
+      </c>
+      <c r="E15" s="18" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F15" s="18" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+      <c r="G15" s="18" t="n">
+        <v>0.0772325318535918</v>
+      </c>
+      <c r="H15" s="17" t="n">
+        <v>68.37025389707453</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <v>71.27192912967681</v>
+      </c>
+      <c r="J15" s="17" t="n">
+        <v>78.09935855938541</v>
+      </c>
+      <c r="K15" s="17" t="n">
+        <v>68.37025389707453</v>
+      </c>
+      <c r="L15" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N12" s="19" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="19" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="M15" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N15" s="16" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="16" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="16" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="20" t="n">
-        <v>66.84999847412109</v>
-      </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.0627802516039144</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>-0.012693954565347</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.06657407220854521</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>62.65313875019448</v>
-      </c>
-      <c r="I13" s="20" t="n">
-        <v>66.00140763079708</v>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>71.30047509967838</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>62.65313875019448</v>
-      </c>
-      <c r="L13" s="19" t="inlineStr">
+      <c r="D16" s="17" t="n">
+        <v>19.35000038146973</v>
+      </c>
+      <c r="E16" s="18" t="n">
+        <v>-0.1036118867092948</v>
+      </c>
+      <c r="F16" s="18" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G16" s="18" t="n">
+        <v>0.0471306356513333</v>
+      </c>
+      <c r="H16" s="17" t="n">
+        <v>17.34511033412008</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <v>19.12063686208256</v>
+      </c>
+      <c r="J16" s="17" t="n">
+        <v>20.26197819930194</v>
+      </c>
+      <c r="K16" s="17" t="n">
+        <v>17.34511033412008</v>
+      </c>
+      <c r="L16" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N13" s="19" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="19" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="20" t="n">
-        <v>75.05000305175781</v>
-      </c>
-      <c r="E14" s="21" t="n">
-        <v>-0.056962015212765</v>
-      </c>
-      <c r="F14" s="21" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-      <c r="G14" s="21" t="n">
-        <v>0.1080536875032713</v>
-      </c>
-      <c r="H14" s="20" t="n">
-        <v>70.77500363620553</v>
-      </c>
-      <c r="I14" s="20" t="n">
-        <v>73.77873310261967</v>
-      </c>
-      <c r="J14" s="20" t="n">
-        <v>83.15943262863202</v>
-      </c>
-      <c r="K14" s="20" t="n">
-        <v>70.77500363620553</v>
-      </c>
-      <c r="L14" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N14" s="19" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="19" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="19" t="n">
-        <v>14</v>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="20" t="n">
-        <v>19.70999908447266</v>
-      </c>
-      <c r="E15" s="21" t="n">
-        <v>-0.1036118867092948</v>
-      </c>
-      <c r="F15" s="21" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G15" s="21" t="n">
-        <v>0.0471306356513333</v>
-      </c>
-      <c r="H15" s="20" t="n">
-        <v>17.66780889229197</v>
-      </c>
-      <c r="I15" s="20" t="n">
-        <v>19.47636835227578</v>
-      </c>
-      <c r="J15" s="20" t="n">
-        <v>20.63894387001105</v>
-      </c>
-      <c r="K15" s="20" t="n">
-        <v>17.66780889229197</v>
-      </c>
-      <c r="L15" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="19" t="n">
-        <v>77.20999999999999</v>
-      </c>
-      <c r="N15" s="19" t="inlineStr">
+      <c r="M16" s="16" t="n">
+        <v>80.94</v>
+      </c>
+      <c r="N16" s="16" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O15" s="19" t="inlineStr">
+      <c r="O16" s="16" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O15"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1831,7 +1838,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1848,7 +1855,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1930,7 +1937,7 @@
       </c>
       <c r="C4" s="13" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D4" s="13" t="inlineStr">
@@ -1939,16 +1946,16 @@
         </is>
       </c>
       <c r="E4" s="15" t="n">
-        <v>-0.0885167464114832</v>
+        <v>-0.1161405598570577</v>
       </c>
       <c r="F4" s="15" t="n">
-        <v>-0.0246694885084334</v>
+        <v>-0.06630545471470151</v>
       </c>
       <c r="G4" s="15" t="n">
-        <v>0.0247374545953591</v>
+        <v>-0.0034836882092904</v>
       </c>
       <c r="H4" s="15" t="n">
-        <v>-0.0713714963421137</v>
+        <v>-0.06869623298648229</v>
       </c>
       <c r="I4" s="13" t="inlineStr">
         <is>
@@ -1956,7 +1963,7 @@
         </is>
       </c>
       <c r="J4" s="15" t="n">
-        <v>0.0194215259434294</v>
+        <v>0.0195645190366367</v>
       </c>
       <c r="K4" s="15" t="n">
         <v>0.0190289400950367</v>
@@ -1982,16 +1989,16 @@
         </is>
       </c>
       <c r="E5" s="15" t="n">
-        <v>-0.06721535049550589</v>
+        <v>-0.0549604248695095</v>
       </c>
       <c r="F5" s="15" t="n">
-        <v>0.0124069478908188</v>
+        <v>-0.0068527123561459</v>
       </c>
       <c r="G5" s="15" t="n">
-        <v>-0.0111488270370058</v>
+        <v>-0.0235804094480834</v>
       </c>
       <c r="H5" s="15" t="n">
-        <v>-0.1779043813425157</v>
+        <v>-0.2218187629716418</v>
       </c>
       <c r="I5" s="13" t="inlineStr">
         <is>
@@ -1999,53 +2006,53 @@
         </is>
       </c>
       <c r="J5" s="15" t="n">
-        <v>0.0212480672808465</v>
+        <v>0.0211896104248744</v>
       </c>
       <c r="K5" s="15" t="n">
-        <v>0.0185278352337725</v>
+        <v>0.0185277148899571</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="13" t="n">
+      <c r="A6" s="16" t="n">
         <v>3</v>
       </c>
-      <c r="B6" s="13" t="inlineStr">
+      <c r="B6" s="16" t="inlineStr">
         <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C6" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="13" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E6" s="15" t="n">
-        <v>-0.0075471698113207</v>
-      </c>
-      <c r="F6" s="15" t="n">
-        <v>0.0587761934873471</v>
-      </c>
-      <c r="G6" s="15" t="n">
-        <v>-0.0607142857142857</v>
-      </c>
-      <c r="H6" s="15" t="n">
-        <v>-0.2401145978594463</v>
-      </c>
-      <c r="I6" s="13" t="inlineStr">
+      <c r="C6" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D6" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E6" s="18" t="n">
+        <v>0.0200154443855289</v>
+      </c>
+      <c r="F6" s="18" t="n">
+        <v>0.052422544830267</v>
+      </c>
+      <c r="G6" s="18" t="n">
+        <v>-0.0453890699801251</v>
+      </c>
+      <c r="H6" s="18" t="n">
+        <v>-0.2655962934158726</v>
+      </c>
+      <c r="I6" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="15" t="n">
-        <v>0.0221600754600607</v>
-      </c>
-      <c r="K6" s="15" t="n">
-        <v>0.0567878660082687</v>
+      <c r="J6" s="18" t="n">
+        <v>0.022117758262729</v>
+      </c>
+      <c r="K6" s="18" t="n">
+        <v>-0.0082889988742848</v>
       </c>
     </row>
     <row r="7">
@@ -2064,20 +2071,20 @@
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>SAT</t>
         </is>
       </c>
       <c r="E7" s="18" t="n">
-        <v>-0.0544511668107173</v>
+        <v>-0.0683012259194395</v>
       </c>
       <c r="F7" s="18" t="n">
-        <v>-0.1385826771653543</v>
+        <v>-0.1713395638629283</v>
       </c>
       <c r="G7" s="18" t="n">
-        <v>-0.1558641975308642</v>
+        <v>-0.1667971808927173</v>
       </c>
       <c r="H7" s="18" t="n">
-        <v>-0.2990371871898438</v>
+        <v>-0.3045283536767756</v>
       </c>
       <c r="I7" s="16" t="inlineStr">
         <is>
@@ -2085,182 +2092,182 @@
         </is>
       </c>
       <c r="J7" s="18" t="n">
-        <v>0.0179550241285408</v>
+        <v>0.0181503837264588</v>
       </c>
       <c r="K7" s="18" t="n">
-        <v>0.0115131578947369</v>
+        <v>-0.0241174841137557</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="19" t="n">
+      <c r="A8" s="16" t="n">
         <v>5</v>
       </c>
-      <c r="B8" s="19" t="inlineStr">
+      <c r="B8" s="16" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="16" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E8" s="18" t="n">
+        <v>-0.0038632228990456</v>
+      </c>
+      <c r="F8" s="18" t="n">
+        <v>0.08931801867797361</v>
+      </c>
+      <c r="G8" s="18" t="n">
+        <v>-0.0393827377547005</v>
+      </c>
+      <c r="H8" s="18" t="n">
+        <v>-0.2810937155408158</v>
+      </c>
+      <c r="I8" s="16" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J8" s="18" t="n">
+        <v>0.0262521718013245</v>
+      </c>
+      <c r="K8" s="18" t="n">
+        <v>-0.0089743807627755</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="19" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="19" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n">
+        <v>-0.0283929575621983</v>
+      </c>
+      <c r="F9" s="20" t="n">
+        <v>-0.0398428224821392</v>
+      </c>
+      <c r="G9" s="20" t="n">
+        <v>-0.1496023424516733</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>-0.0475215182332378</v>
+      </c>
+      <c r="I9" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="20" t="n">
+        <v>0.0213113629797197</v>
+      </c>
+      <c r="K9" s="20" t="n">
+        <v>0.0125688346543615</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="16" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="16" t="inlineStr">
         <is>
           <t>EREGL.IS</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C10" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="19" t="inlineStr">
+      <c r="D10" s="16" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="21" t="n">
-        <v>0.0033203910877523</v>
-      </c>
-      <c r="F8" s="21" t="n">
-        <v>-0.1427896223278293</v>
-      </c>
-      <c r="G8" s="21" t="n">
-        <v>0.1682462518215937</v>
-      </c>
-      <c r="H8" s="21" t="n">
-        <v>-0.4166007613604728</v>
-      </c>
-      <c r="I8" s="19" t="inlineStr">
+      <c r="E10" s="18" t="n">
+        <v>-0.0219659329291974</v>
+      </c>
+      <c r="F10" s="18" t="n">
+        <v>-0.1567235436440995</v>
+      </c>
+      <c r="G10" s="18" t="n">
+        <v>0.1410975132262459</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>-0.4374885110924027</v>
+      </c>
+      <c r="I10" s="16" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J8" s="21" t="n">
-        <v>0.0238393622678929</v>
-      </c>
-      <c r="K8" s="21" t="n">
-        <v>-0.0210279373987021</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="22" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="22" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="22" t="inlineStr">
+      <c r="J10" s="18" t="n">
+        <v>0.0239188266614011</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>-0.0089037202852425</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="16" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="16" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="16" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E9" s="23" t="n">
-        <v>-0.0584988467066824</v>
-      </c>
-      <c r="F9" s="23" t="n">
-        <v>-0.035067855436785</v>
-      </c>
-      <c r="G9" s="23" t="n">
-        <v>-0.1512437507287779</v>
-      </c>
-      <c r="H9" s="23" t="n">
-        <v>-0.0469174948540891</v>
-      </c>
-      <c r="I9" s="22" t="inlineStr">
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E11" s="18" t="n">
+        <v>-0.0102880661666325</v>
+      </c>
+      <c r="F11" s="18" t="n">
+        <v>-0.1333333608266469</v>
+      </c>
+      <c r="G11" s="18" t="n">
+        <v>-0.1784799470385798</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>-0.4297401766535514</v>
+      </c>
+      <c r="I11" s="16" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="23" t="n">
-        <v>0.0213332669094879</v>
-      </c>
-      <c r="K9" s="23" t="n">
-        <v>0.0125687493441779</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="22" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="22" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E10" s="23" t="n">
-        <v>-0.0722597663968105</v>
-      </c>
-      <c r="F10" s="23" t="n">
-        <v>0.2349885919682477</v>
-      </c>
-      <c r="G10" s="23" t="n">
-        <v>0.4288934039768077</v>
-      </c>
-      <c r="H10" s="23" t="n">
-        <v>-0.2797918847497309</v>
-      </c>
-      <c r="I10" s="22" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="23" t="n">
-        <v>0.0267961516085757</v>
-      </c>
-      <c r="K10" s="23" t="n">
-        <v>0.0186683182612425</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="22" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="22" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="23" t="n">
-        <v>-0.0237014466763041</v>
-      </c>
-      <c r="F11" s="23" t="n">
-        <v>-0.1318385376523962</v>
-      </c>
-      <c r="G11" s="23" t="n">
-        <v>-0.1676698150327801</v>
-      </c>
-      <c r="H11" s="23" t="n">
-        <v>-0.3947890261345917</v>
-      </c>
-      <c r="I11" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="23" t="n">
-        <v>0.0201020435035757</v>
-      </c>
-      <c r="K11" s="23" t="n">
-        <v>0.0008189588123605</v>
+      <c r="J11" s="18" t="n">
+        <v>0.0201065650051323</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>-0.005646063733711</v>
       </c>
     </row>
     <row r="12">
@@ -2279,375 +2286,375 @@
       </c>
       <c r="D12" s="19" t="inlineStr">
         <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n">
+        <v>-0.0502121014936132</v>
+      </c>
+      <c r="F12" s="20" t="n">
+        <v>0.009015754269078699</v>
+      </c>
+      <c r="G12" s="20" t="n">
+        <v>-0.1489226840654248</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>-0.1727093423606177</v>
+      </c>
+      <c r="I12" s="19" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="20" t="n">
+        <v>0.0237856144820836</v>
+      </c>
+      <c r="K12" s="20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="19" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="19" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="19" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n">
+        <v>-0.1296752843077038</v>
+      </c>
+      <c r="F13" s="20" t="n">
+        <v>0.1574278255139025</v>
+      </c>
+      <c r="G13" s="20" t="n">
+        <v>0.3900210619989481</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>-0.2907817358936067</v>
+      </c>
+      <c r="I13" s="19" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="20" t="n">
+        <v>0.0276004494794109</v>
+      </c>
+      <c r="K13" s="20" t="n">
+        <v>0.0195381803197951</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="21" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="21" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.1210525914242393</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.1798648796241673</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>-0.3745318245039286</v>
+      </c>
+      <c r="H14" s="22" t="n">
+        <v>-0.1855480646588513</v>
+      </c>
+      <c r="I14" s="21" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="22" t="n">
+        <v>0.0184803206796285</v>
+      </c>
+      <c r="K14" s="22" t="n">
+        <v>0.020342480870896</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="23" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.0656883910156765</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>0.0022488985418591</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.1478648683922098</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.1463350037254664</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
+      <c r="E15" s="24" t="n">
+        <v>-0.1681009898953201</v>
+      </c>
+      <c r="F15" s="24" t="n">
+        <v>-0.2643328487577674</v>
+      </c>
+      <c r="G15" s="24" t="n">
+        <v>-0.3887015098417582</v>
+      </c>
+      <c r="H15" s="24" t="n">
+        <v>-0.083775766156647</v>
+      </c>
+      <c r="I15" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J12" s="21" t="n">
-        <v>0.023782163861295</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>-0.012693954565347</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="22" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="22" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="22" t="inlineStr">
+      <c r="J15" s="24" t="n">
+        <v>0.0158754109693756</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <v>-0.016938908556182</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="21" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="21" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D13" s="22" t="inlineStr">
+      <c r="D16" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="23" t="n">
-        <v>0.0107588072309898</v>
-      </c>
-      <c r="F13" s="23" t="n">
-        <v>0.08642727023240621</v>
-      </c>
-      <c r="G13" s="23" t="n">
-        <v>-0.0525477581263276</v>
-      </c>
-      <c r="H13" s="23" t="n">
-        <v>-0.2608541483895467</v>
-      </c>
-      <c r="I13" s="22" t="inlineStr">
+      <c r="E16" s="22" t="n">
+        <v>-0.1348239046908782</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.2165644359003546</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>-0.3218268992107163</v>
+      </c>
+      <c r="H16" s="22" t="n">
+        <v>-0.2941763752031232</v>
+      </c>
+      <c r="I16" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J13" s="23" t="n">
-        <v>0.0262386681832899</v>
-      </c>
-      <c r="K13" s="23" t="n">
-        <v>0.0012391857819089</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="24" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="24" t="inlineStr">
+      <c r="J16" s="22" t="n">
+        <v>0.0184980759114234</v>
+      </c>
+      <c r="K16" s="22" t="n">
+        <v>0.0147321564810616</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="23" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="24" t="inlineStr">
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n">
+        <v>-0.09748134797235231</v>
+      </c>
+      <c r="F17" s="24" t="n">
+        <v>-0.1291628722130455</v>
+      </c>
+      <c r="G17" s="24" t="n">
+        <v>-0.1204545281150124</v>
+      </c>
+      <c r="H17" s="24" t="n">
+        <v>-0.2354957719389704</v>
+      </c>
+      <c r="I17" s="23" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="24" t="n">
+        <v>0.0366080697765715</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="21" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="21" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="21" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D18" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="25" t="n">
-        <v>-0.1052291054566574</v>
-      </c>
-      <c r="F14" s="25" t="n">
-        <v>-0.1454993297703778</v>
-      </c>
-      <c r="G14" s="25" t="n">
-        <v>-0.3468425631630822</v>
-      </c>
-      <c r="H14" s="25" t="n">
-        <v>-0.184823647196279</v>
-      </c>
-      <c r="I14" s="24" t="inlineStr">
+      <c r="E18" s="22" t="n">
+        <v>-0.1739894551845342</v>
+      </c>
+      <c r="F18" s="22" t="n">
+        <v>-0.2100840336134454</v>
+      </c>
+      <c r="G18" s="22" t="n">
+        <v>-0.2140468227424748</v>
+      </c>
+      <c r="H18" s="22" t="n">
+        <v>-0.2230967507945747</v>
+      </c>
+      <c r="I18" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="25" t="n">
-        <v>0.0180080585291347</v>
-      </c>
-      <c r="K14" s="25" t="n">
-        <v>0.0417059171430678</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="26" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="26" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="26" t="inlineStr">
+      <c r="J18" s="22" t="n">
+        <v>0.0258657962097724</v>
+      </c>
+      <c r="K18" s="22" t="n">
+        <v>0.0378562161969006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="21" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="27" t="n">
-        <v>-0.163788266832782</v>
-      </c>
-      <c r="F15" s="27" t="n">
-        <v>-0.2388437706573017</v>
-      </c>
-      <c r="G15" s="27" t="n">
-        <v>-0.3629032164049853</v>
-      </c>
-      <c r="H15" s="27" t="n">
-        <v>-0.0341178763549946</v>
-      </c>
-      <c r="I15" s="26" t="inlineStr">
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="22" t="n">
+        <v>-0.1354795439302482</v>
+      </c>
+      <c r="F19" s="22" t="n">
+        <v>-0.129054054054054</v>
+      </c>
+      <c r="G19" s="22" t="n">
+        <v>-0.2267546490701859</v>
+      </c>
+      <c r="H19" s="22" t="n">
+        <v>0.0091614930640857</v>
+      </c>
+      <c r="I19" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="27" t="n">
-        <v>0.0154349832021613</v>
-      </c>
-      <c r="K15" s="27" t="n">
-        <v>-0.0169389726508262</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="J19" s="22" t="n">
+        <v>0.032041761700043</v>
+      </c>
+      <c r="K19" s="22" t="n">
+        <v>0.0248447188033209</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="21" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D20" s="21" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.1498002693552206</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.2180037075212559</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.3174773234502706</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.2911065832810884</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E20" s="22" t="n">
+        <v>-0.1039878607510293</v>
+      </c>
+      <c r="F20" s="22" t="n">
+        <v>-0.1861531208325939</v>
+      </c>
+      <c r="G20" s="22" t="n">
+        <v>-0.2542225752588232</v>
+      </c>
+      <c r="H20" s="22" t="n">
+        <v>-0.4324468295623667</v>
+      </c>
+      <c r="I20" s="21" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0184935998639454</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>0.0147321564810616</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="26" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="26" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="26" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="26" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="27" t="n">
-        <v>-0.08495829866634361</v>
-      </c>
-      <c r="F17" s="27" t="n">
-        <v>-0.07551597717622929</v>
-      </c>
-      <c r="G17" s="27" t="n">
-        <v>-0.1065276717299021</v>
-      </c>
-      <c r="H17" s="27" t="n">
-        <v>-0.2143560266767461</v>
-      </c>
-      <c r="I17" s="26" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="27" t="n">
-        <v>0.0369537734981878</v>
-      </c>
-      <c r="K17" s="27" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="24" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="25" t="n">
-        <v>-0.1040157998683344</v>
-      </c>
-      <c r="F18" s="25" t="n">
-        <v>-0.0548611111111111</v>
-      </c>
-      <c r="G18" s="25" t="n">
-        <v>-0.1736490588949605</v>
-      </c>
-      <c r="H18" s="25" t="n">
-        <v>-0.018716959054709</v>
-      </c>
-      <c r="I18" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="25" t="n">
-        <v>0.0315706199152426</v>
-      </c>
-      <c r="K18" s="25" t="n">
-        <v>0.0339372257730323</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.1484320770157339</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1853333536783854</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.1798657922936766</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.2416322795488767</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.02548291720417</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>0.0428598924856524</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="24" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="24" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="24" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="25" t="n">
-        <v>-0.1000497866408884</v>
-      </c>
-      <c r="F20" s="25" t="n">
-        <v>-0.1625752757792875</v>
-      </c>
-      <c r="G20" s="25" t="n">
-        <v>-0.2381455010880332</v>
-      </c>
-      <c r="H20" s="25" t="n">
-        <v>-0.4221787009784454</v>
-      </c>
-      <c r="I20" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="25" t="n">
-        <v>0.0265453263368255</v>
-      </c>
-      <c r="K20" s="25" t="n">
-        <v>0.0905550690718651</v>
+      <c r="J20" s="22" t="n">
+        <v>0.0265684710708643</v>
+      </c>
+      <c r="K20" s="22" t="n">
+        <v>0.0569024956991131</v>
       </c>
     </row>
   </sheetData>
@@ -2672,7 +2679,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,7 +2687,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2705,7 +2712,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS, GARAN.IS</t>
+          <t>BIMAS.IS, KCHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2717,7 +2724,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>THYAO.IS</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2729,7 +2736,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>EREGL.IS, AKBNK.IS, ARCLK.IS, PETKM.IS</t>
+          <t>GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2748,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, TUPRS.IS, TCELL.IS, YKBNK.IS, FROTO.IS, PGSUS.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
+          <t>SAHOL.IS, AKBNK.IS, TUPRS.IS, FROTO.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2760,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %1.85 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2765,7 +2772,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2798,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2799,7 +2806,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2896,7 +2903,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>INCREASED</t>
+          <t>UNCHANGED</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3049,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3050,7 +3057,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3074,7 +3081,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11430.099609375</v>
+        <v>11797.7001953125</v>
       </c>
     </row>
     <row r="5">
@@ -3084,7 +3091,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13623.40651855469</v>
+        <v>13626.08751953125</v>
       </c>
     </row>
     <row r="6">
@@ -3118,7 +3125,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>77.20999999999999</v>
+        <v>80.94</v>
       </c>
     </row>
     <row r="9">
@@ -3145,7 +3152,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -3153,7 +3160,7 @@
     <col width="18" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
@@ -3161,7 +3168,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-16</t>
+          <t>Rapor Tarihi: 2026-10-19</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3175,7 +3182,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-20 06:46</t>
+          <t>Son Güncelleme: 2026-10-21 06:41</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3239,23 +3246,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n">
+      <c r="C4" s="25" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="28" t="n">
-        <v>204</v>
-      </c>
-      <c r="E4" s="29" t="n">
-        <v>0.03553299492385786</v>
-      </c>
-      <c r="F4" s="28" t="n">
-        <v>103271.1328843357</v>
-      </c>
-      <c r="G4" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H4" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D4" s="25" t="n">
+        <v>202.8999938964844</v>
+      </c>
+      <c r="E4" s="26" t="n">
+        <v>0.02994920759636743</v>
+      </c>
+      <c r="F4" s="25" t="n">
+        <v>87042.72195722954</v>
+      </c>
+      <c r="G4" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H4" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="5">
@@ -3269,23 +3276,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n">
+      <c r="C5" s="25" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="28" t="n">
-        <v>85.30000305175781</v>
-      </c>
-      <c r="E5" s="29" t="n">
-        <v>-0.1160621445413699</v>
-      </c>
-      <c r="F5" s="28" t="n">
-        <v>-10191.93681402173</v>
-      </c>
-      <c r="G5" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H5" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D5" s="25" t="n">
+        <v>85.55000305175781</v>
+      </c>
+      <c r="E5" s="26" t="n">
+        <v>-0.1134714709662403</v>
+      </c>
+      <c r="F5" s="25" t="n">
+        <v>-9964.438162434555</v>
+      </c>
+      <c r="G5" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H5" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="6">
@@ -3299,23 +3306,23 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="C6" s="28" t="n">
+      <c r="C6" s="25" t="n">
         <v>405.5</v>
       </c>
-      <c r="D6" s="28" t="n">
-        <v>381</v>
-      </c>
-      <c r="E6" s="29" t="n">
-        <v>-0.06041923551171391</v>
-      </c>
-      <c r="F6" s="28" t="n">
-        <v>-171331.9322412787</v>
-      </c>
-      <c r="G6" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H6" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D6" s="25" t="n">
+        <v>371</v>
+      </c>
+      <c r="E6" s="26" t="n">
+        <v>-0.0850801479654747</v>
+      </c>
+      <c r="F6" s="25" t="n">
+        <v>-241263.333156086</v>
+      </c>
+      <c r="G6" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H6" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="7">
@@ -3329,23 +3336,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n">
+      <c r="C7" s="25" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D7" s="28" t="n">
-        <v>69.30000305175781</v>
-      </c>
-      <c r="E7" s="29" t="n">
-        <v>-0.1046511410133867</v>
-      </c>
-      <c r="F7" s="28" t="n">
-        <v>-468532.056568299</v>
-      </c>
-      <c r="G7" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H7" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D7" s="25" t="n">
+        <v>66.80000305175781</v>
+      </c>
+      <c r="E7" s="26" t="n">
+        <v>-0.1369508819786903</v>
+      </c>
+      <c r="F7" s="25" t="n">
+        <v>-613140.7432443597</v>
+      </c>
+      <c r="G7" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H7" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
     <row r="8">
@@ -3359,57 +3366,27 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="25" t="n">
         <v>387</v>
       </c>
-      <c r="D8" s="28" t="n">
-        <v>375.5</v>
-      </c>
-      <c r="E8" s="29" t="n">
-        <v>-0.02971576227390182</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-128314.6122865686</v>
-      </c>
-      <c r="G8" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H8" s="29" t="n">
-        <v>-0.1446511824786558</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-16</t>
-        </is>
-      </c>
-      <c r="C9" s="28" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="D9" s="28" t="n">
-        <v>131.5</v>
-      </c>
-      <c r="E9" s="29" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="28" t="n">
-        <v>1.862645149230957e-09</v>
-      </c>
-      <c r="G9" s="28" t="n">
-        <v>29135129.59190654</v>
-      </c>
-      <c r="H9" s="29" t="n">
-        <v>-0.1446511824786558</v>
+      <c r="D8" s="25" t="n">
+        <v>356.75</v>
+      </c>
+      <c r="E8" s="26" t="n">
+        <v>-0.07816537467700257</v>
+      </c>
+      <c r="F8" s="25" t="n">
+        <v>-337523.2192755393</v>
+      </c>
+      <c r="G8" s="25" t="n">
+        <v>28810856.79717723</v>
+      </c>
+      <c r="H8" s="26" t="n">
+        <v>-0.1659296840794658</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A3:H9"/>
+  <autoFilter ref="A3:H8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -16,8 +16,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PAPER_TRADE" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$22</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -62,7 +62,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -99,6 +99,11 @@
         <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FCE4D6"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -126,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -153,6 +158,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -571,14 +579,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
@@ -607,7 +615,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -624,7 +632,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -675,7 +683,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.94/100</t>
+          <t>Güven Puanı: 81.03/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -735,7 +743,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: BIMAS.IS, KCHOL.IS</t>
+          <t>AL: GARAN.IS, KCHOL.IS, SAHOL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +777,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
+          <t>ÇIK: BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -786,7 +794,7 @@
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>NAKIT: %60</t>
+          <t>NAKIT: %40</t>
         </is>
       </c>
       <c r="B13" s="2" t="n"/>
@@ -884,7 +892,7 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>Qualified opportunities count: 2</t>
+          <t>Qualified opportunities count: 3</t>
         </is>
       </c>
       <c r="B19" s="5" t="inlineStr">
@@ -941,12 +949,12 @@
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
         <is>
-          <t>Rejected opportunities count: 3</t>
+          <t>Rejected opportunities count: 2</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
@@ -955,25 +963,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.20384932543041</v>
+        <v>0.2225985965411588</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>20384.932543041</v>
+        <v>22259.85965411588</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0190289400950367</v>
+        <v>0.0567878719657279</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>387.9036602028913</v>
+        <v>1264.090060013005</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>378.0597367752586</v>
+        <v>142.2436540167083</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>352.45</v>
+        <v>125.881001496126</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.3805788019007337</v>
+        <v>0.8766651994557298</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -984,7 +992,7 @@
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
         <is>
-          <t>Cash allocation %: %60</t>
+          <t>Cash allocation %: %40</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
@@ -998,25 +1006,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.19615067456959</v>
+        <v>0.2095677741579692</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>19615.067456959</v>
+        <v>20956.77741579692</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0185277148899571</v>
+        <v>0.0232680790823229</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>363.4223773898121</v>
+        <v>487.6239542214013</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>206.6592671345725</v>
+        <v>213.2490614352234</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>192.7549942016601</v>
+        <v>197.9799942016601</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705542977991442</v>
+        <v>0.4653615816464596</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1025,42 +1033,83 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="10" t="n">
+      <c r="A22" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="n">
+        <v>0.167833629300872</v>
+      </c>
+      <c r="E22" s="8" t="n">
+        <v>16783.3629300872</v>
+      </c>
+      <c r="F22" s="7" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>131.2886437451299</v>
+      </c>
+      <c r="H22" s="8" t="n">
+        <v>89.89776810830038</v>
+      </c>
+      <c r="I22" s="8" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="J22" s="6" t="n">
+        <v>0.1004971927995564</v>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="B23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="C22" s="10" t="inlineStr">
+      <c r="C23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
-      <c r="D22" s="11" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="E22" s="12" t="n">
-        <v>60000</v>
-      </c>
-      <c r="F22" s="11" t="n">
+      <c r="D23" s="12" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>40000</v>
+      </c>
+      <c r="F23" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="G22" s="12" t="n">
+      <c r="G23" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H22" s="12" t="inlineStr"/>
-      <c r="I22" s="12" t="inlineStr"/>
-      <c r="J22" s="10" t="inlineStr"/>
-      <c r="K22" s="10" t="inlineStr">
+      <c r="H23" s="13" t="inlineStr"/>
+      <c r="I23" s="13" t="inlineStr"/>
+      <c r="J23" s="11" t="inlineStr"/>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>CASH</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A19:K22"/>
+  <autoFilter ref="A19:K23"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1071,7 +1120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1094,7 +1143,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1115,7 +1164,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1157,7 +1206,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 9</t>
+          <t>Toplam önerilen/satılacak satır: 10</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1295,520 +1344,577 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="13" t="n">
+      <c r="A8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="13" t="inlineStr">
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>-0.0302466271968858</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>0.0914169657590902</v>
+      </c>
+      <c r="H8" s="15" t="n">
+        <v>202.0965969732642</v>
+      </c>
+      <c r="I8" s="15" t="n">
+        <v>213.2490614352234</v>
+      </c>
+      <c r="J8" s="15" t="n">
+        <v>227.4512890027139</v>
+      </c>
+      <c r="K8" s="15" t="n">
+        <v>197.9799942016601</v>
+      </c>
+      <c r="L8" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M8" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N8" s="14" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O8" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C8" s="13" t="inlineStr">
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>385.5</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.0475400966137377</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>-0.0036968334151564</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0383027129081878</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>367.1732927554041</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>384.0748707184572</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>400.2656958261064</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>366.225</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>371</v>
-      </c>
-      <c r="E8" s="15" t="n">
-        <v>-0.0205581560241685</v>
-      </c>
-      <c r="F8" s="15" t="n">
-        <v>0.0190289400950367</v>
-      </c>
-      <c r="G8" s="15" t="n">
-        <v>0.06844627048378669</v>
-      </c>
-      <c r="H8" s="14" t="n">
-        <v>363.3729241150335</v>
-      </c>
-      <c r="I8" s="14" t="n">
-        <v>378.0597367752586</v>
-      </c>
-      <c r="J8" s="14" t="n">
-        <v>396.3935663494848</v>
-      </c>
-      <c r="K8" s="14" t="n">
-        <v>352.45</v>
-      </c>
-      <c r="L8" s="13" t="inlineStr">
+      <c r="D10" s="15" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="E10" s="16" t="n">
+        <v>-0.06477714867772109</v>
+      </c>
+      <c r="F10" s="16" t="n">
+        <v>0.0567878719657279</v>
+      </c>
+      <c r="G10" s="16" t="n">
+        <v>0.1272216922975995</v>
+      </c>
+      <c r="H10" s="15" t="n">
+        <v>125.881001496126</v>
+      </c>
+      <c r="I10" s="15" t="n">
+        <v>142.2436540167083</v>
+      </c>
+      <c r="J10" s="15" t="n">
+        <v>151.7240466632721</v>
+      </c>
+      <c r="K10" s="15" t="n">
+        <v>125.881001496126</v>
+      </c>
+      <c r="L10" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M8" s="13" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N8" s="13" t="inlineStr">
-        <is>
-          <t>trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O8" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B9" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="13" t="inlineStr">
+      <c r="M10" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N10" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="14" t="inlineStr">
+        <is>
+          <t>alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D11" s="18" t="n">
+        <v>273.5</v>
+      </c>
+      <c r="E11" s="19" t="n">
+        <v>-0.0621242939763079</v>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+      <c r="G11" s="19" t="n">
+        <v>0.0948783870299643</v>
+      </c>
+      <c r="H11" s="18" t="n">
+        <v>256.5090055974798</v>
+      </c>
+      <c r="I11" s="18" t="n">
+        <v>269.6613787891161</v>
+      </c>
+      <c r="J11" s="18" t="n">
+        <v>299.4492388526953</v>
+      </c>
+      <c r="K11" s="18" t="n">
+        <v>256.5090055974798</v>
+      </c>
+      <c r="L11" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M11" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N11" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
-        <v>202.8999938964844</v>
-      </c>
-      <c r="E9" s="15" t="n">
-        <v>-0.0302466271968858</v>
-      </c>
-      <c r="F9" s="15" t="n">
-        <v>0.0185277148899571</v>
-      </c>
-      <c r="G9" s="15" t="n">
-        <v>0.0466707608184535</v>
-      </c>
-      <c r="H9" s="14" t="n">
-        <v>196.762953422847</v>
-      </c>
-      <c r="I9" s="14" t="n">
-        <v>206.6592671345725</v>
-      </c>
-      <c r="J9" s="14" t="n">
-        <v>212.3694909816929</v>
-      </c>
-      <c r="K9" s="14" t="n">
-        <v>192.7549942016601</v>
-      </c>
-      <c r="L9" s="13" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M9" s="13" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N9" s="13" t="inlineStr">
-        <is>
-          <t>trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="13" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="D12" s="15" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.0778384618230588</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.093714156045322</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>89.89776810830038</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>97.55929938149201</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>82.25680639116948</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="14" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
-        <v>132.5</v>
-      </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0597513661055632</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1264267348706023</v>
-      </c>
-      <c r="H10" s="17" t="n">
-        <v>124.5829439910129</v>
-      </c>
-      <c r="I10" s="17" t="n">
-        <v>131.4017076491573</v>
-      </c>
-      <c r="J10" s="17" t="n">
-        <v>149.2515423703548</v>
-      </c>
-      <c r="K10" s="17" t="n">
-        <v>124.5829439910129</v>
-      </c>
-      <c r="L10" s="16" t="inlineStr">
+      <c r="D13" s="18" t="n">
+        <v>36.65999984741211</v>
+      </c>
+      <c r="E13" s="19" t="n">
+        <v>-0.053387959227386</v>
+      </c>
+      <c r="F13" s="19" t="n">
+        <v>-0.0095238211722357</v>
+      </c>
+      <c r="G13" s="19" t="n">
+        <v>0.0919879432419712</v>
+      </c>
+      <c r="H13" s="18" t="n">
+        <v>34.7027972702825</v>
+      </c>
+      <c r="I13" s="18" t="n">
+        <v>36.31085656469117</v>
+      </c>
+      <c r="J13" s="18" t="n">
+        <v>40.03227783262653</v>
+      </c>
+      <c r="K13" s="18" t="n">
+        <v>34.7027972702825</v>
+      </c>
+      <c r="L13" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M10" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N10" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="16" t="inlineStr">
+      <c r="M13" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N13" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O13" s="17" t="inlineStr">
         <is>
           <t>alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B14" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
-        <v>266</v>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0628618693134822</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>0.128113826384147</v>
-      </c>
-      <c r="H11" s="17" t="n">
-        <v>249.2787427626137</v>
-      </c>
-      <c r="I11" s="17" t="n">
-        <v>259.584749225741</v>
-      </c>
-      <c r="J11" s="17" t="n">
-        <v>300.0782778181831</v>
-      </c>
-      <c r="K11" s="17" t="n">
-        <v>249.2787427626137</v>
-      </c>
-      <c r="L11" s="16" t="inlineStr">
+      <c r="D14" s="18" t="n">
+        <v>37.18000030517578</v>
+      </c>
+      <c r="E14" s="19" t="n">
+        <v>-0.0653061001718057</v>
+      </c>
+      <c r="F14" s="19" t="n">
+        <v>-0.0210280210184544</v>
+      </c>
+      <c r="G14" s="19" t="n">
+        <v>0.0345194815014007</v>
+      </c>
+      <c r="H14" s="18" t="n">
+        <v>34.75191948085821</v>
+      </c>
+      <c r="I14" s="18" t="n">
+        <v>36.3981784772924</v>
+      </c>
+      <c r="J14" s="18" t="n">
+        <v>38.46343463793237</v>
+      </c>
+      <c r="K14" s="18" t="n">
+        <v>34.75191948085821</v>
+      </c>
+      <c r="L14" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N11" s="16" t="inlineStr">
+      <c r="M14" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N14" s="17" t="inlineStr">
+        <is>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="17" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="n">
+        <v>132</v>
+      </c>
+      <c r="E15" s="19" t="n">
+        <v>-0.0759511873012769</v>
+      </c>
+      <c r="F15" s="19" t="n">
+        <v>-0.0097276264591439</v>
+      </c>
+      <c r="G15" s="19" t="n">
+        <v>0.1305235121113319</v>
+      </c>
+      <c r="H15" s="18" t="n">
+        <v>121.9744432762314</v>
+      </c>
+      <c r="I15" s="18" t="n">
+        <v>130.715953307393</v>
+      </c>
+      <c r="J15" s="18" t="n">
+        <v>149.2291035986958</v>
+      </c>
+      <c r="K15" s="18" t="n">
+        <v>121.9744432762314</v>
+      </c>
+      <c r="L15" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M15" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N15" s="17" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O11" s="16" t="inlineStr">
+      <c r="O15" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="16" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="16" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D12" s="17" t="n">
-        <v>36.09999847412109</v>
-      </c>
-      <c r="E12" s="18" t="n">
-        <v>-0.0432691842646411</v>
-      </c>
-      <c r="F12" s="18" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-      <c r="G12" s="18" t="n">
-        <v>0.1020406439773782</v>
-      </c>
-      <c r="H12" s="17" t="n">
-        <v>34.53798098819109</v>
-      </c>
-      <c r="I12" s="17" t="n">
-        <v>35.77602334227872</v>
-      </c>
-      <c r="J12" s="17" t="n">
-        <v>39.78366556600278</v>
-      </c>
-      <c r="K12" s="17" t="n">
-        <v>34.20459175018073</v>
-      </c>
-      <c r="L12" s="16" t="inlineStr">
+      <c r="D16" s="18" t="n">
+        <v>342.75</v>
+      </c>
+      <c r="E16" s="19" t="n">
+        <v>-0.110731767703003</v>
+      </c>
+      <c r="F16" s="19" t="n">
+        <v>-0.0588766952961986</v>
+      </c>
+      <c r="G16" s="19" t="n">
+        <v>0.0478184256278046</v>
+      </c>
+      <c r="H16" s="18" t="n">
+        <v>304.7966866197957</v>
+      </c>
+      <c r="I16" s="18" t="n">
+        <v>322.570012687228</v>
+      </c>
+      <c r="J16" s="18" t="n">
+        <v>359.1397653839301</v>
+      </c>
+      <c r="K16" s="18" t="n">
+        <v>304.7966866197957</v>
+      </c>
+      <c r="L16" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N12" s="16" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O12" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="16" t="inlineStr">
+      <c r="M16" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N16" s="17" t="inlineStr">
+        <is>
+          <t>hacim artışı var</t>
+        </is>
+      </c>
+      <c r="O16" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="17" t="n">
-        <v>35.61999893188477</v>
-      </c>
-      <c r="E13" s="18" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F13" s="18" t="n">
-        <v>-0.0089037202852425</v>
-      </c>
-      <c r="G13" s="18" t="n">
-        <v>0.0346109210006035</v>
-      </c>
-      <c r="H13" s="17" t="n">
-        <v>33.29379571351949</v>
-      </c>
-      <c r="I13" s="17" t="n">
-        <v>35.30284842483463</v>
-      </c>
-      <c r="J13" s="17" t="n">
-        <v>36.85283990095781</v>
-      </c>
-      <c r="K13" s="17" t="n">
-        <v>33.29379571351949</v>
-      </c>
-      <c r="L13" s="16" t="inlineStr">
+      <c r="D17" s="18" t="n">
+        <v>19.60000038146973</v>
+      </c>
+      <c r="E17" s="19" t="n">
+        <v>-0.0502792716997244</v>
+      </c>
+      <c r="F17" s="19" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+      <c r="G17" s="19" t="n">
+        <v>0.0113636098814375</v>
+      </c>
+      <c r="H17" s="18" t="n">
+        <v>18.61452663697511</v>
+      </c>
+      <c r="I17" s="18" t="n">
+        <v>19.36767350917732</v>
+      </c>
+      <c r="J17" s="18" t="n">
+        <v>19.82272713948078</v>
+      </c>
+      <c r="K17" s="18" t="n">
+        <v>18.16560873150732</v>
+      </c>
+      <c r="L17" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N13" s="16" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O13" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D14" s="17" t="n">
-        <v>96.19999694824219</v>
-      </c>
-      <c r="E14" s="18" t="n">
-        <v>-0.0435844439966387</v>
-      </c>
-      <c r="F14" s="18" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-      <c r="G14" s="18" t="n">
-        <v>0.0266034411993621</v>
-      </c>
-      <c r="H14" s="17" t="n">
-        <v>92.0071735687747</v>
-      </c>
-      <c r="I14" s="17" t="n">
-        <v>95.65684563428961</v>
-      </c>
-      <c r="J14" s="17" t="n">
-        <v>98.75924791043356</v>
-      </c>
-      <c r="K14" s="17" t="n">
-        <v>91.38999710083007</v>
-      </c>
-      <c r="L14" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M14" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N14" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="16" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="16" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="17" t="n">
-        <v>72.5</v>
-      </c>
-      <c r="E15" s="18" t="n">
-        <v>-0.056962015212765</v>
-      </c>
-      <c r="F15" s="18" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-      <c r="G15" s="18" t="n">
-        <v>0.0772325318535918</v>
-      </c>
-      <c r="H15" s="17" t="n">
-        <v>68.37025389707453</v>
-      </c>
-      <c r="I15" s="17" t="n">
-        <v>71.27192912967681</v>
-      </c>
-      <c r="J15" s="17" t="n">
-        <v>78.09935855938541</v>
-      </c>
-      <c r="K15" s="17" t="n">
-        <v>68.37025389707453</v>
-      </c>
-      <c r="L15" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N15" s="16" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="16" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="16" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="16" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="17" t="n">
-        <v>19.35000038146973</v>
-      </c>
-      <c r="E16" s="18" t="n">
-        <v>-0.1036118867092948</v>
-      </c>
-      <c r="F16" s="18" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G16" s="18" t="n">
-        <v>0.0471306356513333</v>
-      </c>
-      <c r="H16" s="17" t="n">
-        <v>17.34511033412008</v>
-      </c>
-      <c r="I16" s="17" t="n">
-        <v>19.12063686208256</v>
-      </c>
-      <c r="J16" s="17" t="n">
-        <v>20.26197819930194</v>
-      </c>
-      <c r="K16" s="17" t="n">
-        <v>17.34511033412008</v>
-      </c>
-      <c r="L16" s="16" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="16" t="n">
-        <v>80.94</v>
-      </c>
-      <c r="N16" s="16" t="inlineStr">
+      <c r="M17" s="17" t="n">
+        <v>81.03</v>
+      </c>
+      <c r="N17" s="17" t="inlineStr">
         <is>
           <t>Model skoru portföy için yeterli</t>
         </is>
       </c>
-      <c r="O16" s="16" t="inlineStr">
+      <c r="O17" s="17" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A7:O16"/>
+  <autoFilter ref="A7:O17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1838,7 +1944,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1855,7 +1961,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1927,734 +2033,734 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="13" t="n">
+      <c r="A4" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="13" t="inlineStr">
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>KCHOL.IS</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E4" s="16" t="n">
+        <v>-0.0625281554856169</v>
+      </c>
+      <c r="F4" s="16" t="n">
+        <v>0.0514631539116814</v>
+      </c>
+      <c r="G4" s="16" t="n">
+        <v>0.0190708747994345</v>
+      </c>
+      <c r="H4" s="16" t="n">
+        <v>-0.2313857694396462</v>
+      </c>
+      <c r="I4" s="14" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J4" s="16" t="n">
+        <v>0.0211053561538639</v>
+      </c>
+      <c r="K4" s="16" t="n">
+        <v>0.0232680790823229</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="B5" s="17" t="inlineStr">
         <is>
           <t>BIMAS.IS</t>
         </is>
       </c>
-      <c r="C4" s="13" t="inlineStr">
+      <c r="C5" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D4" s="13" t="inlineStr">
+      <c r="D5" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.1096997690531177</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>-0.0068319270468597</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>0.0451798027804024</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.0900637285735935</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.0199896884255374</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>-0.0036968334151564</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="14" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="14" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="14" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E4" s="15" t="n">
-        <v>-0.1161405598570577</v>
-      </c>
-      <c r="F4" s="15" t="n">
-        <v>-0.06630545471470151</v>
-      </c>
-      <c r="G4" s="15" t="n">
-        <v>-0.0034836882092904</v>
-      </c>
-      <c r="H4" s="15" t="n">
-        <v>-0.06869623298648229</v>
-      </c>
-      <c r="I4" s="13" t="inlineStr">
+      <c r="E6" s="16" t="n">
+        <v>0.0112697214967323</v>
+      </c>
+      <c r="F6" s="16" t="n">
+        <v>0.07680004882812499</v>
+      </c>
+      <c r="G6" s="16" t="n">
+        <v>-0.0175182036239734</v>
+      </c>
+      <c r="H6" s="16" t="n">
+        <v>-0.2872987491383497</v>
+      </c>
+      <c r="I6" s="14" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J4" s="15" t="n">
-        <v>0.0195645190366367</v>
-      </c>
-      <c r="K4" s="15" t="n">
-        <v>0.0190289400950367</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="13" t="n">
-        <v>2</v>
-      </c>
-      <c r="B5" s="13" t="inlineStr">
-        <is>
-          <t>KCHOL.IS</t>
-        </is>
-      </c>
-      <c r="C5" s="13" t="inlineStr">
+      <c r="J6" s="16" t="n">
+        <v>0.0221699973140994</v>
+      </c>
+      <c r="K6" s="16" t="n">
+        <v>0.0567878719657279</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="17" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="17" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D5" s="13" t="inlineStr">
+      <c r="D7" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E7" s="19" t="n">
+        <v>-0.06814310051107331</v>
+      </c>
+      <c r="F7" s="19" t="n">
+        <v>-0.1254996003197441</v>
+      </c>
+      <c r="G7" s="19" t="n">
+        <v>-0.1379038613081166</v>
+      </c>
+      <c r="H7" s="19" t="n">
+        <v>-0.3211878254901774</v>
+      </c>
+      <c r="I7" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J7" s="19" t="n">
+        <v>0.0183237247160637</v>
+      </c>
+      <c r="K7" s="19" t="n">
+        <v>-0.0140351781019522</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="14" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="14" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E5" s="15" t="n">
-        <v>-0.0549604248695095</v>
-      </c>
-      <c r="F5" s="15" t="n">
-        <v>-0.0068527123561459</v>
-      </c>
-      <c r="G5" s="15" t="n">
-        <v>-0.0235804094480834</v>
-      </c>
-      <c r="H5" s="15" t="n">
-        <v>-0.2218187629716418</v>
-      </c>
-      <c r="I5" s="13" t="inlineStr">
+      <c r="E8" s="16" t="n">
+        <v>-0.0149089570184107</v>
+      </c>
+      <c r="F8" s="16" t="n">
+        <v>0.0142126213004374</v>
+      </c>
+      <c r="G8" s="16" t="n">
+        <v>-0.1035176186106312</v>
+      </c>
+      <c r="H8" s="16" t="n">
+        <v>-0.0581451764026649</v>
+      </c>
+      <c r="I8" s="14" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="16" t="n">
+        <v>0.0219273868966153</v>
+      </c>
+      <c r="K8" s="16" t="n">
+        <v>0.007822546905052701</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="17" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="17" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="17" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>0.0021869330878356</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.1022249458045725</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>-0.0218783272369083</v>
+      </c>
+      <c r="H9" s="19" t="n">
+        <v>-0.2972354995612898</v>
+      </c>
+      <c r="I9" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="15" t="n">
-        <v>0.0211896104248744</v>
-      </c>
-      <c r="K5" s="15" t="n">
-        <v>0.0185277148899571</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="16" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
+      <c r="J9" s="19" t="n">
+        <v>0.0263089279639388</v>
+      </c>
+      <c r="K9" s="19" t="n">
+        <v>-0.0095238211722357</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D6" s="16" t="inlineStr">
+      <c r="D10" s="17" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
-        <v>0.0200154443855289</v>
-      </c>
-      <c r="F6" s="18" t="n">
-        <v>0.052422544830267</v>
-      </c>
-      <c r="G6" s="18" t="n">
-        <v>-0.0453890699801251</v>
-      </c>
-      <c r="H6" s="18" t="n">
-        <v>-0.2655962934158726</v>
-      </c>
-      <c r="I6" s="16" t="inlineStr">
+      <c r="E10" s="19" t="n">
+        <v>-0.005350475046135</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>-0.158823537026944</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.2195967321886922</v>
+      </c>
+      <c r="H10" s="19" t="n">
+        <v>-0.4672271139985361</v>
+      </c>
+      <c r="I10" s="17" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="18" t="n">
-        <v>0.022117758262729</v>
-      </c>
-      <c r="K6" s="18" t="n">
-        <v>-0.0082889988742848</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="16" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
+      <c r="J10" s="19" t="n">
+        <v>0.0238351539109441</v>
+      </c>
+      <c r="K10" s="19" t="n">
+        <v>-0.0210280210184544</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="16" t="inlineStr">
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="21" t="n">
+        <v>-0.0225225221785121</v>
+      </c>
+      <c r="F11" s="21" t="n">
+        <v>-0.06999998546781989</v>
+      </c>
+      <c r="G11" s="21" t="n">
+        <v>-0.1675191902357281</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>-0.4414806906738988</v>
+      </c>
+      <c r="I11" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>0.019083963827017</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>0.0139752661812804</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="20" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="21" t="n">
+        <v>-0.1196778060214621</v>
+      </c>
+      <c r="F12" s="21" t="n">
+        <v>-0.2272727272727273</v>
+      </c>
+      <c r="G12" s="21" t="n">
+        <v>-0.3405172413793104</v>
+      </c>
+      <c r="H12" s="21" t="n">
+        <v>-0.08619076076584919</v>
+      </c>
+      <c r="I12" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J12" s="21" t="n">
+        <v>0.0175460603555207</v>
+      </c>
+      <c r="K12" s="21" t="n">
+        <v>0.0318628326773948</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C13" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E13" s="21" t="n">
+        <v>-0.1115441285294764</v>
+      </c>
+      <c r="F13" s="21" t="n">
+        <v>0.1716600104443737</v>
+      </c>
+      <c r="G13" s="21" t="n">
+        <v>0.3749516646374315</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>-0.3150624841004493</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>0.0276418940598797</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>0.0195382818194833</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="22" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="22" t="inlineStr">
+        <is>
+          <t>AKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D14" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="n">
+        <v>-0.0572808015361147</v>
+      </c>
+      <c r="F14" s="23" t="n">
+        <v>0.0186428030291823</v>
+      </c>
+      <c r="G14" s="23" t="n">
+        <v>-0.1254800974882294</v>
+      </c>
+      <c r="H14" s="23" t="n">
+        <v>-0.1873317437379973</v>
+      </c>
+      <c r="I14" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="23" t="n">
+        <v>0.0238625739044733</v>
+      </c>
+      <c r="K14" s="23" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="22" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="22" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="22" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="n">
+        <v>-0.1207450444460015</v>
+      </c>
+      <c r="F15" s="23" t="n">
+        <v>-0.13790937490181</v>
+      </c>
+      <c r="G15" s="23" t="n">
+        <v>-0.3536355433241898</v>
+      </c>
+      <c r="H15" s="23" t="n">
+        <v>-0.201379322000936</v>
+      </c>
+      <c r="I15" s="22" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="23" t="n">
+        <v>0.0185820899062162</v>
+      </c>
+      <c r="K15" s="23" t="n">
+        <v>0.0758986426936193</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="24" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="24" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D16" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
-        <v>-0.0683012259194395</v>
-      </c>
-      <c r="F7" s="18" t="n">
-        <v>-0.1713395638629283</v>
-      </c>
-      <c r="G7" s="18" t="n">
-        <v>-0.1667971808927173</v>
-      </c>
-      <c r="H7" s="18" t="n">
-        <v>-0.3045283536767756</v>
-      </c>
-      <c r="I7" s="16" t="inlineStr">
+      <c r="E16" s="25" t="n">
+        <v>-0.1269841093635378</v>
+      </c>
+      <c r="F16" s="25" t="n">
+        <v>-0.1770573252939933</v>
+      </c>
+      <c r="G16" s="25" t="n">
+        <v>-0.2903225806451612</v>
+      </c>
+      <c r="H16" s="25" t="n">
+        <v>-0.3213083269485385</v>
+      </c>
+      <c r="I16" s="24" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="18" t="n">
-        <v>0.0181503837264588</v>
-      </c>
-      <c r="K7" s="18" t="n">
-        <v>-0.0241174841137557</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="16" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="16" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="16" t="inlineStr">
+      <c r="J16" s="25" t="n">
+        <v>0.0190171517281646</v>
+      </c>
+      <c r="K16" s="25" t="n">
+        <v>-0.0097276264591439</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="24" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="16" t="inlineStr">
+      <c r="D17" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
-        <v>-0.0038632228990456</v>
-      </c>
-      <c r="F8" s="18" t="n">
-        <v>0.08931801867797361</v>
-      </c>
-      <c r="G8" s="18" t="n">
-        <v>-0.0393827377547005</v>
-      </c>
-      <c r="H8" s="18" t="n">
-        <v>-0.2810937155408158</v>
-      </c>
-      <c r="I8" s="16" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J8" s="18" t="n">
-        <v>0.0262521718013245</v>
-      </c>
-      <c r="K8" s="18" t="n">
-        <v>-0.0089743807627755</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="19" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="19" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="E17" s="25" t="n">
+        <v>-0.0932539682539682</v>
+      </c>
+      <c r="F17" s="25" t="n">
+        <v>-0.08903654485049831</v>
+      </c>
+      <c r="G17" s="25" t="n">
+        <v>-0.166058394160584</v>
+      </c>
+      <c r="H17" s="25" t="n">
+        <v>0.0228223229737185</v>
+      </c>
+      <c r="I17" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J17" s="25" t="n">
+        <v>0.0330049754383154</v>
+      </c>
+      <c r="K17" s="25" t="n">
+        <v>-0.0588766952961986</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="22" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="22" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D18" s="22" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E9" s="20" t="n">
-        <v>-0.0283929575621983</v>
-      </c>
-      <c r="F9" s="20" t="n">
-        <v>-0.0398428224821392</v>
-      </c>
-      <c r="G9" s="20" t="n">
-        <v>-0.1496023424516733</v>
-      </c>
-      <c r="H9" s="20" t="n">
-        <v>-0.0475215182332378</v>
-      </c>
-      <c r="I9" s="19" t="inlineStr">
+      <c r="E18" s="23" t="n">
+        <v>-0.1803448381095097</v>
+      </c>
+      <c r="F18" s="23" t="n">
+        <v>-0.1696069975607259</v>
+      </c>
+      <c r="G18" s="23" t="n">
+        <v>-0.1753686142298622</v>
+      </c>
+      <c r="H18" s="23" t="n">
+        <v>-0.2029227843381598</v>
+      </c>
+      <c r="I18" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J9" s="20" t="n">
-        <v>0.0213113629797197</v>
-      </c>
-      <c r="K9" s="20" t="n">
-        <v>0.0125688346543615</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="16" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="16" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="16" t="inlineStr">
+      <c r="J18" s="23" t="n">
+        <v>0.0255519291609806</v>
+      </c>
+      <c r="K18" s="23" t="n">
+        <v>0.0378562161969006</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="24" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="24" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="16" t="inlineStr">
+      <c r="D19" s="24" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E10" s="18" t="n">
-        <v>-0.0219659329291974</v>
-      </c>
-      <c r="F10" s="18" t="n">
-        <v>-0.1567235436440995</v>
-      </c>
-      <c r="G10" s="18" t="n">
-        <v>0.1410975132262459</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>-0.4374885110924027</v>
-      </c>
-      <c r="I10" s="16" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>0.0239188266614011</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>-0.0089037202852425</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="16" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="16" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="16" t="inlineStr">
+      <c r="E19" s="25" t="n">
+        <v>-0.0798121557034113</v>
+      </c>
+      <c r="F19" s="25" t="n">
+        <v>-0.1312056362829798</v>
+      </c>
+      <c r="G19" s="25" t="n">
+        <v>-0.1358024639445516</v>
+      </c>
+      <c r="H19" s="25" t="n">
+        <v>-0.2500893749285049</v>
+      </c>
+      <c r="I19" s="24" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J19" s="25" t="n">
+        <v>0.0365916230113574</v>
+      </c>
+      <c r="K19" s="25" t="n">
+        <v>-0.0118534116209535</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="22" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D11" s="16" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="n">
-        <v>-0.0102880661666325</v>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>-0.1333333608266469</v>
-      </c>
-      <c r="G11" s="18" t="n">
-        <v>-0.1784799470385798</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>-0.4297401766535514</v>
-      </c>
-      <c r="I11" s="16" t="inlineStr">
+      <c r="D20" s="22" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="n">
+        <v>-0.1020812405743142</v>
+      </c>
+      <c r="F20" s="23" t="n">
+        <v>-0.1703296376998283</v>
+      </c>
+      <c r="G20" s="23" t="n">
+        <v>-0.2172493539078707</v>
+      </c>
+      <c r="H20" s="23" t="n">
+        <v>-0.4529853867406843</v>
+      </c>
+      <c r="I20" s="22" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J11" s="18" t="n">
-        <v>0.0201065650051323</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>-0.005646063733711</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="19" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>AKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n">
-        <v>-0.0502121014936132</v>
-      </c>
-      <c r="F12" s="20" t="n">
-        <v>0.009015754269078699</v>
-      </c>
-      <c r="G12" s="20" t="n">
-        <v>-0.1489226840654248</v>
-      </c>
-      <c r="H12" s="20" t="n">
-        <v>-0.1727093423606177</v>
-      </c>
-      <c r="I12" s="19" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="20" t="n">
-        <v>0.0237856144820836</v>
-      </c>
-      <c r="K12" s="20" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="19" t="n">
-        <v>10</v>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>TUPRS.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n">
-        <v>-0.1296752843077038</v>
-      </c>
-      <c r="F13" s="20" t="n">
-        <v>0.1574278255139025</v>
-      </c>
-      <c r="G13" s="20" t="n">
-        <v>0.3900210619989481</v>
-      </c>
-      <c r="H13" s="20" t="n">
-        <v>-0.2907817358936067</v>
-      </c>
-      <c r="I13" s="19" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="20" t="n">
-        <v>0.0276004494794109</v>
-      </c>
-      <c r="K13" s="20" t="n">
-        <v>0.0195381803197951</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="21" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="21" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D14" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E14" s="22" t="n">
-        <v>-0.1210525914242393</v>
-      </c>
-      <c r="F14" s="22" t="n">
-        <v>-0.1798648796241673</v>
-      </c>
-      <c r="G14" s="22" t="n">
-        <v>-0.3745318245039286</v>
-      </c>
-      <c r="H14" s="22" t="n">
-        <v>-0.1855480646588513</v>
-      </c>
-      <c r="I14" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J14" s="22" t="n">
-        <v>0.0184803206796285</v>
-      </c>
-      <c r="K14" s="22" t="n">
-        <v>0.020342480870896</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="23" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="23" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E15" s="24" t="n">
-        <v>-0.1681009898953201</v>
-      </c>
-      <c r="F15" s="24" t="n">
-        <v>-0.2643328487577674</v>
-      </c>
-      <c r="G15" s="24" t="n">
-        <v>-0.3887015098417582</v>
-      </c>
-      <c r="H15" s="24" t="n">
-        <v>-0.083775766156647</v>
-      </c>
-      <c r="I15" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J15" s="24" t="n">
-        <v>0.0158754109693756</v>
-      </c>
-      <c r="K15" s="24" t="n">
-        <v>-0.016938908556182</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="21" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="21" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D16" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E16" s="22" t="n">
-        <v>-0.1348239046908782</v>
-      </c>
-      <c r="F16" s="22" t="n">
-        <v>-0.2165644359003546</v>
-      </c>
-      <c r="G16" s="22" t="n">
-        <v>-0.3218268992107163</v>
-      </c>
-      <c r="H16" s="22" t="n">
-        <v>-0.2941763752031232</v>
-      </c>
-      <c r="I16" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J16" s="22" t="n">
-        <v>0.0184980759114234</v>
-      </c>
-      <c r="K16" s="22" t="n">
-        <v>0.0147321564810616</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="23" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="23" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="23" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="24" t="n">
-        <v>-0.09748134797235231</v>
-      </c>
-      <c r="F17" s="24" t="n">
-        <v>-0.1291628722130455</v>
-      </c>
-      <c r="G17" s="24" t="n">
-        <v>-0.1204545281150124</v>
-      </c>
-      <c r="H17" s="24" t="n">
-        <v>-0.2354957719389704</v>
-      </c>
-      <c r="I17" s="23" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J17" s="24" t="n">
-        <v>0.0366080697765715</v>
-      </c>
-      <c r="K17" s="24" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="21" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="21" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D18" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E18" s="22" t="n">
-        <v>-0.1739894551845342</v>
-      </c>
-      <c r="F18" s="22" t="n">
-        <v>-0.2100840336134454</v>
-      </c>
-      <c r="G18" s="22" t="n">
-        <v>-0.2140468227424748</v>
-      </c>
-      <c r="H18" s="22" t="n">
-        <v>-0.2230967507945747</v>
-      </c>
-      <c r="I18" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J18" s="22" t="n">
-        <v>0.0258657962097724</v>
-      </c>
-      <c r="K18" s="22" t="n">
-        <v>0.0378562161969006</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="21" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="21" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E19" s="22" t="n">
-        <v>-0.1354795439302482</v>
-      </c>
-      <c r="F19" s="22" t="n">
-        <v>-0.129054054054054</v>
-      </c>
-      <c r="G19" s="22" t="n">
-        <v>-0.2267546490701859</v>
-      </c>
-      <c r="H19" s="22" t="n">
-        <v>0.0091614930640857</v>
-      </c>
-      <c r="I19" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="22" t="n">
-        <v>0.032041761700043</v>
-      </c>
-      <c r="K19" s="22" t="n">
-        <v>0.0248447188033209</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="21" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="21" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="21" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="22" t="n">
-        <v>-0.1039878607510293</v>
-      </c>
-      <c r="F20" s="22" t="n">
-        <v>-0.1861531208325939</v>
-      </c>
-      <c r="G20" s="22" t="n">
-        <v>-0.2542225752588232</v>
-      </c>
-      <c r="H20" s="22" t="n">
-        <v>-0.4324468295623667</v>
-      </c>
-      <c r="I20" s="21" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="22" t="n">
-        <v>0.0265684710708643</v>
-      </c>
-      <c r="K20" s="22" t="n">
-        <v>0.0569024956991131</v>
+      <c r="J20" s="23" t="n">
+        <v>0.0267319379708561</v>
+      </c>
+      <c r="K20" s="23" t="n">
+        <v>0.0595845018212652</v>
       </c>
     </row>
   </sheetData>
@@ -2679,7 +2785,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2687,7 +2793,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2712,7 +2818,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, KCHOL.IS</t>
+          <t>KCHOL.IS, GARAN.IS, SAHOL.IS</t>
         </is>
       </c>
     </row>
@@ -2736,7 +2842,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>GARAN.IS, THYAO.IS, YKBNK.IS, EREGL.IS, TCELL.IS, ARCLK.IS, PETKM.IS</t>
+          <t>BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2748,7 +2854,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>SAHOL.IS, AKBNK.IS, TUPRS.IS, FROTO.IS, PGSUS.IS, TOASO.IS, ASELS.IS, SISE.IS</t>
+          <t>TCELL.IS, ARCLK.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2760,7 +2866,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.00 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %0.78 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2772,7 +2878,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -2798,7 +2904,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2806,7 +2912,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2867,7 +2973,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>REDUCED</t>
         </is>
       </c>
     </row>
@@ -2903,7 +3009,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -2951,7 +3057,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>UNCHANGED</t>
+          <t>INCREASED</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3155,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3057,7 +3163,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3081,7 +3187,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11797.7001953125</v>
+        <v>11577.099609375</v>
       </c>
     </row>
     <row r="5">
@@ -3091,7 +3197,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13626.08751953125</v>
+        <v>13626.481015625</v>
       </c>
     </row>
     <row r="6">
@@ -3125,7 +3231,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>80.94</v>
+        <v>81.03</v>
       </c>
     </row>
     <row r="9">
@@ -3157,18 +3263,18 @@
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
     <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-19</t>
+          <t>Rapor Tarihi: 2026-10-20</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3182,7 +3288,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-21 06:41</t>
+          <t>Son Güncelleme: 2026-10-22 06:43</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3246,23 +3352,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n">
+      <c r="C4" s="26" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="25" t="n">
-        <v>202.8999938964844</v>
-      </c>
-      <c r="E4" s="26" t="n">
-        <v>0.02994920759636743</v>
-      </c>
-      <c r="F4" s="25" t="n">
-        <v>87042.72195722954</v>
-      </c>
-      <c r="G4" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H4" s="26" t="n">
-        <v>-0.1659296840794658</v>
+      <c r="D4" s="26" t="n">
+        <v>208.3999938964844</v>
+      </c>
+      <c r="E4" s="27" t="n">
+        <v>0.05786798932225579</v>
+      </c>
+      <c r="F4" s="26" t="n">
+        <v>168184.326366351</v>
+      </c>
+      <c r="G4" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H4" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="5">
@@ -3276,113 +3382,113 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="25" t="n">
+      <c r="C5" s="26" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="25" t="n">
-        <v>85.55000305175781</v>
-      </c>
-      <c r="E5" s="26" t="n">
-        <v>-0.1134714709662403</v>
-      </c>
-      <c r="F5" s="25" t="n">
-        <v>-9964.438162434555</v>
-      </c>
-      <c r="G5" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H5" s="26" t="n">
-        <v>-0.1659296840794658</v>
+      <c r="D5" s="26" t="n">
+        <v>89.19999694824219</v>
+      </c>
+      <c r="E5" s="27" t="n">
+        <v>-0.07564770001821564</v>
+      </c>
+      <c r="F5" s="26" t="n">
+        <v>-6642.963403428294</v>
+      </c>
+      <c r="G5" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H5" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>FROTO.IS</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
-        </is>
-      </c>
-      <c r="C6" s="25" t="n">
-        <v>405.5</v>
-      </c>
-      <c r="D6" s="25" t="n">
-        <v>371</v>
-      </c>
-      <c r="E6" s="26" t="n">
-        <v>-0.0850801479654747</v>
-      </c>
-      <c r="F6" s="25" t="n">
-        <v>-241263.333156086</v>
-      </c>
-      <c r="G6" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H6" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-09-24</t>
+        </is>
+      </c>
+      <c r="C6" s="26" t="n">
+        <v>77.40000152587891</v>
+      </c>
+      <c r="D6" s="26" t="n">
+        <v>68.44999694824219</v>
+      </c>
+      <c r="E6" s="27" t="n">
+        <v>-0.1156331317983793</v>
+      </c>
+      <c r="F6" s="26" t="n">
+        <v>-517699.3630867111</v>
+      </c>
+      <c r="G6" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H6" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>FROTO.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="C7" s="25" t="n">
-        <v>77.40000152587891</v>
-      </c>
-      <c r="D7" s="25" t="n">
-        <v>66.80000305175781</v>
-      </c>
-      <c r="E7" s="26" t="n">
-        <v>-0.1369508819786903</v>
-      </c>
-      <c r="F7" s="25" t="n">
-        <v>-613140.7432443597</v>
-      </c>
-      <c r="G7" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H7" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="C7" s="26" t="n">
+        <v>387</v>
+      </c>
+      <c r="D7" s="26" t="n">
+        <v>362</v>
+      </c>
+      <c r="E7" s="27" t="n">
+        <v>-0.06459948320413433</v>
+      </c>
+      <c r="F7" s="26" t="n">
+        <v>-278944.8093186272</v>
+      </c>
+      <c r="G7" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H7" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>GARAN.IS</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
-        </is>
-      </c>
-      <c r="C8" s="25" t="n">
-        <v>387</v>
-      </c>
-      <c r="D8" s="25" t="n">
-        <v>356.75</v>
-      </c>
-      <c r="E8" s="26" t="n">
-        <v>-0.07816537467700257</v>
-      </c>
-      <c r="F8" s="25" t="n">
-        <v>-337523.2192755393</v>
-      </c>
-      <c r="G8" s="25" t="n">
-        <v>28810856.79717723</v>
-      </c>
-      <c r="H8" s="26" t="n">
-        <v>-0.1659296840794658</v>
+          <t>2026-10-20</t>
+        </is>
+      </c>
+      <c r="C8" s="26" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="D8" s="26" t="n">
+        <v>134.6000061035156</v>
+      </c>
+      <c r="E8" s="27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="26" t="n">
+        <v>29150740.19778639</v>
+      </c>
+      <c r="H8" s="27" t="n">
+        <v>-0.139105356442462</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -17,7 +17,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'YONETICI_OZETI'!$A$19:$K$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'PORTFOY_ONERISI'!$A$7:$O$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'ILK_20_SIRALAMA'!$A$3:$K$20</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'AL_SAT_OZET'!$A$3:$B$9</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PORTFOY_DEGISIMI'!$A$3:$B$20</definedName>
@@ -86,17 +86,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00FFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00F4CCCC"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E7E6E6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -131,7 +131,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
@@ -157,7 +157,7 @@
     <xf numFmtId="4" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -181,31 +190,31 @@
     <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="4" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="10" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="0" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -587,7 +596,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="20" customWidth="1" min="4" max="4"/>
     <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
     <col width="20" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -615,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -632,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -683,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 81.03/100</t>
+          <t>Güven Puanı: 80.80/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -760,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: -</t>
+          <t>AZALT: BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -777,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
+          <t>ÇIK: YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -963,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2225985965411588</v>
+        <v>0.2253112896284994</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22259.85965411588</v>
+        <v>22531.12896284994</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.0567878719657279</v>
+        <v>0.05678787196572799</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1264.090060013005</v>
+        <v>1279.494866785628</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>142.2436540167083</v>
+        <v>140.1300782727768</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>125.881001496126</v>
+        <v>125.9700057983398</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.8766651994557298</v>
+        <v>1.135757439314558</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,25 +1015,25 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2095677741579692</v>
+        <v>0.2055238060841062</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20956.77741579692</v>
+        <v>20552.38060841062</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.01852771488995719</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>487.6239542214013</v>
+        <v>380.7886482225169</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>213.2490614352234</v>
+        <v>207.0666875454282</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>197.9799942016601</v>
+        <v>193.1350028991699</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.4653615816464596</v>
+        <v>0.3705542977991433</v>
       </c>
       <c r="K21" s="9" t="inlineStr">
         <is>
@@ -1047,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.167833629300872</v>
+        <v>0.1691649042873944</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16783.3629300872</v>
+        <v>16916.49042873943</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.007822546905052701</v>
+        <v>0.01031479137899316</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>131.2886437451299</v>
+        <v>174.4900696371818</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>89.89776810830038</v>
+        <v>89.05925040167628</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>82.25680639116948</v>
+        <v>81.14630294548057</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1004971927995564</v>
+        <v>0.1298241015600161</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1120,16 +1129,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O17"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
     <col width="19" customWidth="1" min="10" max="10"/>
@@ -1143,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1164,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1206,7 +1215,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Toplam önerilen/satılacak satır: 10</t>
+          <t>Toplam önerilen/satılacak satır: 9</t>
         </is>
       </c>
       <c r="B4" s="2" t="n"/>
@@ -1349,45 +1358,45 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>208.3999938964844</v>
+        <v>385.5</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.0302466271968858</v>
+        <v>-0.02055785179873293</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.006068867739039252</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.0914169657590902</v>
+        <v>0.06844627048378671</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>202.0965969732642</v>
+        <v>377.5749481315884</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>213.2490614352234</v>
+        <v>387.8395485133996</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>227.4512890027139</v>
+        <v>411.8860372714998</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>197.9799942016601</v>
+        <v>366.225</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>81.03</v>
+        <v>80.8</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
@@ -1406,515 +1415,458 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>203.3000030517578</v>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>-0.03024662719688587</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>0.01852771488995719</v>
+      </c>
+      <c r="G9" s="19" t="n">
+        <v>0.0466707658152421</v>
+      </c>
+      <c r="H9" s="18" t="n">
+        <v>197.1508636503255</v>
+      </c>
+      <c r="I9" s="18" t="n">
+        <v>207.0666875454282</v>
+      </c>
+      <c r="J9" s="18" t="n">
+        <v>212.7881698844244</v>
+      </c>
+      <c r="K9" s="18" t="n">
+        <v>193.1350028991699</v>
+      </c>
+      <c r="L9" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M9" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N9" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O9" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="17" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.0446736587600064</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.05678787196572799</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.1240418332017574</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>126.6762786792724</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>140.1300782727768</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>149.0479539431599</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>125.9700057983398</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
-        <v>385.5</v>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>-0.0475400966137377</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>-0.0036968334151564</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>0.0383027129081878</v>
-      </c>
-      <c r="H9" s="18" t="n">
-        <v>367.1732927554041</v>
-      </c>
-      <c r="I9" s="18" t="n">
-        <v>384.0748707184572</v>
-      </c>
-      <c r="J9" s="18" t="n">
-        <v>400.2656958261064</v>
-      </c>
-      <c r="K9" s="18" t="n">
-        <v>366.225</v>
-      </c>
-      <c r="L9" s="17" t="inlineStr">
+      <c r="D11" s="21" t="n">
+        <v>36.41999816894531</v>
+      </c>
+      <c r="E11" s="22" t="n">
+        <v>-0.02777781264366352</v>
+      </c>
+      <c r="F11" s="22" t="n">
+        <v>-0.00924906731649483</v>
+      </c>
+      <c r="G11" s="22" t="n">
+        <v>0.07188239616583897</v>
+      </c>
+      <c r="H11" s="21" t="n">
+        <v>35.40833028332578</v>
+      </c>
+      <c r="I11" s="21" t="n">
+        <v>36.08314715421412</v>
+      </c>
+      <c r="J11" s="21" t="n">
+        <v>39.03795490568457</v>
+      </c>
+      <c r="K11" s="21" t="n">
+        <v>34.50212993691391</v>
+      </c>
+      <c r="L11" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M9" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N9" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O9" s="17" t="inlineStr">
+      <c r="M11" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N11" s="20" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; trend desteği var</t>
+        </is>
+      </c>
+      <c r="O11" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B10" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="14" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
-        <v>134.6000061035156</v>
-      </c>
-      <c r="E10" s="16" t="n">
-        <v>-0.06477714867772109</v>
-      </c>
-      <c r="F10" s="16" t="n">
-        <v>0.0567878719657279</v>
-      </c>
-      <c r="G10" s="16" t="n">
-        <v>0.1272216922975995</v>
-      </c>
-      <c r="H10" s="15" t="n">
-        <v>125.881001496126</v>
-      </c>
-      <c r="I10" s="15" t="n">
-        <v>142.2436540167083</v>
-      </c>
-      <c r="J10" s="15" t="n">
-        <v>151.7240466632721</v>
-      </c>
-      <c r="K10" s="15" t="n">
-        <v>125.881001496126</v>
-      </c>
-      <c r="L10" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="M10" s="14" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N10" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="14" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="D12" s="18" t="n">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="E12" s="19" t="n">
+        <v>-0.07945205285495327</v>
+      </c>
+      <c r="F12" s="19" t="n">
+        <v>0.01031479137899316</v>
+      </c>
+      <c r="G12" s="19" t="n">
+        <v>0.09404613143246554</v>
+      </c>
+      <c r="H12" s="18" t="n">
+        <v>81.14630294548057</v>
+      </c>
+      <c r="I12" s="18" t="n">
+        <v>89.05925040167628</v>
+      </c>
+      <c r="J12" s="18" t="n">
+        <v>96.44016815515374</v>
+      </c>
+      <c r="K12" s="18" t="n">
+        <v>81.14630294548057</v>
+      </c>
+      <c r="L12" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M12" s="17" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N12" s="17" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B13" s="20" t="inlineStr">
         <is>
           <t>THYAO.IS</t>
         </is>
       </c>
-      <c r="C11" s="17" t="inlineStr">
+      <c r="C13" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
-        <v>273.5</v>
-      </c>
-      <c r="E11" s="19" t="n">
-        <v>-0.0621242939763079</v>
-      </c>
-      <c r="F11" s="19" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-      <c r="G11" s="19" t="n">
-        <v>0.0948783870299643</v>
-      </c>
-      <c r="H11" s="18" t="n">
-        <v>256.5090055974798</v>
-      </c>
-      <c r="I11" s="18" t="n">
-        <v>269.6613787891161</v>
-      </c>
-      <c r="J11" s="18" t="n">
-        <v>299.4492388526953</v>
-      </c>
-      <c r="K11" s="18" t="n">
-        <v>256.5090055974798</v>
-      </c>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="D13" s="21" t="n">
+        <v>265</v>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.06286186931348225</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>0.05123038157605908</v>
+      </c>
+      <c r="H13" s="21" t="n">
+        <v>248.3416046319272</v>
+      </c>
+      <c r="I13" s="21" t="n">
+        <v>255.9370556167268</v>
+      </c>
+      <c r="J13" s="21" t="n">
+        <v>278.5760511176557</v>
+      </c>
+      <c r="K13" s="21" t="n">
+        <v>248.3416046319272</v>
+      </c>
+      <c r="L13" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N11" s="17" t="inlineStr">
+      <c r="M13" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N13" s="20" t="inlineStr">
         <is>
           <t>volatilite görece düşük</t>
         </is>
       </c>
-      <c r="O11" s="17" t="inlineStr">
+      <c r="O13" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="15" t="n">
-        <v>89.19999694824219</v>
-      </c>
-      <c r="E12" s="16" t="n">
-        <v>-0.0778384618230588</v>
-      </c>
-      <c r="F12" s="16" t="n">
-        <v>0.007822546905052701</v>
-      </c>
-      <c r="G12" s="16" t="n">
-        <v>0.093714156045322</v>
-      </c>
-      <c r="H12" s="15" t="n">
-        <v>82.25680639116948</v>
-      </c>
-      <c r="I12" s="15" t="n">
-        <v>89.89776810830038</v>
-      </c>
-      <c r="J12" s="15" t="n">
-        <v>97.55929938149201</v>
-      </c>
-      <c r="K12" s="15" t="n">
-        <v>82.25680639116948</v>
-      </c>
-      <c r="L12" s="14" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="20" t="n">
+        <v>10</v>
+      </c>
+      <c r="B14" s="20" t="inlineStr">
+        <is>
+          <t>ARCLK.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="D14" s="21" t="n">
+        <v>74.5</v>
+      </c>
+      <c r="E14" s="22" t="n">
+        <v>-0.056962015212765</v>
+      </c>
+      <c r="F14" s="22" t="n">
+        <v>-0.01693897265082622</v>
+      </c>
+      <c r="G14" s="22" t="n">
+        <v>0.1111908721424226</v>
+      </c>
+      <c r="H14" s="21" t="n">
+        <v>70.25632986664901</v>
+      </c>
+      <c r="I14" s="21" t="n">
+        <v>73.23804653751344</v>
+      </c>
+      <c r="J14" s="21" t="n">
+        <v>82.78371997461049</v>
+      </c>
+      <c r="K14" s="21" t="n">
+        <v>70.25632986664901</v>
+      </c>
+      <c r="L14" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M12" s="14" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N12" s="14" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="14" t="inlineStr">
+      <c r="M14" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N14" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O14" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C13" s="17" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="20" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="20" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D13" s="18" t="n">
-        <v>36.65999984741211</v>
-      </c>
-      <c r="E13" s="19" t="n">
-        <v>-0.053387959227386</v>
-      </c>
-      <c r="F13" s="19" t="n">
-        <v>-0.0095238211722357</v>
-      </c>
-      <c r="G13" s="19" t="n">
-        <v>0.0919879432419712</v>
-      </c>
-      <c r="H13" s="18" t="n">
-        <v>34.7027972702825</v>
-      </c>
-      <c r="I13" s="18" t="n">
-        <v>36.31085656469117</v>
-      </c>
-      <c r="J13" s="18" t="n">
-        <v>40.03227783262653</v>
-      </c>
-      <c r="K13" s="18" t="n">
-        <v>34.7027972702825</v>
-      </c>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="D15" s="21" t="n">
+        <v>129.3000030517578</v>
+      </c>
+      <c r="E15" s="22" t="n">
+        <v>-0.05370672771557694</v>
+      </c>
+      <c r="F15" s="22" t="n">
+        <v>-0.02052976338254109</v>
+      </c>
+      <c r="G15" s="22" t="n">
+        <v>0.1090029643218295</v>
+      </c>
+      <c r="H15" s="21" t="n">
+        <v>122.3557229942338</v>
+      </c>
+      <c r="I15" s="21" t="n">
+        <v>126.6455045837434</v>
+      </c>
+      <c r="J15" s="21" t="n">
+        <v>143.394086671221</v>
+      </c>
+      <c r="K15" s="21" t="n">
+        <v>122.3557229942338</v>
+      </c>
+      <c r="L15" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M13" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N13" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O13" s="17" t="inlineStr">
-        <is>
-          <t>alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C14" s="17" t="inlineStr">
+      <c r="M15" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N15" s="20" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O15" s="20" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="20" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="20" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C16" s="20" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="D14" s="18" t="n">
-        <v>37.18000030517578</v>
-      </c>
-      <c r="E14" s="19" t="n">
-        <v>-0.0653061001718057</v>
-      </c>
-      <c r="F14" s="19" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-      <c r="G14" s="19" t="n">
-        <v>0.0345194815014007</v>
-      </c>
-      <c r="H14" s="18" t="n">
-        <v>34.75191948085821</v>
-      </c>
-      <c r="I14" s="18" t="n">
-        <v>36.3981784772924</v>
-      </c>
-      <c r="J14" s="18" t="n">
-        <v>38.46343463793237</v>
-      </c>
-      <c r="K14" s="18" t="n">
-        <v>34.75191948085821</v>
-      </c>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="D16" s="21" t="n">
+        <v>19.04999923706055</v>
+      </c>
+      <c r="E16" s="22" t="n">
+        <v>-0.1689400445284157</v>
+      </c>
+      <c r="F16" s="22" t="n">
+        <v>-0.05027927169972446</v>
+      </c>
+      <c r="G16" s="22" t="n">
+        <v>0.01865484715630311</v>
+      </c>
+      <c r="H16" s="21" t="n">
+        <v>15.83169151768525</v>
+      </c>
+      <c r="I16" s="21" t="n">
+        <v>18.09217914954084</v>
+      </c>
+      <c r="J16" s="21" t="n">
+        <v>19.4053740611556</v>
+      </c>
+      <c r="K16" s="21" t="n">
+        <v>15.83169151768525</v>
+      </c>
+      <c r="L16" s="20" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M14" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N14" s="17" t="inlineStr">
-        <is>
-          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O14" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="17" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D15" s="18" t="n">
-        <v>132</v>
-      </c>
-      <c r="E15" s="19" t="n">
-        <v>-0.0759511873012769</v>
-      </c>
-      <c r="F15" s="19" t="n">
-        <v>-0.0097276264591439</v>
-      </c>
-      <c r="G15" s="19" t="n">
-        <v>0.1305235121113319</v>
-      </c>
-      <c r="H15" s="18" t="n">
-        <v>121.9744432762314</v>
-      </c>
-      <c r="I15" s="18" t="n">
-        <v>130.715953307393</v>
-      </c>
-      <c r="J15" s="18" t="n">
-        <v>149.2291035986958</v>
-      </c>
-      <c r="K15" s="18" t="n">
-        <v>121.9744432762314</v>
-      </c>
-      <c r="L15" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M15" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N15" s="17" t="inlineStr">
-        <is>
-          <t>volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O15" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="17" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D16" s="18" t="n">
-        <v>342.75</v>
-      </c>
-      <c r="E16" s="19" t="n">
-        <v>-0.110731767703003</v>
-      </c>
-      <c r="F16" s="19" t="n">
-        <v>-0.0588766952961986</v>
-      </c>
-      <c r="G16" s="19" t="n">
-        <v>0.0478184256278046</v>
-      </c>
-      <c r="H16" s="18" t="n">
-        <v>304.7966866197957</v>
-      </c>
-      <c r="I16" s="18" t="n">
-        <v>322.570012687228</v>
-      </c>
-      <c r="J16" s="18" t="n">
-        <v>359.1397653839301</v>
-      </c>
-      <c r="K16" s="18" t="n">
-        <v>304.7966866197957</v>
-      </c>
-      <c r="L16" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M16" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N16" s="17" t="inlineStr">
-        <is>
-          <t>hacim artışı var</t>
-        </is>
-      </c>
-      <c r="O16" s="17" t="inlineStr">
+      <c r="M16" s="20" t="n">
+        <v>80.8</v>
+      </c>
+      <c r="N16" s="20" t="inlineStr">
+        <is>
+          <t>Model skoru portföy için yeterli</t>
+        </is>
+      </c>
+      <c r="O16" s="20" t="inlineStr">
         <is>
           <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="17" t="n">
-        <v>16</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D17" s="18" t="n">
-        <v>19.60000038146973</v>
-      </c>
-      <c r="E17" s="19" t="n">
-        <v>-0.0502792716997244</v>
-      </c>
-      <c r="F17" s="19" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-      <c r="G17" s="19" t="n">
-        <v>0.0113636098814375</v>
-      </c>
-      <c r="H17" s="18" t="n">
-        <v>18.61452663697511</v>
-      </c>
-      <c r="I17" s="18" t="n">
-        <v>19.36767350917732</v>
-      </c>
-      <c r="J17" s="18" t="n">
-        <v>19.82272713948078</v>
-      </c>
-      <c r="K17" s="18" t="n">
-        <v>18.16560873150732</v>
-      </c>
-      <c r="L17" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M17" s="17" t="n">
-        <v>81.03</v>
-      </c>
-      <c r="N17" s="17" t="inlineStr">
-        <is>
-          <t>Model skoru portföy için yeterli</t>
-        </is>
-      </c>
-      <c r="O17" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A7:O17"/>
+  <autoFilter ref="A7:O16"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1932,19 +1884,19 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="21" customWidth="1" min="5" max="5"/>
-    <col width="21" customWidth="1" min="6" max="6"/>
-    <col width="21" customWidth="1" min="7" max="7"/>
-    <col width="21" customWidth="1" min="8" max="8"/>
+    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="21" customWidth="1" min="10" max="10"/>
     <col width="24" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1961,7 +1913,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2038,7 +1990,7 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
       <c r="C4" s="14" t="inlineStr">
@@ -2048,20 +2000,20 @@
       </c>
       <c r="D4" s="14" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="E4" s="16" t="n">
-        <v>-0.0625281554856169</v>
+        <v>-0.1040092969203951</v>
       </c>
       <c r="F4" s="16" t="n">
-        <v>0.0514631539116814</v>
+        <v>0.01993983580440606</v>
       </c>
       <c r="G4" s="16" t="n">
-        <v>0.0190708747994345</v>
+        <v>0.01922116148021913</v>
       </c>
       <c r="H4" s="16" t="n">
-        <v>-0.2313857694396462</v>
+        <v>-0.09548611179691424</v>
       </c>
       <c r="I4" s="14" t="inlineStr">
         <is>
@@ -2069,10 +2021,10 @@
         </is>
       </c>
       <c r="J4" s="16" t="n">
-        <v>0.0211053561538639</v>
+        <v>0.01970341923595139</v>
       </c>
       <c r="K4" s="16" t="n">
-        <v>0.0232680790823229</v>
+        <v>0.006068867739039252</v>
       </c>
     </row>
     <row r="5">
@@ -2081,7 +2033,7 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>KCHOL.IS</t>
         </is>
       </c>
       <c r="C5" s="17" t="inlineStr">
@@ -2091,332 +2043,332 @@
       </c>
       <c r="D5" s="17" t="inlineStr">
         <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E5" s="19" t="n">
+        <v>-0.08050656969870962</v>
+      </c>
+      <c r="F5" s="19" t="n">
+        <v>0.02884613751102894</v>
+      </c>
+      <c r="G5" s="19" t="n">
+        <v>-0.04013219961060555</v>
+      </c>
+      <c r="H5" s="19" t="n">
+        <v>-0.2427035483688954</v>
+      </c>
+      <c r="I5" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J5" s="19" t="n">
+        <v>0.02134321070648489</v>
+      </c>
+      <c r="K5" s="19" t="n">
+        <v>0.01852771488995719</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="B6" s="17" t="inlineStr">
+        <is>
+          <t>GARAN.IS</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D6" s="17" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="E6" s="19" t="n">
+        <v>-0.009708647141341564</v>
+      </c>
+      <c r="F6" s="19" t="n">
+        <v>0.05238100082155261</v>
+      </c>
+      <c r="G6" s="19" t="n">
+        <v>-0.09426221563046211</v>
+      </c>
+      <c r="H6" s="19" t="n">
+        <v>-0.3034241564012312</v>
+      </c>
+      <c r="I6" s="17" t="inlineStr">
+        <is>
+          <t>Kısmen trend üstü</t>
+        </is>
+      </c>
+      <c r="J6" s="19" t="n">
+        <v>0.022247395736596</v>
+      </c>
+      <c r="K6" s="19" t="n">
+        <v>0.05678787196572799</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="B7" s="20" t="inlineStr">
+        <is>
+          <t>YKBNK.IS</t>
+        </is>
+      </c>
+      <c r="C7" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E5" s="19" t="n">
-        <v>-0.1096997690531177</v>
-      </c>
-      <c r="F5" s="19" t="n">
-        <v>-0.0068319270468597</v>
-      </c>
-      <c r="G5" s="19" t="n">
-        <v>0.0451798027804024</v>
-      </c>
-      <c r="H5" s="19" t="n">
-        <v>-0.0900637285735935</v>
-      </c>
-      <c r="I5" s="17" t="inlineStr">
+      <c r="E7" s="22" t="n">
+        <v>-0.009249188468779868</v>
+      </c>
+      <c r="F7" s="22" t="n">
+        <v>0.09172654384317469</v>
+      </c>
+      <c r="G7" s="22" t="n">
+        <v>-0.07328247134924482</v>
+      </c>
+      <c r="H7" s="22" t="n">
+        <v>-0.3067808245277756</v>
+      </c>
+      <c r="I7" s="20" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J5" s="19" t="n">
-        <v>0.0199896884255374</v>
-      </c>
-      <c r="K5" s="19" t="n">
-        <v>-0.0036968334151564</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="14" t="n">
-        <v>3</v>
-      </c>
-      <c r="B6" s="14" t="inlineStr">
-        <is>
-          <t>GARAN.IS</t>
-        </is>
-      </c>
-      <c r="C6" s="14" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
-        </is>
-      </c>
-      <c r="D6" s="14" t="inlineStr">
+      <c r="J7" s="22" t="n">
+        <v>0.02632987820502872</v>
+      </c>
+      <c r="K7" s="22" t="n">
+        <v>-0.00924906731649483</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="17" t="n">
+        <v>5</v>
+      </c>
+      <c r="B8" s="17" t="inlineStr">
+        <is>
+          <t>SAHOL.IS</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D8" s="17" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="E6" s="16" t="n">
-        <v>0.0112697214967323</v>
-      </c>
-      <c r="F6" s="16" t="n">
-        <v>0.07680004882812499</v>
-      </c>
-      <c r="G6" s="16" t="n">
-        <v>-0.0175182036239734</v>
-      </c>
-      <c r="H6" s="16" t="n">
-        <v>-0.2872987491383497</v>
-      </c>
-      <c r="I6" s="14" t="inlineStr">
+      <c r="E8" s="19" t="n">
+        <v>-0.03291278057903546</v>
+      </c>
+      <c r="F8" s="19" t="n">
+        <v>0.01205514431862809</v>
+      </c>
+      <c r="G8" s="19" t="n">
+        <v>-0.1612749495178709</v>
+      </c>
+      <c r="H8" s="19" t="n">
+        <v>-0.06089244453678866</v>
+      </c>
+      <c r="I8" s="17" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J8" s="19" t="n">
+        <v>0.02194467792107834</v>
+      </c>
+      <c r="K8" s="19" t="n">
+        <v>0.01031479137899316</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="20" t="n">
+        <v>6</v>
+      </c>
+      <c r="B9" s="20" t="inlineStr">
+        <is>
+          <t>THYAO.IS</t>
+        </is>
+      </c>
+      <c r="C9" s="20" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E9" s="22" t="n">
+        <v>-0.1107382550335571</v>
+      </c>
+      <c r="F9" s="22" t="n">
+        <v>-0.1506410256410257</v>
+      </c>
+      <c r="G9" s="22" t="n">
+        <v>-0.1945288753799392</v>
+      </c>
+      <c r="H9" s="22" t="n">
+        <v>-0.3526028585518355</v>
+      </c>
+      <c r="I9" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J9" s="22" t="n">
+        <v>0.01868741571633192</v>
+      </c>
+      <c r="K9" s="22" t="n">
+        <v>-0.03419979012555929</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="23" t="n">
+        <v>7</v>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>EREGL.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n">
+        <v>-0.03437332753967359</v>
+      </c>
+      <c r="F10" s="24" t="n">
+        <v>-0.1561922022226782</v>
+      </c>
+      <c r="G10" s="24" t="n">
+        <v>0.1553234033959283</v>
+      </c>
+      <c r="H10" s="24" t="n">
+        <v>-0.4698951097882514</v>
+      </c>
+      <c r="I10" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J6" s="16" t="n">
-        <v>0.0221699973140994</v>
-      </c>
-      <c r="K6" s="16" t="n">
-        <v>0.0567878719657279</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="17" t="n">
-        <v>4</v>
-      </c>
-      <c r="B7" s="17" t="inlineStr">
-        <is>
-          <t>THYAO.IS</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
+      <c r="J10" s="24" t="n">
+        <v>0.02380020121545784</v>
+      </c>
+      <c r="K10" s="24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="23" t="n">
+        <v>8</v>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D7" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="n">
-        <v>-0.06814310051107331</v>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>-0.1254996003197441</v>
-      </c>
-      <c r="G7" s="19" t="n">
-        <v>-0.1379038613081166</v>
-      </c>
-      <c r="H7" s="19" t="n">
-        <v>-0.3211878254901774</v>
-      </c>
-      <c r="I7" s="17" t="inlineStr">
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E11" s="24" t="n">
+        <v>-0.05284150439180801</v>
+      </c>
+      <c r="F11" s="24" t="n">
+        <v>-0.0838958264635673</v>
+      </c>
+      <c r="G11" s="24" t="n">
+        <v>-0.2116182572614108</v>
+      </c>
+      <c r="H11" s="24" t="n">
+        <v>-0.4329946693010961</v>
+      </c>
+      <c r="I11" s="23" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J7" s="19" t="n">
-        <v>0.0183237247160637</v>
-      </c>
-      <c r="K7" s="19" t="n">
-        <v>-0.0140351781019522</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="14" t="n">
-        <v>5</v>
-      </c>
-      <c r="B8" s="14" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C8" s="14" t="inlineStr">
+      <c r="J11" s="24" t="n">
+        <v>0.01931544065071443</v>
+      </c>
+      <c r="K11" s="24" t="n">
+        <v>0.01245929909775567</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="23" t="n">
+        <v>9</v>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>TUPRS.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D8" s="14" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="E8" s="16" t="n">
-        <v>-0.0149089570184107</v>
-      </c>
-      <c r="F8" s="16" t="n">
-        <v>0.0142126213004374</v>
-      </c>
-      <c r="G8" s="16" t="n">
-        <v>-0.1035176186106312</v>
-      </c>
-      <c r="H8" s="16" t="n">
-        <v>-0.0581451764026649</v>
-      </c>
-      <c r="I8" s="14" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J8" s="16" t="n">
-        <v>0.0219273868966153</v>
-      </c>
-      <c r="K8" s="16" t="n">
-        <v>0.007822546905052701</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="17" t="n">
-        <v>6</v>
-      </c>
-      <c r="B9" s="17" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>0.0021869330878356</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>0.1022249458045725</v>
-      </c>
-      <c r="G9" s="19" t="n">
-        <v>-0.0218783272369083</v>
-      </c>
-      <c r="H9" s="19" t="n">
-        <v>-0.2972354995612898</v>
-      </c>
-      <c r="I9" s="17" t="inlineStr">
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n">
+        <v>-0.07887210208546558</v>
+      </c>
+      <c r="F12" s="24" t="n">
+        <v>0.2019319283588819</v>
+      </c>
+      <c r="G12" s="24" t="n">
+        <v>0.4454062761127906</v>
+      </c>
+      <c r="H12" s="24" t="n">
+        <v>-0.3490137343630424</v>
+      </c>
+      <c r="I12" s="23" t="inlineStr">
         <is>
           <t>Kısmen trend üstü</t>
         </is>
       </c>
-      <c r="J9" s="19" t="n">
-        <v>0.0263089279639388</v>
-      </c>
-      <c r="K9" s="19" t="n">
-        <v>-0.0095238211722357</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="17" t="n">
-        <v>7</v>
-      </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>EREGL.IS</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.005350475046135</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>-0.158823537026944</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.2195967321886922</v>
-      </c>
-      <c r="H10" s="19" t="n">
-        <v>-0.4672271139985361</v>
-      </c>
-      <c r="I10" s="17" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J10" s="19" t="n">
-        <v>0.0238351539109441</v>
-      </c>
-      <c r="K10" s="19" t="n">
-        <v>-0.0210280210184544</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>8</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>TCELL.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E11" s="21" t="n">
-        <v>-0.0225225221785121</v>
-      </c>
-      <c r="F11" s="21" t="n">
-        <v>-0.06999998546781989</v>
-      </c>
-      <c r="G11" s="21" t="n">
-        <v>-0.1675191902357281</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>-0.4414806906738988</v>
-      </c>
-      <c r="I11" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>0.019083963827017</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>0.0139752661812804</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="20" t="n">
-        <v>9</v>
-      </c>
-      <c r="B12" s="20" t="inlineStr">
-        <is>
-          <t>ARCLK.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="20" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E12" s="21" t="n">
-        <v>-0.1196778060214621</v>
-      </c>
-      <c r="F12" s="21" t="n">
-        <v>-0.2272727272727273</v>
-      </c>
-      <c r="G12" s="21" t="n">
-        <v>-0.3405172413793104</v>
-      </c>
-      <c r="H12" s="21" t="n">
-        <v>-0.08619076076584919</v>
-      </c>
-      <c r="I12" s="20" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J12" s="21" t="n">
-        <v>0.0175460603555207</v>
-      </c>
-      <c r="K12" s="21" t="n">
-        <v>0.0318628326773948</v>
+      <c r="J12" s="24" t="n">
+        <v>0.02730165577321778</v>
+      </c>
+      <c r="K12" s="24" t="n">
+        <v>0.01866835301293379</v>
       </c>
     </row>
     <row r="13">
@@ -2425,7 +2377,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>TUPRS.IS</t>
+          <t>ARCLK.IS</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -2435,332 +2387,332 @@
       </c>
       <c r="D13" s="20" t="inlineStr">
         <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E13" s="22" t="n">
+        <v>-0.1534090909090909</v>
+      </c>
+      <c r="F13" s="22" t="n">
+        <v>-0.2474747474747475</v>
+      </c>
+      <c r="G13" s="22" t="n">
+        <v>-0.3723672964163184</v>
+      </c>
+      <c r="H13" s="22" t="n">
+        <v>-0.1084551721176786</v>
+      </c>
+      <c r="I13" s="20" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J13" s="22" t="n">
+        <v>0.01775942047506572</v>
+      </c>
+      <c r="K13" s="22" t="n">
+        <v>-0.01693897265082622</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="25" t="n">
+        <v>11</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>FROTO.IS</t>
+        </is>
+      </c>
+      <c r="C14" s="25" t="inlineStr">
+        <is>
+          <t>MEDIUM</t>
+        </is>
+      </c>
+      <c r="D14" s="25" t="inlineStr">
+        <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E13" s="21" t="n">
-        <v>-0.1115441285294764</v>
-      </c>
-      <c r="F13" s="21" t="n">
-        <v>0.1716600104443737</v>
-      </c>
-      <c r="G13" s="21" t="n">
-        <v>0.3749516646374315</v>
-      </c>
-      <c r="H13" s="21" t="n">
-        <v>-0.3150624841004493</v>
-      </c>
-      <c r="I13" s="20" t="inlineStr">
-        <is>
-          <t>Kısmen trend üstü</t>
-        </is>
-      </c>
-      <c r="J13" s="21" t="n">
-        <v>0.0276418940598797</v>
-      </c>
-      <c r="K13" s="21" t="n">
-        <v>0.0195382818194833</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="22" t="n">
-        <v>11</v>
-      </c>
-      <c r="B14" s="22" t="inlineStr">
+      <c r="E14" s="26" t="n">
+        <v>-0.1559343301767033</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>-0.1537974876693532</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>-0.3883806348800831</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>-0.2265403160351237</v>
+      </c>
+      <c r="I14" s="25" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>0.01877018636727422</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0.1100915187953706</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="27" t="n">
+        <v>12</v>
+      </c>
+      <c r="B15" s="27" t="inlineStr">
+        <is>
+          <t>PGSUS.IS</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D15" s="27" t="inlineStr">
+        <is>
+          <t>SAT</t>
+        </is>
+      </c>
+      <c r="E15" s="28" t="n">
+        <v>-0.1454064742647366</v>
+      </c>
+      <c r="F15" s="28" t="n">
+        <v>-0.1998762489592203</v>
+      </c>
+      <c r="G15" s="28" t="n">
+        <v>-0.3433214471315104</v>
+      </c>
+      <c r="H15" s="28" t="n">
+        <v>-0.3450696693831004</v>
+      </c>
+      <c r="I15" s="27" t="inlineStr">
+        <is>
+          <t>Trend altı</t>
+        </is>
+      </c>
+      <c r="J15" s="28" t="n">
+        <v>0.01909646760520952</v>
+      </c>
+      <c r="K15" s="28" t="n">
+        <v>-0.02052976338254109</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n">
+        <v>13</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
         <is>
           <t>AKBNK.IS</t>
         </is>
       </c>
-      <c r="C14" s="22" t="inlineStr">
+      <c r="C16" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D14" s="22" t="inlineStr">
+      <c r="D16" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E14" s="23" t="n">
-        <v>-0.0572808015361147</v>
-      </c>
-      <c r="F14" s="23" t="n">
-        <v>0.0186428030291823</v>
-      </c>
-      <c r="G14" s="23" t="n">
-        <v>-0.1254800974882294</v>
-      </c>
-      <c r="H14" s="23" t="n">
-        <v>-0.1873317437379973</v>
-      </c>
-      <c r="I14" s="22" t="inlineStr">
+      <c r="E16" s="26" t="n">
+        <v>-0.08071137686777963</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>-0.005917182469050486</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>-0.1956912687769392</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>-0.2002797183603302</v>
+      </c>
+      <c r="I16" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J14" s="23" t="n">
-        <v>0.0238625739044733</v>
-      </c>
-      <c r="K14" s="23" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="22" t="n">
-        <v>12</v>
-      </c>
-      <c r="B15" s="22" t="inlineStr">
-        <is>
-          <t>FROTO.IS</t>
-        </is>
-      </c>
-      <c r="C15" s="22" t="inlineStr">
+      <c r="J16" s="26" t="n">
+        <v>0.02393358873201926</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0.02272459099683133</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="25" t="n">
+        <v>14</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>ASELS.IS</t>
+        </is>
+      </c>
+      <c r="C17" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D15" s="22" t="inlineStr">
+      <c r="D17" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E15" s="23" t="n">
-        <v>-0.1207450444460015</v>
-      </c>
-      <c r="F15" s="23" t="n">
-        <v>-0.13790937490181</v>
-      </c>
-      <c r="G15" s="23" t="n">
-        <v>-0.3536355433241898</v>
-      </c>
-      <c r="H15" s="23" t="n">
-        <v>-0.201379322000936</v>
-      </c>
-      <c r="I15" s="22" t="inlineStr">
+      <c r="E17" s="26" t="n">
+        <v>-0.07676902536715624</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>-0.09072978303747536</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>-0.1648550724637681</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>0.05168476071470662</v>
+      </c>
+      <c r="I17" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J15" s="23" t="n">
-        <v>0.0185820899062162</v>
-      </c>
-      <c r="K15" s="23" t="n">
-        <v>0.0758986426936193</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="24" t="n">
-        <v>13</v>
-      </c>
-      <c r="B16" s="24" t="inlineStr">
-        <is>
-          <t>PGSUS.IS</t>
-        </is>
-      </c>
-      <c r="C16" s="24" t="inlineStr">
+      <c r="J17" s="26" t="n">
+        <v>0.03299519539563162</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0.07743072735755496</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="27" t="n">
+        <v>15</v>
+      </c>
+      <c r="B18" s="27" t="inlineStr">
+        <is>
+          <t>PETKM.IS</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D16" s="24" t="inlineStr">
+      <c r="D18" s="27" t="inlineStr">
         <is>
           <t>SAT</t>
         </is>
       </c>
-      <c r="E16" s="25" t="n">
-        <v>-0.1269841093635378</v>
-      </c>
-      <c r="F16" s="25" t="n">
-        <v>-0.1770573252939933</v>
-      </c>
-      <c r="G16" s="25" t="n">
-        <v>-0.2903225806451612</v>
-      </c>
-      <c r="H16" s="25" t="n">
-        <v>-0.3213083269485385</v>
-      </c>
-      <c r="I16" s="24" t="inlineStr">
+      <c r="E18" s="28" t="n">
+        <v>-0.08938818510581359</v>
+      </c>
+      <c r="F18" s="28" t="n">
+        <v>-0.1348774368283894</v>
+      </c>
+      <c r="G18" s="28" t="n">
+        <v>-0.1333030193902212</v>
+      </c>
+      <c r="H18" s="28" t="n">
+        <v>-0.2567757456456938</v>
+      </c>
+      <c r="I18" s="27" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J16" s="25" t="n">
-        <v>0.0190171517281646</v>
-      </c>
-      <c r="K16" s="25" t="n">
-        <v>-0.0097276264591439</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="24" t="n">
-        <v>14</v>
-      </c>
-      <c r="B17" s="24" t="inlineStr">
-        <is>
-          <t>ASELS.IS</t>
-        </is>
-      </c>
-      <c r="C17" s="24" t="inlineStr">
+      <c r="J18" s="28" t="n">
+        <v>0.03663594021851863</v>
+      </c>
+      <c r="K18" s="28" t="n">
+        <v>-0.05027927169972446</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="25" t="n">
+        <v>16</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>TOASO.IS</t>
+        </is>
+      </c>
+      <c r="C19" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D17" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E17" s="25" t="n">
-        <v>-0.0932539682539682</v>
-      </c>
-      <c r="F17" s="25" t="n">
-        <v>-0.08903654485049831</v>
-      </c>
-      <c r="G17" s="25" t="n">
-        <v>-0.166058394160584</v>
-      </c>
-      <c r="H17" s="25" t="n">
-        <v>0.0228223229737185</v>
-      </c>
-      <c r="I17" s="24" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
+        <is>
+          <t>PORTFOY_DISI</t>
+        </is>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>-0.1968282153427864</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>-0.1889679932509453</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>-0.2261460309117679</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>-0.1869806033062829</v>
+      </c>
+      <c r="I19" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J17" s="25" t="n">
-        <v>0.0330049754383154</v>
-      </c>
-      <c r="K17" s="25" t="n">
-        <v>-0.0588766952961986</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="22" t="n">
-        <v>15</v>
-      </c>
-      <c r="B18" s="22" t="inlineStr">
-        <is>
-          <t>TOASO.IS</t>
-        </is>
-      </c>
-      <c r="C18" s="22" t="inlineStr">
+      <c r="J19" s="26" t="n">
+        <v>0.02593876575596387</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0.03285253990814896</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="25" t="n">
+        <v>17</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>SISE.IS</t>
+        </is>
+      </c>
+      <c r="C20" s="25" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="D18" s="22" t="inlineStr">
+      <c r="D20" s="25" t="inlineStr">
         <is>
           <t>PORTFOY_DISI</t>
         </is>
       </c>
-      <c r="E18" s="23" t="n">
-        <v>-0.1803448381095097</v>
-      </c>
-      <c r="F18" s="23" t="n">
-        <v>-0.1696069975607259</v>
-      </c>
-      <c r="G18" s="23" t="n">
-        <v>-0.1753686142298622</v>
-      </c>
-      <c r="H18" s="23" t="n">
-        <v>-0.2029227843381598</v>
-      </c>
-      <c r="I18" s="22" t="inlineStr">
+      <c r="E20" s="26" t="n">
+        <v>-0.1241927523212472</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>-0.1879318330613905</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>-0.2611033187848746</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>-0.4636418708734003</v>
+      </c>
+      <c r="I20" s="25" t="inlineStr">
         <is>
           <t>Trend altı</t>
         </is>
       </c>
-      <c r="J18" s="23" t="n">
-        <v>0.0255519291609806</v>
-      </c>
-      <c r="K18" s="23" t="n">
-        <v>0.0378562161969006</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="24" t="n">
-        <v>16</v>
-      </c>
-      <c r="B19" s="24" t="inlineStr">
-        <is>
-          <t>PETKM.IS</t>
-        </is>
-      </c>
-      <c r="C19" s="24" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D19" s="24" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="E19" s="25" t="n">
-        <v>-0.0798121557034113</v>
-      </c>
-      <c r="F19" s="25" t="n">
-        <v>-0.1312056362829798</v>
-      </c>
-      <c r="G19" s="25" t="n">
-        <v>-0.1358024639445516</v>
-      </c>
-      <c r="H19" s="25" t="n">
-        <v>-0.2500893749285049</v>
-      </c>
-      <c r="I19" s="24" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J19" s="25" t="n">
-        <v>0.0365916230113574</v>
-      </c>
-      <c r="K19" s="25" t="n">
-        <v>-0.0118534116209535</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="22" t="n">
-        <v>17</v>
-      </c>
-      <c r="B20" s="22" t="inlineStr">
-        <is>
-          <t>SISE.IS</t>
-        </is>
-      </c>
-      <c r="C20" s="22" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D20" s="22" t="inlineStr">
-        <is>
-          <t>PORTFOY_DISI</t>
-        </is>
-      </c>
-      <c r="E20" s="23" t="n">
-        <v>-0.1020812405743142</v>
-      </c>
-      <c r="F20" s="23" t="n">
-        <v>-0.1703296376998283</v>
-      </c>
-      <c r="G20" s="23" t="n">
-        <v>-0.2172493539078707</v>
-      </c>
-      <c r="H20" s="23" t="n">
-        <v>-0.4529853867406843</v>
-      </c>
-      <c r="I20" s="22" t="inlineStr">
-        <is>
-          <t>Trend altı</t>
-        </is>
-      </c>
-      <c r="J20" s="23" t="n">
-        <v>0.0267319379708561</v>
-      </c>
-      <c r="K20" s="23" t="n">
-        <v>0.0595845018212652</v>
+      <c r="J20" s="26" t="n">
+        <v>0.02690597743166475</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0.1001576921543033</v>
       </c>
     </row>
   </sheetData>
@@ -2785,7 +2737,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2793,7 +2745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -2830,7 +2782,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>BIMAS.IS</t>
         </is>
       </c>
     </row>
@@ -2842,7 +2794,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>BIMAS.IS, THYAO.IS, YKBNK.IS, EREGL.IS, PGSUS.IS, ASELS.IS, PETKM.IS</t>
+          <t>YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
         </is>
       </c>
     </row>
@@ -2854,7 +2806,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>TCELL.IS, ARCLK.IS, TUPRS.IS, AKBNK.IS, FROTO.IS, TOASO.IS, SISE.IS</t>
+          <t>EREGL.IS, TCELL.IS, TUPRS.IS, FROTO.IS, AKBNK.IS, ASELS.IS, TOASO.IS, SISE.IS</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2818,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Beklenen getiri etkin %0.78 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
+          <t>Beklenen getiri etkin %1.03 eşiğinin altında ise AL önerisi verilmez; kalan sermaye CASH olur.</t>
         </is>
       </c>
     </row>
@@ -2904,7 +2856,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2912,7 +2864,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3155,7 +3107,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3163,7 +3115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3187,7 +3139,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>11577.099609375</v>
+        <v>11220.400390625</v>
       </c>
     </row>
     <row r="5">
@@ -3197,7 +3149,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>13626.481015625</v>
+        <v>13624.07301757812</v>
       </c>
     </row>
     <row r="6">
@@ -3231,7 +3183,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>81.03</v>
+        <v>80.8</v>
       </c>
     </row>
     <row r="9">
@@ -3268,13 +3220,13 @@
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="19" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-20</t>
+          <t>Rapor Tarihi: 2026-10-21</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3288,7 +3240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-22 06:43</t>
+          <t>Son Güncelleme: 2026-10-23 06:39</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -3352,23 +3304,23 @@
           <t>2026-07-16</t>
         </is>
       </c>
-      <c r="C4" s="26" t="n">
+      <c r="C4" s="29" t="n">
         <v>197</v>
       </c>
-      <c r="D4" s="26" t="n">
-        <v>208.3999938964844</v>
-      </c>
-      <c r="E4" s="27" t="n">
-        <v>0.05786798932225579</v>
-      </c>
-      <c r="F4" s="26" t="n">
-        <v>168184.326366351</v>
-      </c>
-      <c r="G4" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H4" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D4" s="29" t="n">
+        <v>203.3000030517578</v>
+      </c>
+      <c r="E4" s="30" t="n">
+        <v>0.03197971092262852</v>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>92944.06461854326</v>
+      </c>
+      <c r="G4" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H4" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="5">
@@ -3382,23 +3334,23 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="C5" s="26" t="n">
+      <c r="C5" s="29" t="n">
         <v>96.5</v>
       </c>
-      <c r="D5" s="26" t="n">
-        <v>89.19999694824219</v>
-      </c>
-      <c r="E5" s="27" t="n">
-        <v>-0.07564770001821564</v>
-      </c>
-      <c r="F5" s="26" t="n">
-        <v>-6642.963403428294</v>
-      </c>
-      <c r="G5" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H5" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D5" s="29" t="n">
+        <v>88.15000152587891</v>
+      </c>
+      <c r="E5" s="30" t="n">
+        <v>-0.0865284815971098</v>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>-7598.453574469648</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H5" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="6">
@@ -3412,23 +3364,23 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="C6" s="26" t="n">
+      <c r="C6" s="29" t="n">
         <v>77.40000152587891</v>
       </c>
-      <c r="D6" s="26" t="n">
-        <v>68.44999694824219</v>
-      </c>
-      <c r="E6" s="27" t="n">
-        <v>-0.1156331317983793</v>
-      </c>
-      <c r="F6" s="26" t="n">
-        <v>-517699.3630867111</v>
-      </c>
-      <c r="G6" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H6" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D6" s="29" t="n">
+        <v>66.84999847412109</v>
+      </c>
+      <c r="E6" s="30" t="n">
+        <v>-0.1363049463019763</v>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>-610248.8342972519</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H6" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="7">
@@ -3442,23 +3394,23 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="C7" s="26" t="n">
+      <c r="C7" s="29" t="n">
         <v>387</v>
       </c>
-      <c r="D7" s="26" t="n">
-        <v>362</v>
-      </c>
-      <c r="E7" s="27" t="n">
-        <v>-0.06459948320413433</v>
-      </c>
-      <c r="F7" s="26" t="n">
-        <v>-278944.8093186272</v>
-      </c>
-      <c r="G7" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H7" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D7" s="29" t="n">
+        <v>359.25</v>
+      </c>
+      <c r="E7" s="30" t="n">
+        <v>-0.07170542635658916</v>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>-309628.7383436766</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H7" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
     <row r="8">
@@ -3472,23 +3424,23 @@
           <t>2026-10-20</t>
         </is>
       </c>
-      <c r="C8" s="26" t="n">
+      <c r="C8" s="29" t="n">
         <v>134.6000061035156</v>
       </c>
-      <c r="D8" s="26" t="n">
-        <v>134.6000061035156</v>
-      </c>
-      <c r="E8" s="27" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="26" t="n">
-        <v>29150740.19778639</v>
-      </c>
-      <c r="H8" s="27" t="n">
-        <v>-0.139105356442462</v>
+      <c r="D8" s="29" t="n">
+        <v>132.6000061035156</v>
+      </c>
+      <c r="E8" s="30" t="n">
+        <v>-0.01485884033661844</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>-267407.6121233664</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>28683903.43350858</v>
+      </c>
+      <c r="H8" s="30" t="n">
+        <v>-0.1552028889831436</v>
       </c>
     </row>
   </sheetData>

--- a/results/monthly_investor_report.xlsx
+++ b/results/monthly_investor_report.xlsx
@@ -172,6 +172,15 @@
     <xf numFmtId="4" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -179,15 +188,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="10" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -624,7 +624,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -641,7 +641,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -692,7 +692,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Güven Puanı: 80.80/100</t>
+          <t>Güven Puanı: 79.14/100</t>
         </is>
       </c>
       <c r="B6" s="2" t="n"/>
@@ -752,7 +752,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>AL: GARAN.IS, KCHOL.IS, SAHOL.IS</t>
+          <t>AL: GARAN.IS, SAHOL.IS, TCELL.IS</t>
         </is>
       </c>
       <c r="B10" s="2" t="n"/>
@@ -769,7 +769,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>AZALT: BIMAS.IS</t>
+          <t>AZALT: KCHOL.IS, BIMAS.IS</t>
         </is>
       </c>
       <c r="B11" s="2" t="n"/>
@@ -786,7 +786,7 @@
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ÇIK: YKBNK.IS, THYAO.IS, ARCLK.IS, PGSUS.IS, PETKM.IS</t>
+          <t>ÇIK: THYAO.IS, TUPRS.IS, EREGL.IS, PGSUS.IS</t>
         </is>
       </c>
       <c r="B12" s="2" t="n"/>
@@ -972,25 +972,25 @@
         </is>
       </c>
       <c r="D20" s="7" t="n">
-        <v>0.2253112896284994</v>
+        <v>0.2062966470662178</v>
       </c>
       <c r="E20" s="8" t="n">
-        <v>22531.12896284994</v>
+        <v>20629.66470662178</v>
       </c>
       <c r="F20" s="7" t="n">
-        <v>0.05678787196572799</v>
+        <v>0.03311743610603668</v>
       </c>
       <c r="G20" s="8" t="n">
-        <v>1279.494866785628</v>
+        <v>683.2016028105068</v>
       </c>
       <c r="H20" s="8" t="n">
-        <v>140.1300782727768</v>
+        <v>132.7555905396257</v>
       </c>
       <c r="I20" s="8" t="n">
-        <v>125.9700057983398</v>
+        <v>122.075</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>1.135757439314558</v>
+        <v>0.6623487221207304</v>
       </c>
       <c r="K20" s="9" t="inlineStr">
         <is>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>KCHOL.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C21" s="6" t="inlineStr">
@@ -1015,29 +1015,29 @@
         </is>
       </c>
       <c r="D21" s="7" t="n">
-        <v>0.2055238060841062</v>
+        <v>0.2052078655889579</v>
       </c>
       <c r="E21" s="8" t="n">
-        <v>20552.38060841062</v>
+        <v>20520.78655889579</v>
       </c>
       <c r="F21" s="7" t="n">
-        <v>0.01852771488995719</v>
+        <v>0.02241108024750615</v>
       </c>
       <c r="G21" s="8" t="n">
-        <v>380.7886482225169</v>
+        <v>459.8929943133593</v>
       </c>
       <c r="H21" s="8" t="n">
-        <v>207.0666875454282</v>
+        <v>89.51209319582017</v>
       </c>
       <c r="I21" s="8" t="n">
-        <v>193.1350028991699</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.3705542977991433</v>
-      </c>
-      <c r="K21" s="9" t="inlineStr">
-        <is>
-          <t>MEDIUM</t>
+        <v>0.2643676751424494</v>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
     </row>
@@ -1047,7 +1047,7 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>SAHOL.IS</t>
+          <t>TCELL.IS</t>
         </is>
       </c>
       <c r="C22" s="6" t="inlineStr">
@@ -1056,25 +1056,25 @@
         </is>
       </c>
       <c r="D22" s="7" t="n">
-        <v>0.1691649042873944</v>
+        <v>0.1884954873448242</v>
       </c>
       <c r="E22" s="8" t="n">
-        <v>16916.49042873943</v>
+        <v>18849.54873448243</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>0.01031479137899316</v>
+        <v>0.01547529527999503</v>
       </c>
       <c r="G22" s="8" t="n">
-        <v>174.4900696371818</v>
+        <v>291.7023325607721</v>
       </c>
       <c r="H22" s="8" t="n">
-        <v>89.05925040167628</v>
+        <v>94.74384814860821</v>
       </c>
       <c r="I22" s="8" t="n">
-        <v>81.14630294548057</v>
+        <v>88.63500289916992</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.1298241015600161</v>
+        <v>0.3095059055999017</v>
       </c>
       <c r="K22" s="10" t="inlineStr">
         <is>
@@ -1137,7 +1137,7 @@
     <col width="12" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
     <col width="21" customWidth="1" min="7" max="7"/>
     <col width="19" customWidth="1" min="8" max="8"/>
     <col width="19" customWidth="1" min="9" max="9"/>
@@ -1152,7 +1152,7 @@
     <row r="1">
       <c r="A1" s="2" t="inlineStr">
         <is>
-          <t>Rapor Tarihi: 2026-10-21</t>
+          <t>Rapor Tarihi: 2026-10-22</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1173,7 +1173,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Son Güncelleme: 2026-10-23 06:39</t>
+          <t>Son Güncelleme: 2026-10-24 06:36</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1358,37 +1358,37 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>BIMAS.IS</t>
+          <t>SAHOL.IS</t>
         </is>
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>TUT</t>
+          <t>AL</t>
         </is>
       </c>
       <c r="D8" s="15" t="n">
-        <v>385.5</v>
+        <v>87.55000305175781</v>
       </c>
       <c r="E8" s="16" t="n">
-        <v>-0.02055785179873293</v>
+        <v>-0.08477239222015492</v>
       </c>
       <c r="F8" s="16" t="n">
-        <v>0.006068867739039252</v>
+        <v>0.02241108024750615</v>
       </c>
       <c r="G8" s="16" t="n">
-        <v>0.06844627048378671</v>
+        <v>0.1293436503428227</v>
       </c>
       <c r="H8" s="15" t="n">
-        <v>377.5749481315884</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>387.8395485133996</v>
+        <v>89.51209319582017</v>
       </c>
       <c r="J8" s="15" t="n">
-        <v>411.8860372714998</v>
+        <v>98.87404003399743</v>
       </c>
       <c r="K8" s="15" t="n">
-        <v>366.225</v>
+        <v>80.12817985417844</v>
       </c>
       <c r="L8" s="14" t="inlineStr">
         <is>
@@ -1396,16 +1396,16 @@
         </is>
       </c>
       <c r="M8" s="14" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N8" s="14" t="inlineStr">
         <is>
-          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
+          <t>3A momentum destekli; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O8" s="14" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1420,49 +1420,49 @@
       </c>
       <c r="C9" s="17" t="inlineStr">
         <is>
-          <t>AL</t>
+          <t>TUT</t>
         </is>
       </c>
       <c r="D9" s="18" t="n">
-        <v>203.3000030517578</v>
+        <v>196.1000061035156</v>
       </c>
       <c r="E9" s="19" t="n">
         <v>-0.03024662719688587</v>
       </c>
       <c r="F9" s="19" t="n">
-        <v>0.01852771488995719</v>
+        <v>0.01244258503774698</v>
       </c>
       <c r="G9" s="19" t="n">
-        <v>0.0466707658152421</v>
+        <v>0.07297590341186155</v>
       </c>
       <c r="H9" s="18" t="n">
-        <v>197.1508636503255</v>
+        <v>190.1686423255956</v>
       </c>
       <c r="I9" s="18" t="n">
-        <v>207.0666875454282</v>
+        <v>198.5399971053613</v>
       </c>
       <c r="J9" s="18" t="n">
-        <v>212.7881698844244</v>
+        <v>210.4105812079912</v>
       </c>
       <c r="K9" s="18" t="n">
-        <v>193.1350028991699</v>
+        <v>186.2950057983398</v>
       </c>
       <c r="L9" s="17" t="inlineStr">
         <is>
-          <t>MEDIUM</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="M9" s="17" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N9" s="17" t="inlineStr">
         <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O9" s="17" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1472,168 +1472,168 @@
       </c>
       <c r="B10" s="17" t="inlineStr">
         <is>
+          <t>BIMAS.IS</t>
+        </is>
+      </c>
+      <c r="C10" s="17" t="inlineStr">
+        <is>
+          <t>TUT</t>
+        </is>
+      </c>
+      <c r="D10" s="18" t="n">
+        <v>369</v>
+      </c>
+      <c r="E10" s="19" t="n">
+        <v>-0.01299463649111321</v>
+      </c>
+      <c r="F10" s="19" t="n">
+        <v>0.01286270803657807</v>
+      </c>
+      <c r="G10" s="19" t="n">
+        <v>0.0890313241273375</v>
+      </c>
+      <c r="H10" s="18" t="n">
+        <v>364.2049791347793</v>
+      </c>
+      <c r="I10" s="18" t="n">
+        <v>373.7463392654973</v>
+      </c>
+      <c r="J10" s="18" t="n">
+        <v>401.8525586029875</v>
+      </c>
+      <c r="K10" s="18" t="n">
+        <v>350.55</v>
+      </c>
+      <c r="L10" s="17" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="M10" s="17" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N10" s="17" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O10" s="17" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="14" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="14" t="inlineStr">
+        <is>
           <t>GARAN.IS</t>
         </is>
       </c>
-      <c r="C10" s="17" t="inlineStr">
+      <c r="C11" s="14" t="inlineStr">
         <is>
           <t>AL</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
-        <v>132.6000061035156</v>
-      </c>
-      <c r="E10" s="19" t="n">
-        <v>-0.0446736587600064</v>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.05678787196572799</v>
-      </c>
-      <c r="G10" s="19" t="n">
-        <v>0.1240418332017574</v>
-      </c>
-      <c r="H10" s="18" t="n">
-        <v>126.6762786792724</v>
-      </c>
-      <c r="I10" s="18" t="n">
-        <v>140.1300782727768</v>
-      </c>
-      <c r="J10" s="18" t="n">
-        <v>149.0479539431599</v>
-      </c>
-      <c r="K10" s="18" t="n">
-        <v>125.9700057983398</v>
-      </c>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="D11" s="15" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="E11" s="16" t="n">
+        <v>-0.04923849891315546</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.03311743610603668</v>
+      </c>
+      <c r="G11" s="16" t="n">
+        <v>0.07411146367770827</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>122.1728528896595</v>
+      </c>
+      <c r="I11" s="15" t="n">
+        <v>132.7555905396257</v>
+      </c>
+      <c r="J11" s="15" t="n">
+        <v>138.0233230825855</v>
+      </c>
+      <c r="K11" s="15" t="n">
+        <v>122.075</v>
+      </c>
+      <c r="L11" s="14" t="inlineStr">
         <is>
           <t>MEDIUM</t>
         </is>
       </c>
-      <c r="M10" s="17" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N10" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O10" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="B11" s="20" t="inlineStr">
-        <is>
-          <t>YKBNK.IS</t>
-        </is>
-      </c>
-      <c r="C11" s="20" t="inlineStr">
-        <is>
-          <t>SAT</t>
-        </is>
-      </c>
-      <c r="D11" s="21" t="n">
-        <v>36.41999816894531</v>
-      </c>
-      <c r="E11" s="22" t="n">
-        <v>-0.02777781264366352</v>
-      </c>
-      <c r="F11" s="22" t="n">
-        <v>-0.00924906731649483</v>
-      </c>
-      <c r="G11" s="22" t="n">
-        <v>0.07188239616583897</v>
-      </c>
-      <c r="H11" s="21" t="n">
-        <v>35.40833028332578</v>
-      </c>
-      <c r="I11" s="21" t="n">
-        <v>36.08314715421412</v>
-      </c>
-      <c r="J11" s="21" t="n">
-        <v>39.03795490568457</v>
-      </c>
-      <c r="K11" s="21" t="n">
-        <v>34.50212993691391</v>
-      </c>
-      <c r="L11" s="20" t="inlineStr">
+      <c r="M11" s="14" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N11" s="14" t="inlineStr">
+        <is>
+          <t>3A momentum destekli; volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O11" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="14" t="n">
+        <v>5</v>
+      </c>
+      <c r="B12" s="14" t="inlineStr">
+        <is>
+          <t>TCELL.IS</t>
+        </is>
+      </c>
+      <c r="C12" s="14" t="inlineStr">
+        <is>
+          <t>AL</t>
+        </is>
+      </c>
+      <c r="D12" s="15" t="n">
+        <v>93.30000305175781</v>
+      </c>
+      <c r="E12" s="16" t="n">
+        <v>-0.04480283081837821</v>
+      </c>
+      <c r="F12" s="16" t="n">
+        <v>0.01547529527999503</v>
+      </c>
+      <c r="G12" s="16" t="n">
+        <v>0.06738542065873321</v>
+      </c>
+      <c r="H12" s="15" t="n">
+        <v>89.11989879967574</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>94.74384814860821</v>
+      </c>
+      <c r="J12" s="15" t="n">
+        <v>99.58706300486161</v>
+      </c>
+      <c r="K12" s="15" t="n">
+        <v>88.63500289916992</v>
+      </c>
+      <c r="L12" s="14" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
       </c>
-      <c r="M11" s="20" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N11" s="20" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; trend desteği var</t>
-        </is>
-      </c>
-      <c r="O11" s="20" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="17" t="n">
-        <v>5</v>
-      </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>SAHOL.IS</t>
-        </is>
-      </c>
-      <c r="C12" s="17" t="inlineStr">
-        <is>
-          <t>AL</t>
-        </is>
-      </c>
-      <c r="D12" s="18" t="n">
-        <v>88.15000152587891</v>
-      </c>
-      <c r="E12" s="19" t="n">
-        <v>-0.07945205285495327</v>
-      </c>
-      <c r="F12" s="19" t="n">
-        <v>0.01031479137899316</v>
-      </c>
-      <c r="G12" s="19" t="n">
-        <v>0.09404613143246554</v>
-      </c>
-      <c r="H12" s="18" t="n">
-        <v>81.14630294548057</v>
-      </c>
-      <c r="I12" s="18" t="n">
-        <v>89.05925040167628</v>
-      </c>
-      <c r="J12" s="18" t="n">
-        <v>96.44016815515374</v>
-      </c>
-      <c r="K12" s="18" t="n">
-        <v>81.14630294548057</v>
-      </c>
-      <c r="L12" s="17" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="M12" s="17" t="n">
-        <v>80.8</v>
-      </c>
-      <c r="N12" s="17" t="inlineStr">
-        <is>
-          <t>3A momentum destekli; volatilite görece düşük</t>
-        </is>
-      </c>
-      <c r="O12" s="17" t="inlineStr">
-        <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+      <c r="M12" s="14" t="n">
+        <v>79.14</v>
+      </c>
+      <c r="N12" s="14" t="inlineStr">
+        <is>
+          <t>volatilite görece düşük</t>
+        </is>
+      </c>
+      <c r="O12" s="14" t="inlineStr">
+        <is>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf</t>
         </is>
       </c>
     </row>
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="D13" s="21" t="n">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="E13" s="22" t="n">
-        <v>-0.06286186931348225</v>
+        <v>-0.05964963819696248</v>
       </c>
       <c r="F13" s="22" t="n">
         <v>-0.03419979012555929</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>0.05123038157605908</v>
+        <v>0.1088930485621326</v>
       </c>
       <c r="H13" s="21" t="n">
-        <v>248.3416046319272</v>
+        <v>243.5507437069867</v>
       </c>
       <c r="I13" s="21" t="n">
-        <v>255.9370556167268</v>
+        <v>250.1422543574801</v>
       </c>
       <c r="J13" s="21" t="n">
-        <v>278.5760511176557</v>
+        <v>287.2032995775924</v>
       </c>
       <c r="K13" s="21" t="n">
-        <v>248.3416046319272</v>
+        <v>243.5507437069867</v>
       </c>
       <c r="L13" s="20" t="inlineStr">
         <is>
@@ -1681,7 +1681,7 @@
         </is>
       </c>
       <c r="M13" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N13" s="20" t="inlineStr">
         <is>
@@ -1696,11 +1696,11 @@
     </row>
     <row r="14">
       <c r="A14" s="20" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>ARCLK.IS</t>
+          <t>TUPRS.IS</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -1709,28 +1709,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>74.5</v>
+        <v>352.25</v>
       </c>
       <c r="E14" s="22" t="n">
-        <v>-0.056962015212765</v>
+        <v>-0.06378737541528234</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>-0.01693897265082622</v>
+        <v>-0.004932991768213713</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>0.1111908721424226</v>
+        <v>0.1114567484586793</v>
       </c>
       <c r="H14" s="21" t="n">
-        <v>70.25632986664901</v>
+        <v>329.7808970099668</v>
       </c>
       <c r="I14" s="21" t="n">
-        <v>73.23804653751344</v>
+        <v>350.5123536496467</v>
       </c>
       <c r="J14" s="21" t="n">
-        <v>82.78371997461049</v>
+        <v>391.5106396445698</v>
       </c>
       <c r="K14" s="21" t="n">
-        <v>70.25632986664901</v>
+        <v>329.7808970099668</v>
       </c>
       <c r="L14" s="20" t="inlineStr">
         <is>
@@ -1738,26 +1738,26 @@
         </is>
       </c>
       <c r="M14" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N14" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; 3A momentum destekli; trend desteği var</t>
         </is>
       </c>
       <c r="O14" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="20" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>PGSUS.IS</t>
+          <t>EREGL.IS</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -1766,28 +1766,28 @@
         </is>
       </c>
       <c r="D15" s="21" t="n">
-        <v>129.3000030517578</v>
+        <v>35.09999847412109</v>
       </c>
       <c r="E15" s="22" t="n">
-        <v>-0.05370672771557694</v>
+        <v>-0.06530610017180571</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>-0.02052976338254109</v>
+        <v>-0.0327142098683611</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>0.1090029643218295</v>
+        <v>0.03380764349298043</v>
       </c>
       <c r="H15" s="21" t="n">
-        <v>122.3557229942338</v>
+        <v>32.80775445773991</v>
       </c>
       <c r="I15" s="21" t="n">
-        <v>126.6455045837434</v>
+        <v>33.95172975765954</v>
       </c>
       <c r="J15" s="21" t="n">
-        <v>143.394086671221</v>
+        <v>36.28664670913834</v>
       </c>
       <c r="K15" s="21" t="n">
-        <v>122.3557229942338</v>
+        <v>32.80775445773991</v>
       </c>
       <c r="L15" s="20" t="inlineStr">
         <is>
@@ -1795,26 +1795,26 @@
         </is>
       </c>
       <c r="M15" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N15" s="20" t="inlineStr">
         <is>
-          <t>volatilite görece düşük</t>
+          <t>6A momentum pozitif; trend desteği var; volatilite görece düşük</t>
         </is>
       </c>
       <c r="O15" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
+          <t>kisa vadeli momentum negatif; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="20" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>PETKM.IS</t>
+          <t>PGSUS.IS</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -1823,28 +1823,28 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>19.04999923706055</v>
+        <v>126.4000015258789</v>
       </c>
       <c r="E16" s="22" t="n">
-        <v>-0.1689400445284157</v>
+        <v>-0.05280088922285953</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>-0.05027927169972446</v>
+        <v>-0.01999250815041453</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>0.01865484715630311</v>
+        <v>0.07265370930011067</v>
       </c>
       <c r="H16" s="21" t="n">
-        <v>15.83169151768525</v>
+        <v>119.7259690475417</v>
       </c>
       <c r="I16" s="21" t="n">
-        <v>18.09217914954084</v>
+        <v>123.8729484651604</v>
       </c>
       <c r="J16" s="21" t="n">
-        <v>19.4053740611556</v>
+        <v>135.5834304922737</v>
       </c>
       <c r="K16" s="21" t="n">
-        <v>15.83169151768525</v>
+        <v>119.7259690475417</v>
       </c>
       <c r="L16" s="20" t="inlineStr">
         <is>
@@ -1852,16 +1852,16 @@
         </is>
       </c>
       <c r="M16" s="20" t="n">
-        <v>80.8</v>
+        <v>79.14</v>
       </c>
       <c r="N16" s="20" t="inlineStr">
         <is>
-          <t>Model skoru portföy için yeterli</t>
+          <t>volatilite görece düşük</t>
         </is>
       </c>
       <c r="O16" s="20" t="inlineStr">
         <is>
-          <t>kisa vadeli momentum negatif; trend desteği zayıf; volatilite yüksek</t>
+          <t>kisa vadeli momentum negatif; trend desteği zayıf; alt bant riski belirgin</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="23" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
     <col width="23" customWidth="1" min="6" max="6"/>
     <col width="22" customWidth="1" min="7" max="7"/>
     <col width="22" customWidth="1" min="8" max="8"/>
@@ -1896,7 